--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -974,52 +974,52 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ИРЕСТ СТРОЙ»</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>7825134181</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>+7 (812) 326-11-53</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>kanoner.com (данные 2013 г.)</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>средняя (ИНН совпал, но источник старый — сверить)</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>1800000</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Графит»</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>7841505154</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 944-62-49</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ООО «Магистраль северной столицы»</t>
+          <t>ООО «ИНТРА ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>7710884741</t>
+          <t>7806519718</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
+          <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
+          <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>514</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1069,57 +1069,57 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ООО «НПО «АМБ»</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>7804516528</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2000000</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ИРЕСТ СТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>7825134181</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>+7 (812) 326-11-53</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>kanoner.com (данные 2013 г.)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но источник старый — сверить)</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПСМ» (Промстроймонтаж)</t>
+          <t>ООО «Магистраль северной столицы»</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>7814118903</t>
+          <t>7710884741</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
+          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
+          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>833</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1179,27 +1179,27 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ООО «Розенберг Северо-Запад»</t>
+          <t>ООО «НПО «АМБ»</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>7816592450</t>
+          <t>7804516528</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1229,27 +1229,27 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ООО «СтарКом»</t>
+          <t>ООО «ПСМ» (Промстроймонтаж)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>7841416641</t>
+          <t>7814118903</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>727</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -1279,131 +1279,147 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>ООО «Розенберг Северо-Запад»</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>7816592450</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>ООО «СтарКом»</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>7841416641</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>ООО «ТМГ ГРУП»</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>7705405168</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 680-30-20</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>2000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>7810255553</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr"/>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr"/>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>АО «ВОЛХОН»</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>7810383403</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr"/>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1413,29 +1429,29 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>АО «Полиспаст»</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>7805744573</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr"/>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr"/>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -1455,18 +1471,18 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>АО «Стройинвест»</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>7825697956</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr"/>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr"/>
@@ -1477,7 +1493,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -1497,18 +1513,18 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>7811405770</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr"/>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr"/>
@@ -1519,7 +1535,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -1539,18 +1555,18 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr"/>
@@ -1561,7 +1577,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -1571,7 +1587,7 @@
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1581,29 +1597,29 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ЗАО «Эра-Инжиниринг»</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7811405770</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>519</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -1613,7 +1629,7 @@
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1623,29 +1639,29 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -1665,29 +1681,29 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -1707,29 +1723,29 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr"/>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -1739,7 +1755,7 @@
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1749,18 +1765,18 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
@@ -1771,7 +1787,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -1781,7 +1797,7 @@
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1791,18 +1807,18 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr"/>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
@@ -1813,7 +1829,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -1833,29 +1849,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -1865,7 +1881,7 @@
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1875,18 +1891,18 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr"/>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
@@ -1897,7 +1913,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -1917,29 +1933,29 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr"/>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -1949,7 +1965,7 @@
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1959,18 +1975,18 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr"/>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
@@ -1981,7 +1997,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -1991,7 +2007,7 @@
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -2001,18 +2017,18 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr"/>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
@@ -2023,7 +2039,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -2033,7 +2049,7 @@
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2043,18 +2059,18 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr"/>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
@@ -2065,7 +2081,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -2075,7 +2091,7 @@
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2085,29 +2101,29 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr"/>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -2117,7 +2133,7 @@
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2127,18 +2143,18 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
@@ -2149,7 +2165,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2159,7 +2175,7 @@
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2169,18 +2185,18 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr"/>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
@@ -2191,22 +2207,526 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>ООО «НПФ «Тест»</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>7805098168</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr"/>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr"/>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>1800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>ООО «НСК» (Невская строительная компания)</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>7805500513</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr"/>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Нордик»</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>7804596040</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr"/>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>7804384374</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr"/>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Промстрой»</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>7814656860</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr"/>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr"/>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Потенциал»</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>7814558855</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>1700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУ-17»</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>7807028906</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>2300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУАР-Групп»</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>7802270195</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr"/>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СЭМ»</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>7810201646</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr"/>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr"/>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr"/>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr"/>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
           <t>657</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J37"/>
+  <autoFilter ref="A1:J49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2289,7 +2809,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -2299,7 +2819,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -2309,7 +2829,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -629,27 +629,27 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>АО «Невский Проект»</t>
+          <t>АО «НГ» (Нордград)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>7802148357</t>
+          <t>7813427641</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 457-23-42</t>
+          <t>+7 (812) 317-01-51</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>198095 СПб, Митрофаньевское ш. 5к2Б; ОГРН 1027801564196; ген.дир. Лисовский А.Л.</t>
+          <t>191123 СПб, ул.Шпалерная 34Б пом.1-Н/12; ОГРН 1089847395791; ген.дир. Феськов А.Н.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>companies.rbc.ru/id/1027801564196; sbis.ru; saby.ru</t>
+          <t>rusprofile.ru/id/1174734; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>698</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -679,27 +679,27 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>АО «Омега»</t>
+          <t>АО «Невский Проект»</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>7806016873</t>
+          <t>7802148357</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 226-34-54</t>
+          <t>+7 (812) 457-23-42</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>СПб, 6-й Предпортовый пр. 10А оф.1; ОГРН 1027804178082; ген.дир. Гальперин Л.Б.; ~127 сотр.</t>
+          <t>198095 СПб, Митрофаньевское ш. 5к2Б; ОГРН 1027801564196; ген.дир. Лисовский А.Л.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/1481264; companies.rbc.ru; sbis.ru</t>
+          <t>companies.rbc.ru/id/1027801564196; sbis.ru; saby.ru</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>606</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -729,27 +729,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>АО «ПИ-№1» (Проектный институт №1)</t>
+          <t>АО «Омега»</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>7812008359</t>
+          <t>7806016873</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 334-02-44; +7 (812) 244-57-57; +7 (812) 244-57-24; +7 (931) 314-46-56</t>
+          <t>+7 (812) 226-34-54</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>191015 СПб, 9-я Советская 4-6А пом.102; ОГРН 1037851020173; ген.дир. Окунева М.П.</t>
+          <t>СПб, 6-й Предпортовый пр. 10А оф.1; ОГРН 1027804178082; ген.дир. Гальперин Л.Б.; ~127 сотр.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/1549030; checko.ru; saby.ru</t>
+          <t>rusprofile.ru/id/1481264; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>597</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -779,27 +779,27 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ОАО «БСМЗ» (Балтийский судомеханический завод)</t>
+          <t>АО «ПИ-№1» (Проектный институт №1)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>7805029037</t>
+          <t>7812008359</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 335-71-13; +7 (812) 321-68-50</t>
+          <t>+7 (812) 334-02-44; +7 (812) 244-57-57; +7 (812) 244-57-24; +7 (931) 314-46-56</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>198096 СПб, дор. на Турухтанные Острова 26к5; ОГРН 1027802760930; ген.дир. Савкин Е.А.</t>
+          <t>191015 СПб, 9-я Советская 4-6А пом.102; ОГРН 1037851020173; ген.дир. Окунева М.П.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/1416533; companies.rbc.ru; sbis.ru</t>
+          <t>rusprofile.ru/id/1549030; checko.ru; saby.ru</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>731</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -829,27 +829,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ООО «БАСТ»</t>
+          <t>ОАО «БСМЗ» (Балтийский судомеханический завод)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>7816196826</t>
+          <t>7805029037</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 766-64-80; +7 (812) 766-63-35; +7 (812) 766-48-07</t>
+          <t>+7 (812) 335-71-13; +7 (812) 321-68-50</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>191015 СПб, ул.Таврическая 17А оф.311; ОГРН 1037835049130; ген.дир. Филимонов Д.В.</t>
+          <t>198096 СПб, дор. на Турухтанные Острова 26к5; ОГРН 1027802760930; ген.дир. Савкин Е.А.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3208204; companies.rbc.ru; checko.ru</t>
+          <t>rusprofile.ru/id/1416533; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -879,27 +879,27 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>ООО «БалтМостСтрой»</t>
+          <t>ООО «БАСТ»</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>7801182620</t>
+          <t>7816196826</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 422-44-02; +7 (812) 677-23-78</t>
+          <t>+7 (812) 766-64-80; +7 (812) 766-63-35; +7 (812) 766-48-07</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>192029 СПб, ул.Бабушкина 3А пом.34Н; ОГРН 1027808912031; строительство мостов и тоннелей</t>
+          <t>191015 СПб, ул.Таврическая 17А оф.311; ОГРН 1037835049130; ген.дир. Филимонов Д.В.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/4221107; synapsenet.ru; casebook.ru</t>
+          <t>rusprofile.ru/id/3208204; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>634</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -929,27 +929,27 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ООО «ВИЗОТЕК РУС»</t>
+          <t>ООО «БалтМостСтрой»</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>7805665201</t>
+          <t>7801182620</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 238-03-28; +7 (812) 346-83-43; +7 (931) 007-70-99</t>
+          <t>+7 (812) 422-44-02; +7 (812) 677-23-78</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>198097 СПб, пр.Стачек 47У; ОГРН 1147847414219; рук. Семенов Н.М.; обработка металлов</t>
+          <t>192029 СПб, ул.Бабушкина 3А пом.34Н; ОГРН 1027808912031; строительство мостов и тоннелей</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7560433; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/4221107; synapsenet.ru; casebook.ru</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>764</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -979,27 +979,27 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ООО «Графит»</t>
+          <t>ООО «ВИЗОТЕК РУС»</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>7841505154</t>
+          <t>7805665201</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 944-62-49</t>
+          <t>+7 (812) 238-03-28; +7 (812) 346-83-43; +7 (931) 007-70-99</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+          <t>198097 СПб, пр.Стачек 47У; ОГРН 1147847414219; рук. Семенов Н.М.; обработка металлов</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+          <t>rusprofile.ru/id/7560433; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>579</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ООО «ИНТРА ПРОЕКТ»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>7806519718</t>
+          <t>7816500610</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
+          <t>+7 (812) 603-29-07</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
+          <t>199106 СПб, пл.Морской Славы 1А пом.5069; ОГРН 1107847385040; ген.дир. Власенко А.В. | в источнике также обрывок «365-66-38» без кода города — уточнить</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/5307814; focus.kontur.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>611</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1074,52 +1074,52 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ИРЕСТ СТРОЙ»</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>7825134181</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>+7 (812) 326-11-53</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>kanoner.com (данные 2013 г.)</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>средняя (ИНН совпал, но источник старый — сверить)</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>1800000</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Графит»</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>7841505154</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 944-62-49</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ООО «Магистраль северной столицы»</t>
+          <t>ООО «ИНТРА ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>7710884741</t>
+          <t>7806519718</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
+          <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
+          <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>514</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1169,57 +1169,57 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>ООО «НПО «АМБ»</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>7804516528</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2000000</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ИРЕСТ СТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>7825134181</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>+7 (812) 326-11-53</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>kanoner.com (данные 2013 г.)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но источник старый — сверить)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -1229,27 +1229,27 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПСМ» (Промстроймонтаж)</t>
+          <t>ООО «Магистраль северной столицы»</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>7814118903</t>
+          <t>7710884741</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
+          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
+          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>833</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1279,27 +1279,27 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ООО «Розенберг Северо-Запад»</t>
+          <t>ООО «НПО «АМБ»</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>7816592450</t>
+          <t>7804516528</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1329,27 +1329,27 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ООО «СтарКом»</t>
+          <t>ООО «ПО «Энергосистема»</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>7841416641</t>
+          <t>7805654520</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>336</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1379,173 +1379,197 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>ООО «ПСМ» (Промстроймонтаж)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>7814118903</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Розенберг Северо-Запад»</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>7816592450</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ООО «СтарКом»</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>7841416641</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>ООО «ТМГ ГРУП»</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>7705405168</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 680-30-20</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>2000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>7810255553</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr"/>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>АО «ВОЛХОН»</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>7810383403</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr"/>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr"/>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>АО «Полиспаст»</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>7805744573</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr"/>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1555,18 +1579,18 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>АО «Стройинвест»</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>7825697956</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr"/>
@@ -1577,7 +1601,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -1597,29 +1621,29 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>7811405770</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -1639,29 +1663,29 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>АО «НОУДИГ» (Per Aarsleff)</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7802108837</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>699</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -1671,7 +1695,7 @@
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1681,29 +1705,29 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -1713,7 +1737,7 @@
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1723,29 +1747,29 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr"/>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -1765,29 +1789,29 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ЗАО «Эра-Инжиниринг»</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7811405770</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>519</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -1807,18 +1831,18 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr"/>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
@@ -1829,7 +1853,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -1849,29 +1873,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -1881,7 +1905,7 @@
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1891,29 +1915,25 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr"/>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
-        </is>
-      </c>
+      <c r="E30" s="11" t="inlineStr"/>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -1923,7 +1943,7 @@
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1933,29 +1953,29 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr"/>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -1965,7 +1985,7 @@
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1975,29 +1995,29 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr"/>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -2007,7 +2027,7 @@
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2017,18 +2037,18 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr"/>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
@@ -2039,7 +2059,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -2059,18 +2079,18 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr"/>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
@@ -2081,7 +2101,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -2091,7 +2111,7 @@
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2101,18 +2121,18 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr"/>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
@@ -2123,7 +2143,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -2143,18 +2163,18 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
@@ -2165,7 +2185,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2175,7 +2195,7 @@
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2185,29 +2205,29 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr"/>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -2227,18 +2247,18 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr"/>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
@@ -2249,7 +2269,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -2259,7 +2279,7 @@
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -2269,29 +2289,29 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr"/>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -2301,7 +2321,7 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2311,20 +2331,16 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr"/>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
-        </is>
-      </c>
+      <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="11" t="inlineStr"/>
       <c r="G40" s="11" t="inlineStr">
         <is>
@@ -2333,7 +2349,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2343,7 +2359,7 @@
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2353,18 +2369,18 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr"/>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -2375,7 +2391,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -2385,7 +2401,7 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2395,18 +2411,18 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
@@ -2417,7 +2433,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2427,7 +2443,7 @@
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2437,29 +2453,29 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr"/>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -2469,7 +2485,7 @@
       </c>
       <c r="J43" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2479,18 +2495,18 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
@@ -2501,7 +2517,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2511,7 +2527,7 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2521,29 +2537,29 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr"/>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2553,7 +2569,7 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2563,29 +2579,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr"/>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2595,7 +2611,7 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2605,29 +2621,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr"/>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2637,7 +2653,7 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2647,29 +2663,29 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr"/>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2679,7 +2695,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2689,18 +2705,18 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr"/>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
@@ -2711,22 +2727,1022 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>ООО «НПФ «Тест»</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>7805098168</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr"/>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>1800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>ООО «НСК» (Невская строительная компания)</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>7805500513</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr"/>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Новый век»</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>7806113612</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr"/>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr"/>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Нордик»</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>7804596040</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr"/>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Омега Строй»</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>7802711097</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr"/>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>7814822228</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr"/>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>7804384374</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr"/>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>7811659380</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr"/>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПСТ»</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>7813448257</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr"/>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПТГ»</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>5013050270</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr"/>
+      <c r="E59" s="11" t="inlineStr"/>
+      <c r="F59" s="11" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Промстрой»</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>7814656860</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr"/>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr"/>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Профиль»</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>7802182380</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr"/>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РЕССТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>7820012849</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr"/>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr"/>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>7826123721</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr"/>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Потенциал»</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>7814558855</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr"/>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr"/>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>1700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>7825055370</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr"/>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr"/>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУ-17»</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>7807028906</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr"/>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr"/>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>2300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУАР-Групп»</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>7802270195</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr"/>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr"/>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СЭМ»</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>7810201646</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr"/>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr"/>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СтройГрад»</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>7813692632</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr"/>
+      <c r="E69" s="11" t="inlineStr"/>
+      <c r="F69" s="11" t="inlineStr"/>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr"/>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr"/>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr"/>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr"/>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr"/>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
           <t>657</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J49" s="10" t="inlineStr">
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr"/>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr"/>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J49"/>
+  <autoFilter ref="A1:J73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2809,7 +3825,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -2819,7 +3835,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -2829,7 +3845,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1479,347 +1479,395 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>7810206161</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>5609095128</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>7801349149</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Северный Альянс»</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>7805662306</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Спецтехкомплект»</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>7811127120</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 362-09-21</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>ООО «СтарКом»</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>7841416641</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>508</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>5000000</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>ООО «ТМГ ГРУП»</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>7705405168</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 680-30-20</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>7810255553</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr"/>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>АО «ВОЛХОН»</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>7810383403</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr"/>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>АО «НОУДИГ» (Per Aarsleff)</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>7802108837</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr"/>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>АО «Полиспаст»</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>7805744573</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr"/>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>АО «Стройинвест»</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>7825697956</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr"/>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr"/>
-      <c r="G26" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>7811405770</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr"/>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr"/>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Транспромстрой»</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>7804591155</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 449-31-21</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>СПб, ул.Савушкина 83к3А оф.401-402; ОГРН 1177847074250; ген.дир. Аванесов Д.Б.; ~467 сотрудников</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; companies.rbc.ru; sbis.ru</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -1831,29 +1879,29 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr"/>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -1863,7 +1911,7 @@
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1873,18 +1921,18 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
@@ -1895,7 +1943,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -1905,7 +1953,7 @@
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1915,16 +1963,20 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7813007615</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr"/>
-      <c r="E30" s="11" t="inlineStr"/>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
+        </is>
+      </c>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -1933,7 +1985,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -1943,7 +1995,7 @@
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -1953,29 +2005,29 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>АО «НОУДИГ» (Per Aarsleff)</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7802108837</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr"/>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>699</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -1985,7 +2037,7 @@
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1995,18 +2047,18 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr"/>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
@@ -2017,7 +2069,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -2037,18 +2089,18 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr"/>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
@@ -2059,7 +2111,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -2079,29 +2131,29 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ЗАО «Агентство Шушары»</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7820016970</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr"/>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
+          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -2111,7 +2163,7 @@
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2121,18 +2173,18 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ЗАО «Эра-Инжиниринг»</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7811405770</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr"/>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
@@ -2143,7 +2195,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>519</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -2163,18 +2215,18 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
@@ -2185,7 +2237,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2205,29 +2257,29 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr"/>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -2237,7 +2289,7 @@
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2247,20 +2299,16 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr"/>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
-        </is>
-      </c>
+      <c r="E38" s="11" t="inlineStr"/>
       <c r="F38" s="11" t="inlineStr"/>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2269,7 +2317,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -2279,7 +2327,7 @@
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2289,29 +2337,29 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr"/>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -2321,7 +2369,7 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -2331,25 +2379,29 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr"/>
-      <c r="E40" s="11" t="inlineStr"/>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+        </is>
+      </c>
       <c r="F40" s="11" t="inlineStr"/>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2359,7 +2411,7 @@
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2369,29 +2421,29 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr"/>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -2401,7 +2453,7 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2411,29 +2463,29 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2453,29 +2505,29 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr"/>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -2495,29 +2547,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2537,18 +2589,18 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr"/>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
@@ -2559,7 +2611,7 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2579,29 +2631,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr"/>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2611,7 +2663,7 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2621,18 +2673,18 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr"/>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
@@ -2643,7 +2695,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2663,18 +2715,18 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr"/>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
@@ -2685,7 +2737,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2695,7 +2747,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -2705,18 +2757,18 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr"/>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
@@ -2727,7 +2779,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -2747,20 +2799,16 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr"/>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
-        </is>
-      </c>
+      <c r="E50" s="11" t="inlineStr"/>
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="11" t="inlineStr">
         <is>
@@ -2769,7 +2817,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2779,7 +2827,7 @@
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2789,18 +2837,18 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr"/>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
@@ -2811,7 +2859,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -2821,7 +2869,7 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2831,29 +2879,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr"/>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -2873,29 +2921,29 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr"/>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -2905,7 +2953,7 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2915,18 +2963,18 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
@@ -2937,7 +2985,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -2947,7 +2995,7 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2957,18 +3005,18 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr"/>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
@@ -2979,7 +3027,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -2999,29 +3047,29 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3031,7 +3079,7 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3041,29 +3089,29 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr"/>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -3083,18 +3131,18 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr"/>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
@@ -3105,7 +3153,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -3125,16 +3173,20 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr"/>
-      <c r="E59" s="11" t="inlineStr"/>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+        </is>
+      </c>
       <c r="F59" s="11" t="inlineStr"/>
       <c r="G59" s="11" t="inlineStr">
         <is>
@@ -3143,7 +3195,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3163,18 +3215,18 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr"/>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
@@ -3185,7 +3237,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3195,7 +3247,7 @@
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3205,18 +3257,18 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr"/>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -3227,7 +3279,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3237,7 +3289,7 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -3247,29 +3299,29 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr"/>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3279,7 +3331,7 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3289,29 +3341,29 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr"/>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -3331,18 +3383,18 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -3353,7 +3405,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -3363,7 +3415,7 @@
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -3373,18 +3425,18 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr"/>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -3395,7 +3447,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -3405,7 +3457,7 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3415,29 +3467,29 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr"/>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3447,7 +3499,7 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3457,29 +3509,29 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr"/>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -3489,7 +3541,7 @@
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3499,18 +3551,18 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr"/>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -3521,7 +3573,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3531,7 +3583,7 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3541,16 +3593,20 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr"/>
-      <c r="E69" s="11" t="inlineStr"/>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, Ярославский пр.</t>
+        </is>
+      </c>
       <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="11" t="inlineStr">
         <is>
@@ -3559,7 +3615,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3569,7 +3625,7 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -3579,18 +3635,18 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7811659380</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr"/>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -3601,7 +3657,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>607</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -3611,7 +3667,7 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3621,29 +3677,29 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «ПСТ»</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7813448257</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>876</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -3653,7 +3709,7 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3663,20 +3719,16 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «ПТГ»</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>5013050270</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr"/>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
-        </is>
-      </c>
+      <c r="E72" s="11" t="inlineStr"/>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr">
         <is>
@@ -3685,7 +3737,7 @@
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -3695,7 +3747,7 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3705,44 +3757,1048 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «Промстрой»</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7814656860</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr">
         <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Профиль»</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>7802182380</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr"/>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr"/>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РЕССТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>7820012849</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr"/>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr"/>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>7826123721</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr"/>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr"/>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РестСтройГрупп»</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>7839099924</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr"/>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr"/>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
           <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Потенциал»</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>7814558855</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr"/>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr"/>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>1700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК Гарант»</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>7806380022</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr"/>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr"/>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК ПСП»</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>7810502379</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr"/>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr"/>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СПбЭК-Майнинг»</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>7820326027</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr"/>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr"/>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>7825055370</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr"/>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr"/>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУ-17»</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>7807028906</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr"/>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr"/>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>2300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУАР-Групп»</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>7802270195</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr"/>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr"/>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СЭМ»</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>7810201646</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr"/>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr"/>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строительные технологии»</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>7813680179</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr"/>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr"/>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СтройГрад»</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>7813692632</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr"/>
+      <c r="E87" s="11" t="inlineStr"/>
+      <c r="F87" s="11" t="inlineStr"/>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Сфера»</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>2311308786</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr"/>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr"/>
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>7814612968</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr"/>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr"/>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>7839061021</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr"/>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr"/>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Трамплин-строй»</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>7802207193</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr"/>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr"/>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr"/>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr"/>
+      <c r="G92" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr"/>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr"/>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr"/>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr"/>
+      <c r="G94" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr"/>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr"/>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr"/>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr"/>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr"/>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr"/>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J73" s="10" t="inlineStr">
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J97" s="10" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J73"/>
+  <autoFilter ref="A1:J97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3825,7 +4881,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -3835,7 +4891,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -3845,7 +4901,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -729,27 +729,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>АО «Омега»</t>
+          <t>АО «ОДК-Климов»</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>7806016873</t>
+          <t>7802375335</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 226-34-54</t>
+          <t>+7 (812) 301-90-50; +7 (812) 454-71-00; +7 (921) 861-69-31</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>СПб, 6-й Предпортовый пр. 10А оф.1; ОГРН 1027804178082; ген.дир. Гальперин Л.Б.; ~127 сотр.</t>
+          <t>СПб, ул.Кантемировская 11с1; ОГРН 1069847546383; авиадвигатели; в источнике был также +7 (347) 238-33-66 — уфимский код, вероятно не этот адрес</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/1481264; companies.rbc.ru; sbis.ru</t>
+          <t>rusprofile.ru/id/1814140; checko.ru; focus.kontur.ru</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>663</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -779,27 +779,27 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>АО «ПИ-№1» (Проектный институт №1)</t>
+          <t>АО «Омега»</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>7812008359</t>
+          <t>7806016873</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 334-02-44; +7 (812) 244-57-57; +7 (812) 244-57-24; +7 (931) 314-46-56</t>
+          <t>+7 (812) 226-34-54</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>191015 СПб, 9-я Советская 4-6А пом.102; ОГРН 1037851020173; ген.дир. Окунева М.П.</t>
+          <t>СПб, 6-й Предпортовый пр. 10А оф.1; ОГРН 1027804178082; ген.дир. Гальперин Л.Б.; ~127 сотр.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/1549030; checko.ru; saby.ru</t>
+          <t>rusprofile.ru/id/1481264; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>597</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -829,27 +829,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ОАО «БСМЗ» (Балтийский судомеханический завод)</t>
+          <t>АО «ПИ-№1» (Проектный институт №1)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>7805029037</t>
+          <t>7812008359</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 335-71-13; +7 (812) 321-68-50</t>
+          <t>+7 (812) 334-02-44; +7 (812) 244-57-57; +7 (812) 244-57-24; +7 (931) 314-46-56</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>198096 СПб, дор. на Турухтанные Острова 26к5; ОГРН 1027802760930; ген.дир. Савкин Е.А.</t>
+          <t>191015 СПб, 9-я Советская 4-6А пом.102; ОГРН 1037851020173; ген.дир. Окунева М.П.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/1416533; companies.rbc.ru; sbis.ru</t>
+          <t>rusprofile.ru/id/1549030; checko.ru; saby.ru</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>731</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -879,27 +879,27 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>ООО «БАСТ»</t>
+          <t>ОАО «БСМЗ» (Балтийский судомеханический завод)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>7816196826</t>
+          <t>7805029037</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 766-64-80; +7 (812) 766-63-35; +7 (812) 766-48-07</t>
+          <t>+7 (812) 335-71-13; +7 (812) 321-68-50</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>191015 СПб, ул.Таврическая 17А оф.311; ОГРН 1037835049130; ген.дир. Филимонов Д.В.</t>
+          <t>198096 СПб, дор. на Турухтанные Острова 26к5; ОГРН 1027802760930; ген.дир. Савкин Е.А.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3208204; companies.rbc.ru; checko.ru</t>
+          <t>rusprofile.ru/id/1416533; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -929,27 +929,27 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ООО «БалтМостСтрой»</t>
+          <t>ООО «БАСТ»</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>7801182620</t>
+          <t>7816196826</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 422-44-02; +7 (812) 677-23-78</t>
+          <t>+7 (812) 766-64-80; +7 (812) 766-63-35; +7 (812) 766-48-07</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>192029 СПб, ул.Бабушкина 3А пом.34Н; ОГРН 1027808912031; строительство мостов и тоннелей</t>
+          <t>191015 СПб, ул.Таврическая 17А оф.311; ОГРН 1037835049130; ген.дир. Филимонов Д.В.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/4221107; synapsenet.ru; casebook.ru</t>
+          <t>rusprofile.ru/id/3208204; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>634</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -979,27 +979,27 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ООО «ВИЗОТЕК РУС»</t>
+          <t>ООО «БалтМостСтрой»</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>7805665201</t>
+          <t>7801182620</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 238-03-28; +7 (812) 346-83-43; +7 (931) 007-70-99</t>
+          <t>+7 (812) 422-44-02; +7 (812) 677-23-78</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>198097 СПб, пр.Стачек 47У; ОГРН 1147847414219; рук. Семенов Н.М.; обработка металлов</t>
+          <t>192029 СПб, ул.Бабушкина 3А пом.34Н; ОГРН 1027808912031; строительство мостов и тоннелей</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7560433; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/4221107; synapsenet.ru; casebook.ru</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>764</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «ВИЗОТЕК РУС»</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>7816500610</t>
+          <t>7805665201</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 603-29-07</t>
+          <t>+7 (812) 238-03-28; +7 (812) 346-83-43; +7 (931) 007-70-99</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>199106 СПб, пл.Морской Славы 1А пом.5069; ОГРН 1107847385040; ген.дир. Власенко А.В. | в источнике также обрывок «365-66-38» без кода города — уточнить</t>
+          <t>198097 СПб, пр.Стачек 47У; ОГРН 1147847414219; рук. Семенов Н.М.; обработка металлов</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/5307814; focus.kontur.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru/id/7560433; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>579</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1079,27 +1079,27 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>ООО «Графит»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>7841505154</t>
+          <t>7816500610</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 944-62-49</t>
+          <t>+7 (812) 603-29-07</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+          <t>199106 СПб, пл.Морской Славы 1А пом.5069; ОГРН 1107847385040; ген.дир. Власенко А.В. | в источнике также обрывок «365-66-38» без кода города — уточнить</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+          <t>rusprofile.ru/id/5307814; focus.kontur.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>611</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1129,147 +1129,147 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>ООО «Графит»</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>7841505154</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 944-62-49</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>ООО «ИНТРА ПРОЕКТ»</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>7806519718</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>ООО «ИРЕСТ СТРОЙ»</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>7825134181</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>+7 (812) 326-11-53</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>kanoner.com (данные 2013 г.)</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>средняя (ИНН совпал, но источник старый — сверить)</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>1800000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>ООО «Магистраль северной столицы»</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>7710884741</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>833</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1279,27 +1279,27 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ООО «НПО «АМБ»</t>
+          <t>ООО «Магистраль северной столицы»</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>7804516528</t>
+          <t>7710884741</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
+          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
+          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
+          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>833</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1329,27 +1329,27 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПО «Энергосистема»</t>
+          <t>ООО «НПО «АМБ»</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>7805654520</t>
+          <t>7804516528</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
+          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
+          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1379,27 +1379,27 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПСМ» (Промстроймонтаж)</t>
+          <t>ООО «ПО «Энергосистема»</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>7814118903</t>
+          <t>7805654520</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
+          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
+          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>336</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1429,27 +1429,27 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ООО «Розенберг Северо-Запад»</t>
+          <t>ООО «ПСМ» (Промстроймонтаж)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>7816592450</t>
+          <t>7814118903</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>727</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -1479,145 +1479,145 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>ООО «Розенберг Северо-Запад»</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>7816592450</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>7810206161</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>ООО «ССМ» (Стройсервисмонтаж)</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>5609095128</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>1305</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>7801349149</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -1629,27 +1629,27 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ООО «Северный Альянс»</t>
+          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>7805662306</t>
+          <t>7801349149</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
+          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
+          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>627</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1679,27 +1679,27 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>ООО «Спецтехкомплект»</t>
+          <t>ООО «Северный Альянс»</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>7811127120</t>
+          <t>7805662306</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 362-09-21</t>
+          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>ООО «СтарКом»</t>
+          <t>ООО «Спецтехкомплект»</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>7841416641</t>
+          <t>7811127120</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+          <t>+7 (812) 362-09-21</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>626</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1779,27 +1779,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ООО «ТМГ ГРУП»</t>
+          <t>ООО «СтарКом»</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>7705405168</t>
+          <t>7841416641</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 680-30-20</t>
+          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>508</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1829,87 +1829,95 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>ООО «ТМГ ГРУП»</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>7705405168</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 680-30-20</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>ООО «Транспромстрой»</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>7804591155</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 449-31-21</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>СПб, ул.Савушкина 83к3А оф.401-402; ОГРН 1177847074250; ген.дир. Аванесов Д.Б.; ~467 сотрудников</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>spark-interfax.ru; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>752</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>7810255553</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr"/>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr"/>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -1921,18 +1929,18 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>АО «ВОЛХОН»</t>
+          <t>АНО «ВАЛААМ»</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>7810383403</t>
+          <t>7839024647</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr"/>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
+          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
@@ -1943,7 +1951,7 @@
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -1953,7 +1961,7 @@
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1963,18 +1971,18 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
+          <t>АО «Абсолют»</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>7813007615</t>
+          <t>7825663795</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr"/>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
+          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
@@ -1985,7 +1993,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -1995,7 +2003,7 @@
       </c>
       <c r="J30" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2005,18 +2013,18 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>АО «НОУДИГ» (Per Aarsleff)</t>
+          <t>АО «Аспект Северо-Запад»</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>7802108837</t>
+          <t>7810143306</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr"/>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
+          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
@@ -2027,7 +2035,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>735</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -2037,7 +2045,7 @@
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2047,29 +2055,29 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>АО «Полиспаст»</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>7805744573</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr"/>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -2089,18 +2097,18 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>АО «Стройинвест»</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>7825697956</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr"/>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
@@ -2111,7 +2119,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -2131,18 +2139,18 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Агентство Шушары»</t>
+          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>7820016970</t>
+          <t>7813007615</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr"/>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
+          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
@@ -2153,7 +2161,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -2173,18 +2181,18 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
+          <t>АО «НОУДИГ» (Per Aarsleff)</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>7811405770</t>
+          <t>7802108837</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr"/>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
+          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
@@ -2195,7 +2203,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>699</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -2215,29 +2223,29 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>АО «Петрос»</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7816131635</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
+          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>507</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2247,7 +2255,7 @@
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2257,29 +2265,29 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr"/>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -2289,7 +2297,7 @@
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2307,20 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr"/>
-      <c r="E38" s="11" t="inlineStr"/>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+        </is>
+      </c>
       <c r="F38" s="11" t="inlineStr"/>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2317,7 +2329,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -2337,29 +2349,29 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>ООО «БиАр»</t>
+          <t>ЗАО «Агентство Шушары»</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>7802738910</t>
+          <t>7820016970</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr"/>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
+          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -2369,7 +2381,7 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2379,29 +2391,29 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЕРТЕК»</t>
+          <t>ЗАО «Эра-Инжиниринг»</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>7806317711</t>
+          <t>7811405770</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>519</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2411,7 +2423,7 @@
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2421,29 +2433,29 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr"/>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -2463,29 +2475,29 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2495,7 +2507,7 @@
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2505,20 +2517,16 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
-        </is>
-      </c>
+      <c r="E43" s="11" t="inlineStr"/>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2527,7 +2535,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -2547,18 +2555,18 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
@@ -2569,7 +2577,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2579,7 +2587,7 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -2589,29 +2597,29 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr"/>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2621,7 +2629,7 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2631,29 +2639,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr"/>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2673,18 +2681,18 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr"/>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
@@ -2695,7 +2703,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2715,18 +2723,18 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr"/>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
@@ -2737,7 +2745,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2747,7 +2755,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2757,29 +2765,29 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr"/>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -2789,7 +2797,7 @@
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2799,25 +2807,29 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr"/>
-      <c r="E50" s="11" t="inlineStr"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+        </is>
+      </c>
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2837,18 +2849,18 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr"/>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
@@ -2859,7 +2871,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -2869,7 +2881,7 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2879,29 +2891,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr"/>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -2921,29 +2933,29 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr"/>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -2953,7 +2965,7 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -2963,18 +2975,18 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
@@ -2985,7 +2997,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -2995,7 +3007,7 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3005,29 +3017,25 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr"/>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
-        </is>
-      </c>
+      <c r="E55" s="11" t="inlineStr"/>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3047,29 +3055,29 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3089,29 +3097,29 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr"/>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -3131,29 +3139,29 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr"/>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -3173,18 +3181,18 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr"/>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -3195,7 +3203,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3205,7 +3213,7 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3215,29 +3223,29 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>ООО «МонтажСтрой-М» (МСМ)</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>7811447071</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr"/>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3247,7 +3255,7 @@
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3257,18 +3265,18 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr"/>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -3279,7 +3287,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3289,7 +3297,7 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3299,18 +3307,18 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr"/>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
@@ -3321,7 +3329,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3331,7 +3339,7 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3341,29 +3349,29 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr"/>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -3383,18 +3391,18 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -3405,7 +3413,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -3415,7 +3423,7 @@
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3425,18 +3433,18 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr"/>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -3447,7 +3455,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -3457,7 +3465,7 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3467,29 +3475,29 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>7825382561</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr"/>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3499,7 +3507,7 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -3509,18 +3517,18 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr"/>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
@@ -3531,7 +3539,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -3541,7 +3549,7 @@
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3551,18 +3559,18 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr"/>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -3573,7 +3581,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3583,7 +3591,7 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3593,18 +3601,18 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7810685806</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr"/>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, Ярославский пр.</t>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
@@ -3615,7 +3623,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3625,7 +3633,7 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -3635,18 +3643,18 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr"/>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -3657,7 +3665,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -3677,29 +3685,29 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -3709,7 +3717,7 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3719,25 +3727,29 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr"/>
-      <c r="E72" s="11" t="inlineStr"/>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+        </is>
+      </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -3757,29 +3769,29 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -3789,7 +3801,7 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3799,18 +3811,18 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr"/>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+          <t>194017 СПб, Ярославский пр.</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -3821,7 +3833,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -3831,7 +3843,7 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -3841,18 +3853,18 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>7811659380</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr"/>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
@@ -3863,7 +3875,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>607</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -3883,18 +3895,18 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «ПСТ»</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7813448257</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr"/>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
@@ -3905,7 +3917,7 @@
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>876</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -3925,29 +3937,25 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>ООО «РестСтройГрупп»</t>
+          <t>ООО «ПТГ»</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>7839099924</t>
+          <t>5013050270</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr"/>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
-        </is>
-      </c>
+      <c r="E77" s="11" t="inlineStr"/>
       <c r="F77" s="11" t="inlineStr"/>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -3967,18 +3975,18 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «Промстрой»</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7814656860</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr"/>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -3989,7 +3997,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>516</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -3999,7 +4007,7 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -4009,18 +4017,18 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «Профиль»</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7802182380</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr"/>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -4031,7 +4039,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>572</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -4041,7 +4049,7 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4051,18 +4059,18 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «РЕССТРОЙ»</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7820012849</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr"/>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
@@ -4073,7 +4081,7 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>713</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -4093,18 +4101,18 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7826123721</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr"/>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -4115,7 +4123,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>515</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -4135,29 +4143,29 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «РестСтройГрупп»</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7839099924</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr"/>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>673</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -4167,7 +4175,7 @@
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4177,18 +4185,18 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «СК «Алстрой»</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7813417675</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr"/>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -4199,7 +4207,7 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>590</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -4209,7 +4217,7 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -4219,18 +4227,18 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «СК «Потенциал»</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7814558855</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr"/>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -4241,7 +4249,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>675</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -4251,7 +4259,7 @@
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1700000</t>
         </is>
       </c>
     </row>
@@ -4261,29 +4269,29 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «СК Гарант»</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7806380022</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr"/>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -4293,7 +4301,7 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -4303,18 +4311,18 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «СК ПСП»</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7810502379</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr"/>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
@@ -4325,7 +4333,7 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>527</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -4345,16 +4353,20 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «СПбЭК-Майнинг»</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7820326027</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr"/>
-      <c r="E87" s="11" t="inlineStr"/>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
       <c r="F87" s="11" t="inlineStr"/>
       <c r="G87" s="11" t="inlineStr">
         <is>
@@ -4363,7 +4375,7 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>548</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -4373,7 +4385,7 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4383,18 +4395,18 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7825055370</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr"/>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -4405,7 +4417,7 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>573</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -4415,7 +4427,7 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4425,18 +4437,18 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «СУ-17»</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7807028906</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr"/>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
@@ -4447,7 +4459,7 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>747</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -4457,7 +4469,7 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2300000</t>
         </is>
       </c>
     </row>
@@ -4467,18 +4479,18 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «СУАР-Групп»</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7802270195</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr"/>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -4489,7 +4501,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>518</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -4499,7 +4511,7 @@
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4509,29 +4521,29 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «СЭМ»</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7810201646</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr"/>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>700</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -4541,7 +4553,7 @@
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -4551,18 +4563,18 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>7813680179</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr"/>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
@@ -4573,7 +4585,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -4593,29 +4605,29 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «Строй центр»</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7804538240</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr"/>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>732</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -4625,7 +4637,7 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -4635,29 +4647,25 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «СтройГрад»</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7813692632</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr"/>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
-        </is>
-      </c>
+      <c r="E94" s="11" t="inlineStr"/>
       <c r="F94" s="11" t="inlineStr"/>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -4667,7 +4675,7 @@
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4677,18 +4685,18 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Сфера»</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>2311308786</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr"/>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -4699,7 +4707,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -4709,7 +4717,7 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4719,29 +4727,29 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «ТЕЗИС»</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>7804441209</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr"/>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>674</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -4751,7 +4759,7 @@
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>700000</t>
         </is>
       </c>
     </row>
@@ -4761,44 +4769,380 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7814612968</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr"/>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
       <c r="G97" s="11" t="inlineStr">
         <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>7839061021</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr"/>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr"/>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Трамплин-строй»</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>7802207193</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr"/>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr"/>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr"/>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr"/>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr"/>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr"/>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J101" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="inlineStr"/>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr"/>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
           <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
-      <c r="H97" s="10" t="inlineStr">
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J102" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr"/>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr"/>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr"/>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr"/>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr"/>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr"/>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J97" s="10" t="inlineStr">
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J105" s="10" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4881,7 +5225,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
@@ -4891,7 +5235,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -4901,7 +5245,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -879,27 +879,27 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>ОАО «БСМЗ» (Балтийский судомеханический завод)</t>
+          <t>АО «Техномарин»</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>7805029037</t>
+          <t>7805016422</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 335-71-13; +7 (812) 321-68-50</t>
+          <t>+7 (812) 251-12-57; +7 (812) 351-12-57</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>198096 СПб, дор. на Турухтанные Острова 26к5; ОГРН 1027802760930; ген.дир. Савкин Е.А.</t>
+          <t>198035 СПб, ул.Гапсальская 3 оф.427; ОГРН 1037811062167; ген.дир. Сафронов В.Н.; радионавигационная аппаратура</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/1416533; companies.rbc.ru; sbis.ru</t>
+          <t>rusprofile.ru/id/588898; find-org.com; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>644</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -929,27 +929,27 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ООО «БАСТ»</t>
+          <t>ЗАО НТЦ «Мониторинг Мостов»</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>7816196826</t>
+          <t>7816585131</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 766-64-80; +7 (812) 766-63-35; +7 (812) 766-48-07</t>
+          <t>+7 (812) 600-23-13; +7 (903) 628-94-93</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>191015 СПб, ул.Таврическая 17А оф.311; ОГРН 1037835049130; ген.дир. Филимонов Д.В.</t>
+          <t>192007 СПб, Лиговский пр. 150А пом.14н; ОГРН 1147847135006; ген.дир. Попов М.П.; rumyantzeva@b-monitoring.ru; bridge-monitoring.ru</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3208204; companies.rbc.ru; checko.ru</t>
+          <t>rusprofile.ru/id/7309795; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>723</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -979,27 +979,27 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ООО «БалтМостСтрой»</t>
+          <t>ОАО «БСМЗ» (Балтийский судомеханический завод)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>7801182620</t>
+          <t>7805029037</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 422-44-02; +7 (812) 677-23-78</t>
+          <t>+7 (812) 335-71-13; +7 (812) 321-68-50</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>192029 СПб, ул.Бабушкина 3А пом.34Н; ОГРН 1027808912031; строительство мостов и тоннелей</t>
+          <t>198096 СПб, дор. на Турухтанные Острова 26к5; ОГРН 1027802760930; ген.дир. Савкин Е.А.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/4221107; synapsenet.ru; casebook.ru</t>
+          <t>rusprofile.ru/id/1416533; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ООО «ВИЗОТЕК РУС»</t>
+          <t>ООО «БАСТ»</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>7805665201</t>
+          <t>7816196826</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 238-03-28; +7 (812) 346-83-43; +7 (931) 007-70-99</t>
+          <t>+7 (812) 766-64-80; +7 (812) 766-63-35; +7 (812) 766-48-07</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>198097 СПб, пр.Стачек 47У; ОГРН 1147847414219; рук. Семенов Н.М.; обработка металлов</t>
+          <t>191015 СПб, ул.Таврическая 17А оф.311; ОГРН 1037835049130; ген.дир. Филимонов Д.В.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7560433; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/3208204; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>634</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1079,27 +1079,27 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «БалтМостСтрой»</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>7816500610</t>
+          <t>7801182620</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 603-29-07</t>
+          <t>+7 (812) 422-44-02; +7 (812) 677-23-78</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>199106 СПб, пл.Морской Славы 1А пом.5069; ОГРН 1107847385040; ген.дир. Власенко А.В. | в источнике также обрывок «365-66-38» без кода города — уточнить</t>
+          <t>192029 СПб, ул.Бабушкина 3А пом.34Н; ОГРН 1027808912031; строительство мостов и тоннелей</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/5307814; focus.kontur.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru/id/4221107; synapsenet.ru; casebook.ru</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>764</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ООО «Графит»</t>
+          <t>ООО «ВИЗОТЕК РУС»</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>7841505154</t>
+          <t>7805665201</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 944-62-49</t>
+          <t>+7 (812) 238-03-28; +7 (812) 346-83-43; +7 (931) 007-70-99</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+          <t>198097 СПб, пр.Стачек 47У; ОГРН 1147847414219; рук. Семенов Н.М.; обработка металлов</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+          <t>rusprofile.ru/id/7560433; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>579</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1179,27 +1179,27 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ООО «ИНТРА ПРОЕКТ»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>7806519718</t>
+          <t>7816500610</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
+          <t>+7 (812) 603-29-07</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
+          <t>199106 СПб, пл.Морской Славы 1А пом.5069; ОГРН 1107847385040; ген.дир. Власенко А.В. | в источнике также обрывок «365-66-38» без кода города — уточнить</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/5307814; focus.kontur.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>611</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1224,52 +1224,52 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ИРЕСТ СТРОЙ»</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>7825134181</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>+7 (812) 326-11-53</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>kanoner.com (данные 2013 г.)</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>средняя (ИНН совпал, но источник старый — сверить)</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>1800000</t>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Графит»</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>7841505154</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 944-62-49</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1279,27 +1279,27 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ООО «Магистраль северной столицы»</t>
+          <t>ООО «ИНТРА ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>7710884741</t>
+          <t>7806519718</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
+          <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
+          <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>514</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1319,57 +1319,57 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>ООО «НПО «АМБ»</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>7804516528</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2000000</t>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ИРЕСТ СТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>7825134181</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>+7 (812) 326-11-53</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>kanoner.com (данные 2013 г.)</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но источник старый — сверить)</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -1379,27 +1379,27 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПО «Энергосистема»</t>
+          <t>ООО «Магистраль северной столицы»</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>7805654520</t>
+          <t>7710884741</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
+          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
+          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>833</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1429,27 +1429,27 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПСМ» (Промстроймонтаж)</t>
+          <t>ООО «НПО «АМБ»</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>7814118903</t>
+          <t>7804516528</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
+          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
+          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1479,27 +1479,27 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ООО «Розенберг Северо-Запад»</t>
+          <t>ООО «ПО «Энергосистема»</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>7816592450</t>
+          <t>7805654520</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>336</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1529,27 +1529,27 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
+          <t>ООО «ПСМ» (Промстроймонтаж)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>7810206161</t>
+          <t>7814118903</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
+          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
+          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>727</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1569,57 +1569,57 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>5609095128</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>1500000</t>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Розенберг Северо-Запад»</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>7816592450</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1629,27 +1629,27 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
+          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>7801349149</t>
+          <t>7810206161</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
+          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
+          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
+          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>241</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1674,50 +1674,50 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>ООО «Северный Альянс»</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>7805662306</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>5609095128</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>ООО «Спецтехкомплект»</t>
+          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>7811127120</t>
+          <t>7801349149</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 362-09-21</t>
+          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>627</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1779,27 +1779,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ООО «СтарКом»</t>
+          <t>ООО «Северный Альянс»</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>7841416641</t>
+          <t>7805662306</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1829,27 +1829,27 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ООО «ТМГ ГРУП»</t>
+          <t>ООО «Спецтехкомплект»</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>7705405168</t>
+          <t>7811127120</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 680-30-20</t>
+          <t>+7 (812) 362-09-21</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1879,131 +1879,147 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>ООО «СтарКом»</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>7841416641</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ТМГ ГРУП»</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>7705405168</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 680-30-20</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
           <t>ООО «Транспромстрой»</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>7804591155</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 449-31-21</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>СПб, ул.Савушкина 83к3А оф.401-402; ОГРН 1177847074250; ген.дир. Аванесов Д.Б.; ~467 сотрудников</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>spark-interfax.ru; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>752</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>АНО «ВАЛААМ»</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>7839024647</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr"/>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr"/>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>АО «Абсолют»</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>7825663795</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr"/>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr"/>
-      <c r="G30" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2013,29 +2029,29 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>АО «Аспект Северо-Запад»</t>
+          <t>АНО «ВАЛААМ»</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>7810143306</t>
+          <t>7839024647</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr"/>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
+          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -2055,18 +2071,18 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
+          <t>АО «Абсолют»</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>7810255553</t>
+          <t>7825663795</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr"/>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
+          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
@@ -2077,7 +2093,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -2087,7 +2103,7 @@
       </c>
       <c r="J32" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2097,29 +2113,29 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>АО «ВОЛХОН»</t>
+          <t>АО «Аспект Северо-Запад»</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>7810383403</t>
+          <t>7810143306</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr"/>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
+          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>735</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -2129,7 +2145,7 @@
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2139,18 +2155,18 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>7813007615</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr"/>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
@@ -2161,7 +2177,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -2171,7 +2187,7 @@
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2181,29 +2197,29 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>АО «НОУДИГ» (Per Aarsleff)</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>7802108837</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr"/>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -2223,18 +2239,18 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>АО «Петрос»</t>
+          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>7816131635</t>
+          <t>7813007615</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
+          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
@@ -2245,7 +2261,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2255,7 +2271,7 @@
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2265,18 +2281,18 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>АО «Полиспаст»</t>
+          <t>АО «НОУДИГ» (Per Aarsleff)</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>7805744573</t>
+          <t>7802108837</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr"/>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
+          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
@@ -2287,7 +2303,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>699</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -2307,18 +2323,18 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>АО «Стройинвест»</t>
+          <t>АО «Петрос»</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>7825697956</t>
+          <t>7816131635</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr"/>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
@@ -2329,7 +2345,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>507</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -2339,7 +2355,7 @@
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2349,29 +2365,29 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Агентство Шушары»</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>7820016970</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr"/>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -2381,7 +2397,7 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2391,29 +2407,29 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
+          <t>АО «РЭС» (Региональные электрические сети)</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>7811405770</t>
+          <t>7810785984</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
+          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>566</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2423,7 +2439,7 @@
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2433,29 +2449,25 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>АО «СМУ-47»</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7801097276</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr"/>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
-        </is>
-      </c>
+      <c r="E41" s="11" t="inlineStr"/>
       <c r="F41" s="11" t="inlineStr"/>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>687</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -2465,7 +2477,7 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2475,29 +2487,29 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>АО «Селектел»</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7810962785</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (телефон смотреть на selectel.ru)</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2507,7 +2519,7 @@
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2517,16 +2529,20 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="11" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+        </is>
+      </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr">
         <is>
@@ -2535,7 +2551,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -2555,29 +2571,29 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ООО «БиАр»</t>
+          <t>ЗАО «Агентство Шушары»</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>7802738910</t>
+          <t>7820016970</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
+          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2587,7 +2603,7 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2597,29 +2613,29 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЕРТЕК»</t>
+          <t>ЗАО «Институт телекоммуникаций»</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>7806317711</t>
+          <t>7802199182</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr"/>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
+          <t>нет данных (телефон смотреть на itain.ru)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2629,7 +2645,7 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2639,29 +2655,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ЗАО «ПетроЭлектроКомплекс»</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7801128326</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr"/>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>506</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2671,7 +2687,7 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2681,29 +2697,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>ЗАО «Трест СЗКС» (Севзапкурортстрой)</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7809006739</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr"/>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>190013 СПб, Рузовская ул. 16 пом.1н оф.117; ОГРН 1027810295842; ген.дир. Тихомиров С.А.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>630</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2713,7 +2729,7 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2723,29 +2739,29 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ЗАО «Эра-Инжиниринг»</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7811405770</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr"/>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>519</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2765,29 +2781,29 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7813424070</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr"/>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
+          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>684</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -2797,7 +2813,7 @@
       </c>
       <c r="J49" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2807,18 +2823,18 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «АЛЬФА»</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7813411063</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
@@ -2829,7 +2845,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>524</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2839,7 +2855,7 @@
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2849,18 +2865,18 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «АРТ-МАСШТАБ»</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7840076495</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr"/>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
+          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
@@ -2871,7 +2887,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -2881,7 +2897,7 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2891,29 +2907,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «АС Инжиниринг»</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>7810318651</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr"/>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
+          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -2923,7 +2939,7 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2933,29 +2949,33 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «Алисард»</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7814713356</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr"/>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr"/>
+          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>alisard.com</t>
+        </is>
+      </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть e-mail и сайт)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>575</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -2965,7 +2985,7 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2975,20 +2995,16 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «Альфа»</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7802594841</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr"/>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
-        </is>
-      </c>
+      <c r="E54" s="11" t="inlineStr"/>
       <c r="F54" s="11" t="inlineStr"/>
       <c r="G54" s="11" t="inlineStr">
         <is>
@@ -2997,7 +3013,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3007,7 +3023,7 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3017,25 +3033,29 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr"/>
-      <c r="E55" s="11" t="inlineStr"/>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
+        </is>
+      </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3045,7 +3065,7 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3055,18 +3075,18 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «Антей»</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>4708011991</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
@@ -3077,7 +3097,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3087,7 +3107,7 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3097,18 +3117,18 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «Арман»</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7805298463</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr"/>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
@@ -3119,7 +3139,7 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>586</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -3129,7 +3149,7 @@
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3139,29 +3159,25 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «Атлантис»</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>7810914904</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr"/>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
-        </is>
-      </c>
+      <c r="E58" s="11" t="inlineStr"/>
       <c r="F58" s="11" t="inlineStr"/>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -3171,7 +3187,7 @@
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3181,18 +3197,18 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «БАРК»</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7804462262</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr"/>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
+          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -3203,7 +3219,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3213,7 +3229,7 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3223,29 +3239,29 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>7804634666</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr"/>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
+          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3255,7 +3271,7 @@
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3265,18 +3281,18 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «БЕЛНЕВА»</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7839489314</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr"/>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
+          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -3287,7 +3303,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>457</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3297,7 +3313,7 @@
       </c>
       <c r="J61" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3307,29 +3323,29 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr"/>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3339,7 +3355,7 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3349,20 +3365,16 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr"/>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
-        </is>
-      </c>
+      <c r="E63" s="11" t="inlineStr"/>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
@@ -3371,7 +3383,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -3391,29 +3403,29 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «БРАЗСТРОЙ»</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>2630050808</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -3423,7 +3435,7 @@
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3433,29 +3445,29 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>ООО «МонтажСтрой-М» (МСМ)</t>
+          <t>ООО «БелькаРус»</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>7811447071</t>
+          <t>7801665024</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr"/>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
+          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -3465,7 +3477,7 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3475,29 +3487,29 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr"/>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3507,7 +3519,7 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -3517,29 +3529,29 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «Бобёр»</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7801632702</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr"/>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -3549,7 +3561,7 @@
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3559,29 +3571,29 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr"/>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3591,7 +3603,7 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3601,29 +3613,29 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «ВИРА»</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7839139655</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr"/>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3633,7 +3645,7 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3643,18 +3655,18 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr"/>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -3665,7 +3677,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -3675,7 +3687,7 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3685,18 +3697,18 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>7825382561</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
@@ -3707,7 +3719,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -3717,7 +3729,7 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3727,29 +3739,29 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr"/>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -3769,18 +3781,18 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
@@ -3791,7 +3803,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -3811,29 +3823,29 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>7810685806</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr"/>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, Ярославский пр.</t>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -3843,7 +3855,7 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3853,29 +3865,29 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr"/>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -3885,7 +3897,7 @@
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3895,29 +3907,29 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr"/>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -3937,16 +3949,20 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr"/>
-      <c r="E77" s="11" t="inlineStr"/>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+        </is>
+      </c>
       <c r="F77" s="11" t="inlineStr"/>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -3955,7 +3971,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -3965,7 +3981,7 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -3975,18 +3991,18 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr"/>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -3997,7 +4013,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -4007,7 +4023,7 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4017,20 +4033,16 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr"/>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
-        </is>
-      </c>
+      <c r="E79" s="11" t="inlineStr"/>
       <c r="F79" s="11" t="inlineStr"/>
       <c r="G79" s="11" t="inlineStr">
         <is>
@@ -4039,7 +4051,7 @@
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -4049,7 +4061,7 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4059,29 +4071,29 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr"/>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
       <c r="G80" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -4101,18 +4113,18 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr"/>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -4123,7 +4135,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -4143,18 +4155,18 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>ООО «РестСтройГрупп»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>7839099924</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr"/>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
@@ -4165,7 +4177,7 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -4185,18 +4197,18 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Алстрой»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>7813417675</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr"/>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -4207,7 +4219,7 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -4217,7 +4229,7 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4227,29 +4239,29 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr"/>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -4259,7 +4271,7 @@
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4269,18 +4281,18 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr"/>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
@@ -4291,7 +4303,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -4301,7 +4313,7 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4311,29 +4323,29 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr"/>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -4353,18 +4365,18 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr"/>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
@@ -4375,7 +4387,7 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -4395,18 +4407,18 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr"/>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -4417,7 +4429,7 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -4427,7 +4439,7 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4437,18 +4449,18 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr"/>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
@@ -4459,7 +4471,7 @@
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -4469,7 +4481,7 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -4479,18 +4491,18 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr"/>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -4501,7 +4513,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -4511,7 +4523,7 @@
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -4521,18 +4533,18 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr"/>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
@@ -4543,7 +4555,7 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -4553,7 +4565,7 @@
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4563,29 +4575,29 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr"/>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -4605,29 +4617,29 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй центр»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>7804538240</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr"/>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -4637,7 +4649,7 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -4647,16 +4659,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr"/>
-      <c r="E94" s="11" t="inlineStr"/>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+        </is>
+      </c>
       <c r="F94" s="11" t="inlineStr"/>
       <c r="G94" s="11" t="inlineStr">
         <is>
@@ -4665,7 +4681,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -4675,7 +4691,7 @@
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4685,29 +4701,29 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr"/>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -4717,7 +4733,7 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -4727,18 +4743,18 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕЗИС»</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>7804441209</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr"/>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
@@ -4749,7 +4765,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -4759,7 +4775,7 @@
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>700000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4769,29 +4785,29 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr"/>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -4801,7 +4817,7 @@
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4811,18 +4827,18 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr"/>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+          <t>194017 СПб, Ярославский пр.</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
@@ -4833,7 +4849,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
@@ -4843,7 +4859,7 @@
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -4853,18 +4869,18 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7811659380</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr"/>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
@@ -4875,7 +4891,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>607</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -4885,7 +4901,7 @@
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4895,18 +4911,18 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «ПСТ»</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>7813448257</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr"/>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
@@ -4917,7 +4933,7 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>876</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -4937,20 +4953,16 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «ПТГ»</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>5013050270</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr"/>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
-        </is>
-      </c>
+      <c r="E101" s="11" t="inlineStr"/>
       <c r="F101" s="11" t="inlineStr"/>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -4959,7 +4971,7 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -4969,7 +4981,7 @@
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4979,29 +4991,29 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «Промстрой»</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7814656860</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr"/>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr"/>
       <c r="G102" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>516</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -5021,18 +5033,18 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Профиль»</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7802182380</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr"/>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
@@ -5043,7 +5055,7 @@
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>572</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -5063,18 +5075,18 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «РЕССТРОЙ»</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>7820012849</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr"/>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr"/>
@@ -5085,7 +5097,7 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>713</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -5105,44 +5117,1048 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7826123721</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr"/>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
       <c r="G105" s="11" t="inlineStr">
         <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J105" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РестСтройГрупп»</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>7839099924</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr"/>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr"/>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
           <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
-      <c r="H105" s="10" t="inlineStr">
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="I106" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J106" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Алстрой»</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>7813417675</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr"/>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr"/>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J107" s="10" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Потенциал»</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>7814558855</t>
+        </is>
+      </c>
+      <c r="D108" s="13" t="inlineStr"/>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr"/>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I108" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J108" s="10" t="inlineStr">
+        <is>
+          <t>1700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК Гарант»</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>7806380022</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr"/>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr"/>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J109" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК ПСП»</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>7810502379</t>
+        </is>
+      </c>
+      <c r="D110" s="13" t="inlineStr"/>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr"/>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J110" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СПбЭК-Майнинг»</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>7820326027</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr"/>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr"/>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J111" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>7825055370</t>
+        </is>
+      </c>
+      <c r="D112" s="13" t="inlineStr"/>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr"/>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J112" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУ-17»</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>7807028906</t>
+        </is>
+      </c>
+      <c r="D113" s="13" t="inlineStr"/>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr"/>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H113" s="10" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="I113" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J113" s="10" t="inlineStr">
+        <is>
+          <t>2300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУАР-Групп»</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>7802270195</t>
+        </is>
+      </c>
+      <c r="D114" s="13" t="inlineStr"/>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr"/>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="I114" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J114" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СЭМ»</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>7810201646</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="inlineStr"/>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr"/>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I115" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J115" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строительные технологии»</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>7813680179</t>
+        </is>
+      </c>
+      <c r="D116" s="13" t="inlineStr"/>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr"/>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J116" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строй центр»</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>7804538240</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr"/>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr"/>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="I117" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J117" s="10" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СтройГрад»</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>7813692632</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="inlineStr"/>
+      <c r="E118" s="11" t="inlineStr"/>
+      <c r="F118" s="11" t="inlineStr"/>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Сфера»</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>2311308786</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="inlineStr"/>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr"/>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЕЗИС»</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>7804441209</t>
+        </is>
+      </c>
+      <c r="D120" s="13" t="inlineStr"/>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr"/>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>7814612968</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="inlineStr"/>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr"/>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>7839061021</t>
+        </is>
+      </c>
+      <c r="D122" s="13" t="inlineStr"/>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr"/>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Трамплин-строй»</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>7802207193</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr"/>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr"/>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J123" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr"/>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr"/>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J124" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr"/>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr"/>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="inlineStr"/>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr"/>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D127" s="13" t="inlineStr"/>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr"/>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D128" s="13" t="inlineStr"/>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr"/>
+      <c r="G128" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D129" s="13" t="inlineStr"/>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr"/>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J105" s="10" t="inlineStr">
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J129" s="10" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
+  <autoFilter ref="A1:J129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5225,7 +6241,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>104</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8">
@@ -5235,7 +6251,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -5245,7 +6261,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1229,27 +1229,27 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ООО «Графит»</t>
+          <t>ООО «Газпромнефть ИТО»</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>7841505154</t>
+          <t>8905032518</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 944-62-49</t>
+          <t>+7 (812) 493-25-63; +7 (3496) 37-20-89; +7 (495) 123-60-22</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+          <t>190013 СПб, Московский пр. 60/129А пом.1-Н комн.195-207; ОГРН 1038900945995; 100% ПАО «Газпром нефть»; СПб-номер основной, остальные — Ноябрьск и Москва</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+          <t>rusprofile.ru/id/470197; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>957</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1279,147 +1279,147 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>ООО «Графит»</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>7841505154</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 944-62-49</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>ООО «ИНТРА ПРОЕКТ»</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>7806519718</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>514</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>ООО «ИРЕСТ СТРОЙ»</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>7825134181</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>+7 (812) 326-11-53</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>kanoner.com (данные 2013 г.)</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>средняя (ИНН совпал, но источник старый — сверить)</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>1800000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>ООО «Магистраль северной столицы»</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>7710884741</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>833</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1429,27 +1429,27 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ООО «НПО «АМБ»</t>
+          <t>ООО «ИСК» (Инженерно-строительная компания)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>7804516528</t>
+          <t>7814519060</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
+          <t>+7 (812) 244-98-97; +7 (921) 908-42-53</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
+          <t>197350 СПб, Мебельная ул. 12к1А пом.14-Н; ОГРН 1117847529327; ген.дир. Мамедов Р.Т.</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7814519060/781401001; companies.rbc.ru</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>677</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1479,27 +1479,27 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПО «Энергосистема»</t>
+          <t>ООО «Инженерный Дом»</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>7805654520</t>
+          <t>7811474068</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
+          <t>+7 (812) 943-13-43</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
+          <t>СПб, пр.Большевиков 81 кв.49; ОГРН 1107847321207; ген.дир. Климовский Р.А.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
+          <t>sbis.ru/contragents/7811474068/781101001; 2gis.ru/spb</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>719</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1529,27 +1529,27 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПСМ» (Промстроймонтаж)</t>
+          <t>ООО «Капитель»</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>7814118903</t>
+          <t>7816235786</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
+          <t>+7 (812) 244-05-56; +7 (921) 942-96-99</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
+          <t>192102 СПб, ул.Салова 27 оф.315; ОГРН 1097847259399; ген.дир. Кузнецов А.В.</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7816235786/781601001</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>332</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1579,27 +1579,27 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>ООО «Розенберг Северо-Запад»</t>
+          <t>ООО «Магистраль северной столицы»</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>7816592450</t>
+          <t>7710884741</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>833</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1629,27 +1629,27 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
+          <t>ООО «НПО «АМБ»</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>7810206161</t>
+          <t>7804516528</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
+          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
+          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1669,55 +1669,55 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>5609095128</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ПО «Энергосистема»</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>7805654520</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
+          <t>ООО «ПСМ» (Промстроймонтаж)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>7801349149</t>
+          <t>7814118903</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
+          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
+          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
+          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>727</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -1779,27 +1779,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ООО «Северный Альянс»</t>
+          <t>ООО «Розенберг Северо-Запад»</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>7805662306</t>
+          <t>7816592450</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
+          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
+          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1829,27 +1829,27 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ООО «Спецтехкомплект»</t>
+          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>7811127120</t>
+          <t>7810206161</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 362-09-21</t>
+          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>241</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1874,52 +1874,52 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>ООО «СтарКом»</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>7841416641</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>5000000</t>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>5609095128</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1929,27 +1929,27 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ООО «ТМГ ГРУП»</t>
+          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>7705405168</t>
+          <t>7801349149</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 680-30-20</t>
+          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>627</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1979,213 +1979,245 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
+          <t>ООО «Северный Альянс»</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>7805662306</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Спецтехкомплект»</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>7811127120</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 362-09-21</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>ООО «СтарКом»</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>7841416641</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ТМГ ГРУП»</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>7705405168</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 680-30-20</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>ООО «Транспромстрой»</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>7804591155</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 449-31-21</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>СПб, ул.Савушкина 83к3А оф.401-402; ОГРН 1177847074250; ген.дир. Аванесов Д.Б.; ~467 сотрудников</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>spark-interfax.ru; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>752</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>АНО «ВАЛААМ»</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>7839024647</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr"/>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr"/>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>АО «Абсолют»</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>7825663795</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr"/>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr"/>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>АО «Аспект Северо-Запад»</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>7810143306</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr"/>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr"/>
-      <c r="G33" s="11" t="inlineStr">
-        <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>7810255553</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr"/>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="inlineStr"/>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -2197,18 +2229,18 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>АО «ВОЛХОН»</t>
+          <t>АНО «ВАЛААМ»</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>7810383403</t>
+          <t>7839024647</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr"/>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
+          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -2229,7 +2261,7 @@
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2239,18 +2271,18 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
+          <t>АО «Абсолют»</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>7813007615</t>
+          <t>7825663795</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr"/>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
+          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
@@ -2261,7 +2293,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2271,7 +2303,7 @@
       </c>
       <c r="J36" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2281,18 +2313,18 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>АО «НОУДИГ» (Per Aarsleff)</t>
+          <t>АО «Аспект Северо-Запад»</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>7802108837</t>
+          <t>7810143306</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr"/>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
+          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
@@ -2303,7 +2335,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>735</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -2313,7 +2345,7 @@
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2323,18 +2355,18 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>АО «Петрос»</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>7816131635</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr"/>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
@@ -2345,7 +2377,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -2355,7 +2387,7 @@
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2365,29 +2397,29 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>АО «Полиспаст»</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>7805744573</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr"/>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -2407,18 +2439,18 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>АО «РЭС» (Региональные электрические сети)</t>
+          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>7810785984</t>
+          <t>7813007615</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
+          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
@@ -2429,7 +2461,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2439,7 +2471,7 @@
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2449,25 +2481,29 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>АО «СМУ-47»</t>
+          <t>АО «НОУДИГ» (Per Aarsleff)</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>7801097276</t>
+          <t>7802108837</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr"/>
-      <c r="E41" s="11" t="inlineStr"/>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
+        </is>
+      </c>
       <c r="F41" s="11" t="inlineStr"/>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>699</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -2477,7 +2513,7 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2487,29 +2523,29 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>АО «Селектел»</t>
+          <t>АО «Петрос»</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>7810962785</t>
+          <t>7816131635</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
+          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>нет данных (телефон смотреть на selectel.ru)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>507</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2529,29 +2565,29 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>АО «Стройинвест»</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>7825697956</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr"/>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -2571,18 +2607,18 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Агентство Шушары»</t>
+          <t>АО «РЭС» (Региональные электрические сети)</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>7820016970</t>
+          <t>7810785984</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
+          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
@@ -2593,7 +2629,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>566</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2603,7 +2639,7 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2613,29 +2649,25 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Институт телекоммуникаций»</t>
+          <t>АО «СМУ-47»</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>7802199182</t>
+          <t>7801097276</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr"/>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
-        </is>
-      </c>
+      <c r="E45" s="11" t="inlineStr"/>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>нет данных (телефон смотреть на itain.ru)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>687</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2655,29 +2687,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «ПетроЭлектроКомплекс»</t>
+          <t>АО «Селектел»</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>7801128326</t>
+          <t>7810962785</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr"/>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
+          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных (телефон смотреть на selectel.ru)</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2697,18 +2729,18 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Трест СЗКС» (Севзапкурортстрой)</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>7809006739</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr"/>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 16 пом.1н оф.117; ОГРН 1027810295842; ген.дир. Тихомиров С.А.</t>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
@@ -2719,7 +2751,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2729,7 +2761,7 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2739,29 +2771,29 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
+          <t>ЗАО «Агентство Шушары»</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>7811405770</t>
+          <t>7820016970</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr"/>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
+          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2771,7 +2803,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2781,29 +2813,29 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
+          <t>ЗАО «Институт телекоммуникаций»</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>7813424070</t>
+          <t>7802199182</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr"/>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
+          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (телефон смотреть на itain.ru)</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -2823,18 +2855,18 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ООО «АЛЬФА»</t>
+          <t>ЗАО «ПетроЭлектроКомплекс»</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>7813411063</t>
+          <t>7801128326</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
+          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
@@ -2845,7 +2877,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>506</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2865,29 +2897,29 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ООО «АРТ-МАСШТАБ»</t>
+          <t>ЗАО «Трест СЗКС» (Севзапкурортстрой)</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>7840076495</t>
+          <t>7809006739</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr"/>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
+          <t>190013 СПб, Рузовская ул. 16 пом.1н оф.117; ОГРН 1027810295842; ген.дир. Тихомиров С.А.</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>630</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -2907,29 +2939,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ООО «АС Инжиниринг»</t>
+          <t>ЗАО «Эра-Инжиниринг»</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>7810318651</t>
+          <t>7811405770</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr"/>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
+          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>519</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -2939,7 +2971,7 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2949,33 +2981,29 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>ООО «Алисард»</t>
+          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>7814713356</t>
+          <t>7813424070</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr"/>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>alisard.com</t>
-        </is>
-      </c>
+          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть e-mail и сайт)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>684</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -2995,25 +3023,29 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альфа»</t>
+          <t>ООО «АЛЬФА»</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>7802594841</t>
+          <t>7813411063</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr"/>
-      <c r="E54" s="11" t="inlineStr"/>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
+        </is>
+      </c>
       <c r="F54" s="11" t="inlineStr"/>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>524</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3033,18 +3065,18 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>ООО «АРТ-МАСШТАБ»</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7840076495</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr"/>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
+          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
@@ -3055,7 +3087,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3065,7 +3097,7 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3075,29 +3107,29 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>ООО «Антей»</t>
+          <t>ООО «АС Инжиниринг»</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>4708011991</t>
+          <t>7810318651</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
+          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3117,29 +3149,33 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>ООО «Арман»</t>
+          <t>ООО «Алисард»</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>7805298463</t>
+          <t>7814713356</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr"/>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr"/>
+          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>alisard.com</t>
+        </is>
+      </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть e-mail и сайт)</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>575</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -3159,12 +3195,12 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлантис»</t>
+          <t>ООО «Альфа»</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>7810914904</t>
+          <t>7802594841</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr"/>
@@ -3177,7 +3213,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -3197,29 +3233,29 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАРК»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>7804462262</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr"/>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3229,7 +3265,7 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3239,29 +3275,29 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
+          <t>ООО «Антей»</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>7804634666</t>
+          <t>4708011991</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr"/>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
+          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3281,18 +3317,18 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>ООО «БЕЛНЕВА»</t>
+          <t>ООО «Арман»</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7839489314</t>
+          <t>7805298463</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr"/>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
+          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -3303,7 +3339,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>586</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3323,20 +3359,16 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>ООО «Атлантис»</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7810914904</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr"/>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E62" s="11" t="inlineStr"/>
       <c r="F62" s="11" t="inlineStr"/>
       <c r="G62" s="11" t="inlineStr">
         <is>
@@ -3345,7 +3377,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3355,7 +3387,7 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3365,16 +3397,20 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>ООО «БАРК»</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7804462262</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr"/>
-      <c r="E63" s="11" t="inlineStr"/>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
+        </is>
+      </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
@@ -3383,7 +3419,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -3393,7 +3429,7 @@
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3403,29 +3439,29 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>ООО «БРАЗСТРОЙ»</t>
+          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>2630050808</t>
+          <t>7804634666</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
+          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -3445,29 +3481,29 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>ООО «БелькаРус»</t>
+          <t>ООО «БЕЛНЕВА»</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>7801665024</t>
+          <t>7839489314</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr"/>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
+          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>457</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -3487,29 +3523,29 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>ООО «БиАр»</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>7802738910</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr"/>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3519,7 +3555,7 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3529,20 +3565,16 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>ООО «Бобёр»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>7801632702</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr"/>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
-        </is>
-      </c>
+      <c r="E67" s="11" t="inlineStr"/>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr">
         <is>
@@ -3551,7 +3583,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -3561,7 +3593,7 @@
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3571,29 +3603,29 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЕРТЕК»</t>
+          <t>ООО «БРАЗСТРОЙ»</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>7806317711</t>
+          <t>2630050808</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr"/>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3603,7 +3635,7 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3613,18 +3645,18 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИРА»</t>
+          <t>ООО «БелькаРус»</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7839139655</t>
+          <t>7801665024</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr"/>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
+          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
@@ -3635,7 +3667,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3655,29 +3687,29 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr"/>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -3687,7 +3719,7 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -3697,29 +3729,29 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>ООО «Бобёр»</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7801632702</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -3729,7 +3761,7 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3739,29 +3771,29 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr"/>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -3771,7 +3803,7 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3781,29 +3813,25 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «ВИП»</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7802742070</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
-        </is>
-      </c>
+      <c r="E73" s="11" t="inlineStr"/>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>226</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -3813,7 +3841,7 @@
       </c>
       <c r="J73" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3823,18 +3851,18 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «ВИРА»</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7839139655</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr"/>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -3845,7 +3873,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -3855,7 +3883,7 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3865,29 +3893,25 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «ВСК»</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>3525411380</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr"/>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
-        </is>
-      </c>
+      <c r="E75" s="11" t="inlineStr"/>
       <c r="F75" s="11" t="inlineStr"/>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -3897,7 +3921,7 @@
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3907,29 +3931,25 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «ВСК» (Военно-строительная компания)</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>7804018392</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr"/>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
-        </is>
-      </c>
+      <c r="E76" s="11" t="inlineStr"/>
       <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>670</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -3939,7 +3959,7 @@
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3949,20 +3969,16 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «ВЭС»</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7839121496</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr"/>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
-        </is>
-      </c>
+      <c r="E77" s="11" t="inlineStr"/>
       <c r="F77" s="11" t="inlineStr"/>
       <c r="G77" s="11" t="inlineStr">
         <is>
@@ -3971,7 +3987,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>828</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -3981,7 +3997,7 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3991,18 +4007,18 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr"/>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -4013,7 +4029,7 @@
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -4023,7 +4039,7 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4033,25 +4049,29 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr"/>
-      <c r="E79" s="11" t="inlineStr"/>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+        </is>
+      </c>
       <c r="F79" s="11" t="inlineStr"/>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -4071,29 +4091,25 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7603054270</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr"/>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
-        </is>
-      </c>
+      <c r="E80" s="11" t="inlineStr"/>
       <c r="F80" s="11" t="inlineStr"/>
       <c r="G80" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -4103,7 +4119,7 @@
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4113,18 +4129,18 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr"/>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -4135,7 +4151,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -4155,29 +4171,25 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «ГК «СТИ»</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>7814797620</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr"/>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
-        </is>
-      </c>
+      <c r="E82" s="11" t="inlineStr"/>
       <c r="F82" s="11" t="inlineStr"/>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>847</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -4187,7 +4199,7 @@
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4197,29 +4209,29 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr"/>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -4239,18 +4251,18 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr"/>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -4261,7 +4273,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -4281,20 +4293,16 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «Гелиос»</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7804608994</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr"/>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
-        </is>
-      </c>
+      <c r="E85" s="11" t="inlineStr"/>
       <c r="F85" s="11" t="inlineStr"/>
       <c r="G85" s="11" t="inlineStr">
         <is>
@@ -4303,7 +4311,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>565</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -4313,7 +4321,7 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4323,18 +4331,18 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr"/>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
@@ -4345,7 +4353,7 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -4355,7 +4363,7 @@
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4365,20 +4373,16 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «ДСК РЕГИОН»</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7816487198</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr"/>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
-        </is>
-      </c>
+      <c r="E87" s="11" t="inlineStr"/>
       <c r="F87" s="11" t="inlineStr"/>
       <c r="G87" s="11" t="inlineStr">
         <is>
@@ -4387,7 +4391,7 @@
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -4397,7 +4401,7 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4407,20 +4411,16 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «Дорожник СПб»</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>7806421624</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr"/>
-      <c r="E88" s="11" t="inlineStr">
-        <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
-        </is>
-      </c>
+      <c r="E88" s="11" t="inlineStr"/>
       <c r="F88" s="11" t="inlineStr"/>
       <c r="G88" s="11" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>564</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4449,29 +4449,29 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>ООО «МонтажСтрой-М» (МСМ)</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>7811447071</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr"/>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4491,18 +4491,18 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr"/>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -4533,29 +4533,25 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «ЗИТЕК»</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7814691303</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr"/>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
-        </is>
-      </c>
+      <c r="E91" s="11" t="inlineStr"/>
       <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -4565,7 +4561,7 @@
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4575,29 +4571,25 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «Зодчий»</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7810477235</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr"/>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
-        </is>
-      </c>
+      <c r="E92" s="11" t="inlineStr"/>
       <c r="F92" s="11" t="inlineStr"/>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -4607,7 +4599,7 @@
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4617,18 +4609,18 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr"/>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
@@ -4639,7 +4631,7 @@
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -4649,7 +4641,7 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4659,20 +4651,16 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr"/>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
-        </is>
-      </c>
+      <c r="E94" s="11" t="inlineStr"/>
       <c r="F94" s="11" t="inlineStr"/>
       <c r="G94" s="11" t="inlineStr">
         <is>
@@ -4681,7 +4669,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -4701,29 +4689,25 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
+          <t>ООО «ИК «Петротрасса»</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>7825382561</t>
+          <t>7804572970</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr"/>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
-        </is>
-      </c>
+      <c r="E95" s="11" t="inlineStr"/>
       <c r="F95" s="11" t="inlineStr"/>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>712</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -4733,7 +4717,7 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4743,29 +4727,25 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «ИК ИнТехПро»</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>9810000213</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr"/>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
-        </is>
-      </c>
+      <c r="E96" s="11" t="inlineStr"/>
       <c r="F96" s="11" t="inlineStr"/>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -4775,7 +4755,7 @@
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4785,29 +4765,25 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7710910159</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr"/>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
-        </is>
-      </c>
+      <c r="E97" s="11" t="inlineStr"/>
       <c r="F97" s="11" t="inlineStr"/>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>940</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -4817,7 +4793,7 @@
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4827,29 +4803,29 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>7810685806</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr"/>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, Ярославский пр.</t>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
       <c r="G98" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
@@ -4859,7 +4835,7 @@
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4869,20 +4845,16 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «ИНСИ»</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>7839398890</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr"/>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
-        </is>
-      </c>
+      <c r="E99" s="11" t="inlineStr"/>
       <c r="F99" s="11" t="inlineStr"/>
       <c r="G99" s="11" t="inlineStr">
         <is>
@@ -4891,7 +4863,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -4901,7 +4873,7 @@
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4911,20 +4883,16 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «ИСБ-СЕРВИС»</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7811462471</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr"/>
-      <c r="E100" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
-        </is>
-      </c>
+      <c r="E100" s="11" t="inlineStr"/>
       <c r="F100" s="11" t="inlineStr"/>
       <c r="G100" s="11" t="inlineStr">
         <is>
@@ -4933,7 +4901,7 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>295</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -4943,7 +4911,7 @@
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4953,16 +4921,20 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr"/>
-      <c r="E101" s="11" t="inlineStr"/>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+        </is>
+      </c>
       <c r="F101" s="11" t="inlineStr"/>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -4971,7 +4943,7 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -4991,20 +4963,16 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «Импульс»</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7839473240</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr"/>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
-        </is>
-      </c>
+      <c r="E102" s="11" t="inlineStr"/>
       <c r="F102" s="11" t="inlineStr"/>
       <c r="G102" s="11" t="inlineStr">
         <is>
@@ -5013,7 +4981,7 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -5023,7 +4991,7 @@
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5033,29 +5001,29 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr"/>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -5065,7 +5033,7 @@
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5075,20 +5043,16 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «Интер-Строй»</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>5505064975</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr"/>
-      <c r="E104" s="11" t="inlineStr">
-        <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
-        </is>
-      </c>
+      <c r="E104" s="11" t="inlineStr"/>
       <c r="F104" s="11" t="inlineStr"/>
       <c r="G104" s="11" t="inlineStr">
         <is>
@@ -5097,7 +5061,7 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -5107,7 +5071,7 @@
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5117,20 +5081,16 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «Интерпром»</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7805576110</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr"/>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
-        </is>
-      </c>
+      <c r="E105" s="11" t="inlineStr"/>
       <c r="F105" s="11" t="inlineStr"/>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5139,7 +5099,7 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
@@ -5149,7 +5109,7 @@
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5159,29 +5119,29 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>ООО «РестСтройГрупп»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>7839099924</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr"/>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
@@ -5191,7 +5151,7 @@
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -5201,18 +5161,18 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Алстрой»</t>
+          <t>ООО «Компания КОМПЛИТ»</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>7813417675</t>
+          <t>7810793872</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr"/>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -5223,7 +5183,7 @@
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>143</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
@@ -5233,7 +5193,7 @@
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5243,29 +5203,29 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr"/>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr"/>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr">
@@ -5275,7 +5235,7 @@
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5285,18 +5245,18 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr"/>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -5307,7 +5267,7 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
@@ -5317,7 +5277,7 @@
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5327,29 +5287,29 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr"/>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr"/>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
@@ -5369,18 +5329,18 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr"/>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -5391,7 +5351,7 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
@@ -5411,18 +5371,18 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr"/>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -5433,7 +5393,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
@@ -5443,7 +5403,7 @@
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5453,18 +5413,18 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D113" s="13" t="inlineStr"/>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr"/>
@@ -5475,7 +5435,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
@@ -5485,7 +5445,7 @@
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -5495,18 +5455,18 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr"/>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -5517,7 +5477,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
@@ -5527,7 +5487,7 @@
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -5537,18 +5497,18 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr"/>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr"/>
@@ -5559,7 +5519,7 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
@@ -5569,7 +5529,7 @@
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -5579,29 +5539,29 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr"/>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
@@ -5621,29 +5581,29 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй центр»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>7804538240</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr"/>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
@@ -5653,7 +5613,7 @@
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -5663,16 +5623,20 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr"/>
-      <c r="E118" s="11" t="inlineStr"/>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+        </is>
+      </c>
       <c r="F118" s="11" t="inlineStr"/>
       <c r="G118" s="11" t="inlineStr">
         <is>
@@ -5681,7 +5645,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -5691,7 +5655,7 @@
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5701,29 +5665,29 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr"/>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr"/>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -5733,7 +5697,7 @@
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -5743,18 +5707,18 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕЗИС»</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>7804441209</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr"/>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr"/>
@@ -5765,7 +5729,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -5775,7 +5739,7 @@
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>700000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5785,29 +5749,29 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr"/>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr"/>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -5817,7 +5781,7 @@
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -5827,18 +5791,18 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D122" s="13" t="inlineStr"/>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+          <t>194017 СПб, Ярославский пр.</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr"/>
@@ -5849,7 +5813,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -5859,7 +5823,7 @@
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -5869,18 +5833,18 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7811659380</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr"/>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr"/>
@@ -5891,7 +5855,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>607</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -5901,7 +5865,7 @@
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5911,18 +5875,18 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «ПСТ»</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>7813448257</t>
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr"/>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr"/>
@@ -5933,7 +5897,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>876</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -5953,20 +5917,16 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «ПТГ»</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>5013050270</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
-        </is>
-      </c>
+      <c r="E125" s="11" t="inlineStr"/>
       <c r="F125" s="11" t="inlineStr"/>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -5975,7 +5935,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -5985,7 +5945,7 @@
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5995,29 +5955,29 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «Промстрой»</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7814656860</t>
         </is>
       </c>
       <c r="D126" s="13" t="inlineStr"/>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
       <c r="G126" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>516</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
@@ -6037,18 +5997,18 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Профиль»</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7802182380</t>
         </is>
       </c>
       <c r="D127" s="13" t="inlineStr"/>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
@@ -6059,7 +6019,7 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>572</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
@@ -6079,18 +6039,18 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «РЕССТРОЙ»</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>7820012849</t>
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr"/>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
@@ -6101,7 +6061,7 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>713</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr">
@@ -6121,44 +6081,1048 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7826123721</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr"/>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
       <c r="G129" s="11" t="inlineStr">
         <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J129" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РестСтройГрупп»</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>7839099924</t>
+        </is>
+      </c>
+      <c r="D130" s="13" t="inlineStr"/>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr"/>
+      <c r="G130" s="11" t="inlineStr">
+        <is>
           <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
-      <c r="H129" s="10" t="inlineStr">
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Алстрой»</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>7813417675</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr"/>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr"/>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J131" s="10" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Потенциал»</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>7814558855</t>
+        </is>
+      </c>
+      <c r="D132" s="13" t="inlineStr"/>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr"/>
+      <c r="G132" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I132" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J132" s="10" t="inlineStr">
+        <is>
+          <t>1700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК Гарант»</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>7806380022</t>
+        </is>
+      </c>
+      <c r="D133" s="13" t="inlineStr"/>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr"/>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J133" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК ПСП»</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>7810502379</t>
+        </is>
+      </c>
+      <c r="D134" s="13" t="inlineStr"/>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr"/>
+      <c r="G134" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J134" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СПбЭК-Майнинг»</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>7820326027</t>
+        </is>
+      </c>
+      <c r="D135" s="13" t="inlineStr"/>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr"/>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H135" s="10" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="I135" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J135" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>7825055370</t>
+        </is>
+      </c>
+      <c r="D136" s="13" t="inlineStr"/>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr"/>
+      <c r="G136" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J136" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУ-17»</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>7807028906</t>
+        </is>
+      </c>
+      <c r="D137" s="13" t="inlineStr"/>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr"/>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>2300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУАР-Групп»</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>7802270195</t>
+        </is>
+      </c>
+      <c r="D138" s="13" t="inlineStr"/>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr"/>
+      <c r="G138" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J138" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СЭМ»</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>7810201646</t>
+        </is>
+      </c>
+      <c r="D139" s="13" t="inlineStr"/>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr"/>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H139" s="10" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I139" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J139" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строительные технологии»</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>7813680179</t>
+        </is>
+      </c>
+      <c r="D140" s="13" t="inlineStr"/>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+        </is>
+      </c>
+      <c r="F140" s="11" t="inlineStr"/>
+      <c r="G140" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I140" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J140" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строй центр»</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>7804538240</t>
+        </is>
+      </c>
+      <c r="D141" s="13" t="inlineStr"/>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr"/>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H141" s="10" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="I141" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J141" s="10" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СтройГрад»</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>7813692632</t>
+        </is>
+      </c>
+      <c r="D142" s="13" t="inlineStr"/>
+      <c r="E142" s="11" t="inlineStr"/>
+      <c r="F142" s="11" t="inlineStr"/>
+      <c r="G142" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H142" s="10" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="I142" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J142" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Сфера»</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>2311308786</t>
+        </is>
+      </c>
+      <c r="D143" s="13" t="inlineStr"/>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr"/>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H143" s="10" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="I143" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J143" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЕЗИС»</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>7804441209</t>
+        </is>
+      </c>
+      <c r="D144" s="13" t="inlineStr"/>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr"/>
+      <c r="G144" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H144" s="10" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J144" s="10" t="inlineStr">
+        <is>
+          <t>700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>7814612968</t>
+        </is>
+      </c>
+      <c r="D145" s="13" t="inlineStr"/>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr"/>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="I145" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J145" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>7839061021</t>
+        </is>
+      </c>
+      <c r="D146" s="13" t="inlineStr"/>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr"/>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H146" s="10" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="I146" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J146" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Трамплин-строй»</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>7802207193</t>
+        </is>
+      </c>
+      <c r="D147" s="13" t="inlineStr"/>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr"/>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H147" s="10" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="I147" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J147" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D148" s="13" t="inlineStr"/>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr"/>
+      <c r="G148" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H148" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I148" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J148" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D149" s="13" t="inlineStr"/>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="inlineStr"/>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H149" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J149" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D150" s="13" t="inlineStr"/>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr"/>
+      <c r="G150" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H150" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I150" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J150" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D151" s="13" t="inlineStr"/>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr"/>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J151" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D152" s="13" t="inlineStr"/>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr"/>
+      <c r="G152" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J152" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D153" s="13" t="inlineStr"/>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr"/>
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H153" s="10" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="I129" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J129" s="10" t="inlineStr">
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J153" s="10" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J129"/>
+  <autoFilter ref="A1:J153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6241,7 +7205,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>128</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8">
@@ -6251,7 +7215,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -6261,7 +7225,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1579,27 +1579,27 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>ООО «Магистраль северной столицы»</t>
+          <t>ООО «Люксэнергомонтаж»</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>7710884741</t>
+          <t>7805413540</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
+          <t>+7 (812) 346-54-68</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
+          <t>198097 СПб, пр.Стачек 47А пом.24Н; ОГРН 5067847562107; ген.дир. Кузин А.В.; электромонтаж</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
+          <t>sbis.ru/contragents/7805413540/780501001; focus.kontur.ru; b2bsky.ru</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1629,27 +1629,27 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ООО «НПО «АМБ»</t>
+          <t>ООО «Магистраль северной столицы»</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>7804516528</t>
+          <t>7710884741</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
+          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
+          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
+          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>833</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПО «Энергосистема»</t>
+          <t>ООО «Мосты и инженерные проекты»</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>7805654520</t>
+          <t>7734396101</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
+          <t>+7 (812) 987-56-15; +7 (916) 452-59-04</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
+          <t>СПб-офис; e-mail spb@mip.moscow; сайт mip.moscow; проектирование мостов</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru; mip.moscow</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>715</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПСМ» (Промстроймонтаж)</t>
+          <t>ООО «НПО «АМБ»</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>7814118903</t>
+          <t>7804516528</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
+          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
+          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -1779,27 +1779,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ООО «Розенберг Северо-Запад»</t>
+          <t>ООО «Невское РЭУ»</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>7816592450</t>
+          <t>7810819552</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+          <t>+7 (812) 244-52-91</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+          <t>196084 СПб, ул.Заставская 33Ж оф.416; ОГРН 1117847459466; ген.дир. Соловьев М.Ю.</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7810819552/781001001</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1829,27 +1829,27 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
+          <t>ООО «ПИТЕРСТРОЙСЕРВИС»</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>7810206161</t>
+          <t>7810711975</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
+          <t>+7 (812) 385-47-25</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
+          <t>196006 СПб, Заставская ул. 22к2А оф.229; ОГРН 1177847347150; ген.дир. Сорокин А.С.</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7810711975/781001001; companies.rbc.ru</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>696</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1869,55 +1869,55 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>5609095128</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ПО «Энергосистема»</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>7805654520</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -1929,27 +1929,27 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
+          <t>ООО «ПСМ» (Промстроймонтаж)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>7801349149</t>
+          <t>7814118903</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
+          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
+          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
+          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>727</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -1979,27 +1979,27 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ООО «Северный Альянс»</t>
+          <t>ООО «Розенберг Северо-Запад»</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>7805662306</t>
+          <t>7816592450</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
+          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
+          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2029,27 +2029,27 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ООО «Спецтехкомплект»</t>
+          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>7811127120</t>
+          <t>7810206161</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 362-09-21</t>
+          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>241</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2074,52 +2074,52 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>ООО «СтарКом»</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>7841416641</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>5000000</t>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>5609095128</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2129,27 +2129,27 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ООО «ТМГ ГРУП»</t>
+          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>7705405168</t>
+          <t>7801349149</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 680-30-20</t>
+          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>627</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2179,213 +2179,245 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>ООО «Северный Альянс»</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>7805662306</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Спецтехкомплект»</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>7811127120</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 362-09-21</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>ООО «СтарКом»</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>7841416641</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ТМГ ГРУП»</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>7705405168</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 680-30-20</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
           <t>ООО «Транспромстрой»</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>7804591155</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 449-31-21</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>СПб, ул.Савушкина 83к3А оф.401-402; ОГРН 1177847074250; ген.дир. Аванесов Д.Б.; ~467 сотрудников</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>spark-interfax.ru; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>752</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>АНО «ВАЛААМ»</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>7839024647</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr"/>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="inlineStr"/>
-      <c r="G35" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>АО «Абсолют»</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>7825663795</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr"/>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr"/>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>АО «Аспект Северо-Запад»</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>7810143306</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr"/>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr"/>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>7810255553</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr"/>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr"/>
-      <c r="G38" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -2397,18 +2429,18 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>АО «ВОЛХОН»</t>
+          <t>АНО «ВАЛААМ»</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>7810383403</t>
+          <t>7839024647</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr"/>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
+          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
@@ -2419,7 +2451,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -2429,7 +2461,7 @@
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2439,18 +2471,18 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
+          <t>АО «Абсолют»</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>7813007615</t>
+          <t>7825663795</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
+          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
@@ -2461,7 +2493,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2471,7 +2503,7 @@
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2481,18 +2513,18 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>АО «НОУДИГ» (Per Aarsleff)</t>
+          <t>АО «Аспект Северо-Запад»</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>7802108837</t>
+          <t>7810143306</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr"/>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
+          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -2503,7 +2535,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>735</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -2513,7 +2545,7 @@
       </c>
       <c r="J41" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2523,18 +2555,18 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>АО «Петрос»</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>7816131635</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
@@ -2545,7 +2577,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2555,7 +2587,7 @@
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2565,29 +2597,29 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>АО «Полиспаст»</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>7805744573</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr"/>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -2607,18 +2639,18 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>АО «РЭС» (Региональные электрические сети)</t>
+          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>7810785984</t>
+          <t>7813007615</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
+          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
@@ -2629,7 +2661,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2639,7 +2671,7 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2649,25 +2681,29 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>АО «СМУ-47»</t>
+          <t>АО «НОУДИГ» (Per Aarsleff)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>7801097276</t>
+          <t>7802108837</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr"/>
-      <c r="E45" s="11" t="inlineStr"/>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
+        </is>
+      </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>699</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2677,7 +2713,7 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2687,29 +2723,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>АО «Селектел»</t>
+          <t>АО «Петрос»</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>7810962785</t>
+          <t>7816131635</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr"/>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
+          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>нет данных (телефон смотреть на selectel.ru)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>507</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2729,29 +2765,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>АО «Стройинвест»</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>7825697956</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr"/>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2771,18 +2807,18 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Агентство Шушары»</t>
+          <t>АО «РЭС» (Региональные электрические сети)</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>7820016970</t>
+          <t>7810785984</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr"/>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
+          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
@@ -2793,7 +2829,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>566</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2803,7 +2839,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2813,29 +2849,25 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Институт телекоммуникаций»</t>
+          <t>АО «СМУ-47»</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>7802199182</t>
+          <t>7801097276</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr"/>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
-        </is>
-      </c>
+      <c r="E49" s="11" t="inlineStr"/>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>нет данных (телефон смотреть на itain.ru)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>687</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -2855,29 +2887,29 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «ПетроЭлектроКомплекс»</t>
+          <t>АО «Селектел»</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>7801128326</t>
+          <t>7810962785</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
+          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных (телефон смотреть на selectel.ru)</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2897,18 +2929,18 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Трест СЗКС» (Севзапкурортстрой)</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>7809006739</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr"/>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 16 пом.1н оф.117; ОГРН 1027810295842; ген.дир. Тихомиров С.А.</t>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
@@ -2919,7 +2951,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -2929,7 +2961,7 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2939,29 +2971,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
+          <t>ЗАО «Агентство Шушары»</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>7811405770</t>
+          <t>7820016970</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr"/>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
+          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -2971,7 +3003,7 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2981,29 +3013,29 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
+          <t>ЗАО «Институт телекоммуникаций»</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>7813424070</t>
+          <t>7802199182</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr"/>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
+          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (телефон смотреть на itain.ru)</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -3023,18 +3055,18 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>ООО «АЛЬФА»</t>
+          <t>ЗАО «ПетроЭлектроКомплекс»</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>7813411063</t>
+          <t>7801128326</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
+          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
@@ -3045,7 +3077,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>506</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3065,29 +3097,29 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>ООО «АРТ-МАСШТАБ»</t>
+          <t>ЗАО «Трест СЗКС» (Севзапкурортстрой)</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>7840076495</t>
+          <t>7809006739</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr"/>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
+          <t>190013 СПб, Рузовская ул. 16 пом.1н оф.117; ОГРН 1027810295842; ген.дир. Тихомиров С.А.</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>630</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3107,29 +3139,29 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>ООО «АС Инжиниринг»</t>
+          <t>ЗАО «Эра-Инжиниринг»</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>7810318651</t>
+          <t>7811405770</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
+          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>519</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3139,7 +3171,7 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3149,33 +3181,29 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>ООО «Алисард»</t>
+          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>7814713356</t>
+          <t>7813424070</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr"/>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>alisard.com</t>
-        </is>
-      </c>
+          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть e-mail и сайт)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>684</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -3195,25 +3223,29 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альфа»</t>
+          <t>ООО «АЛЬФА»</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>7802594841</t>
+          <t>7813411063</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr"/>
-      <c r="E58" s="11" t="inlineStr"/>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
+        </is>
+      </c>
       <c r="F58" s="11" t="inlineStr"/>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>524</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -3233,18 +3265,18 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>ООО «АРТ-МАСШТАБ»</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7840076495</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr"/>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
+          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -3255,7 +3287,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3265,7 +3297,7 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3275,29 +3307,29 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>ООО «Антей»</t>
+          <t>ООО «АС Инжиниринг»</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>4708011991</t>
+          <t>7810318651</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr"/>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
+          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3317,29 +3349,33 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>ООО «Арман»</t>
+          <t>ООО «Алисард»</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7805298463</t>
+          <t>7814713356</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr"/>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
-        </is>
-      </c>
-      <c r="F61" s="11" t="inlineStr"/>
+          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>alisard.com</t>
+        </is>
+      </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть e-mail и сайт)</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>575</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3359,12 +3395,12 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлантис»</t>
+          <t>ООО «Альфа»</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>7810914904</t>
+          <t>7802594841</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr"/>
@@ -3377,7 +3413,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3397,29 +3433,29 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАРК»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>7804462262</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr"/>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -3429,7 +3465,7 @@
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3439,29 +3475,29 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
+          <t>ООО «Антей»</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>7804634666</t>
+          <t>4708011991</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
+          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -3481,18 +3517,18 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>ООО «БЕЛНЕВА»</t>
+          <t>ООО «Арман»</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>7839489314</t>
+          <t>7805298463</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr"/>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
+          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -3503,7 +3539,7 @@
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>586</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -3523,20 +3559,16 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>ООО «Атлантис»</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7810914904</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr"/>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E66" s="11" t="inlineStr"/>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3545,7 +3577,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3555,7 +3587,7 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3565,16 +3597,20 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>ООО «БАРК»</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7804462262</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr"/>
-      <c r="E67" s="11" t="inlineStr"/>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
+        </is>
+      </c>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr">
         <is>
@@ -3583,7 +3619,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -3593,7 +3629,7 @@
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3603,29 +3639,29 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>ООО «БРАЗСТРОЙ»</t>
+          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2630050808</t>
+          <t>7804634666</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr"/>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
+          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3645,29 +3681,29 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>ООО «БелькаРус»</t>
+          <t>ООО «БЕЛНЕВА»</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7801665024</t>
+          <t>7839489314</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr"/>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
+          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>457</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3687,29 +3723,29 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>ООО «БиАр»</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>7802738910</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr"/>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -3719,7 +3755,7 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3729,20 +3765,16 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>ООО «Бобёр»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>7801632702</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
-        </is>
-      </c>
+      <c r="E71" s="11" t="inlineStr"/>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3751,7 +3783,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -3761,7 +3793,7 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3771,29 +3803,29 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЕРТЕК»</t>
+          <t>ООО «БРАЗСТРОЙ»</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>7806317711</t>
+          <t>2630050808</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr"/>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -3803,7 +3835,7 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3813,25 +3845,29 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИП»</t>
+          <t>ООО «БелькаРус»</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>7802742070</t>
+          <t>7801665024</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
-      <c r="E73" s="11" t="inlineStr"/>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
+        </is>
+      </c>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -3851,18 +3887,18 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИРА»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>7839139655</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr"/>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -3873,7 +3909,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -3883,7 +3919,7 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -3893,16 +3929,20 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК»</t>
+          <t>ООО «Бобёр»</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>3525411380</t>
+          <t>7801632702</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr"/>
-      <c r="E75" s="11" t="inlineStr"/>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
+        </is>
+      </c>
       <c r="F75" s="11" t="inlineStr"/>
       <c r="G75" s="11" t="inlineStr">
         <is>
@@ -3911,7 +3951,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -3931,25 +3971,29 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК» (Военно-строительная компания)</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>7804018392</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr"/>
-      <c r="E76" s="11" t="inlineStr"/>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+        </is>
+      </c>
       <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -3959,7 +4003,7 @@
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3969,12 +4013,12 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЭС»</t>
+          <t>ООО «ВИП»</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>7839121496</t>
+          <t>7802742070</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr"/>
@@ -3987,7 +4031,7 @@
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>226</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -4007,29 +4051,29 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «ВИРА»</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7839139655</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr"/>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -4039,7 +4083,7 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4049,29 +4093,25 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>ООО «ВСК»</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>3525411380</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr"/>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
-        </is>
-      </c>
+      <c r="E79" s="11" t="inlineStr"/>
       <c r="F79" s="11" t="inlineStr"/>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -4081,7 +4121,7 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4131,12 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
+          <t>ООО «ВСК» (Военно-строительная компания)</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>7603054270</t>
+          <t>7804018392</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr"/>
@@ -4109,7 +4149,7 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>670</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -4129,20 +4169,16 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ООО «ВЭС»</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7839121496</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr"/>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
-        </is>
-      </c>
+      <c r="E81" s="11" t="inlineStr"/>
       <c r="F81" s="11" t="inlineStr"/>
       <c r="G81" s="11" t="inlineStr">
         <is>
@@ -4151,7 +4187,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>828</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -4161,7 +4197,7 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4171,16 +4207,20 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГК «СТИ»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>7814797620</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr"/>
-      <c r="E82" s="11" t="inlineStr"/>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+        </is>
+      </c>
       <c r="F82" s="11" t="inlineStr"/>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4189,7 +4229,7 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -4199,7 +4239,7 @@
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4209,18 +4249,18 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr"/>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -4231,7 +4271,7 @@
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -4241,7 +4281,7 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4251,29 +4291,25 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7603054270</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr"/>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
-        </is>
-      </c>
+      <c r="E84" s="11" t="inlineStr"/>
       <c r="F84" s="11" t="inlineStr"/>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -4283,7 +4319,7 @@
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4293,16 +4329,20 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гелиос»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>7804608994</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr"/>
-      <c r="E85" s="11" t="inlineStr"/>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+        </is>
+      </c>
       <c r="F85" s="11" t="inlineStr"/>
       <c r="G85" s="11" t="inlineStr">
         <is>
@@ -4311,7 +4351,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -4321,7 +4361,7 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4331,29 +4371,25 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «ГК «СТИ»</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7814797620</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr"/>
-      <c r="E86" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
-        </is>
-      </c>
+      <c r="E86" s="11" t="inlineStr"/>
       <c r="F86" s="11" t="inlineStr"/>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>847</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -4363,7 +4399,7 @@
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4373,25 +4409,29 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>ООО «ДСК РЕГИОН»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>7816487198</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr"/>
-      <c r="E87" s="11" t="inlineStr"/>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
+        </is>
+      </c>
       <c r="F87" s="11" t="inlineStr"/>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -4401,7 +4441,7 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4411,25 +4451,29 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>ООО «Дорожник СПб»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>7806421624</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr"/>
-      <c r="E88" s="11" t="inlineStr"/>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+        </is>
+      </c>
       <c r="F88" s="11" t="inlineStr"/>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -4439,7 +4483,7 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4449,29 +4493,25 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «Гелиос»</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>7804608994</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr"/>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
-        </is>
-      </c>
+      <c r="E89" s="11" t="inlineStr"/>
       <c r="F89" s="11" t="inlineStr"/>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>565</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -4481,7 +4521,7 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4491,29 +4531,29 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr"/>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -4523,7 +4563,7 @@
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4573,12 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЗИТЕК»</t>
+          <t>ООО «ДСК РЕГИОН»</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>7814691303</t>
+          <t>7816487198</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr"/>
@@ -4551,7 +4591,7 @@
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -4571,12 +4611,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>ООО «Зодчий»</t>
+          <t>ООО «Дорожник СПб»</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>7810477235</t>
+          <t>7806421624</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr"/>
@@ -4589,7 +4629,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>564</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -4609,29 +4649,29 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr"/>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -4651,16 +4691,20 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr"/>
-      <c r="E94" s="11" t="inlineStr"/>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+        </is>
+      </c>
       <c r="F94" s="11" t="inlineStr"/>
       <c r="G94" s="11" t="inlineStr">
         <is>
@@ -4669,7 +4713,7 @@
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -4679,7 +4723,7 @@
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -4689,12 +4733,12 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК «Петротрасса»</t>
+          <t>ООО «ЗИТЕК»</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>7804572970</t>
+          <t>7814691303</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr"/>
@@ -4707,7 +4751,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -4727,12 +4771,12 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ИнТехПро»</t>
+          <t>ООО «Зодчий»</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>9810000213</t>
+          <t>7810477235</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr"/>
@@ -4745,7 +4789,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -4765,16 +4809,20 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>7710910159</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr"/>
-      <c r="E97" s="11" t="inlineStr"/>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+        </is>
+      </c>
       <c r="F97" s="11" t="inlineStr"/>
       <c r="G97" s="11" t="inlineStr">
         <is>
@@ -4783,7 +4831,7 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -4793,7 +4841,7 @@
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4803,29 +4851,25 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr"/>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
-        </is>
-      </c>
+      <c r="E98" s="11" t="inlineStr"/>
       <c r="F98" s="11" t="inlineStr"/>
       <c r="G98" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
@@ -4845,12 +4889,12 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНСИ»</t>
+          <t>ООО «ИК «Петротрасса»</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>7839398890</t>
+          <t>7804572970</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr"/>
@@ -4863,7 +4907,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>712</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -4883,12 +4927,12 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИСБ-СЕРВИС»</t>
+          <t>ООО «ИК ИнТехПро»</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>7811462471</t>
+          <t>9810000213</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr"/>
@@ -4901,7 +4945,7 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -4921,20 +4965,16 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7710910159</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr"/>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
-        </is>
-      </c>
+      <c r="E101" s="11" t="inlineStr"/>
       <c r="F101" s="11" t="inlineStr"/>
       <c r="G101" s="11" t="inlineStr">
         <is>
@@ -4943,7 +4983,7 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>940</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -4953,7 +4993,7 @@
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4963,25 +5003,29 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>ООО «Импульс»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>7839473240</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr"/>
-      <c r="E102" s="11" t="inlineStr"/>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+        </is>
+      </c>
       <c r="F102" s="11" t="inlineStr"/>
       <c r="G102" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -4991,7 +5035,7 @@
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5001,29 +5045,25 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «ИНСИ»</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>7839398890</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr"/>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
-        </is>
-      </c>
+      <c r="E103" s="11" t="inlineStr"/>
       <c r="F103" s="11" t="inlineStr"/>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -5033,7 +5073,7 @@
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5083,12 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интер-Строй»</t>
+          <t>ООО «ИСБ-СЕРВИС»</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>5505064975</t>
+          <t>7811462471</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr"/>
@@ -5061,7 +5101,7 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>295</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -5081,16 +5121,20 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интерпром»</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>7805576110</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr"/>
-      <c r="E105" s="11" t="inlineStr"/>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="inlineStr"/>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5099,7 +5143,7 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
@@ -5109,7 +5153,7 @@
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5119,20 +5163,16 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «Импульс»</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7839473240</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr"/>
-      <c r="E106" s="11" t="inlineStr">
-        <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
-        </is>
-      </c>
+      <c r="E106" s="11" t="inlineStr"/>
       <c r="F106" s="11" t="inlineStr"/>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5141,7 +5181,7 @@
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
@@ -5151,7 +5191,7 @@
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5161,29 +5201,29 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>ООО «Компания КОМПЛИТ»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>7810793872</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr"/>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
@@ -5193,7 +5233,7 @@
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5203,29 +5243,25 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «Интер-Строй»</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>5505064975</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr"/>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
-        </is>
-      </c>
+      <c r="E108" s="11" t="inlineStr"/>
       <c r="F108" s="11" t="inlineStr"/>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr">
@@ -5235,7 +5271,7 @@
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5245,20 +5281,16 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «Интерпром»</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7805576110</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr"/>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
-        </is>
-      </c>
+      <c r="E109" s="11" t="inlineStr"/>
       <c r="F109" s="11" t="inlineStr"/>
       <c r="G109" s="11" t="inlineStr">
         <is>
@@ -5267,7 +5299,7 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
@@ -5277,7 +5309,7 @@
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5287,29 +5319,25 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «КС-Инжиниринг»</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>7801615217</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr"/>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
-        </is>
-      </c>
+      <c r="E110" s="11" t="inlineStr"/>
       <c r="F110" s="11" t="inlineStr"/>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>695</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
@@ -5319,7 +5347,7 @@
       </c>
       <c r="J110" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5329,18 +5357,18 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr"/>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -5351,7 +5379,7 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
@@ -5361,7 +5389,7 @@
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -5371,18 +5399,18 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «Компания КОМПЛИТ»</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>7810793872</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr"/>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -5393,7 +5421,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>143</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
@@ -5403,7 +5431,7 @@
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5413,20 +5441,16 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>ООО «МонтажСтрой-М» (МСМ)</t>
+          <t>ООО «Комфорт ЛСТК»</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>7811447071</t>
+          <t>7838428816</t>
         </is>
       </c>
       <c r="D113" s="13" t="inlineStr"/>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
-        </is>
-      </c>
+      <c r="E113" s="11" t="inlineStr"/>
       <c r="F113" s="11" t="inlineStr"/>
       <c r="G113" s="11" t="inlineStr">
         <is>
@@ -5435,7 +5459,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>693</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
@@ -5445,7 +5469,7 @@
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5455,20 +5479,16 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «Корнелиус»</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7802611335</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr"/>
-      <c r="E114" s="11" t="inlineStr">
-        <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
-        </is>
-      </c>
+      <c r="E114" s="11" t="inlineStr"/>
       <c r="F114" s="11" t="inlineStr"/>
       <c r="G114" s="11" t="inlineStr">
         <is>
@@ -5477,7 +5497,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
@@ -5487,7 +5507,7 @@
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5497,29 +5517,25 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «Красный Квадрат»</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7802567950</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr"/>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
-        </is>
-      </c>
+      <c r="E115" s="11" t="inlineStr"/>
       <c r="F115" s="11" t="inlineStr"/>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
@@ -5529,7 +5545,7 @@
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5539,29 +5555,25 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «ЛС-Групп»</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7842036949</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr"/>
-      <c r="E116" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
-        </is>
-      </c>
+      <c r="E116" s="11" t="inlineStr"/>
       <c r="F116" s="11" t="inlineStr"/>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>509</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
@@ -5571,7 +5583,7 @@
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5581,29 +5593,29 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr"/>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
@@ -5613,7 +5625,7 @@
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5623,18 +5635,18 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr"/>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -5645,7 +5657,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -5665,29 +5677,25 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
+          <t>ООО «ЛидерСервис»</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>7825382561</t>
+          <t>7805304438</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr"/>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
-        </is>
-      </c>
+      <c r="E119" s="11" t="inlineStr"/>
       <c r="F119" s="11" t="inlineStr"/>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>902</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -5697,7 +5705,7 @@
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5707,29 +5715,25 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «М-ГРУПП»</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>3128105475</t>
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr"/>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
-        </is>
-      </c>
+      <c r="E120" s="11" t="inlineStr"/>
       <c r="F120" s="11" t="inlineStr"/>
       <c r="G120" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -5739,7 +5743,7 @@
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5749,29 +5753,25 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «М-Сервис»</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7842429918</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr"/>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
-        </is>
-      </c>
+      <c r="E121" s="11" t="inlineStr"/>
       <c r="F121" s="11" t="inlineStr"/>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>722</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5791,20 +5791,16 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
+          <t>ООО «МАН»</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>7810685806</t>
+          <t>7840404386</t>
         </is>
       </c>
       <c r="D122" s="13" t="inlineStr"/>
-      <c r="E122" s="11" t="inlineStr">
-        <is>
-          <t>194017 СПб, Ярославский пр.</t>
-        </is>
-      </c>
+      <c r="E122" s="11" t="inlineStr"/>
       <c r="F122" s="11" t="inlineStr"/>
       <c r="G122" s="11" t="inlineStr">
         <is>
@@ -5813,7 +5809,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>510</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -5823,7 +5819,7 @@
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5833,20 +5829,16 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «МАТИС»</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>7820023103</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr"/>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
-        </is>
-      </c>
+      <c r="E123" s="11" t="inlineStr"/>
       <c r="F123" s="11" t="inlineStr"/>
       <c r="G123" s="11" t="inlineStr">
         <is>
@@ -5855,7 +5847,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>616</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -5865,7 +5857,7 @@
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5875,20 +5867,16 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «МК БАМ»</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7536059295</t>
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr"/>
-      <c r="E124" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
-        </is>
-      </c>
+      <c r="E124" s="11" t="inlineStr"/>
       <c r="F124" s="11" t="inlineStr"/>
       <c r="G124" s="11" t="inlineStr">
         <is>
@@ -5897,7 +5885,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>668</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -5907,7 +5895,7 @@
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5917,25 +5905,29 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr"/>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
+        </is>
+      </c>
       <c r="F125" s="11" t="inlineStr"/>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -5955,18 +5947,18 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D126" s="13" t="inlineStr"/>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
@@ -5977,7 +5969,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
@@ -5987,7 +5979,7 @@
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5997,29 +5989,29 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «Мелстон Инжиниринг»</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7813248219</t>
         </is>
       </c>
       <c r="D127" s="13" t="inlineStr"/>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>669</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
@@ -6029,7 +6021,7 @@
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6039,18 +6031,18 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr"/>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
@@ -6061,7 +6053,7 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr">
@@ -6081,18 +6073,18 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr"/>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
@@ -6103,7 +6095,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
@@ -6113,7 +6105,7 @@
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -6123,29 +6115,25 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>ООО «РестСтройГрупп»</t>
+          <t>ООО «НПО «НАСТ»</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>7839099924</t>
+          <t>7810172762</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr"/>
-      <c r="E130" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
-        </is>
-      </c>
+      <c r="E130" s="11" t="inlineStr"/>
       <c r="F130" s="11" t="inlineStr"/>
       <c r="G130" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>273</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr">
@@ -6155,7 +6143,7 @@
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6165,20 +6153,16 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Алстрой»</t>
+          <t>ООО «НПО «Процесс»</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>7813417675</t>
+          <t>7806468037</t>
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr"/>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
-        </is>
-      </c>
+      <c r="E131" s="11" t="inlineStr"/>
       <c r="F131" s="11" t="inlineStr"/>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -6187,7 +6171,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
@@ -6197,7 +6181,7 @@
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6207,20 +6191,16 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «НПО ПЭМЗ»</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7813361648</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr"/>
-      <c r="E132" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
-        </is>
-      </c>
+      <c r="E132" s="11" t="inlineStr"/>
       <c r="F132" s="11" t="inlineStr"/>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6229,7 +6209,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr">
@@ -6239,7 +6219,7 @@
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6249,18 +6229,18 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «НПП «Путьсервис»</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7810216184</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr"/>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr"/>
@@ -6271,7 +6251,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>733</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
@@ -6281,7 +6261,7 @@
       </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6291,18 +6271,18 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr"/>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr"/>
@@ -6313,7 +6293,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr">
@@ -6323,7 +6303,7 @@
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -6333,20 +6313,16 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «НПХК «Ремстройкомплекс»</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7826000423</t>
         </is>
       </c>
       <c r="D135" s="13" t="inlineStr"/>
-      <c r="E135" s="11" t="inlineStr">
-        <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
-        </is>
-      </c>
+      <c r="E135" s="11" t="inlineStr"/>
       <c r="F135" s="11" t="inlineStr"/>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6355,7 +6331,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
@@ -6365,7 +6341,7 @@
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6375,29 +6351,29 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr"/>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr"/>
       <c r="G136" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr">
@@ -6417,20 +6393,16 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «НСР»</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7801727376</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr"/>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
-        </is>
-      </c>
+      <c r="E137" s="11" t="inlineStr"/>
       <c r="F137" s="11" t="inlineStr"/>
       <c r="G137" s="11" t="inlineStr">
         <is>
@@ -6439,7 +6411,7 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
@@ -6449,7 +6421,7 @@
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6459,29 +6431,29 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr"/>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr"/>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr">
@@ -6491,7 +6463,7 @@
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6501,29 +6473,29 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr"/>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
@@ -6543,20 +6515,16 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «ОСА - Север»</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7801574480</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr"/>
-      <c r="E140" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
-        </is>
-      </c>
+      <c r="E140" s="11" t="inlineStr"/>
       <c r="F140" s="11" t="inlineStr"/>
       <c r="G140" s="11" t="inlineStr">
         <is>
@@ -6565,7 +6533,7 @@
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>834</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr">
@@ -6575,7 +6543,7 @@
       </c>
       <c r="J140" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6585,29 +6553,25 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй центр»</t>
+          <t>ООО «ОблСервис»</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>7804538240</t>
+          <t>4712024087</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr"/>
-      <c r="E141" s="11" t="inlineStr">
-        <is>
-          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
-        </is>
-      </c>
+      <c r="E141" s="11" t="inlineStr"/>
       <c r="F141" s="11" t="inlineStr"/>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
@@ -6617,7 +6581,7 @@
       </c>
       <c r="J141" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6627,12 +6591,12 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «Олимп-Строй»</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7820315709</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr"/>
@@ -6645,7 +6609,7 @@
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>689</t>
         </is>
       </c>
       <c r="I142" s="10" t="inlineStr">
@@ -6655,7 +6619,7 @@
       </c>
       <c r="J142" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6665,18 +6629,18 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr"/>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr"/>
@@ -6687,7 +6651,7 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
@@ -6707,29 +6671,25 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕЗИС»</t>
+          <t>ООО «Основание»</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>7804441209</t>
+          <t>7840083527</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr"/>
-      <c r="E144" s="11" t="inlineStr">
-        <is>
-          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
-        </is>
-      </c>
+      <c r="E144" s="11" t="inlineStr"/>
       <c r="F144" s="11" t="inlineStr"/>
       <c r="G144" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="I144" s="10" t="inlineStr">
@@ -6739,7 +6699,7 @@
       </c>
       <c r="J144" s="10" t="inlineStr">
         <is>
-          <t>700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6749,29 +6709,29 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr"/>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr"/>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
@@ -6781,7 +6741,7 @@
       </c>
       <c r="J145" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -6791,20 +6751,16 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «ПВВ Продукт»</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7840501541</t>
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr"/>
-      <c r="E146" s="11" t="inlineStr">
-        <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
-        </is>
-      </c>
+      <c r="E146" s="11" t="inlineStr"/>
       <c r="F146" s="11" t="inlineStr"/>
       <c r="G146" s="11" t="inlineStr">
         <is>
@@ -6813,7 +6769,7 @@
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>454</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr">
@@ -6823,7 +6779,7 @@
       </c>
       <c r="J146" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6833,20 +6789,16 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «ПВЦ «Восток»</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7802203054</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr"/>
-      <c r="E147" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
-        </is>
-      </c>
+      <c r="E147" s="11" t="inlineStr"/>
       <c r="F147" s="11" t="inlineStr"/>
       <c r="G147" s="11" t="inlineStr">
         <is>
@@ -6855,7 +6807,7 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>534</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
@@ -6865,7 +6817,7 @@
       </c>
       <c r="J147" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6875,29 +6827,29 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr"/>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr"/>
       <c r="G148" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
@@ -6917,20 +6869,16 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «ПЕГАЗ»</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7804700982</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr"/>
-      <c r="E149" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
-        </is>
-      </c>
+      <c r="E149" s="11" t="inlineStr"/>
       <c r="F149" s="11" t="inlineStr"/>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -6939,7 +6887,7 @@
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
@@ -6949,7 +6897,7 @@
       </c>
       <c r="J149" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6959,18 +6907,18 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D150" s="13" t="inlineStr"/>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr"/>
@@ -6981,7 +6929,7 @@
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr">
@@ -6991,7 +6939,7 @@
       </c>
       <c r="J150" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -7001,18 +6949,18 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D151" s="13" t="inlineStr"/>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>194017 СПб, Ярославский пр.</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr"/>
@@ -7023,7 +6971,7 @@
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
@@ -7033,7 +6981,7 @@
       </c>
       <c r="J151" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -7043,29 +6991,33 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>7841469072</t>
         </is>
       </c>
       <c r="D152" s="13" t="inlineStr"/>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
-        </is>
-      </c>
-      <c r="F152" s="11" t="inlineStr"/>
+          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>saby.ru/profile/7841469072-783901001</t>
+        </is>
+      </c>
       <c r="G152" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (найден только белорусский номер — под вопросом)</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>595</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr">
@@ -7075,7 +7027,7 @@
       </c>
       <c r="J152" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7085,44 +7037,1676 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «ПСК «Реставрация»</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7839085696</t>
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr"/>
-      <c r="E153" s="11" t="inlineStr">
-        <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
-        </is>
-      </c>
+      <c r="E153" s="11" t="inlineStr"/>
       <c r="F153" s="11" t="inlineStr"/>
       <c r="G153" s="11" t="inlineStr">
         <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H153" s="10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I153" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J153" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>7811659380</t>
+        </is>
+      </c>
+      <c r="D154" s="13" t="inlineStr"/>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr"/>
+      <c r="G154" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J154" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПСТ»</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>7813448257</t>
+        </is>
+      </c>
+      <c r="D155" s="13" t="inlineStr"/>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr"/>
+      <c r="G155" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J155" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПТГ»</t>
+        </is>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>5013050270</t>
+        </is>
+      </c>
+      <c r="D156" s="13" t="inlineStr"/>
+      <c r="E156" s="11" t="inlineStr"/>
+      <c r="F156" s="11" t="inlineStr"/>
+      <c r="G156" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H156" s="10" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="I156" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J156" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПЭС»</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>7814677411</t>
+        </is>
+      </c>
+      <c r="D157" s="13" t="inlineStr"/>
+      <c r="E157" s="11" t="inlineStr"/>
+      <c r="F157" s="11" t="inlineStr"/>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H157" s="10" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="I157" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J157" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПетроТрейд-инжиниринг»</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>7802490056</t>
+        </is>
+      </c>
+      <c r="D158" s="13" t="inlineStr"/>
+      <c r="E158" s="11" t="inlineStr"/>
+      <c r="F158" s="11" t="inlineStr"/>
+      <c r="G158" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H158" s="10" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="I158" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J158" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Портмарин Инжиниринг»</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>7811777680</t>
+        </is>
+      </c>
+      <c r="D159" s="13" t="inlineStr"/>
+      <c r="E159" s="11" t="inlineStr"/>
+      <c r="F159" s="11" t="inlineStr"/>
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H159" s="10" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="I159" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J159" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПрогрессСтрой»</t>
+        </is>
+      </c>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>7811604013</t>
+        </is>
+      </c>
+      <c r="D160" s="13" t="inlineStr"/>
+      <c r="E160" s="11" t="inlineStr"/>
+      <c r="F160" s="11" t="inlineStr"/>
+      <c r="G160" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H160" s="10" t="inlineStr">
+        <is>
+          <t>1049</t>
+        </is>
+      </c>
+      <c r="I160" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J160" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПромИнвест»</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>7841439543</t>
+        </is>
+      </c>
+      <c r="D161" s="13" t="inlineStr"/>
+      <c r="E161" s="11" t="inlineStr"/>
+      <c r="F161" s="11" t="inlineStr"/>
+      <c r="G161" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H161" s="10" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="I161" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J161" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПромСтрой»</t>
+        </is>
+      </c>
+      <c r="C162" s="12" t="inlineStr">
+        <is>
+          <t>7806156944</t>
+        </is>
+      </c>
+      <c r="D162" s="13" t="inlineStr"/>
+      <c r="E162" s="11" t="inlineStr"/>
+      <c r="F162" s="11" t="inlineStr"/>
+      <c r="G162" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H162" s="10" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="I162" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J162" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Промстрой»</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>7814656860</t>
+        </is>
+      </c>
+      <c r="D163" s="13" t="inlineStr"/>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="inlineStr"/>
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H163" s="10" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="I163" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J163" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Промстройинжиниринг»</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>7814349756</t>
+        </is>
+      </c>
+      <c r="D164" s="13" t="inlineStr"/>
+      <c r="E164" s="11" t="inlineStr"/>
+      <c r="F164" s="11" t="inlineStr"/>
+      <c r="G164" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H164" s="10" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="I164" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J164" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПрофСтрой-И»</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>7810682530</t>
+        </is>
+      </c>
+      <c r="D165" s="13" t="inlineStr"/>
+      <c r="E165" s="11" t="inlineStr"/>
+      <c r="F165" s="11" t="inlineStr"/>
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H165" s="10" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="I165" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J165" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ПрофСтройАльянс»</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
+          <t>7842504114</t>
+        </is>
+      </c>
+      <c r="D166" s="13" t="inlineStr"/>
+      <c r="E166" s="11" t="inlineStr"/>
+      <c r="F166" s="11" t="inlineStr"/>
+      <c r="G166" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H166" s="10" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="I166" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J166" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Профиль»</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>7802182380</t>
+        </is>
+      </c>
+      <c r="D167" s="13" t="inlineStr"/>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr"/>
+      <c r="G167" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="I167" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J167" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РЕССТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>7820012849</t>
+        </is>
+      </c>
+      <c r="D168" s="13" t="inlineStr"/>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr"/>
+      <c r="G168" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H168" s="10" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="I168" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J168" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="inlineStr">
+        <is>
+          <t>7826123721</t>
+        </is>
+      </c>
+      <c r="D169" s="13" t="inlineStr"/>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+        </is>
+      </c>
+      <c r="F169" s="11" t="inlineStr"/>
+      <c r="G169" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H169" s="10" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J169" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>ООО «РестСтройГрупп»</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>7839099924</t>
+        </is>
+      </c>
+      <c r="D170" s="13" t="inlineStr"/>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr"/>
+      <c r="G170" s="11" t="inlineStr">
+        <is>
           <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
-      <c r="H153" s="10" t="inlineStr">
+      <c r="H170" s="10" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="I170" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J170" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Алстрой»</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>7813417675</t>
+        </is>
+      </c>
+      <c r="D171" s="13" t="inlineStr"/>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="inlineStr"/>
+      <c r="G171" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H171" s="10" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="I171" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J171" s="10" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК «Потенциал»</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>7814558855</t>
+        </is>
+      </c>
+      <c r="D172" s="13" t="inlineStr"/>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
+      <c r="F172" s="11" t="inlineStr"/>
+      <c r="G172" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H172" s="10" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I172" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J172" s="10" t="inlineStr">
+        <is>
+          <t>1700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК Гарант»</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>7806380022</t>
+        </is>
+      </c>
+      <c r="D173" s="13" t="inlineStr"/>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="inlineStr"/>
+      <c r="G173" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H173" s="10" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J173" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="10" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК ПСП»</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>7810502379</t>
+        </is>
+      </c>
+      <c r="D174" s="13" t="inlineStr"/>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr"/>
+      <c r="G174" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H174" s="10" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="I174" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J174" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СПбЭК-Майнинг»</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr">
+        <is>
+          <t>7820326027</t>
+        </is>
+      </c>
+      <c r="D175" s="13" t="inlineStr"/>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr"/>
+      <c r="G175" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H175" s="10" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="I175" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J175" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="inlineStr">
+        <is>
+          <t>7825055370</t>
+        </is>
+      </c>
+      <c r="D176" s="13" t="inlineStr"/>
+      <c r="E176" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
+      <c r="F176" s="11" t="inlineStr"/>
+      <c r="G176" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="I176" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J176" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="10" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУ-17»</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>7807028906</t>
+        </is>
+      </c>
+      <c r="D177" s="13" t="inlineStr"/>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
+      <c r="F177" s="11" t="inlineStr"/>
+      <c r="G177" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H177" s="10" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="I177" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J177" s="10" t="inlineStr">
+        <is>
+          <t>2300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУАР-Групп»</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>7802270195</t>
+        </is>
+      </c>
+      <c r="D178" s="13" t="inlineStr"/>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr"/>
+      <c r="G178" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H178" s="10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="I178" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J178" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="10" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СЭМ»</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr">
+        <is>
+          <t>7810201646</t>
+        </is>
+      </c>
+      <c r="D179" s="13" t="inlineStr"/>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="inlineStr"/>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H179" s="10" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I179" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J179" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строительные технологии»</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr">
+        <is>
+          <t>7813680179</t>
+        </is>
+      </c>
+      <c r="D180" s="13" t="inlineStr"/>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+        </is>
+      </c>
+      <c r="F180" s="11" t="inlineStr"/>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H180" s="10" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I180" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J180" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строй центр»</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr">
+        <is>
+          <t>7804538240</t>
+        </is>
+      </c>
+      <c r="D181" s="13" t="inlineStr"/>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="inlineStr"/>
+      <c r="G181" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H181" s="10" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="I181" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J181" s="10" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СтройГрад»</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr">
+        <is>
+          <t>7813692632</t>
+        </is>
+      </c>
+      <c r="D182" s="13" t="inlineStr"/>
+      <c r="E182" s="11" t="inlineStr"/>
+      <c r="F182" s="11" t="inlineStr"/>
+      <c r="G182" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H182" s="10" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="I182" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J182" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="10" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Сфера»</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>2311308786</t>
+        </is>
+      </c>
+      <c r="D183" s="13" t="inlineStr"/>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="inlineStr"/>
+      <c r="G183" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H183" s="10" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="I183" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J183" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЕЗИС»</t>
+        </is>
+      </c>
+      <c r="C184" s="12" t="inlineStr">
+        <is>
+          <t>7804441209</t>
+        </is>
+      </c>
+      <c r="D184" s="13" t="inlineStr"/>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+        </is>
+      </c>
+      <c r="F184" s="11" t="inlineStr"/>
+      <c r="G184" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H184" s="10" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I184" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J184" s="10" t="inlineStr">
+        <is>
+          <t>700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="10" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
+        </is>
+      </c>
+      <c r="C185" s="12" t="inlineStr">
+        <is>
+          <t>7814612968</t>
+        </is>
+      </c>
+      <c r="D185" s="13" t="inlineStr"/>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="inlineStr"/>
+      <c r="G185" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H185" s="10" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="I185" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J185" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr">
+        <is>
+          <t>7839061021</t>
+        </is>
+      </c>
+      <c r="D186" s="13" t="inlineStr"/>
+      <c r="E186" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
+      <c r="F186" s="11" t="inlineStr"/>
+      <c r="G186" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H186" s="10" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="I186" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J186" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="10" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Трамплин-строй»</t>
+        </is>
+      </c>
+      <c r="C187" s="12" t="inlineStr">
+        <is>
+          <t>7802207193</t>
+        </is>
+      </c>
+      <c r="D187" s="13" t="inlineStr"/>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+        </is>
+      </c>
+      <c r="F187" s="11" t="inlineStr"/>
+      <c r="G187" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H187" s="10" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="I187" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J187" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C188" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D188" s="13" t="inlineStr"/>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F188" s="11" t="inlineStr"/>
+      <c r="G188" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H188" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I188" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J188" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D189" s="13" t="inlineStr"/>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="inlineStr"/>
+      <c r="G189" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H189" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I189" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J189" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C190" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D190" s="13" t="inlineStr"/>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F190" s="11" t="inlineStr"/>
+      <c r="G190" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H190" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I190" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J190" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D191" s="13" t="inlineStr"/>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F191" s="11" t="inlineStr"/>
+      <c r="G191" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H191" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I191" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J191" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D192" s="13" t="inlineStr"/>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F192" s="11" t="inlineStr"/>
+      <c r="G192" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H192" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I192" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J192" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="10" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D193" s="13" t="inlineStr"/>
+      <c r="E193" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F193" s="11" t="inlineStr"/>
+      <c r="G193" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H193" s="10" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="I153" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J153" s="10" t="inlineStr">
+      <c r="I193" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J193" s="10" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J153"/>
+  <autoFilter ref="A1:J193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7205,7 +8789,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
@@ -7215,7 +8799,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -7225,7 +8809,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J193"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2229,27 +2229,27 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ООО «Спецтехкомплект»</t>
+          <t>ООО «Сити-ППА»</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>7811127120</t>
+          <t>7802940940</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 362-09-21</t>
+          <t>+7 (812) 985-53-55</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+          <t>194292 СПб, 5-й Верхний пер. 12к2Б оф.11; ОГРН 1237800142380; ген.дир. Прокофьев А.В.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7802940940/780201001</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2279,27 +2279,27 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ООО «СтарКом»</t>
+          <t>ООО «Спецтехкомплект»</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>7841416641</t>
+          <t>7811127120</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+          <t>+7 (812) 362-09-21</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>626</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2329,27 +2329,27 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ООО «ТМГ ГРУП»</t>
+          <t>ООО «СтарКом»</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>7705405168</t>
+          <t>7841416641</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 680-30-20</t>
+          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>508</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -2379,89 +2379,97 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
+          <t>ООО «ТМГ ГРУП»</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>7705405168</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 680-30-20</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
           <t>ООО «Транспромстрой»</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>7804591155</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 449-31-21</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>СПб, ул.Савушкина 83к3А оф.401-402; ОГРН 1177847074250; ген.дир. Аванесов Д.Б.; ~467 сотрудников</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>spark-interfax.ru; companies.rbc.ru; sbis.ru</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>752</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>1500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>АНО «ВАЛААМ»</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>7839024647</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr"/>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr"/>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2471,18 +2479,18 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>АО «Абсолют»</t>
+          <t>АНО «ВАЛААМ»</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>7825663795</t>
+          <t>7839024647</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr"/>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
+          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
@@ -2493,7 +2501,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2513,29 +2521,29 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>АО «Аспект Северо-Запад»</t>
+          <t>АО «Абсолют»</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>7810143306</t>
+          <t>7825663795</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr"/>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
+          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -2555,29 +2563,29 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
+          <t>АО «Аспект Северо-Запад»</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>7810255553</t>
+          <t>7810143306</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr"/>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
+          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>735</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2587,7 +2595,7 @@
       </c>
       <c r="J42" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2597,18 +2605,18 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>АО «ВОЛХОН»</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>7810383403</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr"/>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
@@ -2619,7 +2627,7 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -2639,18 +2647,18 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>7813007615</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
@@ -2661,7 +2669,7 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2671,7 +2679,7 @@
       </c>
       <c r="J44" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2681,29 +2689,29 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>АО «НОУДИГ» (Per Aarsleff)</t>
+          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>7802108837</t>
+          <t>7813007615</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr"/>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
+          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -2713,7 +2721,7 @@
       </c>
       <c r="J45" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -2723,29 +2731,29 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>АО «Петрос»</t>
+          <t>АО «НОУДИГ» (Per Aarsleff)</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>7816131635</t>
+          <t>7802108837</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr"/>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
+          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>699</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2755,7 +2763,7 @@
       </c>
       <c r="J46" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2765,29 +2773,29 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>АО «Полиспаст»</t>
+          <t>АО «Петрос»</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>7805744573</t>
+          <t>7816131635</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr"/>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
+          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>507</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2797,7 +2805,7 @@
       </c>
       <c r="J47" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2807,29 +2815,29 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>АО «РЭС» (Региональные электрические сети)</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>7810785984</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr"/>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2839,7 +2847,7 @@
       </c>
       <c r="J48" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2849,16 +2857,20 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>АО «СМУ-47»</t>
+          <t>АО «РЭС» (Региональные электрические сети)</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>7801097276</t>
+          <t>7810785984</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr"/>
-      <c r="E49" s="11" t="inlineStr"/>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
+        </is>
+      </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr">
         <is>
@@ -2867,7 +2879,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>566</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -2887,29 +2899,25 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>АО «Селектел»</t>
+          <t>АО «СМУ-47»</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>7810962785</t>
+          <t>7801097276</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr"/>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
-        </is>
-      </c>
+      <c r="E50" s="11" t="inlineStr"/>
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>нет данных (телефон смотреть на selectel.ru)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>687</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2929,29 +2937,29 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>АО «Стройинвест»</t>
+          <t>АО «Селектел»</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>7825697956</t>
+          <t>7810962785</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr"/>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (телефон смотреть на selectel.ru)</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -2961,7 +2969,7 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2971,18 +2979,18 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Агентство Шушары»</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>7820016970</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr"/>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
@@ -2993,7 +3001,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -3003,7 +3011,7 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3013,29 +3021,29 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Институт телекоммуникаций»</t>
+          <t>ЗАО «Агентство Шушары»</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>7802199182</t>
+          <t>7820016970</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr"/>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
+          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>нет данных (телефон смотреть на itain.ru)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -3045,7 +3053,7 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3055,29 +3063,29 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «ПетроЭлектроКомплекс»</t>
+          <t>ЗАО «Институт телекоммуникаций»</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>7801128326</t>
+          <t>7802199182</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
+          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных (телефон смотреть на itain.ru)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3097,29 +3105,29 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Трест СЗКС» (Севзапкурортстрой)</t>
+          <t>ЗАО «ПетроЭлектроКомплекс»</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>7809006739</t>
+          <t>7801128326</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr"/>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 16 пом.1н оф.117; ОГРН 1027810295842; ген.дир. Тихомиров С.А.</t>
+          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>506</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3139,29 +3147,29 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
+          <t>ЗАО «Трест СЗКС» (Севзапкурортстрой)</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>7811405770</t>
+          <t>7809006739</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
+          <t>190013 СПб, Рузовская ул. 16 пом.1н оф.117; ОГРН 1027810295842; ген.дир. Тихомиров С.А.</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>630</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3171,7 +3179,7 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3181,29 +3189,29 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
+          <t>ЗАО «Эра-Инжиниринг»</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>7813424070</t>
+          <t>7811405770</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr"/>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
+          <t>СПб, пр.Обуховской Обороны 271; ОГРН 1089847177750</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>519</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -3213,7 +3221,7 @@
       </c>
       <c r="J57" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3223,29 +3231,29 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>ООО «АЛЬФА»</t>
+          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>7813411063</t>
+          <t>7813424070</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr"/>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
+          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>684</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -3265,18 +3273,18 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>ООО «АРТ-МАСШТАБ»</t>
+          <t>ООО «АЛЬФА»</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>7840076495</t>
+          <t>7813411063</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr"/>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
+          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -3287,7 +3295,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>524</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3307,29 +3315,29 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>ООО «АС Инжиниринг»</t>
+          <t>ООО «АРТ-МАСШТАБ»</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>7810318651</t>
+          <t>7840076495</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr"/>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
+          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
       <c r="G60" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3349,33 +3357,29 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>ООО «Алисард»</t>
+          <t>ООО «АС Инжиниринг»</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7814713356</t>
+          <t>7810318651</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr"/>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
-        </is>
-      </c>
-      <c r="F61" s="11" t="inlineStr">
-        <is>
-          <t>alisard.com</t>
-        </is>
-      </c>
+          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr"/>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть e-mail и сайт)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3395,25 +3399,33 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альфа»</t>
+          <t>ООО «Алисард»</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>7802594841</t>
+          <t>7814713356</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr"/>
-      <c r="E62" s="11" t="inlineStr"/>
-      <c r="F62" s="11" t="inlineStr"/>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>alisard.com</t>
+        </is>
+      </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть e-mail и сайт)</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>575</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3433,29 +3445,25 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>ООО «Альфа»</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7802594841</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr"/>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
-        </is>
-      </c>
+      <c r="E63" s="11" t="inlineStr"/>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -3465,7 +3473,7 @@
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3475,18 +3483,18 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>ООО «Антей»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>4708011991</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr"/>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -3497,7 +3505,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -3507,7 +3515,7 @@
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3517,29 +3525,29 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>ООО «Арман»</t>
+          <t>ООО «Антей»</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>7805298463</t>
+          <t>4708011991</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr"/>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
+          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -3559,16 +3567,20 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлантис»</t>
+          <t>ООО «Арман»</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>7810914904</t>
+          <t>7805298463</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr"/>
-      <c r="E66" s="11" t="inlineStr"/>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
+        </is>
+      </c>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr">
         <is>
@@ -3577,7 +3589,7 @@
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>586</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3597,20 +3609,16 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАРК»</t>
+          <t>ООО «Атлантис»</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>7804462262</t>
+          <t>7810914904</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr"/>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
-        </is>
-      </c>
+      <c r="E67" s="11" t="inlineStr"/>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr">
         <is>
@@ -3619,7 +3627,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -3639,18 +3647,18 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
+          <t>ООО «БАРК»</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>7804634666</t>
+          <t>7804462262</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr"/>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
+          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -3661,7 +3669,7 @@
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3681,18 +3689,18 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>ООО «БЕЛНЕВА»</t>
+          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7839489314</t>
+          <t>7804634666</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr"/>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
+          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
@@ -3703,7 +3711,7 @@
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3723,18 +3731,18 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>ООО «БЕЛНЕВА»</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7839489314</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr"/>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -3745,7 +3753,7 @@
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>457</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -3755,7 +3763,7 @@
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3765,16 +3773,20 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
-      <c r="E71" s="11" t="inlineStr"/>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+        </is>
+      </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
@@ -3783,7 +3795,7 @@
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -3793,7 +3805,7 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -3803,29 +3815,25 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>ООО «БРАЗСТРОЙ»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>2630050808</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr"/>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
-        </is>
-      </c>
+      <c r="E72" s="11" t="inlineStr"/>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -3835,7 +3843,7 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3845,18 +3853,18 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>ООО «БелькаРус»</t>
+          <t>ООО «БРАЗСТРОЙ»</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>7801665024</t>
+          <t>2630050808</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
+          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
@@ -3867,7 +3875,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -3887,18 +3895,18 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>ООО «БиАр»</t>
+          <t>ООО «БелькаРус»</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>7802738910</t>
+          <t>7801665024</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr"/>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
+          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -3909,7 +3917,7 @@
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -3919,7 +3927,7 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3929,29 +3937,29 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>ООО «Бобёр»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>7801632702</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr"/>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -3961,7 +3969,7 @@
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -3971,29 +3979,29 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЕРТЕК»</t>
+          <t>ООО «Бобёр»</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>7806317711</t>
+          <t>7801632702</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr"/>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -4003,7 +4011,7 @@
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4013,25 +4021,29 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИП»</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>7802742070</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr"/>
-      <c r="E77" s="11" t="inlineStr"/>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+        </is>
+      </c>
       <c r="F77" s="11" t="inlineStr"/>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -4041,7 +4053,7 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -4051,29 +4063,25 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИРА»</t>
+          <t>ООО «ВИП»</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>7839139655</t>
+          <t>7802742070</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr"/>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
-        </is>
-      </c>
+      <c r="E78" s="11" t="inlineStr"/>
       <c r="F78" s="11" t="inlineStr"/>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>226</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -4093,25 +4101,29 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК»</t>
+          <t>ООО «ВИРА»</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>3525411380</t>
+          <t>7839139655</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr"/>
-      <c r="E79" s="11" t="inlineStr"/>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
+        </is>
+      </c>
       <c r="F79" s="11" t="inlineStr"/>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -4131,12 +4143,12 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК» (Военно-строительная компания)</t>
+          <t>ООО «ВСК»</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>7804018392</t>
+          <t>3525411380</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr"/>
@@ -4149,7 +4161,7 @@
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -4169,12 +4181,12 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЭС»</t>
+          <t>ООО «ВСК» (Военно-строительная компания)</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>7839121496</t>
+          <t>7804018392</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr"/>
@@ -4187,7 +4199,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>670</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -4207,20 +4219,16 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «ВЭС»</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7839121496</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr"/>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
-        </is>
-      </c>
+      <c r="E82" s="11" t="inlineStr"/>
       <c r="F82" s="11" t="inlineStr"/>
       <c r="G82" s="11" t="inlineStr">
         <is>
@@ -4229,7 +4237,7 @@
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>828</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -4239,7 +4247,7 @@
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4249,29 +4257,29 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr"/>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -4281,7 +4289,7 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4291,25 +4299,29 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>7603054270</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr"/>
-      <c r="E84" s="11" t="inlineStr"/>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+        </is>
+      </c>
       <c r="F84" s="11" t="inlineStr"/>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -4319,7 +4331,7 @@
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4329,20 +4341,16 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7603054270</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr"/>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
-        </is>
-      </c>
+      <c r="E85" s="11" t="inlineStr"/>
       <c r="F85" s="11" t="inlineStr"/>
       <c r="G85" s="11" t="inlineStr">
         <is>
@@ -4351,7 +4359,7 @@
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -4361,7 +4369,7 @@
       </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4371,16 +4379,20 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГК «СТИ»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>7814797620</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr"/>
-      <c r="E86" s="11" t="inlineStr"/>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+        </is>
+      </c>
       <c r="F86" s="11" t="inlineStr"/>
       <c r="G86" s="11" t="inlineStr">
         <is>
@@ -4389,7 +4401,7 @@
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -4399,7 +4411,7 @@
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4409,29 +4421,25 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «ГК «СТИ»</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7814797620</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr"/>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
-        </is>
-      </c>
+      <c r="E87" s="11" t="inlineStr"/>
       <c r="F87" s="11" t="inlineStr"/>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>847</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -4441,7 +4449,7 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4451,18 +4459,18 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr"/>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -4473,7 +4481,7 @@
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -4483,7 +4491,7 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4493,25 +4501,29 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гелиос»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>7804608994</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr"/>
-      <c r="E89" s="11" t="inlineStr"/>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+        </is>
+      </c>
       <c r="F89" s="11" t="inlineStr"/>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -4521,7 +4533,7 @@
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4531,29 +4543,25 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «Гелиос»</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7804608994</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr"/>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
-        </is>
-      </c>
+      <c r="E90" s="11" t="inlineStr"/>
       <c r="F90" s="11" t="inlineStr"/>
       <c r="G90" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>565</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -4563,7 +4571,7 @@
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4573,25 +4581,29 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>ООО «ДСК РЕГИОН»</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>7816487198</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr"/>
-      <c r="E91" s="11" t="inlineStr"/>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
+        </is>
+      </c>
       <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -4601,7 +4613,7 @@
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4623,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>ООО «Дорожник СПб»</t>
+          <t>ООО «ДСК РЕГИОН»</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>7806421624</t>
+          <t>7816487198</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr"/>
@@ -4629,7 +4641,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -4649,29 +4661,25 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «Дорожник СПб»</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>7806421624</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr"/>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
-        </is>
-      </c>
+      <c r="E93" s="11" t="inlineStr"/>
       <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>564</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -4681,7 +4689,7 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4691,29 +4699,29 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr"/>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr"/>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -4723,7 +4731,7 @@
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4733,16 +4741,20 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЗИТЕК»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>7814691303</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr"/>
-      <c r="E95" s="11" t="inlineStr"/>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+        </is>
+      </c>
       <c r="F95" s="11" t="inlineStr"/>
       <c r="G95" s="11" t="inlineStr">
         <is>
@@ -4751,7 +4763,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -4761,7 +4773,7 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -4771,12 +4783,12 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>ООО «Зодчий»</t>
+          <t>ООО «ЗИТЕК»</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>7810477235</t>
+          <t>7814691303</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr"/>
@@ -4789,7 +4801,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -4809,20 +4821,16 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «Зодчий»</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7810477235</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr"/>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
-        </is>
-      </c>
+      <c r="E97" s="11" t="inlineStr"/>
       <c r="F97" s="11" t="inlineStr"/>
       <c r="G97" s="11" t="inlineStr">
         <is>
@@ -4831,7 +4839,7 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -4841,7 +4849,7 @@
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4851,16 +4859,20 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr"/>
-      <c r="E98" s="11" t="inlineStr"/>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+        </is>
+      </c>
       <c r="F98" s="11" t="inlineStr"/>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -4869,7 +4881,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
@@ -4889,12 +4901,12 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК «Петротрасса»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>7804572970</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr"/>
@@ -4907,7 +4919,7 @@
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -4917,7 +4929,7 @@
       </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4927,12 +4939,12 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ИнТехПро»</t>
+          <t>ООО «ИК «Петротрасса»</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>9810000213</t>
+          <t>7804572970</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr"/>
@@ -4945,7 +4957,7 @@
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>712</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -4965,12 +4977,12 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
+          <t>ООО «ИК ИнТехПро»</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>7710910159</t>
+          <t>9810000213</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr"/>
@@ -4983,7 +4995,7 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -5003,29 +5015,25 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7710910159</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr"/>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
-        </is>
-      </c>
+      <c r="E102" s="11" t="inlineStr"/>
       <c r="F102" s="11" t="inlineStr"/>
       <c r="G102" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>940</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -5035,7 +5043,7 @@
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5045,25 +5053,29 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНСИ»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>7839398890</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr"/>
-      <c r="E103" s="11" t="inlineStr"/>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+        </is>
+      </c>
       <c r="F103" s="11" t="inlineStr"/>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -5073,7 +5085,7 @@
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5095,12 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИСБ-СЕРВИС»</t>
+          <t>ООО «ИНСИ»</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>7811462471</t>
+          <t>7839398890</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr"/>
@@ -5101,7 +5113,7 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -5121,20 +5133,16 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «ИСБ-СЕРВИС»</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7811462471</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr"/>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
-        </is>
-      </c>
+      <c r="E105" s="11" t="inlineStr"/>
       <c r="F105" s="11" t="inlineStr"/>
       <c r="G105" s="11" t="inlineStr">
         <is>
@@ -5143,7 +5151,7 @@
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>295</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
@@ -5153,7 +5161,7 @@
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5163,16 +5171,20 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>ООО «Импульс»</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>7839473240</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr"/>
-      <c r="E106" s="11" t="inlineStr"/>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+        </is>
+      </c>
       <c r="F106" s="11" t="inlineStr"/>
       <c r="G106" s="11" t="inlineStr">
         <is>
@@ -5181,7 +5193,7 @@
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
@@ -5191,7 +5203,7 @@
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5201,29 +5213,25 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «Импульс»</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>7839473240</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr"/>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
-        </is>
-      </c>
+      <c r="E107" s="11" t="inlineStr"/>
       <c r="F107" s="11" t="inlineStr"/>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
@@ -5233,7 +5241,7 @@
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5243,25 +5251,29 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интер-Строй»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>5505064975</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr"/>
-      <c r="E108" s="11" t="inlineStr"/>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
+        </is>
+      </c>
       <c r="F108" s="11" t="inlineStr"/>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr">
@@ -5271,7 +5283,7 @@
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5293,12 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интерпром»</t>
+          <t>ООО «Интер-Строй»</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>7805576110</t>
+          <t>5505064975</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr"/>
@@ -5299,7 +5311,7 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
@@ -5319,12 +5331,12 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>ООО «КС-Инжиниринг»</t>
+          <t>ООО «Интерпром»</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>7801615217</t>
+          <t>7805576110</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr"/>
@@ -5337,7 +5349,7 @@
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
@@ -5357,20 +5369,16 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «КС-Инжиниринг»</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7801615217</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr"/>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
-        </is>
-      </c>
+      <c r="E111" s="11" t="inlineStr"/>
       <c r="F111" s="11" t="inlineStr"/>
       <c r="G111" s="11" t="inlineStr">
         <is>
@@ -5379,7 +5387,7 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>695</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
@@ -5389,7 +5397,7 @@
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5399,18 +5407,18 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>ООО «Компания КОМПЛИТ»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>7810793872</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr"/>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -5421,7 +5429,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
@@ -5431,7 +5439,7 @@
       </c>
       <c r="J112" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -5441,16 +5449,20 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>ООО «Комфорт ЛСТК»</t>
+          <t>ООО «Компания КОМПЛИТ»</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>7838428816</t>
+          <t>7810793872</t>
         </is>
       </c>
       <c r="D113" s="13" t="inlineStr"/>
-      <c r="E113" s="11" t="inlineStr"/>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
+        </is>
+      </c>
       <c r="F113" s="11" t="inlineStr"/>
       <c r="G113" s="11" t="inlineStr">
         <is>
@@ -5459,7 +5471,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>143</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
@@ -5479,12 +5491,12 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>ООО «Корнелиус»</t>
+          <t>ООО «Комфорт ЛСТК»</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>7802611335</t>
+          <t>7838428816</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr"/>
@@ -5497,7 +5509,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>693</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
@@ -5517,12 +5529,12 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>ООО «Красный Квадрат»</t>
+          <t>ООО «Корнелиус»</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>7802567950</t>
+          <t>7802611335</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr"/>
@@ -5535,7 +5547,7 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
@@ -5555,12 +5567,12 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЛС-Групп»</t>
+          <t>ООО «Красный Квадрат»</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>7842036949</t>
+          <t>7802567950</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr"/>
@@ -5573,7 +5585,7 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
@@ -5593,29 +5605,25 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «ЛС-Групп»</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>7842036949</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr"/>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
-        </is>
-      </c>
+      <c r="E117" s="11" t="inlineStr"/>
       <c r="F117" s="11" t="inlineStr"/>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>509</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
@@ -5625,7 +5633,7 @@
       </c>
       <c r="J117" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5635,29 +5643,29 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr"/>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
       <c r="G118" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -5677,16 +5685,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЛидерСервис»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>7805304438</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr"/>
-      <c r="E119" s="11" t="inlineStr"/>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
+        </is>
+      </c>
       <c r="F119" s="11" t="inlineStr"/>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5695,7 +5707,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -5705,7 +5717,7 @@
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5715,12 +5727,12 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>ООО «М-ГРУПП»</t>
+          <t>ООО «ЛидерСервис»</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>3128105475</t>
+          <t>7805304438</t>
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr"/>
@@ -5733,7 +5745,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>902</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -5753,12 +5765,12 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>ООО «М-Сервис»</t>
+          <t>ООО «М-ГРУПП»</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>7842429918</t>
+          <t>3128105475</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr"/>
@@ -5771,7 +5783,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -5791,12 +5803,12 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>ООО «МАН»</t>
+          <t>ООО «М-Сервис»</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>7840404386</t>
+          <t>7842429918</t>
         </is>
       </c>
       <c r="D122" s="13" t="inlineStr"/>
@@ -5809,7 +5821,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>722</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -5829,12 +5841,12 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>ООО «МАТИС»</t>
+          <t>ООО «МАН»</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>7820023103</t>
+          <t>7840404386</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr"/>
@@ -5847,7 +5859,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>510</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -5867,12 +5879,12 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>ООО «МК БАМ»</t>
+          <t>ООО «МАТИС»</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>7536059295</t>
+          <t>7820023103</t>
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr"/>
@@ -5885,7 +5897,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>616</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -5905,29 +5917,25 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «МК БАМ»</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>7536059295</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
-        </is>
-      </c>
+      <c r="E125" s="11" t="inlineStr"/>
       <c r="F125" s="11" t="inlineStr"/>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>668</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -5937,7 +5945,7 @@
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5947,29 +5955,29 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D126" s="13" t="inlineStr"/>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
       <c r="G126" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
@@ -5989,29 +5997,29 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>ООО «Мелстон Инжиниринг»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>7813248219</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D127" s="13" t="inlineStr"/>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
@@ -6021,7 +6029,7 @@
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6031,29 +6039,29 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «Мелстон Инжиниринг»</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>7813248219</t>
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr"/>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
       <c r="G128" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>669</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr">
@@ -6063,7 +6071,7 @@
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6073,18 +6081,18 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>ООО «МонтажСтрой-М» (МСМ)</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>7811447071</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr"/>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
@@ -6095,7 +6103,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
@@ -6105,7 +6113,7 @@
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6115,16 +6123,20 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО «НАСТ»</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>7810172762</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr"/>
-      <c r="E130" s="11" t="inlineStr"/>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
+        </is>
+      </c>
       <c r="F130" s="11" t="inlineStr"/>
       <c r="G130" s="11" t="inlineStr">
         <is>
@@ -6133,7 +6145,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr">
@@ -6143,7 +6155,7 @@
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -6153,12 +6165,12 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО «Процесс»</t>
+          <t>ООО «НПО «НАСТ»</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>7806468037</t>
+          <t>7810172762</t>
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr"/>
@@ -6171,7 +6183,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>273</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
@@ -6191,12 +6203,12 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО ПЭМЗ»</t>
+          <t>ООО «НПО «Процесс»</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>7813361648</t>
+          <t>7806468037</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr"/>
@@ -6209,7 +6221,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr">
@@ -6229,20 +6241,16 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПП «Путьсервис»</t>
+          <t>ООО «НПО ПЭМЗ»</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>7810216184</t>
+          <t>7813361648</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr"/>
-      <c r="E133" s="11" t="inlineStr">
-        <is>
-          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
-        </is>
-      </c>
+      <c r="E133" s="11" t="inlineStr"/>
       <c r="F133" s="11" t="inlineStr"/>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6251,7 +6259,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
@@ -6271,18 +6279,18 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «НПП «Путьсервис»</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7810216184</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr"/>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr"/>
@@ -6293,7 +6301,7 @@
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>733</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr">
@@ -6303,7 +6311,7 @@
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6313,16 +6321,20 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПХК «Ремстройкомплекс»</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>7826000423</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D135" s="13" t="inlineStr"/>
-      <c r="E135" s="11" t="inlineStr"/>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+        </is>
+      </c>
       <c r="F135" s="11" t="inlineStr"/>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6331,7 +6343,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
@@ -6341,7 +6353,7 @@
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -6351,29 +6363,25 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «НПХК «Ремстройкомплекс»</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7826000423</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr"/>
-      <c r="E136" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
-        </is>
-      </c>
+      <c r="E136" s="11" t="inlineStr"/>
       <c r="F136" s="11" t="inlineStr"/>
       <c r="G136" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr">
@@ -6383,7 +6391,7 @@
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6393,25 +6401,29 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСР»</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>7801727376</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr"/>
-      <c r="E137" s="11" t="inlineStr"/>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+        </is>
+      </c>
       <c r="F137" s="11" t="inlineStr"/>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
@@ -6421,7 +6433,7 @@
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -6431,29 +6443,25 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «НСР»</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7801727376</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr"/>
-      <c r="E138" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
-        </is>
-      </c>
+      <c r="E138" s="11" t="inlineStr"/>
       <c r="F138" s="11" t="inlineStr"/>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr">
@@ -6463,7 +6471,7 @@
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6473,29 +6481,29 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr"/>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
@@ -6505,7 +6513,7 @@
       </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6515,16 +6523,20 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОСА - Север»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>7801574480</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr"/>
-      <c r="E140" s="11" t="inlineStr"/>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+        </is>
+      </c>
       <c r="F140" s="11" t="inlineStr"/>
       <c r="G140" s="11" t="inlineStr">
         <is>
@@ -6533,7 +6545,7 @@
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr">
@@ -6543,7 +6555,7 @@
       </c>
       <c r="J140" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6565,12 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОблСервис»</t>
+          <t>ООО «ОСА - Север»</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>4712024087</t>
+          <t>7801574480</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr"/>
@@ -6571,7 +6583,7 @@
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>834</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
@@ -6591,12 +6603,12 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>ООО «Олимп-Строй»</t>
+          <t>ООО «ОблСервис»</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>7820315709</t>
+          <t>4712024087</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr"/>
@@ -6609,7 +6621,7 @@
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="I142" s="10" t="inlineStr">
@@ -6629,20 +6641,16 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «Олимп-Строй»</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7820315709</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr"/>
-      <c r="E143" s="11" t="inlineStr">
-        <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
-        </is>
-      </c>
+      <c r="E143" s="11" t="inlineStr"/>
       <c r="F143" s="11" t="inlineStr"/>
       <c r="G143" s="11" t="inlineStr">
         <is>
@@ -6651,7 +6659,7 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>689</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
@@ -6661,7 +6669,7 @@
       </c>
       <c r="J143" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6671,16 +6679,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>ООО «Основание»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>7840083527</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr"/>
-      <c r="E144" s="11" t="inlineStr"/>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+        </is>
+      </c>
       <c r="F144" s="11" t="inlineStr"/>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -6689,7 +6701,7 @@
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I144" s="10" t="inlineStr">
@@ -6699,7 +6711,7 @@
       </c>
       <c r="J144" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6709,29 +6721,25 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
+          <t>ООО «Основание»</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>7825382561</t>
+          <t>7840083527</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr"/>
-      <c r="E145" s="11" t="inlineStr">
-        <is>
-          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
-        </is>
-      </c>
+      <c r="E145" s="11" t="inlineStr"/>
       <c r="F145" s="11" t="inlineStr"/>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
@@ -6741,7 +6749,7 @@
       </c>
       <c r="J145" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6751,25 +6759,29 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПВВ Продукт»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>7840501541</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr"/>
-      <c r="E146" s="11" t="inlineStr"/>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
+        </is>
+      </c>
       <c r="F146" s="11" t="inlineStr"/>
       <c r="G146" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr">
@@ -6779,7 +6791,7 @@
       </c>
       <c r="J146" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -6789,12 +6801,12 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПВЦ «Восток»</t>
+          <t>ООО «ПВВ Продукт»</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>7802203054</t>
+          <t>7840501541</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr"/>
@@ -6807,7 +6819,7 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>454</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
@@ -6827,29 +6839,25 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «ПВЦ «Восток»</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>7802203054</t>
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr"/>
-      <c r="E148" s="11" t="inlineStr">
-        <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
-        </is>
-      </c>
+      <c r="E148" s="11" t="inlineStr"/>
       <c r="F148" s="11" t="inlineStr"/>
       <c r="G148" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>534</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
@@ -6859,7 +6867,7 @@
       </c>
       <c r="J148" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6869,25 +6877,29 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕГАЗ»</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>7804700982</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr"/>
-      <c r="E149" s="11" t="inlineStr"/>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+        </is>
+      </c>
       <c r="F149" s="11" t="inlineStr"/>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
@@ -6897,7 +6909,7 @@
       </c>
       <c r="J149" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6907,29 +6919,25 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «ПЕГАЗ»</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7804700982</t>
         </is>
       </c>
       <c r="D150" s="13" t="inlineStr"/>
-      <c r="E150" s="11" t="inlineStr">
-        <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
-        </is>
-      </c>
+      <c r="E150" s="11" t="inlineStr"/>
       <c r="F150" s="11" t="inlineStr"/>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr">
@@ -6939,7 +6947,7 @@
       </c>
       <c r="J150" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6949,29 +6957,29 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>7810685806</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D151" s="13" t="inlineStr"/>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, Ярославский пр.</t>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr"/>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
@@ -6981,7 +6989,7 @@
       </c>
       <c r="J151" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -6991,33 +6999,29 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>7841469072</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D152" s="13" t="inlineStr"/>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
-        </is>
-      </c>
-      <c r="F152" s="11" t="inlineStr">
-        <is>
-          <t>saby.ru/profile/7841469072-783901001</t>
-        </is>
-      </c>
+          <t>194017 СПб, Ярославский пр.</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr"/>
       <c r="G152" s="11" t="inlineStr">
         <is>
-          <t>нет данных (найден только белорусский номер — под вопросом)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr">
@@ -7027,7 +7031,7 @@
       </c>
       <c r="J152" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -7037,25 +7041,33 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСК «Реставрация»</t>
+          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>7839085696</t>
+          <t>7841469072</t>
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr"/>
-      <c r="E153" s="11" t="inlineStr"/>
-      <c r="F153" s="11" t="inlineStr"/>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>saby.ru/profile/7841469072-783901001</t>
+        </is>
+      </c>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (найден только белорусский номер — под вопросом)</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>595</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
@@ -7075,20 +7087,16 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «ПСК «Реставрация»</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>7839085696</t>
         </is>
       </c>
       <c r="D154" s="13" t="inlineStr"/>
-      <c r="E154" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
-        </is>
-      </c>
+      <c r="E154" s="11" t="inlineStr"/>
       <c r="F154" s="11" t="inlineStr"/>
       <c r="G154" s="11" t="inlineStr">
         <is>
@@ -7097,7 +7105,7 @@
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr">
@@ -7107,7 +7115,7 @@
       </c>
       <c r="J154" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7117,18 +7125,18 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7811659380</t>
         </is>
       </c>
       <c r="D155" s="13" t="inlineStr"/>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
@@ -7139,7 +7147,7 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>607</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
@@ -7159,16 +7167,20 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «ПСТ»</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>7813448257</t>
         </is>
       </c>
       <c r="D156" s="13" t="inlineStr"/>
-      <c r="E156" s="11" t="inlineStr"/>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+        </is>
+      </c>
       <c r="F156" s="11" t="inlineStr"/>
       <c r="G156" s="11" t="inlineStr">
         <is>
@@ -7177,7 +7189,7 @@
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>876</t>
         </is>
       </c>
       <c r="I156" s="10" t="inlineStr">
@@ -7197,12 +7209,12 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЭС»</t>
+          <t>ООО «ПТГ»</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>7814677411</t>
+          <t>5013050270</t>
         </is>
       </c>
       <c r="D157" s="13" t="inlineStr"/>
@@ -7215,7 +7227,7 @@
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
@@ -7225,7 +7237,7 @@
       </c>
       <c r="J157" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7235,12 +7247,12 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПетроТрейд-инжиниринг»</t>
+          <t>ООО «ПЭС»</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>7802490056</t>
+          <t>7814677411</t>
         </is>
       </c>
       <c r="D158" s="13" t="inlineStr"/>
@@ -7253,7 +7265,7 @@
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>654</t>
         </is>
       </c>
       <c r="I158" s="10" t="inlineStr">
@@ -7273,12 +7285,12 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>ООО «Портмарин Инжиниринг»</t>
+          <t>ООО «ПетроТрейд-инжиниринг»</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>7811777680</t>
+          <t>7802490056</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr"/>
@@ -7291,7 +7303,7 @@
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>771</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
@@ -7311,12 +7323,12 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрогрессСтрой»</t>
+          <t>ООО «Портмарин Инжиниринг»</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>7811604013</t>
+          <t>7811777680</t>
         </is>
       </c>
       <c r="D160" s="13" t="inlineStr"/>
@@ -7329,7 +7341,7 @@
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="I160" s="10" t="inlineStr">
@@ -7349,12 +7361,12 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПромИнвест»</t>
+          <t>ООО «ПрогрессСтрой»</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>7841439543</t>
+          <t>7811604013</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr"/>
@@ -7367,7 +7379,7 @@
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
@@ -7387,12 +7399,12 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПромСтрой»</t>
+          <t>ООО «ПромИнвест»</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>7806156944</t>
+          <t>7841439543</t>
         </is>
       </c>
       <c r="D162" s="13" t="inlineStr"/>
@@ -7405,7 +7417,7 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr">
@@ -7425,20 +7437,16 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «ПромСтрой»</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7806156944</t>
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr"/>
-      <c r="E163" s="11" t="inlineStr">
-        <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
-        </is>
-      </c>
+      <c r="E163" s="11" t="inlineStr"/>
       <c r="F163" s="11" t="inlineStr"/>
       <c r="G163" s="11" t="inlineStr">
         <is>
@@ -7447,7 +7455,7 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
@@ -7457,7 +7465,7 @@
       </c>
       <c r="J163" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7467,16 +7475,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстройинжиниринг»</t>
+          <t>ООО «Промстрой»</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
-          <t>7814349756</t>
+          <t>7814656860</t>
         </is>
       </c>
       <c r="D164" s="13" t="inlineStr"/>
-      <c r="E164" s="11" t="inlineStr"/>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+        </is>
+      </c>
       <c r="F164" s="11" t="inlineStr"/>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7485,7 +7497,7 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>516</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr">
@@ -7495,7 +7507,7 @@
       </c>
       <c r="J164" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -7505,12 +7517,12 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрофСтрой-И»</t>
+          <t>ООО «Промстройинжиниринг»</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>7810682530</t>
+          <t>7814349756</t>
         </is>
       </c>
       <c r="D165" s="13" t="inlineStr"/>
@@ -7523,7 +7535,7 @@
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>797</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
@@ -7543,12 +7555,12 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрофСтройАльянс»</t>
+          <t>ООО «ПрофСтрой-И»</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>7842504114</t>
+          <t>7810682530</t>
         </is>
       </c>
       <c r="D166" s="13" t="inlineStr"/>
@@ -7561,7 +7573,7 @@
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I166" s="10" t="inlineStr">
@@ -7581,20 +7593,16 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «ПрофСтройАльянс»</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7842504114</t>
         </is>
       </c>
       <c r="D167" s="13" t="inlineStr"/>
-      <c r="E167" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
-        </is>
-      </c>
+      <c r="E167" s="11" t="inlineStr"/>
       <c r="F167" s="11" t="inlineStr"/>
       <c r="G167" s="11" t="inlineStr">
         <is>
@@ -7603,7 +7611,7 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
@@ -7613,7 +7621,7 @@
       </c>
       <c r="J167" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7623,18 +7631,18 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «Профиль»</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>7802182380</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr"/>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr"/>
@@ -7645,7 +7653,7 @@
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>572</t>
         </is>
       </c>
       <c r="I168" s="10" t="inlineStr">
@@ -7655,7 +7663,7 @@
       </c>
       <c r="J168" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -7665,20 +7673,16 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «РД»</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7810062946</t>
         </is>
       </c>
       <c r="D169" s="13" t="inlineStr"/>
-      <c r="E169" s="11" t="inlineStr">
-        <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
-        </is>
-      </c>
+      <c r="E169" s="11" t="inlineStr"/>
       <c r="F169" s="11" t="inlineStr"/>
       <c r="G169" s="11" t="inlineStr">
         <is>
@@ -7687,7 +7691,7 @@
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>365</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
@@ -7697,7 +7701,7 @@
       </c>
       <c r="J169" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7707,29 +7711,29 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>ООО «РестСтройГрупп»</t>
+          <t>ООО «РЕССТРОЙ»</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>7839099924</t>
+          <t>7820012849</t>
         </is>
       </c>
       <c r="D170" s="13" t="inlineStr"/>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr"/>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>713</t>
         </is>
       </c>
       <c r="I170" s="10" t="inlineStr">
@@ -7749,20 +7753,16 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Алстрой»</t>
+          <t>ООО «РИАРДЕН»</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>7813417675</t>
+          <t>7814794789</t>
         </is>
       </c>
       <c r="D171" s="13" t="inlineStr"/>
-      <c r="E171" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
-        </is>
-      </c>
+      <c r="E171" s="11" t="inlineStr"/>
       <c r="F171" s="11" t="inlineStr"/>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>975</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="J171" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7791,20 +7791,16 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «РК ДЕВЕЛОПМЕНТ»</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7814800834</t>
         </is>
       </c>
       <c r="D172" s="13" t="inlineStr"/>
-      <c r="E172" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
-        </is>
-      </c>
+      <c r="E172" s="11" t="inlineStr"/>
       <c r="F172" s="11" t="inlineStr"/>
       <c r="G172" s="11" t="inlineStr">
         <is>
@@ -7813,7 +7809,7 @@
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>861</t>
         </is>
       </c>
       <c r="I172" s="10" t="inlineStr">
@@ -7823,7 +7819,7 @@
       </c>
       <c r="J172" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7833,18 +7829,18 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7826123721</t>
         </is>
       </c>
       <c r="D173" s="13" t="inlineStr"/>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr"/>
@@ -7855,7 +7851,7 @@
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>515</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
@@ -7865,7 +7861,7 @@
       </c>
       <c r="J173" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7875,20 +7871,16 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «РОНИС»</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7840475549</t>
         </is>
       </c>
       <c r="D174" s="13" t="inlineStr"/>
-      <c r="E174" s="11" t="inlineStr">
-        <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
-        </is>
-      </c>
+      <c r="E174" s="11" t="inlineStr"/>
       <c r="F174" s="11" t="inlineStr"/>
       <c r="G174" s="11" t="inlineStr">
         <is>
@@ -7897,7 +7889,7 @@
       </c>
       <c r="H174" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I174" s="10" t="inlineStr">
@@ -7907,7 +7899,7 @@
       </c>
       <c r="J174" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7917,20 +7909,16 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «РОСТРА северо-запад»</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7805234942</t>
         </is>
       </c>
       <c r="D175" s="13" t="inlineStr"/>
-      <c r="E175" s="11" t="inlineStr">
-        <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
-        </is>
-      </c>
+      <c r="E175" s="11" t="inlineStr"/>
       <c r="F175" s="11" t="inlineStr"/>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -7939,7 +7927,7 @@
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>714</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
@@ -7949,7 +7937,7 @@
       </c>
       <c r="J175" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7959,20 +7947,16 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «РСК «ОРДЕР» (реставрационно-строительная)</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7801585837</t>
         </is>
       </c>
       <c r="D176" s="13" t="inlineStr"/>
-      <c r="E176" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
-        </is>
-      </c>
+      <c r="E176" s="11" t="inlineStr"/>
       <c r="F176" s="11" t="inlineStr"/>
       <c r="G176" s="11" t="inlineStr">
         <is>
@@ -7981,7 +7965,7 @@
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>603</t>
         </is>
       </c>
       <c r="I176" s="10" t="inlineStr">
@@ -7991,7 +7975,7 @@
       </c>
       <c r="J176" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8001,20 +7985,16 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «РСК «ТехноСтрой»</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7838061420</t>
         </is>
       </c>
       <c r="D177" s="13" t="inlineStr"/>
-      <c r="E177" s="11" t="inlineStr">
-        <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
-        </is>
-      </c>
+      <c r="E177" s="11" t="inlineStr"/>
       <c r="F177" s="11" t="inlineStr"/>
       <c r="G177" s="11" t="inlineStr">
         <is>
@@ -8023,7 +8003,7 @@
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
@@ -8033,7 +8013,7 @@
       </c>
       <c r="J177" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8043,20 +8023,16 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «РСУ-9»</t>
         </is>
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7814785030</t>
         </is>
       </c>
       <c r="D178" s="13" t="inlineStr"/>
-      <c r="E178" s="11" t="inlineStr">
-        <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
-        </is>
-      </c>
+      <c r="E178" s="11" t="inlineStr"/>
       <c r="F178" s="11" t="inlineStr"/>
       <c r="G178" s="11" t="inlineStr">
         <is>
@@ -8065,7 +8041,7 @@
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>799</t>
         </is>
       </c>
       <c r="I178" s="10" t="inlineStr">
@@ -8075,7 +8051,7 @@
       </c>
       <c r="J178" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8085,29 +8061,29 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «РСФ «Водолей плюс»</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7826040578</t>
         </is>
       </c>
       <c r="D179" s="13" t="inlineStr"/>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+          <t>СПб, Б.Сампсониевский пр. 60И; ОГРН 1027810321659; ген.дир. Колосовская П.В.</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr"/>
       <c r="G179" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>582</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
@@ -8117,7 +8093,7 @@
       </c>
       <c r="J179" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8127,29 +8103,29 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «РестСтройГрупп»</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7839099924</t>
         </is>
       </c>
       <c r="D180" s="13" t="inlineStr"/>
       <c r="E180" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
         </is>
       </c>
       <c r="F180" s="11" t="inlineStr"/>
       <c r="G180" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H180" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>673</t>
         </is>
       </c>
       <c r="I180" s="10" t="inlineStr">
@@ -8169,29 +8145,25 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй центр»</t>
+          <t>ООО «СВМ - Групп»</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>7804538240</t>
+          <t>7843014240</t>
         </is>
       </c>
       <c r="D181" s="13" t="inlineStr"/>
-      <c r="E181" s="11" t="inlineStr">
-        <is>
-          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
-        </is>
-      </c>
+      <c r="E181" s="11" t="inlineStr"/>
       <c r="F181" s="11" t="inlineStr"/>
       <c r="G181" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
@@ -8201,7 +8173,7 @@
       </c>
       <c r="J181" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8211,12 +8183,12 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «СДК Лидер-Строй»</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7806299036</t>
         </is>
       </c>
       <c r="D182" s="13" t="inlineStr"/>
@@ -8229,7 +8201,7 @@
       </c>
       <c r="H182" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="I182" s="10" t="inlineStr">
@@ -8239,7 +8211,7 @@
       </c>
       <c r="J182" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8249,20 +8221,16 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «СЗ «Загородная, 71»</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7817328112</t>
         </is>
       </c>
       <c r="D183" s="13" t="inlineStr"/>
-      <c r="E183" s="11" t="inlineStr">
-        <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
-        </is>
-      </c>
+      <c r="E183" s="11" t="inlineStr"/>
       <c r="F183" s="11" t="inlineStr"/>
       <c r="G183" s="11" t="inlineStr">
         <is>
@@ -8271,7 +8239,7 @@
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr">
@@ -8281,7 +8249,7 @@
       </c>
       <c r="J183" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8291,29 +8259,29 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕЗИС»</t>
+          <t>ООО «СК «Алстрой»</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>7804441209</t>
+          <t>7813417675</t>
         </is>
       </c>
       <c r="D184" s="13" t="inlineStr"/>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr"/>
       <c r="G184" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>590</t>
         </is>
       </c>
       <c r="I184" s="10" t="inlineStr">
@@ -8323,7 +8291,7 @@
       </c>
       <c r="J184" s="10" t="inlineStr">
         <is>
-          <t>700000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -8333,20 +8301,16 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «СК «Орион»</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7816699026</t>
         </is>
       </c>
       <c r="D185" s="13" t="inlineStr"/>
-      <c r="E185" s="11" t="inlineStr">
-        <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
-        </is>
-      </c>
+      <c r="E185" s="11" t="inlineStr"/>
       <c r="F185" s="11" t="inlineStr"/>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8355,7 +8319,7 @@
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>969</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr">
@@ -8365,7 +8329,7 @@
       </c>
       <c r="J185" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8375,18 +8339,18 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «СК «Потенциал»</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7814558855</t>
         </is>
       </c>
       <c r="D186" s="13" t="inlineStr"/>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr"/>
@@ -8397,7 +8361,7 @@
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>675</t>
         </is>
       </c>
       <c r="I186" s="10" t="inlineStr">
@@ -8407,7 +8371,7 @@
       </c>
       <c r="J186" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>1700000</t>
         </is>
       </c>
     </row>
@@ -8417,20 +8381,16 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «СК «СтальСтрой»</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7841052031</t>
         </is>
       </c>
       <c r="D187" s="13" t="inlineStr"/>
-      <c r="E187" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
-        </is>
-      </c>
+      <c r="E187" s="11" t="inlineStr"/>
       <c r="F187" s="11" t="inlineStr"/>
       <c r="G187" s="11" t="inlineStr">
         <is>
@@ -8439,7 +8399,7 @@
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>439</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr">
@@ -8449,7 +8409,7 @@
       </c>
       <c r="J187" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8459,20 +8419,16 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «СК «Стройнорд»</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>7811571992</t>
         </is>
       </c>
       <c r="D188" s="13" t="inlineStr"/>
-      <c r="E188" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
-        </is>
-      </c>
+      <c r="E188" s="11" t="inlineStr"/>
       <c r="F188" s="11" t="inlineStr"/>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8481,7 +8437,7 @@
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>549</t>
         </is>
       </c>
       <c r="I188" s="10" t="inlineStr">
@@ -8491,7 +8447,7 @@
       </c>
       <c r="J188" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8501,18 +8457,18 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «СК Гарант»</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7806380022</t>
         </is>
       </c>
       <c r="D189" s="13" t="inlineStr"/>
       <c r="E189" s="11" t="inlineStr">
         <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
         </is>
       </c>
       <c r="F189" s="11" t="inlineStr"/>
@@ -8523,7 +8479,7 @@
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I189" s="10" t="inlineStr">
@@ -8533,7 +8489,7 @@
       </c>
       <c r="J189" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -8543,29 +8499,25 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «СК Меркурий»</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7819046339</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr"/>
-      <c r="E190" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
-        </is>
-      </c>
+      <c r="E190" s="11" t="inlineStr"/>
       <c r="F190" s="11" t="inlineStr"/>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>983</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr">
@@ -8575,7 +8527,7 @@
       </c>
       <c r="J190" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8585,18 +8537,18 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «СК ПСП»</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7810502379</t>
         </is>
       </c>
       <c r="D191" s="13" t="inlineStr"/>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr"/>
@@ -8607,7 +8559,7 @@
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>527</t>
         </is>
       </c>
       <c r="I191" s="10" t="inlineStr">
@@ -8617,7 +8569,7 @@
       </c>
       <c r="J191" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8627,20 +8579,16 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «СК Профиль групп»</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>7802593414</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr"/>
-      <c r="E192" s="11" t="inlineStr">
-        <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
-        </is>
-      </c>
+      <c r="E192" s="11" t="inlineStr"/>
       <c r="F192" s="11" t="inlineStr"/>
       <c r="G192" s="11" t="inlineStr">
         <is>
@@ -8649,7 +8597,7 @@
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>576</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr">
@@ -8659,7 +8607,7 @@
       </c>
       <c r="J192" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8669,44 +8617,1340 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «СК СФЕРА»</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>9715445653</t>
         </is>
       </c>
       <c r="D193" s="13" t="inlineStr"/>
-      <c r="E193" s="11" t="inlineStr">
-        <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
-        </is>
-      </c>
+      <c r="E193" s="11" t="inlineStr"/>
       <c r="F193" s="11" t="inlineStr"/>
       <c r="G193" s="11" t="inlineStr">
         <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H193" s="10" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="I193" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J193" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СК ТТ»</t>
+        </is>
+      </c>
+      <c r="C194" s="12" t="inlineStr">
+        <is>
+          <t>7813676373</t>
+        </is>
+      </c>
+      <c r="D194" s="13" t="inlineStr"/>
+      <c r="E194" s="11" t="inlineStr"/>
+      <c r="F194" s="11" t="inlineStr"/>
+      <c r="G194" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H194" s="10" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="I194" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J194" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СКМ»</t>
+        </is>
+      </c>
+      <c r="C195" s="12" t="inlineStr">
+        <is>
+          <t>7807239583</t>
+        </is>
+      </c>
+      <c r="D195" s="13" t="inlineStr"/>
+      <c r="E195" s="11" t="inlineStr"/>
+      <c r="F195" s="11" t="inlineStr"/>
+      <c r="G195" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H195" s="10" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I195" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J195" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СКН НВК»</t>
+        </is>
+      </c>
+      <c r="C196" s="12" t="inlineStr">
+        <is>
+          <t>7838057216</t>
+        </is>
+      </c>
+      <c r="D196" s="13" t="inlineStr"/>
+      <c r="E196" s="11" t="inlineStr"/>
+      <c r="F196" s="11" t="inlineStr"/>
+      <c r="G196" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H196" s="10" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="I196" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J196" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="10" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СКП»</t>
+        </is>
+      </c>
+      <c r="C197" s="12" t="inlineStr">
+        <is>
+          <t>7806619896</t>
+        </is>
+      </c>
+      <c r="D197" s="13" t="inlineStr"/>
+      <c r="E197" s="11" t="inlineStr"/>
+      <c r="F197" s="11" t="inlineStr"/>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H197" s="10" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="I197" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J197" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СПбЭК-Майнинг»</t>
+        </is>
+      </c>
+      <c r="C198" s="12" t="inlineStr">
+        <is>
+          <t>7820326027</t>
+        </is>
+      </c>
+      <c r="D198" s="13" t="inlineStr"/>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr"/>
+      <c r="G198" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H198" s="10" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="I198" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J198" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr">
+        <is>
+          <t>7825055370</t>
+        </is>
+      </c>
+      <c r="D199" s="13" t="inlineStr"/>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="inlineStr"/>
+      <c r="G199" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H199" s="10" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="I199" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J199" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУ-17»</t>
+        </is>
+      </c>
+      <c r="C200" s="12" t="inlineStr">
+        <is>
+          <t>7807028906</t>
+        </is>
+      </c>
+      <c r="D200" s="13" t="inlineStr"/>
+      <c r="E200" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
+      <c r="F200" s="11" t="inlineStr"/>
+      <c r="G200" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H200" s="10" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="I200" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J200" s="10" t="inlineStr">
+        <is>
+          <t>2300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СУАР-Групп»</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>7802270195</t>
+        </is>
+      </c>
+      <c r="D201" s="13" t="inlineStr"/>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
+      <c r="F201" s="11" t="inlineStr"/>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H201" s="10" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="I201" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J201" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="10" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СЭМ»</t>
+        </is>
+      </c>
+      <c r="C202" s="12" t="inlineStr">
+        <is>
+          <t>7810201646</t>
+        </is>
+      </c>
+      <c r="D202" s="13" t="inlineStr"/>
+      <c r="E202" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
+      <c r="F202" s="11" t="inlineStr"/>
+      <c r="G202" s="11" t="inlineStr">
+        <is>
           <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
-      <c r="H193" s="10" t="inlineStr">
+      <c r="H202" s="10" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I202" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J202" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="10" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СиФ»</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr">
+        <is>
+          <t>7801075307</t>
+        </is>
+      </c>
+      <c r="D203" s="13" t="inlineStr"/>
+      <c r="E203" s="11" t="inlineStr">
+        <is>
+          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
+        </is>
+      </c>
+      <c r="F203" s="11" t="inlineStr"/>
+      <c r="G203" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H203" s="10" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="I203" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J203" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="10" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="inlineStr">
+        <is>
+          <t>7810691246</t>
+        </is>
+      </c>
+      <c r="D204" s="13" t="inlineStr"/>
+      <c r="E204" s="11" t="inlineStr"/>
+      <c r="F204" s="11" t="inlineStr"/>
+      <c r="G204" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H204" s="10" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I204" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J204" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="10" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Синергия»</t>
+        </is>
+      </c>
+      <c r="C205" s="12" t="inlineStr">
+        <is>
+          <t>7841100278</t>
+        </is>
+      </c>
+      <c r="D205" s="13" t="inlineStr"/>
+      <c r="E205" s="11" t="inlineStr"/>
+      <c r="F205" s="11" t="inlineStr"/>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H205" s="10" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="I205" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J205" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СносСтройИнвест»</t>
+        </is>
+      </c>
+      <c r="C206" s="12" t="inlineStr">
+        <is>
+          <t>7805239355</t>
+        </is>
+      </c>
+      <c r="D206" s="13" t="inlineStr"/>
+      <c r="E206" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
+        </is>
+      </c>
+      <c r="F206" s="11" t="inlineStr"/>
+      <c r="G206" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H206" s="10" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="I206" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J206" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="10" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СпецСтрой»</t>
+        </is>
+      </c>
+      <c r="C207" s="12" t="inlineStr">
+        <is>
+          <t>7802753883</t>
+        </is>
+      </c>
+      <c r="D207" s="13" t="inlineStr"/>
+      <c r="E207" s="11" t="inlineStr"/>
+      <c r="F207" s="11" t="inlineStr"/>
+      <c r="G207" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H207" s="10" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="I207" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J207" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="10" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Спецстроймонтаж»</t>
+        </is>
+      </c>
+      <c r="C208" s="12" t="inlineStr">
+        <is>
+          <t>7826156798</t>
+        </is>
+      </c>
+      <c r="D208" s="13" t="inlineStr"/>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
+        </is>
+      </c>
+      <c r="F208" s="11" t="inlineStr"/>
+      <c r="G208" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H208" s="10" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="I208" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J208" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="10" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строительная компания «ДМ»</t>
+        </is>
+      </c>
+      <c r="C209" s="12" t="inlineStr">
+        <is>
+          <t>4703058442</t>
+        </is>
+      </c>
+      <c r="D209" s="13" t="inlineStr"/>
+      <c r="E209" s="11" t="inlineStr"/>
+      <c r="F209" s="11" t="inlineStr"/>
+      <c r="G209" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H209" s="10" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="I209" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J209" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="10" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строительные технологии»</t>
+        </is>
+      </c>
+      <c r="C210" s="12" t="inlineStr">
+        <is>
+          <t>7813680179</t>
+        </is>
+      </c>
+      <c r="D210" s="13" t="inlineStr"/>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+        </is>
+      </c>
+      <c r="F210" s="11" t="inlineStr"/>
+      <c r="G210" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H210" s="10" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I210" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J210" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="10" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Строй центр»</t>
+        </is>
+      </c>
+      <c r="C211" s="12" t="inlineStr">
+        <is>
+          <t>7804538240</t>
+        </is>
+      </c>
+      <c r="D211" s="13" t="inlineStr"/>
+      <c r="E211" s="11" t="inlineStr">
+        <is>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+        </is>
+      </c>
+      <c r="F211" s="11" t="inlineStr"/>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H211" s="10" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="I211" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J211" s="10" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="10" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СтройГрад»</t>
+        </is>
+      </c>
+      <c r="C212" s="12" t="inlineStr">
+        <is>
+          <t>7813692632</t>
+        </is>
+      </c>
+      <c r="D212" s="13" t="inlineStr"/>
+      <c r="E212" s="11" t="inlineStr"/>
+      <c r="F212" s="11" t="inlineStr"/>
+      <c r="G212" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H212" s="10" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="I212" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J212" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="10" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Сфера»</t>
+        </is>
+      </c>
+      <c r="C213" s="12" t="inlineStr">
+        <is>
+          <t>2311308786</t>
+        </is>
+      </c>
+      <c r="D213" s="13" t="inlineStr"/>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="inlineStr"/>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H213" s="10" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="I213" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J213" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЕЗИС»</t>
+        </is>
+      </c>
+      <c r="C214" s="12" t="inlineStr">
+        <is>
+          <t>7804441209</t>
+        </is>
+      </c>
+      <c r="D214" s="13" t="inlineStr"/>
+      <c r="E214" s="11" t="inlineStr">
+        <is>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+        </is>
+      </c>
+      <c r="F214" s="11" t="inlineStr"/>
+      <c r="G214" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H214" s="10" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I214" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J214" s="10" t="inlineStr">
+        <is>
+          <t>700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="10" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
+        </is>
+      </c>
+      <c r="C215" s="12" t="inlineStr">
+        <is>
+          <t>7814612968</t>
+        </is>
+      </c>
+      <c r="D215" s="13" t="inlineStr"/>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
+      <c r="F215" s="11" t="inlineStr"/>
+      <c r="G215" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H215" s="10" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="I215" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J215" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="10" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+        </is>
+      </c>
+      <c r="C216" s="12" t="inlineStr">
+        <is>
+          <t>7839061021</t>
+        </is>
+      </c>
+      <c r="D216" s="13" t="inlineStr"/>
+      <c r="E216" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
+      <c r="F216" s="11" t="inlineStr"/>
+      <c r="G216" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H216" s="10" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="I216" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J216" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="10" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Трамплин-строй»</t>
+        </is>
+      </c>
+      <c r="C217" s="12" t="inlineStr">
+        <is>
+          <t>7802207193</t>
+        </is>
+      </c>
+      <c r="D217" s="13" t="inlineStr"/>
+      <c r="E217" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+        </is>
+      </c>
+      <c r="F217" s="11" t="inlineStr"/>
+      <c r="G217" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H217" s="10" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="I217" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J217" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C218" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D218" s="13" t="inlineStr"/>
+      <c r="E218" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F218" s="11" t="inlineStr"/>
+      <c r="G218" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H218" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I218" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J218" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C219" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D219" s="13" t="inlineStr"/>
+      <c r="E219" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F219" s="11" t="inlineStr"/>
+      <c r="G219" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H219" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I219" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J219" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="10" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C220" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D220" s="13" t="inlineStr"/>
+      <c r="E220" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F220" s="11" t="inlineStr"/>
+      <c r="G220" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H220" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I220" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J220" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="10" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C221" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D221" s="13" t="inlineStr"/>
+      <c r="E221" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F221" s="11" t="inlineStr"/>
+      <c r="G221" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H221" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I221" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J221" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="10" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C222" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D222" s="13" t="inlineStr"/>
+      <c r="E222" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F222" s="11" t="inlineStr"/>
+      <c r="G222" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H222" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I222" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J222" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="10" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C223" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D223" s="13" t="inlineStr"/>
+      <c r="E223" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F223" s="11" t="inlineStr"/>
+      <c r="G223" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H223" s="10" t="inlineStr">
         <is>
           <t>142</t>
         </is>
       </c>
-      <c r="I193" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J193" s="10" t="inlineStr">
+      <c r="I223" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J223" s="10" t="inlineStr">
         <is>
           <t>2000000</t>
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="10" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="11" t="inlineStr">
+        <is>
+          <t>ООО ПСМ «Спутник»</t>
+        </is>
+      </c>
+      <c r="C224" s="12" t="inlineStr">
+        <is>
+          <t>7810765071</t>
+        </is>
+      </c>
+      <c r="D224" s="13" t="inlineStr"/>
+      <c r="E224" s="11" t="inlineStr"/>
+      <c r="F224" s="11" t="inlineStr"/>
+      <c r="G224" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H224" s="10" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="I224" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J224" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="10" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="11" t="inlineStr">
+        <is>
+          <t>ООО СК «Аврора-Строй»</t>
+        </is>
+      </c>
+      <c r="C225" s="12" t="inlineStr">
+        <is>
+          <t>7801700173</t>
+        </is>
+      </c>
+      <c r="D225" s="13" t="inlineStr"/>
+      <c r="E225" s="11" t="inlineStr"/>
+      <c r="F225" s="11" t="inlineStr"/>
+      <c r="G225" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H225" s="10" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="I225" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J225" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J193"/>
+  <autoFilter ref="A1:J225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8789,7 +10033,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
@@ -8799,7 +10043,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -8809,7 +10053,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>155</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$249</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J225"/>
+  <dimension ref="A1:J249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8183,12 +8183,12 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>ООО «СДК Лидер-Строй»</t>
+          <t>ООО «СГИ»</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>7806299036</t>
+          <t>7816654829</t>
         </is>
       </c>
       <c r="D182" s="13" t="inlineStr"/>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="H182" s="10" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="I182" s="10" t="inlineStr">
@@ -8221,12 +8221,12 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЗ «Загородная, 71»</t>
+          <t>ООО «СДК Лидер-Строй»</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>7817328112</t>
+          <t>7806299036</t>
         </is>
       </c>
       <c r="D183" s="13" t="inlineStr"/>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr">
@@ -8259,20 +8259,16 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Алстрой»</t>
+          <t>ООО «СЗ «Загородная, 71»</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>7813417675</t>
+          <t>7817328112</t>
         </is>
       </c>
       <c r="D184" s="13" t="inlineStr"/>
-      <c r="E184" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
-        </is>
-      </c>
+      <c r="E184" s="11" t="inlineStr"/>
       <c r="F184" s="11" t="inlineStr"/>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8281,7 +8277,7 @@
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="I184" s="10" t="inlineStr">
@@ -8291,7 +8287,7 @@
       </c>
       <c r="J184" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8301,16 +8297,20 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Орион»</t>
+          <t>ООО «СК «Алстрой»</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>7816699026</t>
+          <t>7813417675</t>
         </is>
       </c>
       <c r="D185" s="13" t="inlineStr"/>
-      <c r="E185" s="11" t="inlineStr"/>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+        </is>
+      </c>
       <c r="F185" s="11" t="inlineStr"/>
       <c r="G185" s="11" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>590</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="J185" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -8339,20 +8339,16 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «СК «Орион»</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7816699026</t>
         </is>
       </c>
       <c r="D186" s="13" t="inlineStr"/>
-      <c r="E186" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
-        </is>
-      </c>
+      <c r="E186" s="11" t="inlineStr"/>
       <c r="F186" s="11" t="inlineStr"/>
       <c r="G186" s="11" t="inlineStr">
         <is>
@@ -8361,7 +8357,7 @@
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>969</t>
         </is>
       </c>
       <c r="I186" s="10" t="inlineStr">
@@ -8371,7 +8367,7 @@
       </c>
       <c r="J186" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8381,16 +8377,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «СтальСтрой»</t>
+          <t>ООО «СК «Потенциал»</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>7841052031</t>
+          <t>7814558855</t>
         </is>
       </c>
       <c r="D187" s="13" t="inlineStr"/>
-      <c r="E187" s="11" t="inlineStr"/>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
       <c r="F187" s="11" t="inlineStr"/>
       <c r="G187" s="11" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>675</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="J187" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1700000</t>
         </is>
       </c>
     </row>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Стройнорд»</t>
+          <t>ООО «СК «СтальСтрой»</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>7811571992</t>
+          <t>7841052031</t>
         </is>
       </c>
       <c r="D188" s="13" t="inlineStr"/>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>439</t>
         </is>
       </c>
       <c r="I188" s="10" t="inlineStr">
@@ -8457,20 +8457,16 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «СК «Стройнорд»</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7811571992</t>
         </is>
       </c>
       <c r="D189" s="13" t="inlineStr"/>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
-        </is>
-      </c>
+      <c r="E189" s="11" t="inlineStr"/>
       <c r="F189" s="11" t="inlineStr"/>
       <c r="G189" s="11" t="inlineStr">
         <is>
@@ -8479,7 +8475,7 @@
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>549</t>
         </is>
       </c>
       <c r="I189" s="10" t="inlineStr">
@@ -8489,7 +8485,7 @@
       </c>
       <c r="J189" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8499,16 +8495,20 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Меркурий»</t>
+          <t>ООО «СК Гарант»</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>7819046339</t>
+          <t>7806380022</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr"/>
-      <c r="E190" s="11" t="inlineStr"/>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+        </is>
+      </c>
       <c r="F190" s="11" t="inlineStr"/>
       <c r="G190" s="11" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="J190" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -8537,20 +8537,16 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «СК Меркурий»</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7819046339</t>
         </is>
       </c>
       <c r="D191" s="13" t="inlineStr"/>
-      <c r="E191" s="11" t="inlineStr">
-        <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
-        </is>
-      </c>
+      <c r="E191" s="11" t="inlineStr"/>
       <c r="F191" s="11" t="inlineStr"/>
       <c r="G191" s="11" t="inlineStr">
         <is>
@@ -8559,7 +8555,7 @@
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>983</t>
         </is>
       </c>
       <c r="I191" s="10" t="inlineStr">
@@ -8569,7 +8565,7 @@
       </c>
       <c r="J191" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8579,16 +8575,20 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Профиль групп»</t>
+          <t>ООО «СК ПСП»</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>7802593414</t>
+          <t>7810502379</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr"/>
-      <c r="E192" s="11" t="inlineStr"/>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+        </is>
+      </c>
       <c r="F192" s="11" t="inlineStr"/>
       <c r="G192" s="11" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>527</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="J192" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8617,12 +8617,12 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК СФЕРА»</t>
+          <t>ООО «СК Профиль групп»</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>9715445653</t>
+          <t>7802593414</t>
         </is>
       </c>
       <c r="D193" s="13" t="inlineStr"/>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>576</t>
         </is>
       </c>
       <c r="I193" s="10" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ТТ»</t>
+          <t>ООО «СК СФЕРА»</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>7813676373</t>
+          <t>9715445653</t>
         </is>
       </c>
       <c r="D194" s="13" t="inlineStr"/>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="H194" s="10" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="I194" s="10" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКМ»</t>
+          <t>ООО «СК ТТ»</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>7807239583</t>
+          <t>7813676373</t>
         </is>
       </c>
       <c r="D195" s="13" t="inlineStr"/>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="H195" s="10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="I195" s="10" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКН НВК»</t>
+          <t>ООО «СКМ»</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>7838057216</t>
+          <t>7807239583</t>
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr"/>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I196" s="10" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКП»</t>
+          <t>ООО «СКН НВК»</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>7806619896</t>
+          <t>7838057216</t>
         </is>
       </c>
       <c r="D197" s="13" t="inlineStr"/>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>629</t>
         </is>
       </c>
       <c r="I197" s="10" t="inlineStr">
@@ -8807,20 +8807,16 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «СКП»</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7806619896</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr"/>
-      <c r="E198" s="11" t="inlineStr">
-        <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
-        </is>
-      </c>
+      <c r="E198" s="11" t="inlineStr"/>
       <c r="F198" s="11" t="inlineStr"/>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -8829,7 +8825,7 @@
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="I198" s="10" t="inlineStr">
@@ -8839,7 +8835,7 @@
       </c>
       <c r="J198" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8849,20 +8845,16 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «СМУ 8»</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7810531355</t>
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr"/>
-      <c r="E199" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
-        </is>
-      </c>
+      <c r="E199" s="11" t="inlineStr"/>
       <c r="F199" s="11" t="inlineStr"/>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -8871,7 +8863,7 @@
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>367</t>
         </is>
       </c>
       <c r="I199" s="10" t="inlineStr">
@@ -8881,7 +8873,7 @@
       </c>
       <c r="J199" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8891,18 +8883,18 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «СПбЭК-Майнинг»</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7820326027</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr"/>
       <c r="E200" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
         </is>
       </c>
       <c r="F200" s="11" t="inlineStr"/>
@@ -8913,7 +8905,7 @@
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>548</t>
         </is>
       </c>
       <c r="I200" s="10" t="inlineStr">
@@ -8923,7 +8915,7 @@
       </c>
       <c r="J200" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8933,20 +8925,16 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «СТРОЙ КОРПУС»</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7804553054</t>
         </is>
       </c>
       <c r="D201" s="13" t="inlineStr"/>
-      <c r="E201" s="11" t="inlineStr">
-        <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
-        </is>
-      </c>
+      <c r="E201" s="11" t="inlineStr"/>
       <c r="F201" s="11" t="inlineStr"/>
       <c r="G201" s="11" t="inlineStr">
         <is>
@@ -8955,7 +8943,7 @@
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>679</t>
         </is>
       </c>
       <c r="I201" s="10" t="inlineStr">
@@ -8965,7 +8953,7 @@
       </c>
       <c r="J201" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8975,29 +8963,25 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «СТРОЙГРАД РСУ»</t>
         </is>
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7802703995</t>
         </is>
       </c>
       <c r="D202" s="13" t="inlineStr"/>
-      <c r="E202" s="11" t="inlineStr">
-        <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
-        </is>
-      </c>
+      <c r="E202" s="11" t="inlineStr"/>
       <c r="F202" s="11" t="inlineStr"/>
       <c r="G202" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>877</t>
         </is>
       </c>
       <c r="I202" s="10" t="inlineStr">
@@ -9007,7 +8991,7 @@
       </c>
       <c r="J202" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9017,29 +9001,29 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>ООО «СиФ»</t>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>7801075307</t>
+          <t>7825055370</t>
         </is>
       </c>
       <c r="D203" s="13" t="inlineStr"/>
       <c r="E203" s="11" t="inlineStr">
         <is>
-          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
         </is>
       </c>
       <c r="F203" s="11" t="inlineStr"/>
       <c r="G203" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>573</t>
         </is>
       </c>
       <c r="I203" s="10" t="inlineStr">
@@ -9049,7 +9033,7 @@
       </c>
       <c r="J203" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -9059,16 +9043,20 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
+          <t>ООО «СУ-17»</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>7810691246</t>
+          <t>7807028906</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr"/>
-      <c r="E204" s="11" t="inlineStr"/>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
       <c r="F204" s="11" t="inlineStr"/>
       <c r="G204" s="11" t="inlineStr">
         <is>
@@ -9077,7 +9065,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>747</t>
         </is>
       </c>
       <c r="I204" s="10" t="inlineStr">
@@ -9087,7 +9075,7 @@
       </c>
       <c r="J204" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2300000</t>
         </is>
       </c>
     </row>
@@ -9097,16 +9085,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>ООО «Синергия»</t>
+          <t>ООО «СУАР-Групп»</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>7841100278</t>
+          <t>7802270195</t>
         </is>
       </c>
       <c r="D205" s="13" t="inlineStr"/>
-      <c r="E205" s="11" t="inlineStr"/>
+      <c r="E205" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
       <c r="F205" s="11" t="inlineStr"/>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9115,7 +9107,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>518</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr">
@@ -9125,7 +9117,7 @@
       </c>
       <c r="J205" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -9135,29 +9127,29 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>ООО «СносСтройИнвест»</t>
+          <t>ООО «СФ «Новэк»</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>7805239355</t>
+          <t>7825128540</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr"/>
       <c r="E206" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
+          <t>194352 СПб, ул.Кустодиева 17А; ОГРН 1027809227907; ген.дир. Смирнов Д.И.</t>
         </is>
       </c>
       <c r="F206" s="11" t="inlineStr"/>
       <c r="G206" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>512</t>
         </is>
       </c>
       <c r="I206" s="10" t="inlineStr">
@@ -9177,25 +9169,29 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>ООО «СпецСтрой»</t>
+          <t>ООО «СЭМ»</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>7802753883</t>
+          <t>7810201646</t>
         </is>
       </c>
       <c r="D207" s="13" t="inlineStr"/>
-      <c r="E207" s="11" t="inlineStr"/>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
       <c r="F207" s="11" t="inlineStr"/>
       <c r="G207" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>700</t>
         </is>
       </c>
       <c r="I207" s="10" t="inlineStr">
@@ -9205,7 +9201,7 @@
       </c>
       <c r="J207" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -9215,29 +9211,29 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецстроймонтаж»</t>
+          <t>ООО «СиФ»</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>7826156798</t>
+          <t>7801075307</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr"/>
       <c r="E208" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
+          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
         </is>
       </c>
       <c r="F208" s="11" t="inlineStr"/>
       <c r="G208" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H208" s="10" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I208" s="10" t="inlineStr">
@@ -9257,12 +9253,12 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительная компания «ДМ»</t>
+          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>4703058442</t>
+          <t>7810691246</t>
         </is>
       </c>
       <c r="D209" s="13" t="inlineStr"/>
@@ -9275,7 +9271,7 @@
       </c>
       <c r="H209" s="10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>588</t>
         </is>
       </c>
       <c r="I209" s="10" t="inlineStr">
@@ -9295,20 +9291,16 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «Синергия»</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7841100278</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr"/>
-      <c r="E210" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
-        </is>
-      </c>
+      <c r="E210" s="11" t="inlineStr"/>
       <c r="F210" s="11" t="inlineStr"/>
       <c r="G210" s="11" t="inlineStr">
         <is>
@@ -9317,7 +9309,7 @@
       </c>
       <c r="H210" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="I210" s="10" t="inlineStr">
@@ -9327,7 +9319,7 @@
       </c>
       <c r="J210" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9337,18 +9329,18 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй центр»</t>
+          <t>ООО «СносСтройИнвест»</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>7804538240</t>
+          <t>7805239355</t>
         </is>
       </c>
       <c r="D211" s="13" t="inlineStr"/>
       <c r="E211" s="11" t="inlineStr">
         <is>
-          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
         </is>
       </c>
       <c r="F211" s="11" t="inlineStr"/>
@@ -9359,7 +9351,7 @@
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>351</t>
         </is>
       </c>
       <c r="I211" s="10" t="inlineStr">
@@ -9369,7 +9361,7 @@
       </c>
       <c r="J211" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9379,12 +9371,12 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «СпецСтрой»</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7802753883</t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr"/>
@@ -9397,7 +9389,7 @@
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>267</t>
         </is>
       </c>
       <c r="I212" s="10" t="inlineStr">
@@ -9407,7 +9399,7 @@
       </c>
       <c r="J212" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9417,18 +9409,18 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «Спецстроймонтаж»</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7826156798</t>
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr"/>
       <c r="E213" s="11" t="inlineStr">
         <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
         </is>
       </c>
       <c r="F213" s="11" t="inlineStr"/>
@@ -9439,7 +9431,7 @@
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>505</t>
         </is>
       </c>
       <c r="I213" s="10" t="inlineStr">
@@ -9449,7 +9441,7 @@
       </c>
       <c r="J213" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9459,29 +9451,25 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕЗИС»</t>
+          <t>ООО «Строительная компания «ДМ»</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>7804441209</t>
+          <t>4703058442</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr"/>
-      <c r="E214" s="11" t="inlineStr">
-        <is>
-          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
-        </is>
-      </c>
+      <c r="E214" s="11" t="inlineStr"/>
       <c r="F214" s="11" t="inlineStr"/>
       <c r="G214" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>252</t>
         </is>
       </c>
       <c r="I214" s="10" t="inlineStr">
@@ -9491,7 +9479,7 @@
       </c>
       <c r="J214" s="10" t="inlineStr">
         <is>
-          <t>700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9501,20 +9489,16 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «Строительное дело-СГ»</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7826005559</t>
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr"/>
-      <c r="E215" s="11" t="inlineStr">
-        <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
-        </is>
-      </c>
+      <c r="E215" s="11" t="inlineStr"/>
       <c r="F215" s="11" t="inlineStr"/>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -9523,7 +9507,7 @@
       </c>
       <c r="H215" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>242</t>
         </is>
       </c>
       <c r="I215" s="10" t="inlineStr">
@@ -9533,7 +9517,7 @@
       </c>
       <c r="J215" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9543,20 +9527,16 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «Строительные решения»</t>
         </is>
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7840099703</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr"/>
-      <c r="E216" s="11" t="inlineStr">
-        <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
-        </is>
-      </c>
+      <c r="E216" s="11" t="inlineStr"/>
       <c r="F216" s="11" t="inlineStr"/>
       <c r="G216" s="11" t="inlineStr">
         <is>
@@ -9565,7 +9545,7 @@
       </c>
       <c r="H216" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="I216" s="10" t="inlineStr">
@@ -9575,7 +9555,7 @@
       </c>
       <c r="J216" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9585,18 +9565,18 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7813680179</t>
         </is>
       </c>
       <c r="D217" s="13" t="inlineStr"/>
       <c r="E217" s="11" t="inlineStr">
         <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
         </is>
       </c>
       <c r="F217" s="11" t="inlineStr"/>
@@ -9607,7 +9587,7 @@
       </c>
       <c r="H217" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="I217" s="10" t="inlineStr">
@@ -9617,7 +9597,7 @@
       </c>
       <c r="J217" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9607,16 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>7802880338</t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr"/>
-      <c r="E218" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
-        </is>
-      </c>
+      <c r="E218" s="11" t="inlineStr"/>
       <c r="F218" s="11" t="inlineStr"/>
       <c r="G218" s="11" t="inlineStr">
         <is>
@@ -9649,7 +9625,7 @@
       </c>
       <c r="H218" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>239</t>
         </is>
       </c>
       <c r="I218" s="10" t="inlineStr">
@@ -9659,7 +9635,7 @@
       </c>
       <c r="J218" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9669,29 +9645,29 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «Строй центр»</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7804538240</t>
         </is>
       </c>
       <c r="D219" s="13" t="inlineStr"/>
       <c r="E219" s="11" t="inlineStr">
         <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
         </is>
       </c>
       <c r="F219" s="11" t="inlineStr"/>
       <c r="G219" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H219" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>732</t>
         </is>
       </c>
       <c r="I219" s="10" t="inlineStr">
@@ -9701,7 +9677,7 @@
       </c>
       <c r="J219" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -9711,29 +9687,25 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «Строй-Импульс»</t>
         </is>
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7806313724</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr"/>
-      <c r="E220" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
-        </is>
-      </c>
+      <c r="E220" s="11" t="inlineStr"/>
       <c r="F220" s="11" t="inlineStr"/>
       <c r="G220" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="I220" s="10" t="inlineStr">
@@ -9743,7 +9715,7 @@
       </c>
       <c r="J220" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9753,20 +9725,16 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Строй-С»</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7802373183</t>
         </is>
       </c>
       <c r="D221" s="13" t="inlineStr"/>
-      <c r="E221" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
-        </is>
-      </c>
+      <c r="E221" s="11" t="inlineStr"/>
       <c r="F221" s="11" t="inlineStr"/>
       <c r="G221" s="11" t="inlineStr">
         <is>
@@ -9775,7 +9743,7 @@
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>599</t>
         </is>
       </c>
       <c r="I221" s="10" t="inlineStr">
@@ -9785,7 +9753,7 @@
       </c>
       <c r="J221" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9795,20 +9763,16 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «СтройГрад»</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>7813692632</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr"/>
-      <c r="E222" s="11" t="inlineStr">
-        <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
-        </is>
-      </c>
+      <c r="E222" s="11" t="inlineStr"/>
       <c r="F222" s="11" t="inlineStr"/>
       <c r="G222" s="11" t="inlineStr">
         <is>
@@ -9817,7 +9781,7 @@
       </c>
       <c r="H222" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="I222" s="10" t="inlineStr">
@@ -9827,7 +9791,7 @@
       </c>
       <c r="J222" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -9837,29 +9801,25 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «СтройКом»</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7811469780</t>
         </is>
       </c>
       <c r="D223" s="13" t="inlineStr"/>
-      <c r="E223" s="11" t="inlineStr">
-        <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
-        </is>
-      </c>
+      <c r="E223" s="11" t="inlineStr"/>
       <c r="F223" s="11" t="inlineStr"/>
       <c r="G223" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H223" s="10" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>602</t>
         </is>
       </c>
       <c r="I223" s="10" t="inlineStr">
@@ -9869,7 +9829,7 @@
       </c>
       <c r="J223" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9839,12 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>ООО ПСМ «Спутник»</t>
+          <t>ООО «СтройПроект»</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>7810765071</t>
+          <t>7804554072</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr"/>
@@ -9897,7 +9857,7 @@
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>291</t>
         </is>
       </c>
       <c r="I224" s="10" t="inlineStr">
@@ -9917,12 +9877,12 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>ООО СК «Аврора-Строй»</t>
+          <t>ООО «Стройперспектива»</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>7801700173</t>
+          <t>7810740278</t>
         </is>
       </c>
       <c r="D225" s="13" t="inlineStr"/>
@@ -9935,22 +9895,986 @@
       </c>
       <c r="H225" s="10" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="I225" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J225" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="11" t="inlineStr">
+        <is>
+          <t>ООО «СулуС»</t>
+        </is>
+      </c>
+      <c r="C226" s="12" t="inlineStr">
+        <is>
+          <t>7801369120</t>
+        </is>
+      </c>
+      <c r="D226" s="13" t="inlineStr"/>
+      <c r="E226" s="11" t="inlineStr"/>
+      <c r="F226" s="11" t="inlineStr"/>
+      <c r="G226" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H226" s="10" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="I226" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J226" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="10" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Сфера»</t>
+        </is>
+      </c>
+      <c r="C227" s="12" t="inlineStr">
+        <is>
+          <t>2311308786</t>
+        </is>
+      </c>
+      <c r="D227" s="13" t="inlineStr"/>
+      <c r="E227" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
+      <c r="F227" s="11" t="inlineStr"/>
+      <c r="G227" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H227" s="10" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="I227" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J227" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТАЛИОН»</t>
+        </is>
+      </c>
+      <c r="C228" s="12" t="inlineStr">
+        <is>
+          <t>7801569190</t>
+        </is>
+      </c>
+      <c r="D228" s="13" t="inlineStr"/>
+      <c r="E228" s="11" t="inlineStr">
+        <is>
+          <t>197229 СПб, ул.Новая 51к1 пом.7-Н; ОГРН 1127847128639; ген.дир. Марков А.А.; техконтроль/испытания</t>
+        </is>
+      </c>
+      <c r="F228" s="11" t="inlineStr"/>
+      <c r="G228" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H228" s="10" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="I228" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J228" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТД «Буревестник»</t>
+        </is>
+      </c>
+      <c r="C229" s="12" t="inlineStr">
+        <is>
+          <t>4705075034</t>
+        </is>
+      </c>
+      <c r="D229" s="13" t="inlineStr"/>
+      <c r="E229" s="11" t="inlineStr"/>
+      <c r="F229" s="11" t="inlineStr"/>
+      <c r="G229" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H229" s="10" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="I229" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J229" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЕЗИС»</t>
+        </is>
+      </c>
+      <c r="C230" s="12" t="inlineStr">
+        <is>
+          <t>7804441209</t>
+        </is>
+      </c>
+      <c r="D230" s="13" t="inlineStr"/>
+      <c r="E230" s="11" t="inlineStr">
+        <is>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+        </is>
+      </c>
+      <c r="F230" s="11" t="inlineStr"/>
+      <c r="G230" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H230" s="10" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I230" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J230" s="10" t="inlineStr">
+        <is>
+          <t>700000</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="10" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЕХНОТРАНССТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C231" s="12" t="inlineStr">
+        <is>
+          <t>5190067514</t>
+        </is>
+      </c>
+      <c r="D231" s="13" t="inlineStr"/>
+      <c r="E231" s="11" t="inlineStr"/>
+      <c r="F231" s="11" t="inlineStr"/>
+      <c r="G231" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H231" s="10" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="I231" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J231" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
+        </is>
+      </c>
+      <c r="C232" s="12" t="inlineStr">
+        <is>
+          <t>7814612968</t>
+        </is>
+      </c>
+      <c r="D232" s="13" t="inlineStr"/>
+      <c r="E232" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
+      <c r="F232" s="11" t="inlineStr"/>
+      <c r="G232" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H232" s="10" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="I232" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J232" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТМС»</t>
+        </is>
+      </c>
+      <c r="C233" s="12" t="inlineStr">
+        <is>
+          <t>7801629643</t>
+        </is>
+      </c>
+      <c r="D233" s="13" t="inlineStr"/>
+      <c r="E233" s="11" t="inlineStr"/>
+      <c r="F233" s="11" t="inlineStr"/>
+      <c r="G233" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H233" s="10" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="I233" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J233" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТСК «ОЛИМП»</t>
+        </is>
+      </c>
+      <c r="C234" s="12" t="inlineStr">
+        <is>
+          <t>4205310949</t>
+        </is>
+      </c>
+      <c r="D234" s="13" t="inlineStr"/>
+      <c r="E234" s="11" t="inlineStr"/>
+      <c r="F234" s="11" t="inlineStr"/>
+      <c r="G234" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H234" s="10" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="I234" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J234" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+        </is>
+      </c>
+      <c r="C235" s="12" t="inlineStr">
+        <is>
+          <t>7839061021</t>
+        </is>
+      </c>
+      <c r="D235" s="13" t="inlineStr"/>
+      <c r="E235" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
+      <c r="F235" s="11" t="inlineStr"/>
+      <c r="G235" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H235" s="10" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="I235" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J235" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Текманн»</t>
+        </is>
+      </c>
+      <c r="C236" s="12" t="inlineStr">
+        <is>
+          <t>7842508750</t>
+        </is>
+      </c>
+      <c r="D236" s="13" t="inlineStr"/>
+      <c r="E236" s="11" t="inlineStr"/>
+      <c r="F236" s="11" t="inlineStr"/>
+      <c r="G236" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H236" s="10" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="I236" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J236" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="10" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Технические Системы»</t>
+        </is>
+      </c>
+      <c r="C237" s="12" t="inlineStr">
+        <is>
+          <t>7807345648</t>
+        </is>
+      </c>
+      <c r="D237" s="13" t="inlineStr"/>
+      <c r="E237" s="11" t="inlineStr"/>
+      <c r="F237" s="11" t="inlineStr"/>
+      <c r="G237" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H237" s="10" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="I237" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J237" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Техно Эйр Групп»</t>
+        </is>
+      </c>
+      <c r="C238" s="12" t="inlineStr">
+        <is>
+          <t>7816594954</t>
+        </is>
+      </c>
+      <c r="D238" s="13" t="inlineStr"/>
+      <c r="E238" s="11" t="inlineStr"/>
+      <c r="F238" s="11" t="inlineStr"/>
+      <c r="G238" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H238" s="10" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="I238" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J238" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="10" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Трамплин-строй»</t>
+        </is>
+      </c>
+      <c r="C239" s="12" t="inlineStr">
+        <is>
+          <t>7802207193</t>
+        </is>
+      </c>
+      <c r="D239" s="13" t="inlineStr"/>
+      <c r="E239" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
+        </is>
+      </c>
+      <c r="F239" s="11" t="inlineStr"/>
+      <c r="G239" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H239" s="10" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="I239" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J239" s="10" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Трест «Сантехмонтаж-1»</t>
+        </is>
+      </c>
+      <c r="C240" s="12" t="inlineStr">
+        <is>
+          <t>4706050882</t>
+        </is>
+      </c>
+      <c r="D240" s="13" t="inlineStr"/>
+      <c r="E240" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Мытнинская 12/44А пом.13н оф.14; ОГРН 1224700013230; сантехмонтаж, вентиляция, ИТП</t>
+        </is>
+      </c>
+      <c r="F240" s="11" t="inlineStr"/>
+      <c r="G240" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H240" s="10" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="I240" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J240" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Универсалстрой»</t>
+        </is>
+      </c>
+      <c r="C241" s="12" t="inlineStr">
+        <is>
+          <t>7801227091</t>
+        </is>
+      </c>
+      <c r="D241" s="13" t="inlineStr"/>
+      <c r="E241" s="11" t="inlineStr"/>
+      <c r="F241" s="11" t="inlineStr"/>
+      <c r="G241" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H241" s="10" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="I241" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J241" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C242" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D242" s="13" t="inlineStr"/>
+      <c r="E242" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F242" s="11" t="inlineStr"/>
+      <c r="G242" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H242" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I242" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J242" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C243" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D243" s="13" t="inlineStr"/>
+      <c r="E243" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F243" s="11" t="inlineStr"/>
+      <c r="G243" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H243" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I243" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J243" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C244" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D244" s="13" t="inlineStr"/>
+      <c r="E244" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F244" s="11" t="inlineStr"/>
+      <c r="G244" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H244" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I244" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J244" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C245" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D245" s="13" t="inlineStr"/>
+      <c r="E245" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F245" s="11" t="inlineStr"/>
+      <c r="G245" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H245" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I245" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J245" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C246" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D246" s="13" t="inlineStr"/>
+      <c r="E246" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F246" s="11" t="inlineStr"/>
+      <c r="G246" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H246" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I246" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J246" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C247" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D247" s="13" t="inlineStr"/>
+      <c r="E247" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F247" s="11" t="inlineStr"/>
+      <c r="G247" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H247" s="10" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="I247" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J247" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="11" t="inlineStr">
+        <is>
+          <t>ООО ПСМ «Спутник»</t>
+        </is>
+      </c>
+      <c r="C248" s="12" t="inlineStr">
+        <is>
+          <t>7810765071</t>
+        </is>
+      </c>
+      <c r="D248" s="13" t="inlineStr"/>
+      <c r="E248" s="11" t="inlineStr"/>
+      <c r="F248" s="11" t="inlineStr"/>
+      <c r="G248" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H248" s="10" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="I248" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J248" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="11" t="inlineStr">
+        <is>
+          <t>ООО СК «Аврора-Строй»</t>
+        </is>
+      </c>
+      <c r="C249" s="12" t="inlineStr">
+        <is>
+          <t>7801700173</t>
+        </is>
+      </c>
+      <c r="D249" s="13" t="inlineStr"/>
+      <c r="E249" s="11" t="inlineStr"/>
+      <c r="F249" s="11" t="inlineStr"/>
+      <c r="G249" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H249" s="10" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="I225" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J225" s="10" t="inlineStr">
+      <c r="I249" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J249" s="10" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J225"/>
+  <autoFilter ref="A1:J249"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10033,7 +10957,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>224</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8">
@@ -10053,7 +10977,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$331</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J313"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4391,29 +4391,33 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
+          <t>ИП Богданов Андрей Владимирович</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>7813424070</t>
+          <t>780600194397</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr"/>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
-        </is>
-      </c>
-      <c r="F86" s="11" t="inlineStr"/>
+          <t>СПб; ОГРНИП 316784700337745; автодороги; он же ген.дир. ООО «Дорожник СПб» (ИНН 7806421624)</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/ip/316784700337745</t>
+        </is>
+      </c>
       <c r="G86" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -4423,7 +4427,7 @@
       </c>
       <c r="J86" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4433,25 +4437,33 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>ООО «АВиК Северо-Запад»</t>
+          <t>ИП Ворожцов Дмитрий Валерьевич</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>7817307659</t>
+          <t>781136011393</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr"/>
-      <c r="E87" s="11" t="inlineStr"/>
-      <c r="F87" s="11" t="inlineStr"/>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>СПб; ОГРНИП 325784700092670; рег. 20.03.2025; отделочные работы</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>rusprofile.ru</t>
+        </is>
+      </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
@@ -4461,7 +4473,7 @@
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4471,29 +4483,29 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>ООО «АЛЬФА»</t>
+          <t>ООО «01-СЕРВИС»</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>7813411063</t>
+          <t>7816390598</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr"/>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
+          <t>СПб, ул.Коммуны 59А пом.4-Н оф.1; ОГРН 5067847069681; ген.дир. Ковалев М.А.; электромонтаж/сантехника; выручка 41,8 млн</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
       <c r="G88" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -4503,7 +4515,7 @@
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4513,29 +4525,29 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>ООО «АРТ-МАСШТАБ»</t>
+          <t>ООО «АБЗ СУ №8 Лендорстрой»</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>7840076495</t>
+          <t>7813424070</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr"/>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
+          <t>197101 СПб, ул.Малая Монетная 2М пом.7-Н; ОГРН 1089847334917; ген.дир. Дашкин А.А.; автодороги</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>684</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
@@ -4555,20 +4567,16 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>ООО «АС Инжиниринг»</t>
+          <t>ООО «АВ Трейд»</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>7810318651</t>
+          <t>7842522089</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr"/>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
-        </is>
-      </c>
+      <c r="E90" s="11" t="inlineStr"/>
       <c r="F90" s="11" t="inlineStr"/>
       <c r="G90" s="11" t="inlineStr">
         <is>
@@ -4577,7 +4585,7 @@
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -4587,7 +4595,7 @@
       </c>
       <c r="J90" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4597,33 +4605,25 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>ООО «Алисард»</t>
+          <t>ООО «АВАНТ»</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>7814713356</t>
+          <t>7804612550</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr"/>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
-        </is>
-      </c>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>alisard.com</t>
-        </is>
-      </c>
+      <c r="E91" s="11" t="inlineStr"/>
+      <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть e-mail и сайт)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>972</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="J91" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альфа»</t>
+          <t>ООО «АВЕНТИН СЕРВИС»</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>7802594841</t>
+          <t>7810625892</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr"/>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>958</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="J92" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4681,29 +4681,25 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>ООО «АВС»</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7804154148</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr"/>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
-        </is>
-      </c>
+      <c r="E93" s="11" t="inlineStr"/>
       <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>272</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr">
@@ -4713,7 +4709,7 @@
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4723,29 +4719,25 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>ООО «Антей»</t>
+          <t>ООО «АВТИН»</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>4708011991</t>
+          <t>7814689865</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr"/>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
-        </is>
-      </c>
+      <c r="E94" s="11" t="inlineStr"/>
       <c r="F94" s="11" t="inlineStr"/>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>363</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr">
@@ -4755,7 +4747,7 @@
       </c>
       <c r="J94" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4765,12 +4757,12 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>ООО «АркаСтрой»</t>
+          <t>ООО «АВТОДОРКОМПЛЕКС»</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>7810504390</t>
+          <t>7811755196</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr"/>
@@ -4783,7 +4775,7 @@
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr">
@@ -4793,7 +4785,7 @@
       </c>
       <c r="J95" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4803,20 +4795,16 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>ООО «Арман»</t>
+          <t>ООО «АВиК Северо-Запад»</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>7805298463</t>
+          <t>7817307659</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr"/>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
-        </is>
-      </c>
+      <c r="E96" s="11" t="inlineStr"/>
       <c r="F96" s="11" t="inlineStr"/>
       <c r="G96" s="11" t="inlineStr">
         <is>
@@ -4825,7 +4813,7 @@
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>587</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr">
@@ -4835,7 +4823,7 @@
       </c>
       <c r="J96" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -4845,12 +4833,12 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлантис»</t>
+          <t>ООО «АЕРО-Инжиниринг»</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>7810914904</t>
+          <t>7804534887</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr"/>
@@ -4863,7 +4851,7 @@
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr">
@@ -4873,7 +4861,7 @@
       </c>
       <c r="J97" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4883,20 +4871,16 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАРК»</t>
+          <t>ООО «АЖИО»</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>7804462262</t>
+          <t>7810806923</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr"/>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
-        </is>
-      </c>
+      <c r="E98" s="11" t="inlineStr"/>
       <c r="F98" s="11" t="inlineStr"/>
       <c r="G98" s="11" t="inlineStr">
         <is>
@@ -4905,7 +4889,7 @@
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>308</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr">
@@ -4915,7 +4899,7 @@
       </c>
       <c r="J98" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4925,29 +4909,29 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
+          <t>ООО «АЛЬФА»</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>7804634666</t>
+          <t>7813411063</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr"/>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
+          <t>СПб, ул.Льва Толстого 7А; ОГРН 1089847145596; ген.дир. Воробьев А.В.</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>524</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr">
@@ -4967,29 +4951,29 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>ООО «БЕЛНЕВА»</t>
+          <t>ООО «АРТ-МАСШТАБ»</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>7839489314</t>
+          <t>7840076495</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr"/>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
+          <t>197198 СПб, Петровская коса 1; ОГРН 1187847036805; ген.дир. Зубрицкая Е.В.</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr">
@@ -5009,18 +4993,18 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>ООО «АС Инжиниринг»</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7810318651</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr"/>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr"/>
@@ -5031,7 +5015,7 @@
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr">
@@ -5041,7 +5025,7 @@
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5035,12 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>ООО «Аверс Наследие»</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7801743219</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr"/>
@@ -5069,7 +5053,7 @@
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -5079,7 +5063,7 @@
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5089,29 +5073,25 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>ООО «БРАЗСТРОЙ»</t>
+          <t>ООО «АвиаПроСвет»</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>2630050808</t>
+          <t>7811714538</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr"/>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
-        </is>
-      </c>
+      <c r="E103" s="11" t="inlineStr"/>
       <c r="F103" s="11" t="inlineStr"/>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>929</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -5121,7 +5101,7 @@
       </c>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5131,12 +5111,12 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>ООО «Балтийский альянс»</t>
+          <t>ООО «Айстарт»</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>7838020706</t>
+          <t>7841061413</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr"/>
@@ -5149,7 +5129,7 @@
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>452</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr">
@@ -5159,7 +5139,7 @@
       </c>
       <c r="J104" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5169,29 +5149,25 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>ООО «БелькаРус»</t>
+          <t>ООО «Академия Фасадов»</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>7801665024</t>
+          <t>7814848410</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr"/>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
-        </is>
-      </c>
+      <c r="E105" s="11" t="inlineStr"/>
       <c r="F105" s="11" t="inlineStr"/>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr">
@@ -5201,7 +5177,7 @@
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5211,29 +5187,25 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>ООО «БиАр»</t>
+          <t>ООО «Аквадор»</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>7802738910</t>
+          <t>7811508912</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr"/>
-      <c r="E106" s="11" t="inlineStr">
-        <is>
-          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
-        </is>
-      </c>
+      <c r="E106" s="11" t="inlineStr"/>
       <c r="F106" s="11" t="inlineStr"/>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr">
@@ -5243,7 +5215,7 @@
       </c>
       <c r="J106" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5253,20 +5225,16 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>ООО «Бобёр»</t>
+          <t>ООО «Аквил»</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>7801632702</t>
+          <t>7804425944</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr"/>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
-        </is>
-      </c>
+      <c r="E107" s="11" t="inlineStr"/>
       <c r="F107" s="11" t="inlineStr"/>
       <c r="G107" s="11" t="inlineStr">
         <is>
@@ -5275,7 +5243,7 @@
       </c>
       <c r="H107" s="10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>229</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr">
@@ -5285,7 +5253,7 @@
       </c>
       <c r="J107" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5295,29 +5263,25 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЕРТЕК»</t>
+          <t>ООО «Акканто»</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>7806317711</t>
+          <t>7811815920</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr"/>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
-        </is>
-      </c>
+      <c r="E108" s="11" t="inlineStr"/>
       <c r="F108" s="11" t="inlineStr"/>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr">
@@ -5327,7 +5291,7 @@
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5337,25 +5301,33 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИП»</t>
+          <t>ООО «Алисард»</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>7802742070</t>
+          <t>7814713356</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr"/>
-      <c r="E109" s="11" t="inlineStr"/>
-      <c r="F109" s="11" t="inlineStr"/>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>alisard.com</t>
+        </is>
+      </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть e-mail и сайт)</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>575</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
@@ -5375,29 +5347,25 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИРА»</t>
+          <t>ООО «Альфа»</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>7839139655</t>
+          <t>7802594841</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr"/>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
-        </is>
-      </c>
+      <c r="E110" s="11" t="inlineStr"/>
       <c r="F110" s="11" t="inlineStr"/>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
@@ -5417,25 +5385,29 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>3525411380</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr"/>
-      <c r="E111" s="11" t="inlineStr"/>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
+        </is>
+      </c>
       <c r="F111" s="11" t="inlineStr"/>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
@@ -5445,7 +5417,7 @@
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -5455,25 +5427,29 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК» (Военно-строительная компания)</t>
+          <t>ООО «Антей»</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>7804018392</t>
+          <t>4708011991</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr"/>
-      <c r="E112" s="11" t="inlineStr"/>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
+        </is>
+      </c>
       <c r="F112" s="11" t="inlineStr"/>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
@@ -5493,12 +5469,12 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЭС»</t>
+          <t>ООО «АркаСтрой»</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>7839121496</t>
+          <t>7810504390</t>
         </is>
       </c>
       <c r="D113" s="13" t="inlineStr"/>
@@ -5511,7 +5487,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>542</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
@@ -5521,7 +5497,7 @@
       </c>
       <c r="J113" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -5531,18 +5507,18 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «Арман»</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7805298463</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr"/>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -5553,7 +5529,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>586</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
@@ -5563,7 +5539,7 @@
       </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5573,12 +5549,12 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>ООО «Восток-Техника»</t>
+          <t>ООО «Атлантис»</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>7820049077</t>
+          <t>7810914904</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr"/>
@@ -5591,7 +5567,7 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
@@ -5601,7 +5577,7 @@
       </c>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5611,29 +5587,29 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>ООО «БАРК»</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7804462262</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr"/>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
@@ -5643,7 +5619,7 @@
       </c>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5629,20 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
+          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>7603054270</t>
+          <t>7804634666</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr"/>
-      <c r="E117" s="11" t="inlineStr"/>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
+        </is>
+      </c>
       <c r="F117" s="11" t="inlineStr"/>
       <c r="G117" s="11" t="inlineStr">
         <is>
@@ -5671,7 +5651,7 @@
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
@@ -5691,18 +5671,18 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ООО «БЕЛНЕВА»</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7839489314</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr"/>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -5713,7 +5693,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>457</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -5723,7 +5703,7 @@
       </c>
       <c r="J118" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5733,16 +5713,20 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГК «СТИ»</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>7814797620</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr"/>
-      <c r="E119" s="11" t="inlineStr"/>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+        </is>
+      </c>
       <c r="F119" s="11" t="inlineStr"/>
       <c r="G119" s="11" t="inlineStr">
         <is>
@@ -5751,7 +5735,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -5761,7 +5745,7 @@
       </c>
       <c r="J119" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -5771,29 +5755,25 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr"/>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
-        </is>
-      </c>
+      <c r="E120" s="11" t="inlineStr"/>
       <c r="F120" s="11" t="inlineStr"/>
       <c r="G120" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -5803,7 +5783,7 @@
       </c>
       <c r="J120" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -5813,18 +5793,18 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «БРАЗСТРОЙ»</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>2630050808</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr"/>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr"/>
@@ -5835,7 +5815,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -5845,7 +5825,7 @@
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5835,12 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гелиос»</t>
+          <t>ООО «Балтийский альянс»</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>7804608994</t>
+          <t>7838020706</t>
         </is>
       </c>
       <c r="D122" s="13" t="inlineStr"/>
@@ -5873,7 +5853,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>768</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -5883,7 +5863,7 @@
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -5893,18 +5873,18 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «БелькаРус»</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7801665024</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr"/>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
+          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr"/>
@@ -5915,7 +5895,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -5925,7 +5905,7 @@
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5935,25 +5915,29 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>ООО «ДСК РЕГИОН»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>7816487198</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr"/>
-      <c r="E124" s="11" t="inlineStr"/>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
+        </is>
+      </c>
       <c r="F124" s="11" t="inlineStr"/>
       <c r="G124" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -5963,7 +5947,7 @@
       </c>
       <c r="J124" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -5973,16 +5957,20 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>ООО «Двеста»</t>
+          <t>ООО «Бобёр»</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>0100042992</t>
+          <t>7801632702</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr"/>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
+        </is>
+      </c>
       <c r="F125" s="11" t="inlineStr"/>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -5991,7 +5979,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -6001,7 +5989,7 @@
       </c>
       <c r="J125" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6011,25 +5999,29 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>ООО «Дорожник СПб»</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>7806421624</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D126" s="13" t="inlineStr"/>
-      <c r="E126" s="11" t="inlineStr"/>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+        </is>
+      </c>
       <c r="F126" s="11" t="inlineStr"/>
       <c r="G126" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
@@ -6039,7 +6031,7 @@
       </c>
       <c r="J126" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -6049,29 +6041,25 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «ВИП»</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>7802742070</t>
         </is>
       </c>
       <c r="D127" s="13" t="inlineStr"/>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
-        </is>
-      </c>
+      <c r="E127" s="11" t="inlineStr"/>
       <c r="F127" s="11" t="inlineStr"/>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>226</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
@@ -6081,7 +6069,7 @@
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6091,29 +6079,29 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «ВИРА»</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7839139655</t>
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr"/>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
       <c r="G128" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr">
@@ -6123,7 +6111,7 @@
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6133,12 +6121,12 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЗИТЕК»</t>
+          <t>ООО «ВСК»</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>7814691303</t>
+          <t>3525411380</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr"/>
@@ -6151,7 +6139,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
@@ -6171,12 +6159,12 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>ООО «Зодчий»</t>
+          <t>ООО «ВСК» (Военно-строительная компания)</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>7810477235</t>
+          <t>7804018392</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr"/>
@@ -6189,7 +6177,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>670</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr">
@@ -6209,20 +6197,16 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «ВЭС»</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7839121496</t>
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr"/>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
-        </is>
-      </c>
+      <c r="E131" s="11" t="inlineStr"/>
       <c r="F131" s="11" t="inlineStr"/>
       <c r="G131" s="11" t="inlineStr">
         <is>
@@ -6231,7 +6215,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>828</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
@@ -6241,7 +6225,7 @@
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6251,16 +6235,20 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr"/>
-      <c r="E132" s="11" t="inlineStr"/>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+        </is>
+      </c>
       <c r="F132" s="11" t="inlineStr"/>
       <c r="G132" s="11" t="inlineStr">
         <is>
@@ -6269,7 +6257,7 @@
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr">
@@ -6279,7 +6267,7 @@
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -6289,12 +6277,12 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК «Петротрасса»</t>
+          <t>ООО «Восток-Техника»</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>7804572970</t>
+          <t>7820049077</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr"/>
@@ -6307,7 +6295,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>538</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
@@ -6317,7 +6305,7 @@
       </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -6327,25 +6315,29 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ИнТехПро»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>9810000213</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr"/>
-      <c r="E134" s="11" t="inlineStr"/>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+        </is>
+      </c>
       <c r="F134" s="11" t="inlineStr"/>
       <c r="G134" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr">
@@ -6355,7 +6347,7 @@
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6357,12 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
+          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>7710910159</t>
+          <t>7603054270</t>
         </is>
       </c>
       <c r="D135" s="13" t="inlineStr"/>
@@ -6383,7 +6375,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
@@ -6403,29 +6395,29 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr"/>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr"/>
       <c r="G136" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr">
@@ -6445,12 +6437,12 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНСИ»</t>
+          <t>ООО «ГК «СТИ»</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>7839398890</t>
+          <t>7814797620</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr"/>
@@ -6463,7 +6455,7 @@
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>847</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
@@ -6483,25 +6475,29 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИСБ-СЕРВИС»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>7811462471</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr"/>
-      <c r="E138" s="11" t="inlineStr"/>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
+        </is>
+      </c>
       <c r="F138" s="11" t="inlineStr"/>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr">
@@ -6511,7 +6507,7 @@
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -6521,29 +6517,29 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr"/>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
@@ -6563,12 +6559,12 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>ООО «Импульс»</t>
+          <t>ООО «Гелиос»</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>7839473240</t>
+          <t>7804608994</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr"/>
@@ -6581,7 +6577,7 @@
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>565</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr">
@@ -6601,18 +6597,18 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr"/>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -6623,7 +6619,7 @@
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
@@ -6633,7 +6629,7 @@
       </c>
       <c r="J141" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -6643,12 +6639,12 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интер-Строй»</t>
+          <t>ООО «ДСК РЕГИОН»</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>5505064975</t>
+          <t>7816487198</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr"/>
@@ -6661,7 +6657,7 @@
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I142" s="10" t="inlineStr">
@@ -6681,12 +6677,12 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интерпром»</t>
+          <t>ООО «Двеста»</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>7805576110</t>
+          <t>0100042992</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr"/>
@@ -6699,7 +6695,7 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
@@ -6709,7 +6705,7 @@
       </c>
       <c r="J143" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6715,12 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>ООО «КС-Инжиниринг»</t>
+          <t>ООО «Дорожник СПб»</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>7801615217</t>
+          <t>7806421624</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr"/>
@@ -6737,7 +6733,7 @@
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>564</t>
         </is>
       </c>
       <c r="I144" s="10" t="inlineStr">
@@ -6757,29 +6753,29 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr"/>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr"/>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
@@ -6789,7 +6785,7 @@
       </c>
       <c r="J145" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6799,18 +6795,18 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>ООО «Компания КОМПЛИТ»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>7810793872</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr"/>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr"/>
@@ -6821,7 +6817,7 @@
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr">
@@ -6831,7 +6827,7 @@
       </c>
       <c r="J146" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -6841,12 +6837,12 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>ООО «Комфорт ЛСТК»</t>
+          <t>ООО «ЗИТЕК»</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>7838428816</t>
+          <t>7814691303</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr"/>
@@ -6859,7 +6855,7 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
@@ -6879,20 +6875,16 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>ООО «Концерн «Питер»</t>
+          <t>ООО «Зодчий»</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>7826108410</t>
+          <t>7810477235</t>
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr"/>
-      <c r="E148" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Ефимова 3С пом.417; ОГРН 1027810246750; ген.дир. Петров М.Ю.; застройщик</t>
-        </is>
-      </c>
+      <c r="E148" s="11" t="inlineStr"/>
       <c r="F148" s="11" t="inlineStr"/>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -6901,7 +6893,7 @@
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
@@ -6911,7 +6903,7 @@
       </c>
       <c r="J148" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6921,16 +6913,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>ООО «Корнелиус»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>7802611335</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr"/>
-      <c r="E149" s="11" t="inlineStr"/>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+        </is>
+      </c>
       <c r="F149" s="11" t="inlineStr"/>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -6939,7 +6935,7 @@
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
@@ -6949,7 +6945,7 @@
       </c>
       <c r="J149" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6955,12 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>ООО «Красный Квадрат»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>7802567950</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D150" s="13" t="inlineStr"/>
@@ -6977,7 +6973,7 @@
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr">
@@ -6987,7 +6983,7 @@
       </c>
       <c r="J150" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6993,12 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЛС-Групп»</t>
+          <t>ООО «ИК «Петротрасса»</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>7842036949</t>
+          <t>7804572970</t>
         </is>
       </c>
       <c r="D151" s="13" t="inlineStr"/>
@@ -7015,7 +7011,7 @@
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>712</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
@@ -7035,29 +7031,25 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «ИК ИнТехПро»</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>9810000213</t>
         </is>
       </c>
       <c r="D152" s="13" t="inlineStr"/>
-      <c r="E152" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
-        </is>
-      </c>
+      <c r="E152" s="11" t="inlineStr"/>
       <c r="F152" s="11" t="inlineStr"/>
       <c r="G152" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr">
@@ -7067,7 +7059,7 @@
       </c>
       <c r="J152" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7077,20 +7069,16 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7710910159</t>
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr"/>
-      <c r="E153" s="11" t="inlineStr">
-        <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
-        </is>
-      </c>
+      <c r="E153" s="11" t="inlineStr"/>
       <c r="F153" s="11" t="inlineStr"/>
       <c r="G153" s="11" t="inlineStr">
         <is>
@@ -7099,7 +7087,7 @@
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>940</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
@@ -7109,7 +7097,7 @@
       </c>
       <c r="J153" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7119,25 +7107,29 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЛидерСервис»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>7805304438</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D154" s="13" t="inlineStr"/>
-      <c r="E154" s="11" t="inlineStr"/>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+        </is>
+      </c>
       <c r="F154" s="11" t="inlineStr"/>
       <c r="G154" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr">
@@ -7147,7 +7139,7 @@
       </c>
       <c r="J154" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7157,12 +7149,12 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>ООО «М-ГРУПП»</t>
+          <t>ООО «ИНСИ»</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>3128105475</t>
+          <t>7839398890</t>
         </is>
       </c>
       <c r="D155" s="13" t="inlineStr"/>
@@ -7175,7 +7167,7 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
@@ -7195,12 +7187,12 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>ООО «М-Сервис»</t>
+          <t>ООО «ИСБ-СЕРВИС»</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>7842429918</t>
+          <t>7811462471</t>
         </is>
       </c>
       <c r="D156" s="13" t="inlineStr"/>
@@ -7213,7 +7205,7 @@
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>295</t>
         </is>
       </c>
       <c r="I156" s="10" t="inlineStr">
@@ -7233,16 +7225,20 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>ООО «МАН»</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>7840404386</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D157" s="13" t="inlineStr"/>
-      <c r="E157" s="11" t="inlineStr"/>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+        </is>
+      </c>
       <c r="F157" s="11" t="inlineStr"/>
       <c r="G157" s="11" t="inlineStr">
         <is>
@@ -7251,7 +7247,7 @@
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
@@ -7261,7 +7257,7 @@
       </c>
       <c r="J157" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7267,12 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>ООО «МАТИС»</t>
+          <t>ООО «Импульс»</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>7820023103</t>
+          <t>7839473240</t>
         </is>
       </c>
       <c r="D158" s="13" t="inlineStr"/>
@@ -7289,7 +7285,7 @@
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I158" s="10" t="inlineStr">
@@ -7309,25 +7305,29 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>ООО «МК БАМ»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>7536059295</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr"/>
-      <c r="E159" s="11" t="inlineStr"/>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
+        </is>
+      </c>
       <c r="F159" s="11" t="inlineStr"/>
       <c r="G159" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="J159" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7347,29 +7347,25 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «Интер-Строй»</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>5505064975</t>
         </is>
       </c>
       <c r="D160" s="13" t="inlineStr"/>
-      <c r="E160" s="11" t="inlineStr">
-        <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
-        </is>
-      </c>
+      <c r="E160" s="11" t="inlineStr"/>
       <c r="F160" s="11" t="inlineStr"/>
       <c r="G160" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="I160" s="10" t="inlineStr">
@@ -7379,7 +7375,7 @@
       </c>
       <c r="J160" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7389,12 +7385,12 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>ООО «МСС СЗ»</t>
+          <t>ООО «Интерпром»</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>7804372114</t>
+          <t>7805576110</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr"/>
@@ -7407,7 +7403,7 @@
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
@@ -7417,7 +7413,7 @@
       </c>
       <c r="J161" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7427,20 +7423,16 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «КС-Инжиниринг»</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7801615217</t>
         </is>
       </c>
       <c r="D162" s="13" t="inlineStr"/>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
-        </is>
-      </c>
+      <c r="E162" s="11" t="inlineStr"/>
       <c r="F162" s="11" t="inlineStr"/>
       <c r="G162" s="11" t="inlineStr">
         <is>
@@ -7449,7 +7441,7 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>695</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr">
@@ -7459,7 +7451,7 @@
       </c>
       <c r="J162" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7469,29 +7461,29 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>ООО «Мелстон Инжиниринг»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>7813248219</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr"/>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr"/>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
@@ -7501,7 +7493,7 @@
       </c>
       <c r="J163" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -7511,18 +7503,18 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «Компания КОМПЛИТ»</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>7810793872</t>
         </is>
       </c>
       <c r="D164" s="13" t="inlineStr"/>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr"/>
@@ -7533,7 +7525,7 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>143</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr">
@@ -7543,7 +7535,7 @@
       </c>
       <c r="J164" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7553,20 +7545,16 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>ООО «МонтажСтрой-М» (МСМ)</t>
+          <t>ООО «Комфорт ЛСТК»</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>7811447071</t>
+          <t>7838428816</t>
         </is>
       </c>
       <c r="D165" s="13" t="inlineStr"/>
-      <c r="E165" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
-        </is>
-      </c>
+      <c r="E165" s="11" t="inlineStr"/>
       <c r="F165" s="11" t="inlineStr"/>
       <c r="G165" s="11" t="inlineStr">
         <is>
@@ -7575,7 +7563,7 @@
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>693</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
@@ -7585,7 +7573,7 @@
       </c>
       <c r="J165" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7595,16 +7583,20 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО «НАСТ»</t>
+          <t>ООО «Концерн «Питер»</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>7810172762</t>
+          <t>7826108410</t>
         </is>
       </c>
       <c r="D166" s="13" t="inlineStr"/>
-      <c r="E166" s="11" t="inlineStr"/>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Ефимова 3С пом.417; ОГРН 1027810246750; ген.дир. Петров М.Ю.; застройщик</t>
+        </is>
+      </c>
       <c r="F166" s="11" t="inlineStr"/>
       <c r="G166" s="11" t="inlineStr">
         <is>
@@ -7613,7 +7605,7 @@
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>739</t>
         </is>
       </c>
       <c r="I166" s="10" t="inlineStr">
@@ -7623,7 +7615,7 @@
       </c>
       <c r="J166" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -7633,12 +7625,12 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО «Процесс»</t>
+          <t>ООО «Корнелиус»</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>7806468037</t>
+          <t>7802611335</t>
         </is>
       </c>
       <c r="D167" s="13" t="inlineStr"/>
@@ -7651,7 +7643,7 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
@@ -7671,12 +7663,12 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО ПЭМЗ»</t>
+          <t>ООО «Красный Квадрат»</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>7813361648</t>
+          <t>7802567950</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr"/>
@@ -7689,7 +7681,7 @@
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="I168" s="10" t="inlineStr">
@@ -7709,20 +7701,16 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПП «Путьсервис»</t>
+          <t>ООО «ЛС-Групп»</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>7810216184</t>
+          <t>7842036949</t>
         </is>
       </c>
       <c r="D169" s="13" t="inlineStr"/>
-      <c r="E169" s="11" t="inlineStr">
-        <is>
-          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
-        </is>
-      </c>
+      <c r="E169" s="11" t="inlineStr"/>
       <c r="F169" s="11" t="inlineStr"/>
       <c r="G169" s="11" t="inlineStr">
         <is>
@@ -7731,7 +7719,7 @@
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>509</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
@@ -7751,29 +7739,29 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D170" s="13" t="inlineStr"/>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr"/>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I170" s="10" t="inlineStr">
@@ -7783,7 +7771,7 @@
       </c>
       <c r="J170" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7793,16 +7781,20 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПХК «Ремстройкомплекс»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>7826000423</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D171" s="13" t="inlineStr"/>
-      <c r="E171" s="11" t="inlineStr"/>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
+        </is>
+      </c>
       <c r="F171" s="11" t="inlineStr"/>
       <c r="G171" s="11" t="inlineStr">
         <is>
@@ -7811,7 +7803,7 @@
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
@@ -7821,7 +7813,7 @@
       </c>
       <c r="J171" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7831,29 +7823,25 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «ЛидерСервис»</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7805304438</t>
         </is>
       </c>
       <c r="D172" s="13" t="inlineStr"/>
-      <c r="E172" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
-        </is>
-      </c>
+      <c r="E172" s="11" t="inlineStr"/>
       <c r="F172" s="11" t="inlineStr"/>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>902</t>
         </is>
       </c>
       <c r="I172" s="10" t="inlineStr">
@@ -7863,7 +7851,7 @@
       </c>
       <c r="J172" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7873,12 +7861,12 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСР»</t>
+          <t>ООО «М-ГРУПП»</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>7801727376</t>
+          <t>3128105475</t>
         </is>
       </c>
       <c r="D173" s="13" t="inlineStr"/>
@@ -7891,7 +7879,7 @@
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
@@ -7911,29 +7899,25 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «М-Сервис»</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7842429918</t>
         </is>
       </c>
       <c r="D174" s="13" t="inlineStr"/>
-      <c r="E174" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
-        </is>
-      </c>
+      <c r="E174" s="11" t="inlineStr"/>
       <c r="F174" s="11" t="inlineStr"/>
       <c r="G174" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H174" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>722</t>
         </is>
       </c>
       <c r="I174" s="10" t="inlineStr">
@@ -7943,7 +7927,7 @@
       </c>
       <c r="J174" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7953,20 +7937,16 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «МАН»</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7840404386</t>
         </is>
       </c>
       <c r="D175" s="13" t="inlineStr"/>
-      <c r="E175" s="11" t="inlineStr">
-        <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
-        </is>
-      </c>
+      <c r="E175" s="11" t="inlineStr"/>
       <c r="F175" s="11" t="inlineStr"/>
       <c r="G175" s="11" t="inlineStr">
         <is>
@@ -7975,7 +7955,7 @@
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>510</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
@@ -7985,7 +7965,7 @@
       </c>
       <c r="J175" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7995,12 +7975,12 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОСА - Север»</t>
+          <t>ООО «МАТИС»</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>7801574480</t>
+          <t>7820023103</t>
         </is>
       </c>
       <c r="D176" s="13" t="inlineStr"/>
@@ -8013,7 +7993,7 @@
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>616</t>
         </is>
       </c>
       <c r="I176" s="10" t="inlineStr">
@@ -8033,12 +8013,12 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОблСервис»</t>
+          <t>ООО «МК БАМ»</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>4712024087</t>
+          <t>7536059295</t>
         </is>
       </c>
       <c r="D177" s="13" t="inlineStr"/>
@@ -8051,7 +8031,7 @@
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>668</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
@@ -8071,25 +8051,29 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОлАн»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>7827004614</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D178" s="13" t="inlineStr"/>
-      <c r="E178" s="11" t="inlineStr"/>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
+        </is>
+      </c>
       <c r="F178" s="11" t="inlineStr"/>
       <c r="G178" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I178" s="10" t="inlineStr">
@@ -8099,7 +8083,7 @@
       </c>
       <c r="J178" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8109,12 +8093,12 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>ООО «Олимп-Строй»</t>
+          <t>ООО «МСС СЗ»</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>7820315709</t>
+          <t>7804372114</t>
         </is>
       </c>
       <c r="D179" s="13" t="inlineStr"/>
@@ -8127,7 +8111,7 @@
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>741</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
@@ -8137,7 +8121,7 @@
       </c>
       <c r="J179" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -8147,18 +8131,18 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D180" s="13" t="inlineStr"/>
       <c r="E180" s="11" t="inlineStr">
         <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
         </is>
       </c>
       <c r="F180" s="11" t="inlineStr"/>
@@ -8169,7 +8153,7 @@
       </c>
       <c r="H180" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I180" s="10" t="inlineStr">
@@ -8189,25 +8173,29 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омни Структуре Санкт-Петербург»</t>
+          <t>ООО «Мелстон Инжиниринг»</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>7801641792</t>
+          <t>7813248219</t>
         </is>
       </c>
       <c r="D181" s="13" t="inlineStr"/>
-      <c r="E181" s="11" t="inlineStr"/>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
+        </is>
+      </c>
       <c r="F181" s="11" t="inlineStr"/>
       <c r="G181" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>669</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
@@ -8217,7 +8205,7 @@
       </c>
       <c r="J181" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8227,16 +8215,20 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>ООО «Основание»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>7840083527</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D182" s="13" t="inlineStr"/>
-      <c r="E182" s="11" t="inlineStr"/>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+        </is>
+      </c>
       <c r="F182" s="11" t="inlineStr"/>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8245,7 +8237,7 @@
       </c>
       <c r="H182" s="10" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I182" s="10" t="inlineStr">
@@ -8255,7 +8247,7 @@
       </c>
       <c r="J182" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8265,29 +8257,29 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>7825382561</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D183" s="13" t="inlineStr"/>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr"/>
       <c r="G183" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr">
@@ -8307,12 +8299,12 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПВВ Продукт»</t>
+          <t>ООО «НПО «НАСТ»</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>7840501541</t>
+          <t>7810172762</t>
         </is>
       </c>
       <c r="D184" s="13" t="inlineStr"/>
@@ -8325,7 +8317,7 @@
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>273</t>
         </is>
       </c>
       <c r="I184" s="10" t="inlineStr">
@@ -8345,12 +8337,12 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПВЦ «Восток»</t>
+          <t>ООО «НПО «Процесс»</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>7802203054</t>
+          <t>7806468037</t>
         </is>
       </c>
       <c r="D185" s="13" t="inlineStr"/>
@@ -8363,7 +8355,7 @@
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr">
@@ -8383,29 +8375,25 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «НПО ПЭМЗ»</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>7813361648</t>
         </is>
       </c>
       <c r="D186" s="13" t="inlineStr"/>
-      <c r="E186" s="11" t="inlineStr">
-        <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
-        </is>
-      </c>
+      <c r="E186" s="11" t="inlineStr"/>
       <c r="F186" s="11" t="inlineStr"/>
       <c r="G186" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="I186" s="10" t="inlineStr">
@@ -8415,7 +8403,7 @@
       </c>
       <c r="J186" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8425,16 +8413,20 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕГАЗ»</t>
+          <t>ООО «НПП «Путьсервис»</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>7804700982</t>
+          <t>7810216184</t>
         </is>
       </c>
       <c r="D187" s="13" t="inlineStr"/>
-      <c r="E187" s="11" t="inlineStr"/>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
+        </is>
+      </c>
       <c r="F187" s="11" t="inlineStr"/>
       <c r="G187" s="11" t="inlineStr">
         <is>
@@ -8443,7 +8435,7 @@
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>733</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr">
@@ -8463,16 +8455,20 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОТОРГ»</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>7810518322</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D188" s="13" t="inlineStr"/>
-      <c r="E188" s="11" t="inlineStr"/>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
+        </is>
+      </c>
       <c r="F188" s="11" t="inlineStr"/>
       <c r="G188" s="11" t="inlineStr">
         <is>
@@ -8481,7 +8477,7 @@
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I188" s="10" t="inlineStr">
@@ -8491,7 +8487,7 @@
       </c>
       <c r="J188" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -8501,29 +8497,25 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «НПХК «Ремстройкомплекс»</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7826000423</t>
         </is>
       </c>
       <c r="D189" s="13" t="inlineStr"/>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
-        </is>
-      </c>
+      <c r="E189" s="11" t="inlineStr"/>
       <c r="F189" s="11" t="inlineStr"/>
       <c r="G189" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I189" s="10" t="inlineStr">
@@ -8533,7 +8525,7 @@
       </c>
       <c r="J189" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8543,29 +8535,29 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>7810685806</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr"/>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, Ярославский пр.</t>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr"/>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr">
@@ -8575,7 +8567,7 @@
       </c>
       <c r="J190" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -8585,33 +8577,25 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
+          <t>ООО «НСР»</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>7841469072</t>
+          <t>7801727376</t>
         </is>
       </c>
       <c r="D191" s="13" t="inlineStr"/>
-      <c r="E191" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
-        </is>
-      </c>
-      <c r="F191" s="11" t="inlineStr">
-        <is>
-          <t>saby.ru/profile/7841469072-783901001</t>
-        </is>
-      </c>
+      <c r="E191" s="11" t="inlineStr"/>
+      <c r="F191" s="11" t="inlineStr"/>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>нет данных (найден только белорусский номер — под вопросом)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="I191" s="10" t="inlineStr">
@@ -8631,25 +8615,29 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСК «Реставрация»</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>7839085696</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr"/>
-      <c r="E192" s="11" t="inlineStr"/>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
+        </is>
+      </c>
       <c r="F192" s="11" t="inlineStr"/>
       <c r="G192" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr">
@@ -8659,7 +8647,7 @@
       </c>
       <c r="J192" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8669,18 +8657,18 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D193" s="13" t="inlineStr"/>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr"/>
@@ -8691,7 +8679,7 @@
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I193" s="10" t="inlineStr">
@@ -8701,7 +8689,7 @@
       </c>
       <c r="J193" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -8711,20 +8699,16 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «ОСА - Север»</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7801574480</t>
         </is>
       </c>
       <c r="D194" s="13" t="inlineStr"/>
-      <c r="E194" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
-        </is>
-      </c>
+      <c r="E194" s="11" t="inlineStr"/>
       <c r="F194" s="11" t="inlineStr"/>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -8733,7 +8717,7 @@
       </c>
       <c r="H194" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>834</t>
         </is>
       </c>
       <c r="I194" s="10" t="inlineStr">
@@ -8743,7 +8727,7 @@
       </c>
       <c r="J194" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8737,12 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «ОблСервис»</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>4712024087</t>
         </is>
       </c>
       <c r="D195" s="13" t="inlineStr"/>
@@ -8771,7 +8755,7 @@
       </c>
       <c r="H195" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="I195" s="10" t="inlineStr">
@@ -8781,7 +8765,7 @@
       </c>
       <c r="J195" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8791,12 +8775,12 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТО Сервис»</t>
+          <t>ООО «ОлАн»</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>7839334494</t>
+          <t>7827004614</t>
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr"/>
@@ -8809,7 +8793,7 @@
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>685</t>
         </is>
       </c>
       <c r="I196" s="10" t="inlineStr">
@@ -8829,12 +8813,12 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТФ «КонСис»</t>
+          <t>ООО «Олимп-Строй»</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>7805068406</t>
+          <t>7820315709</t>
         </is>
       </c>
       <c r="D197" s="13" t="inlineStr"/>
@@ -8847,7 +8831,7 @@
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>689</t>
         </is>
       </c>
       <c r="I197" s="10" t="inlineStr">
@@ -8857,7 +8841,7 @@
       </c>
       <c r="J197" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8867,16 +8851,20 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЭС»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>7814677411</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr"/>
-      <c r="E198" s="11" t="inlineStr"/>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+        </is>
+      </c>
       <c r="F198" s="11" t="inlineStr"/>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -8885,7 +8873,7 @@
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I198" s="10" t="inlineStr">
@@ -8895,7 +8883,7 @@
       </c>
       <c r="J198" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8905,12 +8893,12 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>ООО «Паритет Плюс»</t>
+          <t>ООО «Омни Структуре Санкт-Петербург»</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>7806471030</t>
+          <t>7801641792</t>
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr"/>
@@ -8923,7 +8911,7 @@
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>562</t>
         </is>
       </c>
       <c r="I199" s="10" t="inlineStr">
@@ -8933,7 +8921,7 @@
       </c>
       <c r="J199" s="10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -8943,12 +8931,12 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПетроТрейд-инжиниринг»</t>
+          <t>ООО «Основание»</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>7802490056</t>
+          <t>7840083527</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr"/>
@@ -8961,7 +8949,7 @@
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="I200" s="10" t="inlineStr">
@@ -8981,25 +8969,29 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>ООО «Портмарин Инжиниринг»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>7811777680</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D201" s="13" t="inlineStr"/>
-      <c r="E201" s="11" t="inlineStr"/>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
+        </is>
+      </c>
       <c r="F201" s="11" t="inlineStr"/>
       <c r="G201" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I201" s="10" t="inlineStr">
@@ -9009,7 +9001,7 @@
       </c>
       <c r="J201" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -9019,12 +9011,12 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрогрессСтрой»</t>
+          <t>ООО «ПВВ Продукт»</t>
         </is>
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>7811604013</t>
+          <t>7840501541</t>
         </is>
       </c>
       <c r="D202" s="13" t="inlineStr"/>
@@ -9037,7 +9029,7 @@
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>454</t>
         </is>
       </c>
       <c r="I202" s="10" t="inlineStr">
@@ -9057,12 +9049,12 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПромИнвест»</t>
+          <t>ООО «ПВЦ «Восток»</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>7841439543</t>
+          <t>7802203054</t>
         </is>
       </c>
       <c r="D203" s="13" t="inlineStr"/>
@@ -9075,7 +9067,7 @@
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>534</t>
         </is>
       </c>
       <c r="I203" s="10" t="inlineStr">
@@ -9095,25 +9087,29 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПромСтрой»</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>7806156944</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr"/>
-      <c r="E204" s="11" t="inlineStr"/>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+        </is>
+      </c>
       <c r="F204" s="11" t="inlineStr"/>
       <c r="G204" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I204" s="10" t="inlineStr">
@@ -9123,7 +9119,7 @@
       </c>
       <c r="J204" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9133,20 +9129,16 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «ПЕГАЗ»</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7804700982</t>
         </is>
       </c>
       <c r="D205" s="13" t="inlineStr"/>
-      <c r="E205" s="11" t="inlineStr">
-        <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
-        </is>
-      </c>
+      <c r="E205" s="11" t="inlineStr"/>
       <c r="F205" s="11" t="inlineStr"/>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9155,7 +9147,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr">
@@ -9165,7 +9157,7 @@
       </c>
       <c r="J205" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9167,12 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстройинжиниринг»</t>
+          <t>ООО «ПЕТРОТОРГ»</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>7814349756</t>
+          <t>7810518322</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr"/>
@@ -9193,7 +9185,7 @@
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>751</t>
         </is>
       </c>
       <c r="I206" s="10" t="inlineStr">
@@ -9203,7 +9195,7 @@
       </c>
       <c r="J206" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -9213,25 +9205,29 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрофСтрой-И»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>7810682530</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D207" s="13" t="inlineStr"/>
-      <c r="E207" s="11" t="inlineStr"/>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
+        </is>
+      </c>
       <c r="F207" s="11" t="inlineStr"/>
       <c r="G207" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I207" s="10" t="inlineStr">
@@ -9241,7 +9237,7 @@
       </c>
       <c r="J207" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -9251,16 +9247,20 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрофСтройАльянс»</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>7842504114</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr"/>
-      <c r="E208" s="11" t="inlineStr"/>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, Ярославский пр.</t>
+        </is>
+      </c>
       <c r="F208" s="11" t="inlineStr"/>
       <c r="G208" s="11" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="H208" s="10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I208" s="10" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="J208" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -9289,29 +9289,33 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7841469072</t>
         </is>
       </c>
       <c r="D209" s="13" t="inlineStr"/>
       <c r="E209" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
-        </is>
-      </c>
-      <c r="F209" s="11" t="inlineStr"/>
+          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="inlineStr">
+        <is>
+          <t>saby.ru/profile/7841469072-783901001</t>
+        </is>
+      </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (найден только белорусский номер — под вопросом)</t>
         </is>
       </c>
       <c r="H209" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>595</t>
         </is>
       </c>
       <c r="I209" s="10" t="inlineStr">
@@ -9321,7 +9325,7 @@
       </c>
       <c r="J209" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9331,12 +9335,12 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>ООО «РД»</t>
+          <t>ООО «ПСК «Реставрация»</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>7810062946</t>
+          <t>7839085696</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr"/>
@@ -9349,7 +9353,7 @@
       </c>
       <c r="H210" s="10" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I210" s="10" t="inlineStr">
@@ -9369,18 +9373,18 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>7811659380</t>
         </is>
       </c>
       <c r="D211" s="13" t="inlineStr"/>
       <c r="E211" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
         </is>
       </c>
       <c r="F211" s="11" t="inlineStr"/>
@@ -9391,7 +9395,7 @@
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>607</t>
         </is>
       </c>
       <c r="I211" s="10" t="inlineStr">
@@ -9411,16 +9415,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>ООО «РИАРДЕН»</t>
+          <t>ООО «ПСТ»</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>7814794789</t>
+          <t>7813448257</t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr"/>
-      <c r="E212" s="11" t="inlineStr"/>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+        </is>
+      </c>
       <c r="F212" s="11" t="inlineStr"/>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -9429,7 +9437,7 @@
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>876</t>
         </is>
       </c>
       <c r="I212" s="10" t="inlineStr">
@@ -9439,7 +9447,7 @@
       </c>
       <c r="J212" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9449,12 +9457,12 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>ООО «РК ДЕВЕЛОПМЕНТ»</t>
+          <t>ООО «ПТГ»</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>7814800834</t>
+          <t>5013050270</t>
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr"/>
@@ -9467,7 +9475,7 @@
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="I213" s="10" t="inlineStr">
@@ -9477,7 +9485,7 @@
       </c>
       <c r="J213" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9487,20 +9495,16 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «ПТО Сервис»</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7839334494</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr"/>
-      <c r="E214" s="11" t="inlineStr">
-        <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
-        </is>
-      </c>
+      <c r="E214" s="11" t="inlineStr"/>
       <c r="F214" s="11" t="inlineStr"/>
       <c r="G214" s="11" t="inlineStr">
         <is>
@@ -9509,7 +9513,7 @@
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I214" s="10" t="inlineStr">
@@ -9519,7 +9523,7 @@
       </c>
       <c r="J214" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -9529,12 +9533,12 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>ООО «РОНИС»</t>
+          <t>ООО «ПТФ «КонСис»</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>7840475549</t>
+          <t>7805068406</t>
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr"/>
@@ -9547,7 +9551,7 @@
       </c>
       <c r="H215" s="10" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>642</t>
         </is>
       </c>
       <c r="I215" s="10" t="inlineStr">
@@ -9557,7 +9561,7 @@
       </c>
       <c r="J215" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -9567,12 +9571,12 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>ООО «РОСТРА северо-запад»</t>
+          <t>ООО «ПЭС»</t>
         </is>
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>7805234942</t>
+          <t>7814677411</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr"/>
@@ -9585,7 +9589,7 @@
       </c>
       <c r="H216" s="10" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>654</t>
         </is>
       </c>
       <c r="I216" s="10" t="inlineStr">
@@ -9605,12 +9609,12 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСК «ОРДЕР» (реставрационно-строительная)</t>
+          <t>ООО «Паритет Плюс»</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>7801585837</t>
+          <t>7806471030</t>
         </is>
       </c>
       <c r="D217" s="13" t="inlineStr"/>
@@ -9623,7 +9627,7 @@
       </c>
       <c r="H217" s="10" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I217" s="10" t="inlineStr">
@@ -9633,7 +9637,7 @@
       </c>
       <c r="J217" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
@@ -9643,12 +9647,12 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСК «ТехноСтрой»</t>
+          <t>ООО «ПетроТрейд-инжиниринг»</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>7838061420</t>
+          <t>7802490056</t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr"/>
@@ -9661,7 +9665,7 @@
       </c>
       <c r="H218" s="10" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>771</t>
         </is>
       </c>
       <c r="I218" s="10" t="inlineStr">
@@ -9681,12 +9685,12 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСУ-9»</t>
+          <t>ООО «Портмарин Инжиниринг»</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>7814785030</t>
+          <t>7811777680</t>
         </is>
       </c>
       <c r="D219" s="13" t="inlineStr"/>
@@ -9699,7 +9703,7 @@
       </c>
       <c r="H219" s="10" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="I219" s="10" t="inlineStr">
@@ -9719,20 +9723,16 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСФ «Водолей плюс»</t>
+          <t>ООО «ПрогрессСтрой»</t>
         </is>
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>7826040578</t>
+          <t>7811604013</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr"/>
-      <c r="E220" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Б.Сампсониевский пр. 60И; ОГРН 1027810321659; ген.дир. Колосовская П.В.</t>
-        </is>
-      </c>
+      <c r="E220" s="11" t="inlineStr"/>
       <c r="F220" s="11" t="inlineStr"/>
       <c r="G220" s="11" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="I220" s="10" t="inlineStr">
@@ -9761,29 +9761,25 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>ООО «РестСтройГрупп»</t>
+          <t>ООО «ПромИнвест»</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>7839099924</t>
+          <t>7841439543</t>
         </is>
       </c>
       <c r="D221" s="13" t="inlineStr"/>
-      <c r="E221" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
-        </is>
-      </c>
+      <c r="E221" s="11" t="inlineStr"/>
       <c r="F221" s="11" t="inlineStr"/>
       <c r="G221" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I221" s="10" t="inlineStr">
@@ -9793,7 +9789,7 @@
       </c>
       <c r="J221" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9803,12 +9799,12 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>ООО «СВМ - Групп»</t>
+          <t>ООО «ПромСтрой»</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>7843014240</t>
+          <t>7806156944</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr"/>
@@ -9821,7 +9817,7 @@
       </c>
       <c r="H222" s="10" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I222" s="10" t="inlineStr">
@@ -9841,16 +9837,20 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>ООО «СГИ»</t>
+          <t>ООО «Промстрой»</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>7816654829</t>
+          <t>7814656860</t>
         </is>
       </c>
       <c r="D223" s="13" t="inlineStr"/>
-      <c r="E223" s="11" t="inlineStr"/>
+      <c r="E223" s="11" t="inlineStr">
+        <is>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+        </is>
+      </c>
       <c r="F223" s="11" t="inlineStr"/>
       <c r="G223" s="11" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="H223" s="10" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>516</t>
         </is>
       </c>
       <c r="I223" s="10" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="J223" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>ООО «СДК Лидер-Строй»</t>
+          <t>ООО «Промстройинжиниринг»</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>7806299036</t>
+          <t>7814349756</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr"/>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>797</t>
         </is>
       </c>
       <c r="I224" s="10" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЗ «Загородная, 71»</t>
+          <t>ООО «ПрофСтрой-И»</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>7817328112</t>
+          <t>7810682530</t>
         </is>
       </c>
       <c r="D225" s="13" t="inlineStr"/>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="H225" s="10" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I225" s="10" t="inlineStr">
@@ -9955,20 +9955,16 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Алстрой»</t>
+          <t>ООО «ПрофСтройАльянс»</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>7813417675</t>
+          <t>7842504114</t>
         </is>
       </c>
       <c r="D226" s="13" t="inlineStr"/>
-      <c r="E226" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
-        </is>
-      </c>
+      <c r="E226" s="11" t="inlineStr"/>
       <c r="F226" s="11" t="inlineStr"/>
       <c r="G226" s="11" t="inlineStr">
         <is>
@@ -9977,7 +9973,7 @@
       </c>
       <c r="H226" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I226" s="10" t="inlineStr">
@@ -9987,7 +9983,7 @@
       </c>
       <c r="J226" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9997,18 +9993,18 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Дальпитерстрой»</t>
+          <t>ООО «Профиль»</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>7842021879</t>
+          <t>7802182380</t>
         </is>
       </c>
       <c r="D227" s="13" t="inlineStr"/>
       <c r="E227" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.16Н; ОГРН 1157847026402; дир. Скоров М.А.</t>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
         </is>
       </c>
       <c r="F227" s="11" t="inlineStr"/>
@@ -10019,7 +10015,7 @@
       </c>
       <c r="H227" s="10" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>572</t>
         </is>
       </c>
       <c r="I227" s="10" t="inlineStr">
@@ -10029,7 +10025,7 @@
       </c>
       <c r="J227" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10035,12 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Орион»</t>
+          <t>ООО «РД»</t>
         </is>
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>7816699026</t>
+          <t>7810062946</t>
         </is>
       </c>
       <c r="D228" s="13" t="inlineStr"/>
@@ -10057,7 +10053,7 @@
       </c>
       <c r="H228" s="10" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>365</t>
         </is>
       </c>
       <c r="I228" s="10" t="inlineStr">
@@ -10077,18 +10073,18 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «РЕССТРОЙ»</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7820012849</t>
         </is>
       </c>
       <c r="D229" s="13" t="inlineStr"/>
       <c r="E229" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
         </is>
       </c>
       <c r="F229" s="11" t="inlineStr"/>
@@ -10099,7 +10095,7 @@
       </c>
       <c r="H229" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>713</t>
         </is>
       </c>
       <c r="I229" s="10" t="inlineStr">
@@ -10109,7 +10105,7 @@
       </c>
       <c r="J229" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10119,12 +10115,12 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «СтальСтрой»</t>
+          <t>ООО «РИАРДЕН»</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>7841052031</t>
+          <t>7814794789</t>
         </is>
       </c>
       <c r="D230" s="13" t="inlineStr"/>
@@ -10137,7 +10133,7 @@
       </c>
       <c r="H230" s="10" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>975</t>
         </is>
       </c>
       <c r="I230" s="10" t="inlineStr">
@@ -10157,12 +10153,12 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «СтиФ»</t>
+          <t>ООО «РК ДЕВЕЛОПМЕНТ»</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>7825475600</t>
+          <t>7814800834</t>
         </is>
       </c>
       <c r="D231" s="13" t="inlineStr"/>
@@ -10175,7 +10171,7 @@
       </c>
       <c r="H231" s="10" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>861</t>
         </is>
       </c>
       <c r="I231" s="10" t="inlineStr">
@@ -10185,7 +10181,7 @@
       </c>
       <c r="J231" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10195,16 +10191,20 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Стройнорд»</t>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>7811571992</t>
+          <t>7826123721</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr"/>
-      <c r="E232" s="11" t="inlineStr"/>
+      <c r="E232" s="11" t="inlineStr">
+        <is>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+        </is>
+      </c>
       <c r="F232" s="11" t="inlineStr"/>
       <c r="G232" s="11" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="H232" s="10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>515</t>
         </is>
       </c>
       <c r="I232" s="10" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="J232" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10233,20 +10233,16 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «РОНИС»</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7840475549</t>
         </is>
       </c>
       <c r="D233" s="13" t="inlineStr"/>
-      <c r="E233" s="11" t="inlineStr">
-        <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
-        </is>
-      </c>
+      <c r="E233" s="11" t="inlineStr"/>
       <c r="F233" s="11" t="inlineStr"/>
       <c r="G233" s="11" t="inlineStr">
         <is>
@@ -10255,7 +10251,7 @@
       </c>
       <c r="H233" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I233" s="10" t="inlineStr">
@@ -10265,7 +10261,7 @@
       </c>
       <c r="J233" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10271,12 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Меркурий»</t>
+          <t>ООО «РОСТРА северо-запад»</t>
         </is>
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>7819046339</t>
+          <t>7805234942</t>
         </is>
       </c>
       <c r="D234" s="13" t="inlineStr"/>
@@ -10293,7 +10289,7 @@
       </c>
       <c r="H234" s="10" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>714</t>
         </is>
       </c>
       <c r="I234" s="10" t="inlineStr">
@@ -10313,12 +10309,12 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПРАГМА СТРОЙ»</t>
+          <t>ООО «РСК «ОРДЕР» (реставрационно-строительная)</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>7802313956</t>
+          <t>7801585837</t>
         </is>
       </c>
       <c r="D235" s="13" t="inlineStr"/>
@@ -10331,7 +10327,7 @@
       </c>
       <c r="H235" s="10" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>603</t>
         </is>
       </c>
       <c r="I235" s="10" t="inlineStr">
@@ -10341,7 +10337,7 @@
       </c>
       <c r="J235" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10351,20 +10347,16 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «РСК «ТехноСтрой»</t>
         </is>
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7838061420</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr"/>
-      <c r="E236" s="11" t="inlineStr">
-        <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
-        </is>
-      </c>
+      <c r="E236" s="11" t="inlineStr"/>
       <c r="F236" s="11" t="inlineStr"/>
       <c r="G236" s="11" t="inlineStr">
         <is>
@@ -10373,7 +10365,7 @@
       </c>
       <c r="H236" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I236" s="10" t="inlineStr">
@@ -10383,7 +10375,7 @@
       </c>
       <c r="J236" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10393,12 +10385,12 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Профиль групп»</t>
+          <t>ООО «РСУ-9»</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>7802593414</t>
+          <t>7814785030</t>
         </is>
       </c>
       <c r="D237" s="13" t="inlineStr"/>
@@ -10411,7 +10403,7 @@
       </c>
       <c r="H237" s="10" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>799</t>
         </is>
       </c>
       <c r="I237" s="10" t="inlineStr">
@@ -10431,16 +10423,20 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК СФЕРА»</t>
+          <t>ООО «РСФ «Водолей плюс»</t>
         </is>
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>9715445653</t>
+          <t>7826040578</t>
         </is>
       </c>
       <c r="D238" s="13" t="inlineStr"/>
-      <c r="E238" s="11" t="inlineStr"/>
+      <c r="E238" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Б.Сампсониевский пр. 60И; ОГРН 1027810321659; ген.дир. Колосовская П.В.</t>
+        </is>
+      </c>
       <c r="F238" s="11" t="inlineStr"/>
       <c r="G238" s="11" t="inlineStr">
         <is>
@@ -10449,7 +10445,7 @@
       </c>
       <c r="H238" s="10" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>582</t>
         </is>
       </c>
       <c r="I238" s="10" t="inlineStr">
@@ -10469,25 +10465,29 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Стройкомплект»</t>
+          <t>ООО «РестСтройГрупп»</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>7806133873</t>
+          <t>7839099924</t>
         </is>
       </c>
       <c r="D239" s="13" t="inlineStr"/>
-      <c r="E239" s="11" t="inlineStr"/>
+      <c r="E239" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+        </is>
+      </c>
       <c r="F239" s="11" t="inlineStr"/>
       <c r="G239" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H239" s="10" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>673</t>
         </is>
       </c>
       <c r="I239" s="10" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="J239" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ТТ»</t>
+          <t>ООО «СВМ - Групп»</t>
         </is>
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>7813676373</t>
+          <t>7843014240</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr"/>
@@ -10525,7 +10525,7 @@
       </c>
       <c r="H240" s="10" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I240" s="10" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКМ»</t>
+          <t>ООО «СГИ»</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>7807239583</t>
+          <t>7816654829</t>
         </is>
       </c>
       <c r="D241" s="13" t="inlineStr"/>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="H241" s="10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="I241" s="10" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКН НВК»</t>
+          <t>ООО «СДК Лидер-Строй»</t>
         </is>
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>7838057216</t>
+          <t>7806299036</t>
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr"/>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="H242" s="10" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="I242" s="10" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКП»</t>
+          <t>ООО «СЗ «Загородная, 71»</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>7806619896</t>
+          <t>7817328112</t>
         </is>
       </c>
       <c r="D243" s="13" t="inlineStr"/>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="H243" s="10" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="I243" s="10" t="inlineStr">
@@ -10659,16 +10659,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>ООО «СМУ 8»</t>
+          <t>ООО «СК «Алстрой»</t>
         </is>
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>7810531355</t>
+          <t>7813417675</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr"/>
-      <c r="E244" s="11" t="inlineStr"/>
+      <c r="E244" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+        </is>
+      </c>
       <c r="F244" s="11" t="inlineStr"/>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -10677,7 +10681,7 @@
       </c>
       <c r="H244" s="10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>590</t>
         </is>
       </c>
       <c r="I244" s="10" t="inlineStr">
@@ -10687,7 +10691,7 @@
       </c>
       <c r="J244" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -10697,16 +10701,20 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПМК - 18»</t>
+          <t>ООО «СК «Дальпитерстрой»</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>7814624120</t>
+          <t>7842021879</t>
         </is>
       </c>
       <c r="D245" s="13" t="inlineStr"/>
-      <c r="E245" s="11" t="inlineStr"/>
+      <c r="E245" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.16Н; ОГРН 1157847026402; дир. Скоров М.А.</t>
+        </is>
+      </c>
       <c r="F245" s="11" t="inlineStr"/>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -10715,7 +10723,7 @@
       </c>
       <c r="H245" s="10" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>622</t>
         </is>
       </c>
       <c r="I245" s="10" t="inlineStr">
@@ -10735,20 +10743,16 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «СК «Орион»</t>
         </is>
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7816699026</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr"/>
-      <c r="E246" s="11" t="inlineStr">
-        <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
-        </is>
-      </c>
+      <c r="E246" s="11" t="inlineStr"/>
       <c r="F246" s="11" t="inlineStr"/>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -10757,7 +10761,7 @@
       </c>
       <c r="H246" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>969</t>
         </is>
       </c>
       <c r="I246" s="10" t="inlineStr">
@@ -10767,7 +10771,7 @@
       </c>
       <c r="J246" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10777,16 +10781,20 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОИТЕЛЬ»</t>
+          <t>ООО «СК «Потенциал»</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>7804338561</t>
+          <t>7814558855</t>
         </is>
       </c>
       <c r="D247" s="13" t="inlineStr"/>
-      <c r="E247" s="11" t="inlineStr"/>
+      <c r="E247" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
       <c r="F247" s="11" t="inlineStr"/>
       <c r="G247" s="11" t="inlineStr">
         <is>
@@ -10795,7 +10803,7 @@
       </c>
       <c r="H247" s="10" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>675</t>
         </is>
       </c>
       <c r="I247" s="10" t="inlineStr">
@@ -10805,7 +10813,7 @@
       </c>
       <c r="J247" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1700000</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10823,12 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙ КОРПУС»</t>
+          <t>ООО «СК «СтальСтрой»</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>7804553054</t>
+          <t>7841052031</t>
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr"/>
@@ -10833,7 +10841,7 @@
       </c>
       <c r="H248" s="10" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>439</t>
         </is>
       </c>
       <c r="I248" s="10" t="inlineStr">
@@ -10853,12 +10861,12 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙГРАД РСУ»</t>
+          <t>ООО «СК «СтиФ»</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>7802703995</t>
+          <t>7825475600</t>
         </is>
       </c>
       <c r="D249" s="13" t="inlineStr"/>
@@ -10871,7 +10879,7 @@
       </c>
       <c r="H249" s="10" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>581</t>
         </is>
       </c>
       <c r="I249" s="10" t="inlineStr">
@@ -10881,7 +10889,7 @@
       </c>
       <c r="J249" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -10891,20 +10899,16 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «СК «Стройнорд»</t>
         </is>
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7811571992</t>
         </is>
       </c>
       <c r="D250" s="13" t="inlineStr"/>
-      <c r="E250" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
-        </is>
-      </c>
+      <c r="E250" s="11" t="inlineStr"/>
       <c r="F250" s="11" t="inlineStr"/>
       <c r="G250" s="11" t="inlineStr">
         <is>
@@ -10913,7 +10917,7 @@
       </c>
       <c r="H250" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>549</t>
         </is>
       </c>
       <c r="I250" s="10" t="inlineStr">
@@ -10923,7 +10927,7 @@
       </c>
       <c r="J250" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10933,16 +10937,20 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОНСУЛЬТ»</t>
+          <t>ООО «СК Гарант»</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>7810289545</t>
+          <t>7806380022</t>
         </is>
       </c>
       <c r="D251" s="13" t="inlineStr"/>
-      <c r="E251" s="11" t="inlineStr"/>
+      <c r="E251" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+        </is>
+      </c>
       <c r="F251" s="11" t="inlineStr"/>
       <c r="G251" s="11" t="inlineStr">
         <is>
@@ -10951,7 +10959,7 @@
       </c>
       <c r="H251" s="10" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I251" s="10" t="inlineStr">
@@ -10961,7 +10969,7 @@
       </c>
       <c r="J251" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -10971,20 +10979,16 @@
       </c>
       <c r="B252" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «СК Меркурий»</t>
         </is>
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7819046339</t>
         </is>
       </c>
       <c r="D252" s="13" t="inlineStr"/>
-      <c r="E252" s="11" t="inlineStr">
-        <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
-        </is>
-      </c>
+      <c r="E252" s="11" t="inlineStr"/>
       <c r="F252" s="11" t="inlineStr"/>
       <c r="G252" s="11" t="inlineStr">
         <is>
@@ -10993,7 +10997,7 @@
       </c>
       <c r="H252" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>983</t>
         </is>
       </c>
       <c r="I252" s="10" t="inlineStr">
@@ -11003,7 +11007,7 @@
       </c>
       <c r="J252" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11013,20 +11017,16 @@
       </c>
       <c r="B253" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «СК ПРАГМА СТРОЙ»</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7802313956</t>
         </is>
       </c>
       <c r="D253" s="13" t="inlineStr"/>
-      <c r="E253" s="11" t="inlineStr">
-        <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
-        </is>
-      </c>
+      <c r="E253" s="11" t="inlineStr"/>
       <c r="F253" s="11" t="inlineStr"/>
       <c r="G253" s="11" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
       </c>
       <c r="H253" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>737</t>
         </is>
       </c>
       <c r="I253" s="10" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="J253" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11055,18 +11055,18 @@
       </c>
       <c r="B254" s="11" t="inlineStr">
         <is>
-          <t>ООО «СФ «Новэк»</t>
+          <t>ООО «СК ПСП»</t>
         </is>
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>7825128540</t>
+          <t>7810502379</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr"/>
       <c r="E254" s="11" t="inlineStr">
         <is>
-          <t>194352 СПб, ул.Кустодиева 17А; ОГРН 1027809227907; ген.дир. Смирнов Д.И.</t>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
         </is>
       </c>
       <c r="F254" s="11" t="inlineStr"/>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="H254" s="10" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>527</t>
         </is>
       </c>
       <c r="I254" s="10" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="J254" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11097,29 +11097,25 @@
       </c>
       <c r="B255" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «СК Профиль групп»</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7802593414</t>
         </is>
       </c>
       <c r="D255" s="13" t="inlineStr"/>
-      <c r="E255" s="11" t="inlineStr">
-        <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
-        </is>
-      </c>
+      <c r="E255" s="11" t="inlineStr"/>
       <c r="F255" s="11" t="inlineStr"/>
       <c r="G255" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H255" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>576</t>
         </is>
       </c>
       <c r="I255" s="10" t="inlineStr">
@@ -11129,7 +11125,7 @@
       </c>
       <c r="J255" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11139,12 +11135,12 @@
       </c>
       <c r="B256" s="11" t="inlineStr">
         <is>
-          <t>ООО «Свой Дом»</t>
+          <t>ООО «СК СФЕРА»</t>
         </is>
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>7813322254</t>
+          <t>9715445653</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr"/>
@@ -11157,7 +11153,7 @@
       </c>
       <c r="H256" s="10" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="I256" s="10" t="inlineStr">
@@ -11167,7 +11163,7 @@
       </c>
       <c r="J256" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11177,29 +11173,25 @@
       </c>
       <c r="B257" s="11" t="inlineStr">
         <is>
-          <t>ООО «СиФ»</t>
+          <t>ООО «СК Стройкомплект»</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>7801075307</t>
+          <t>7806133873</t>
         </is>
       </c>
       <c r="D257" s="13" t="inlineStr"/>
-      <c r="E257" s="11" t="inlineStr">
-        <is>
-          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
-        </is>
-      </c>
+      <c r="E257" s="11" t="inlineStr"/>
       <c r="F257" s="11" t="inlineStr"/>
       <c r="G257" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H257" s="10" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>641</t>
         </is>
       </c>
       <c r="I257" s="10" t="inlineStr">
@@ -11209,7 +11201,7 @@
       </c>
       <c r="J257" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11219,12 +11211,12 @@
       </c>
       <c r="B258" s="11" t="inlineStr">
         <is>
-          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
+          <t>ООО «СК ТТ»</t>
         </is>
       </c>
       <c r="C258" s="12" t="inlineStr">
         <is>
-          <t>7810691246</t>
+          <t>7813676373</t>
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr"/>
@@ -11237,7 +11229,7 @@
       </c>
       <c r="H258" s="10" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="I258" s="10" t="inlineStr">
@@ -11257,12 +11249,12 @@
       </c>
       <c r="B259" s="11" t="inlineStr">
         <is>
-          <t>ООО «Синергия»</t>
+          <t>ООО «СКМ»</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>7841100278</t>
+          <t>7807239583</t>
         </is>
       </c>
       <c r="D259" s="13" t="inlineStr"/>
@@ -11275,7 +11267,7 @@
       </c>
       <c r="H259" s="10" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I259" s="10" t="inlineStr">
@@ -11295,29 +11287,25 @@
       </c>
       <c r="B260" s="11" t="inlineStr">
         <is>
-          <t>ООО «СносСтройИнвест»</t>
+          <t>ООО «СКН НВК»</t>
         </is>
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>7805239355</t>
+          <t>7838057216</t>
         </is>
       </c>
       <c r="D260" s="13" t="inlineStr"/>
-      <c r="E260" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E260" s="11" t="inlineStr"/>
       <c r="F260" s="11" t="inlineStr"/>
       <c r="G260" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H260" s="10" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>629</t>
         </is>
       </c>
       <c r="I260" s="10" t="inlineStr">
@@ -11337,12 +11325,12 @@
       </c>
       <c r="B261" s="11" t="inlineStr">
         <is>
-          <t>ООО «СпецСтрой»</t>
+          <t>ООО «СКП»</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>7802753883</t>
+          <t>7806619896</t>
         </is>
       </c>
       <c r="D261" s="13" t="inlineStr"/>
@@ -11355,7 +11343,7 @@
       </c>
       <c r="H261" s="10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="I261" s="10" t="inlineStr">
@@ -11375,12 +11363,12 @@
       </c>
       <c r="B262" s="11" t="inlineStr">
         <is>
-          <t>ООО «СпецТехнологии»</t>
+          <t>ООО «СМУ 8»</t>
         </is>
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>7839332955</t>
+          <t>7810531355</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr"/>
@@ -11393,7 +11381,7 @@
       </c>
       <c r="H262" s="10" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>367</t>
         </is>
       </c>
       <c r="I262" s="10" t="inlineStr">
@@ -11403,7 +11391,7 @@
       </c>
       <c r="J262" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11413,12 +11401,12 @@
       </c>
       <c r="B263" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецмонтаж»</t>
+          <t>ООО «СПМК - 18»</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>7806403311</t>
+          <t>7814624120</t>
         </is>
       </c>
       <c r="D263" s="13" t="inlineStr"/>
@@ -11431,7 +11419,7 @@
       </c>
       <c r="H263" s="10" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>537</t>
         </is>
       </c>
       <c r="I263" s="10" t="inlineStr">
@@ -11451,16 +11439,20 @@
       </c>
       <c r="B264" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецстрой»</t>
+          <t>ООО «СПбЭК-Майнинг»</t>
         </is>
       </c>
       <c r="C264" s="12" t="inlineStr">
         <is>
-          <t>7802182340</t>
+          <t>7820326027</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr"/>
-      <c r="E264" s="11" t="inlineStr"/>
+      <c r="E264" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
       <c r="F264" s="11" t="inlineStr"/>
       <c r="G264" s="11" t="inlineStr">
         <is>
@@ -11469,7 +11461,7 @@
       </c>
       <c r="H264" s="10" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>548</t>
         </is>
       </c>
       <c r="I264" s="10" t="inlineStr">
@@ -11479,7 +11471,7 @@
       </c>
       <c r="J264" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11489,20 +11481,16 @@
       </c>
       <c r="B265" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецстроймонтаж»</t>
+          <t>ООО «СТРОИТЕЛЬ»</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>7826156798</t>
+          <t>7804338561</t>
         </is>
       </c>
       <c r="D265" s="13" t="inlineStr"/>
-      <c r="E265" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E265" s="11" t="inlineStr"/>
       <c r="F265" s="11" t="inlineStr"/>
       <c r="G265" s="11" t="inlineStr">
         <is>
@@ -11511,7 +11499,7 @@
       </c>
       <c r="H265" s="10" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>678</t>
         </is>
       </c>
       <c r="I265" s="10" t="inlineStr">
@@ -11521,7 +11509,7 @@
       </c>
       <c r="J265" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11519,12 @@
       </c>
       <c r="B266" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительная компания «ДМ»</t>
+          <t>ООО «СТРОЙ КОРПУС»</t>
         </is>
       </c>
       <c r="C266" s="12" t="inlineStr">
         <is>
-          <t>4703058442</t>
+          <t>7804553054</t>
         </is>
       </c>
       <c r="D266" s="13" t="inlineStr"/>
@@ -11549,7 +11537,7 @@
       </c>
       <c r="H266" s="10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>679</t>
         </is>
       </c>
       <c r="I266" s="10" t="inlineStr">
@@ -11569,12 +11557,12 @@
       </c>
       <c r="B267" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительное дело-СГ»</t>
+          <t>ООО «СТРОЙГРАД РСУ»</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>7826005559</t>
+          <t>7802703995</t>
         </is>
       </c>
       <c r="D267" s="13" t="inlineStr"/>
@@ -11587,7 +11575,7 @@
       </c>
       <c r="H267" s="10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>877</t>
         </is>
       </c>
       <c r="I267" s="10" t="inlineStr">
@@ -11607,16 +11595,20 @@
       </c>
       <c r="B268" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные решения»</t>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
         </is>
       </c>
       <c r="C268" s="12" t="inlineStr">
         <is>
-          <t>7840099703</t>
+          <t>7825055370</t>
         </is>
       </c>
       <c r="D268" s="13" t="inlineStr"/>
-      <c r="E268" s="11" t="inlineStr"/>
+      <c r="E268" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
       <c r="F268" s="11" t="inlineStr"/>
       <c r="G268" s="11" t="inlineStr">
         <is>
@@ -11625,7 +11617,7 @@
       </c>
       <c r="H268" s="10" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>573</t>
         </is>
       </c>
       <c r="I268" s="10" t="inlineStr">
@@ -11635,7 +11627,7 @@
       </c>
       <c r="J268" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -11645,20 +11637,16 @@
       </c>
       <c r="B269" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «СТРОЙКОНСУЛЬТ»</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7810289545</t>
         </is>
       </c>
       <c r="D269" s="13" t="inlineStr"/>
-      <c r="E269" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
-        </is>
-      </c>
+      <c r="E269" s="11" t="inlineStr"/>
       <c r="F269" s="11" t="inlineStr"/>
       <c r="G269" s="11" t="inlineStr">
         <is>
@@ -11667,7 +11655,7 @@
       </c>
       <c r="H269" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>672</t>
         </is>
       </c>
       <c r="I269" s="10" t="inlineStr">
@@ -11677,7 +11665,7 @@
       </c>
       <c r="J269" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11687,16 +11675,20 @@
       </c>
       <c r="B270" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «СУ-17»</t>
         </is>
       </c>
       <c r="C270" s="12" t="inlineStr">
         <is>
-          <t>7802880338</t>
+          <t>7807028906</t>
         </is>
       </c>
       <c r="D270" s="13" t="inlineStr"/>
-      <c r="E270" s="11" t="inlineStr"/>
+      <c r="E270" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
       <c r="F270" s="11" t="inlineStr"/>
       <c r="G270" s="11" t="inlineStr">
         <is>
@@ -11705,7 +11697,7 @@
       </c>
       <c r="H270" s="10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>747</t>
         </is>
       </c>
       <c r="I270" s="10" t="inlineStr">
@@ -11715,7 +11707,7 @@
       </c>
       <c r="J270" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2300000</t>
         </is>
       </c>
     </row>
@@ -11725,16 +11717,20 @@
       </c>
       <c r="B271" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительный Цех»</t>
+          <t>ООО «СУАР-Групп»</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>7842391502</t>
+          <t>7802270195</t>
         </is>
       </c>
       <c r="D271" s="13" t="inlineStr"/>
-      <c r="E271" s="11" t="inlineStr"/>
+      <c r="E271" s="11" t="inlineStr">
+        <is>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
+        </is>
+      </c>
       <c r="F271" s="11" t="inlineStr"/>
       <c r="G271" s="11" t="inlineStr">
         <is>
@@ -11743,7 +11739,7 @@
       </c>
       <c r="H271" s="10" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>518</t>
         </is>
       </c>
       <c r="I271" s="10" t="inlineStr">
@@ -11753,7 +11749,7 @@
       </c>
       <c r="J271" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -11763,29 +11759,29 @@
       </c>
       <c r="B272" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй центр»</t>
+          <t>ООО «СФ «Новэк»</t>
         </is>
       </c>
       <c r="C272" s="12" t="inlineStr">
         <is>
-          <t>7804538240</t>
+          <t>7825128540</t>
         </is>
       </c>
       <c r="D272" s="13" t="inlineStr"/>
       <c r="E272" s="11" t="inlineStr">
         <is>
-          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+          <t>194352 СПб, ул.Кустодиева 17А; ОГРН 1027809227907; ген.дир. Смирнов Д.И.</t>
         </is>
       </c>
       <c r="F272" s="11" t="inlineStr"/>
       <c r="G272" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H272" s="10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>512</t>
         </is>
       </c>
       <c r="I272" s="10" t="inlineStr">
@@ -11795,7 +11791,7 @@
       </c>
       <c r="J272" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11805,25 +11801,29 @@
       </c>
       <c r="B273" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй-Импульс»</t>
+          <t>ООО «СЭМ»</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>7806313724</t>
+          <t>7810201646</t>
         </is>
       </c>
       <c r="D273" s="13" t="inlineStr"/>
-      <c r="E273" s="11" t="inlineStr"/>
+      <c r="E273" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
       <c r="F273" s="11" t="inlineStr"/>
       <c r="G273" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H273" s="10" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>700</t>
         </is>
       </c>
       <c r="I273" s="10" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="J273" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -11843,12 +11843,12 @@
       </c>
       <c r="B274" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй-С»</t>
+          <t>ООО «Свой Дом»</t>
         </is>
       </c>
       <c r="C274" s="12" t="inlineStr">
         <is>
-          <t>7802373183</t>
+          <t>7813322254</t>
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr"/>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="H274" s="10" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>591</t>
         </is>
       </c>
       <c r="I274" s="10" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="J274" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11881,25 +11881,29 @@
       </c>
       <c r="B275" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «СиФ»</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7801075307</t>
         </is>
       </c>
       <c r="D275" s="13" t="inlineStr"/>
-      <c r="E275" s="11" t="inlineStr"/>
+      <c r="E275" s="11" t="inlineStr">
+        <is>
+          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
+        </is>
+      </c>
       <c r="F275" s="11" t="inlineStr"/>
       <c r="G275" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H275" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I275" s="10" t="inlineStr">
@@ -11909,7 +11913,7 @@
       </c>
       <c r="J275" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11923,12 @@
       </c>
       <c r="B276" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройКом»</t>
+          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
         </is>
       </c>
       <c r="C276" s="12" t="inlineStr">
         <is>
-          <t>7811469780</t>
+          <t>7810691246</t>
         </is>
       </c>
       <c r="D276" s="13" t="inlineStr"/>
@@ -11937,7 +11941,7 @@
       </c>
       <c r="H276" s="10" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>588</t>
         </is>
       </c>
       <c r="I276" s="10" t="inlineStr">
@@ -11957,12 +11961,12 @@
       </c>
       <c r="B277" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройПроект»</t>
+          <t>ООО «Синергия»</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>7804554072</t>
+          <t>7841100278</t>
         </is>
       </c>
       <c r="D277" s="13" t="inlineStr"/>
@@ -11975,7 +11979,7 @@
       </c>
       <c r="H277" s="10" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="I277" s="10" t="inlineStr">
@@ -11995,25 +11999,29 @@
       </c>
       <c r="B278" s="11" t="inlineStr">
         <is>
-          <t>ООО «Стройперспектива»</t>
+          <t>ООО «СносСтройИнвест»</t>
         </is>
       </c>
       <c r="C278" s="12" t="inlineStr">
         <is>
-          <t>7810740278</t>
+          <t>7805239355</t>
         </is>
       </c>
       <c r="D278" s="13" t="inlineStr"/>
-      <c r="E278" s="11" t="inlineStr"/>
+      <c r="E278" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
+        </is>
+      </c>
       <c r="F278" s="11" t="inlineStr"/>
       <c r="G278" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H278" s="10" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>351</t>
         </is>
       </c>
       <c r="I278" s="10" t="inlineStr">
@@ -12033,12 +12041,12 @@
       </c>
       <c r="B279" s="11" t="inlineStr">
         <is>
-          <t>ООО «СулуС»</t>
+          <t>ООО «СпецСтрой»</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>7801369120</t>
+          <t>7802753883</t>
         </is>
       </c>
       <c r="D279" s="13" t="inlineStr"/>
@@ -12051,7 +12059,7 @@
       </c>
       <c r="H279" s="10" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>267</t>
         </is>
       </c>
       <c r="I279" s="10" t="inlineStr">
@@ -12071,20 +12079,16 @@
       </c>
       <c r="B280" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «СпецТехнологии»</t>
         </is>
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7839332955</t>
         </is>
       </c>
       <c r="D280" s="13" t="inlineStr"/>
-      <c r="E280" s="11" t="inlineStr">
-        <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
-        </is>
-      </c>
+      <c r="E280" s="11" t="inlineStr"/>
       <c r="F280" s="11" t="inlineStr"/>
       <c r="G280" s="11" t="inlineStr">
         <is>
@@ -12093,7 +12097,7 @@
       </c>
       <c r="H280" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>680</t>
         </is>
       </c>
       <c r="I280" s="10" t="inlineStr">
@@ -12103,7 +12107,7 @@
       </c>
       <c r="J280" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -12113,20 +12117,16 @@
       </c>
       <c r="B281" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТАЛИОН»</t>
+          <t>ООО «Спецмонтаж»</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>7801569190</t>
+          <t>7806403311</t>
         </is>
       </c>
       <c r="D281" s="13" t="inlineStr"/>
-      <c r="E281" s="11" t="inlineStr">
-        <is>
-          <t>197229 СПб, ул.Новая 51к1 пом.7-Н; ОГРН 1127847128639; ген.дир. Марков А.А.; техконтроль/испытания</t>
-        </is>
-      </c>
+      <c r="E281" s="11" t="inlineStr"/>
       <c r="F281" s="11" t="inlineStr"/>
       <c r="G281" s="11" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="H281" s="10" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>526</t>
         </is>
       </c>
       <c r="I281" s="10" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="J281" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -12155,12 +12155,12 @@
       </c>
       <c r="B282" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТД «Буревестник»</t>
+          <t>ООО «Спецстрой»</t>
         </is>
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>4705075034</t>
+          <t>7802182340</t>
         </is>
       </c>
       <c r="D282" s="13" t="inlineStr"/>
@@ -12173,7 +12173,7 @@
       </c>
       <c r="H282" s="10" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>521</t>
         </is>
       </c>
       <c r="I282" s="10" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="J282" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -12193,29 +12193,29 @@
       </c>
       <c r="B283" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕЗИС»</t>
+          <t>ООО «Спецстроймонтаж»</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>7804441209</t>
+          <t>7826156798</t>
         </is>
       </c>
       <c r="D283" s="13" t="inlineStr"/>
       <c r="E283" s="11" t="inlineStr">
         <is>
-          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
         </is>
       </c>
       <c r="F283" s="11" t="inlineStr"/>
       <c r="G283" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H283" s="10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>505</t>
         </is>
       </c>
       <c r="I283" s="10" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="J283" s="10" t="inlineStr">
         <is>
-          <t>700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12235,12 +12235,12 @@
       </c>
       <c r="B284" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕХНОТРАНССТРОЙ»</t>
+          <t>ООО «Строительная компания «ДМ»</t>
         </is>
       </c>
       <c r="C284" s="12" t="inlineStr">
         <is>
-          <t>5190067514</t>
+          <t>4703058442</t>
         </is>
       </c>
       <c r="D284" s="13" t="inlineStr"/>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="H284" s="10" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>252</t>
         </is>
       </c>
       <c r="I284" s="10" t="inlineStr">
@@ -12273,20 +12273,16 @@
       </c>
       <c r="B285" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «Строительное дело-СГ»</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7826005559</t>
         </is>
       </c>
       <c r="D285" s="13" t="inlineStr"/>
-      <c r="E285" s="11" t="inlineStr">
-        <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
-        </is>
-      </c>
+      <c r="E285" s="11" t="inlineStr"/>
       <c r="F285" s="11" t="inlineStr"/>
       <c r="G285" s="11" t="inlineStr">
         <is>
@@ -12295,7 +12291,7 @@
       </c>
       <c r="H285" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>242</t>
         </is>
       </c>
       <c r="I285" s="10" t="inlineStr">
@@ -12305,7 +12301,7 @@
       </c>
       <c r="J285" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12315,12 +12311,12 @@
       </c>
       <c r="B286" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТМС»</t>
+          <t>ООО «Строительные решения»</t>
         </is>
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>7801629643</t>
+          <t>7840099703</t>
         </is>
       </c>
       <c r="D286" s="13" t="inlineStr"/>
@@ -12333,7 +12329,7 @@
       </c>
       <c r="H286" s="10" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="I286" s="10" t="inlineStr">
@@ -12353,16 +12349,20 @@
       </c>
       <c r="B287" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТСК «ОЛИМП»</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>4205310949</t>
+          <t>7813680179</t>
         </is>
       </c>
       <c r="D287" s="13" t="inlineStr"/>
-      <c r="E287" s="11" t="inlineStr"/>
+      <c r="E287" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+        </is>
+      </c>
       <c r="F287" s="11" t="inlineStr"/>
       <c r="G287" s="11" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="H287" s="10" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="I287" s="10" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="J287" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -12391,20 +12391,16 @@
       </c>
       <c r="B288" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C288" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7802880338</t>
         </is>
       </c>
       <c r="D288" s="13" t="inlineStr"/>
-      <c r="E288" s="11" t="inlineStr">
-        <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
-        </is>
-      </c>
+      <c r="E288" s="11" t="inlineStr"/>
       <c r="F288" s="11" t="inlineStr"/>
       <c r="G288" s="11" t="inlineStr">
         <is>
@@ -12413,7 +12409,7 @@
       </c>
       <c r="H288" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>239</t>
         </is>
       </c>
       <c r="I288" s="10" t="inlineStr">
@@ -12423,7 +12419,7 @@
       </c>
       <c r="J288" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12433,12 +12429,12 @@
       </c>
       <c r="B289" s="11" t="inlineStr">
         <is>
-          <t>ООО «Текманн»</t>
+          <t>ООО «Строительный Цех»</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>7842508750</t>
+          <t>7842391502</t>
         </is>
       </c>
       <c r="D289" s="13" t="inlineStr"/>
@@ -12451,7 +12447,7 @@
       </c>
       <c r="H289" s="10" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>554</t>
         </is>
       </c>
       <c r="I289" s="10" t="inlineStr">
@@ -12461,7 +12457,7 @@
       </c>
       <c r="J289" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -12471,25 +12467,29 @@
       </c>
       <c r="B290" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТехЭнерго»</t>
+          <t>ООО «Строй центр»</t>
         </is>
       </c>
       <c r="C290" s="12" t="inlineStr">
         <is>
-          <t>7816531513</t>
+          <t>7804538240</t>
         </is>
       </c>
       <c r="D290" s="13" t="inlineStr"/>
-      <c r="E290" s="11" t="inlineStr"/>
+      <c r="E290" s="11" t="inlineStr">
+        <is>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
+        </is>
+      </c>
       <c r="F290" s="11" t="inlineStr"/>
       <c r="G290" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H290" s="10" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>732</t>
         </is>
       </c>
       <c r="I290" s="10" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="J290" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -12509,12 +12509,12 @@
       </c>
       <c r="B291" s="11" t="inlineStr">
         <is>
-          <t>ООО «Технические Системы»</t>
+          <t>ООО «Строй-Импульс»</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>7807345648</t>
+          <t>7806313724</t>
         </is>
       </c>
       <c r="D291" s="13" t="inlineStr"/>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="H291" s="10" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="I291" s="10" t="inlineStr">
@@ -12547,12 +12547,12 @@
       </c>
       <c r="B292" s="11" t="inlineStr">
         <is>
-          <t>ООО «Техно Эйр Групп»</t>
+          <t>ООО «Строй-С»</t>
         </is>
       </c>
       <c r="C292" s="12" t="inlineStr">
         <is>
-          <t>7816594954</t>
+          <t>7802373183</t>
         </is>
       </c>
       <c r="D292" s="13" t="inlineStr"/>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="H292" s="10" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>599</t>
         </is>
       </c>
       <c r="I292" s="10" t="inlineStr">
@@ -12585,20 +12585,16 @@
       </c>
       <c r="B293" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «СтройГрад»</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7813692632</t>
         </is>
       </c>
       <c r="D293" s="13" t="inlineStr"/>
-      <c r="E293" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
-        </is>
-      </c>
+      <c r="E293" s="11" t="inlineStr"/>
       <c r="F293" s="11" t="inlineStr"/>
       <c r="G293" s="11" t="inlineStr">
         <is>
@@ -12607,7 +12603,7 @@
       </c>
       <c r="H293" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="I293" s="10" t="inlineStr">
@@ -12617,7 +12613,7 @@
       </c>
       <c r="J293" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -12627,20 +12623,16 @@
       </c>
       <c r="B294" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трест «Сантехмонтаж-1»</t>
+          <t>ООО «СтройКом»</t>
         </is>
       </c>
       <c r="C294" s="12" t="inlineStr">
         <is>
-          <t>4706050882</t>
+          <t>7811469780</t>
         </is>
       </c>
       <c r="D294" s="13" t="inlineStr"/>
-      <c r="E294" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Мытнинская 12/44А пом.13н оф.14; ОГРН 1224700013230; сантехмонтаж, вентиляция, ИТП</t>
-        </is>
-      </c>
+      <c r="E294" s="11" t="inlineStr"/>
       <c r="F294" s="11" t="inlineStr"/>
       <c r="G294" s="11" t="inlineStr">
         <is>
@@ -12649,7 +12641,7 @@
       </c>
       <c r="H294" s="10" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>602</t>
         </is>
       </c>
       <c r="I294" s="10" t="inlineStr">
@@ -12669,20 +12661,16 @@
       </c>
       <c r="B295" s="11" t="inlineStr">
         <is>
-          <t>ООО «УМ «Эталон»</t>
+          <t>ООО «СтройПроект»</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>7810048170</t>
+          <t>7804554072</t>
         </is>
       </c>
       <c r="D295" s="13" t="inlineStr"/>
-      <c r="E295" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Богатырский пр. 2А каб.0.09; ОГРН 1057813303767; ген.дир. Харитонов О.В.; башенные краны; УК 463 млн</t>
-        </is>
-      </c>
+      <c r="E295" s="11" t="inlineStr"/>
       <c r="F295" s="11" t="inlineStr"/>
       <c r="G295" s="11" t="inlineStr">
         <is>
@@ -12691,7 +12679,7 @@
       </c>
       <c r="H295" s="10" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>291</t>
         </is>
       </c>
       <c r="I295" s="10" t="inlineStr">
@@ -12701,7 +12689,7 @@
       </c>
       <c r="J295" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12711,12 +12699,12 @@
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>ООО «УМ-11»</t>
+          <t>ООО «Стройперспектива»</t>
         </is>
       </c>
       <c r="C296" s="12" t="inlineStr">
         <is>
-          <t>7805802232</t>
+          <t>7810740278</t>
         </is>
       </c>
       <c r="D296" s="13" t="inlineStr"/>
@@ -12729,7 +12717,7 @@
       </c>
       <c r="H296" s="10" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>932</t>
         </is>
       </c>
       <c r="I296" s="10" t="inlineStr">
@@ -12749,12 +12737,12 @@
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>ООО «УСН»</t>
+          <t>ООО «СулуС»</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>7819306040</t>
+          <t>7801369120</t>
         </is>
       </c>
       <c r="D297" s="13" t="inlineStr"/>
@@ -12767,7 +12755,7 @@
       </c>
       <c r="H297" s="10" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>754</t>
         </is>
       </c>
       <c r="I297" s="10" t="inlineStr">
@@ -12787,16 +12775,20 @@
       </c>
       <c r="B298" s="11" t="inlineStr">
         <is>
-          <t>ООО «Универсалстрой»</t>
+          <t>ООО «Сфера»</t>
         </is>
       </c>
       <c r="C298" s="12" t="inlineStr">
         <is>
-          <t>7801227091</t>
+          <t>2311308786</t>
         </is>
       </c>
       <c r="D298" s="13" t="inlineStr"/>
-      <c r="E298" s="11" t="inlineStr"/>
+      <c r="E298" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
       <c r="F298" s="11" t="inlineStr"/>
       <c r="G298" s="11" t="inlineStr">
         <is>
@@ -12805,7 +12797,7 @@
       </c>
       <c r="H298" s="10" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="I298" s="10" t="inlineStr">
@@ -12815,7 +12807,7 @@
       </c>
       <c r="J298" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -12825,16 +12817,20 @@
       </c>
       <c r="B299" s="11" t="inlineStr">
         <is>
-          <t>ООО «ФОРЕСТ ДОРС»</t>
+          <t>ООО «ТАЛИОН»</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>7820045700</t>
+          <t>7801569190</t>
         </is>
       </c>
       <c r="D299" s="13" t="inlineStr"/>
-      <c r="E299" s="11" t="inlineStr"/>
+      <c r="E299" s="11" t="inlineStr">
+        <is>
+          <t>197229 СПб, ул.Новая 51к1 пом.7-Н; ОГРН 1127847128639; ген.дир. Марков А.А.; техконтроль/испытания</t>
+        </is>
+      </c>
       <c r="F299" s="11" t="inlineStr"/>
       <c r="G299" s="11" t="inlineStr">
         <is>
@@ -12843,7 +12839,7 @@
       </c>
       <c r="H299" s="10" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="I299" s="10" t="inlineStr">
@@ -12853,7 +12849,7 @@
       </c>
       <c r="J299" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12863,12 +12859,12 @@
       </c>
       <c r="B300" s="11" t="inlineStr">
         <is>
-          <t>ООО «ФОРТИС»</t>
+          <t>ООО «ТД «Буревестник»</t>
         </is>
       </c>
       <c r="C300" s="12" t="inlineStr">
         <is>
-          <t>7817119800</t>
+          <t>4705075034</t>
         </is>
       </c>
       <c r="D300" s="13" t="inlineStr"/>
@@ -12881,7 +12877,7 @@
       </c>
       <c r="H300" s="10" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="I300" s="10" t="inlineStr">
@@ -12901,25 +12897,29 @@
       </c>
       <c r="B301" s="11" t="inlineStr">
         <is>
-          <t>ООО «Холодпроф»</t>
+          <t>ООО «ТЕЗИС»</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>7842418360</t>
+          <t>7804441209</t>
         </is>
       </c>
       <c r="D301" s="13" t="inlineStr"/>
-      <c r="E301" s="11" t="inlineStr"/>
+      <c r="E301" s="11" t="inlineStr">
+        <is>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+        </is>
+      </c>
       <c r="F301" s="11" t="inlineStr"/>
       <c r="G301" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H301" s="10" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>674</t>
         </is>
       </c>
       <c r="I301" s="10" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="J301" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>700000</t>
         </is>
       </c>
     </row>
@@ -12939,20 +12939,16 @@
       </c>
       <c r="B302" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «ТЕХНОТРАНССТРОЙ»</t>
         </is>
       </c>
       <c r="C302" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>5190067514</t>
         </is>
       </c>
       <c r="D302" s="13" t="inlineStr"/>
-      <c r="E302" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
-        </is>
-      </c>
+      <c r="E302" s="11" t="inlineStr"/>
       <c r="F302" s="11" t="inlineStr"/>
       <c r="G302" s="11" t="inlineStr">
         <is>
@@ -12961,7 +12957,7 @@
       </c>
       <c r="H302" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>787</t>
         </is>
       </c>
       <c r="I302" s="10" t="inlineStr">
@@ -12971,7 +12967,7 @@
       </c>
       <c r="J302" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12981,16 +12977,20 @@
       </c>
       <c r="B303" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦИКЛОН»</t>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>7801225591</t>
+          <t>7814612968</t>
         </is>
       </c>
       <c r="D303" s="13" t="inlineStr"/>
-      <c r="E303" s="11" t="inlineStr"/>
+      <c r="E303" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
       <c r="F303" s="11" t="inlineStr"/>
       <c r="G303" s="11" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="H303" s="10" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>335</t>
         </is>
       </c>
       <c r="I303" s="10" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="J303" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -13019,12 +13019,12 @@
       </c>
       <c r="B304" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦИТАДЕЛЬ»</t>
+          <t>ООО «ТМС»</t>
         </is>
       </c>
       <c r="C304" s="12" t="inlineStr">
         <is>
-          <t>7817122190</t>
+          <t>7801629643</t>
         </is>
       </c>
       <c r="D304" s="13" t="inlineStr"/>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="H304" s="10" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I304" s="10" t="inlineStr">
@@ -13057,20 +13057,16 @@
       </c>
       <c r="B305" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «ТСК «ОЛИМП»</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>4205310949</t>
         </is>
       </c>
       <c r="D305" s="13" t="inlineStr"/>
-      <c r="E305" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
-        </is>
-      </c>
+      <c r="E305" s="11" t="inlineStr"/>
       <c r="F305" s="11" t="inlineStr"/>
       <c r="G305" s="11" t="inlineStr">
         <is>
@@ -13079,7 +13075,7 @@
       </c>
       <c r="H305" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>244</t>
         </is>
       </c>
       <c r="I305" s="10" t="inlineStr">
@@ -13089,7 +13085,7 @@
       </c>
       <c r="J305" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13099,29 +13095,29 @@
       </c>
       <c r="B306" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
         </is>
       </c>
       <c r="C306" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7839061021</t>
         </is>
       </c>
       <c r="D306" s="13" t="inlineStr"/>
       <c r="E306" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
         </is>
       </c>
       <c r="F306" s="11" t="inlineStr"/>
       <c r="G306" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H306" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I306" s="10" t="inlineStr">
@@ -13131,7 +13127,7 @@
       </c>
       <c r="J306" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -13141,12 +13137,12 @@
       </c>
       <c r="B307" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энерго Альянс»</t>
+          <t>ООО «Текманн»</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>7813579997</t>
+          <t>7842508750</t>
         </is>
       </c>
       <c r="D307" s="13" t="inlineStr"/>
@@ -13159,7 +13155,7 @@
       </c>
       <c r="H307" s="10" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>694</t>
         </is>
       </c>
       <c r="I307" s="10" t="inlineStr">
@@ -13179,12 +13175,12 @@
       </c>
       <c r="B308" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЭнергоИнвест»</t>
+          <t>ООО «ТехЭнерго»</t>
         </is>
       </c>
       <c r="C308" s="12" t="inlineStr">
         <is>
-          <t>7841378040</t>
+          <t>7816531513</t>
         </is>
       </c>
       <c r="D308" s="13" t="inlineStr"/>
@@ -13197,7 +13193,7 @@
       </c>
       <c r="H308" s="10" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I308" s="10" t="inlineStr">
@@ -13207,7 +13203,7 @@
       </c>
       <c r="J308" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13217,20 +13213,16 @@
       </c>
       <c r="B309" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Технические Системы»</t>
         </is>
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7807345648</t>
         </is>
       </c>
       <c r="D309" s="13" t="inlineStr"/>
-      <c r="E309" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
-        </is>
-      </c>
+      <c r="E309" s="11" t="inlineStr"/>
       <c r="F309" s="11" t="inlineStr"/>
       <c r="G309" s="11" t="inlineStr">
         <is>
@@ -13239,7 +13231,7 @@
       </c>
       <c r="H309" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>511</t>
         </is>
       </c>
       <c r="I309" s="10" t="inlineStr">
@@ -13249,7 +13241,7 @@
       </c>
       <c r="J309" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13259,20 +13251,16 @@
       </c>
       <c r="B310" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «Техно Эйр Групп»</t>
         </is>
       </c>
       <c r="C310" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>7816594954</t>
         </is>
       </c>
       <c r="D310" s="13" t="inlineStr"/>
-      <c r="E310" s="11" t="inlineStr">
-        <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
-        </is>
-      </c>
+      <c r="E310" s="11" t="inlineStr"/>
       <c r="F310" s="11" t="inlineStr"/>
       <c r="G310" s="11" t="inlineStr">
         <is>
@@ -13281,7 +13269,7 @@
       </c>
       <c r="H310" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>661</t>
         </is>
       </c>
       <c r="I310" s="10" t="inlineStr">
@@ -13291,7 +13279,7 @@
       </c>
       <c r="J310" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13301,29 +13289,29 @@
       </c>
       <c r="B311" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «Трамплин-строй»</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7802207193</t>
         </is>
       </c>
       <c r="D311" s="13" t="inlineStr"/>
       <c r="E311" s="11" t="inlineStr">
         <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
         </is>
       </c>
       <c r="F311" s="11" t="inlineStr"/>
       <c r="G311" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H311" s="10" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>726</t>
         </is>
       </c>
       <c r="I311" s="10" t="inlineStr">
@@ -13333,7 +13321,7 @@
       </c>
       <c r="J311" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -13343,16 +13331,20 @@
       </c>
       <c r="B312" s="11" t="inlineStr">
         <is>
-          <t>ООО ПСМ «Спутник»</t>
+          <t>ООО «Трест «Сантехмонтаж-1»</t>
         </is>
       </c>
       <c r="C312" s="12" t="inlineStr">
         <is>
-          <t>7810765071</t>
+          <t>4706050882</t>
         </is>
       </c>
       <c r="D312" s="13" t="inlineStr"/>
-      <c r="E312" s="11" t="inlineStr"/>
+      <c r="E312" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Мытнинская 12/44А пом.13н оф.14; ОГРН 1224700013230; сантехмонтаж, вентиляция, ИТП</t>
+        </is>
+      </c>
       <c r="F312" s="11" t="inlineStr"/>
       <c r="G312" s="11" t="inlineStr">
         <is>
@@ -13361,7 +13353,7 @@
       </c>
       <c r="H312" s="10" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="I312" s="10" t="inlineStr">
@@ -13381,16 +13373,20 @@
       </c>
       <c r="B313" s="11" t="inlineStr">
         <is>
-          <t>ООО СК «Аврора-Строй»</t>
+          <t>ООО «УМ «Эталон»</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>7801700173</t>
+          <t>7810048170</t>
         </is>
       </c>
       <c r="D313" s="13" t="inlineStr"/>
-      <c r="E313" s="11" t="inlineStr"/>
+      <c r="E313" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Богатырский пр. 2А каб.0.09; ОГРН 1057813303767; ген.дир. Харитонов О.В.; башенные краны; УК 463 млн</t>
+        </is>
+      </c>
       <c r="F313" s="11" t="inlineStr"/>
       <c r="G313" s="11" t="inlineStr">
         <is>
@@ -13399,22 +13395,730 @@
       </c>
       <c r="H313" s="10" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="I313" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J313" s="10" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="10" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="11" t="inlineStr">
+        <is>
+          <t>ООО «УМ-11»</t>
+        </is>
+      </c>
+      <c r="C314" s="12" t="inlineStr">
+        <is>
+          <t>7805802232</t>
+        </is>
+      </c>
+      <c r="D314" s="13" t="inlineStr"/>
+      <c r="E314" s="11" t="inlineStr"/>
+      <c r="F314" s="11" t="inlineStr"/>
+      <c r="G314" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H314" s="10" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="I314" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J314" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="10" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="11" t="inlineStr">
+        <is>
+          <t>ООО «УСН»</t>
+        </is>
+      </c>
+      <c r="C315" s="12" t="inlineStr">
+        <is>
+          <t>7819306040</t>
+        </is>
+      </c>
+      <c r="D315" s="13" t="inlineStr"/>
+      <c r="E315" s="11" t="inlineStr"/>
+      <c r="F315" s="11" t="inlineStr"/>
+      <c r="G315" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H315" s="10" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="I315" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J315" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="10" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Универсалстрой»</t>
+        </is>
+      </c>
+      <c r="C316" s="12" t="inlineStr">
+        <is>
+          <t>7801227091</t>
+        </is>
+      </c>
+      <c r="D316" s="13" t="inlineStr"/>
+      <c r="E316" s="11" t="inlineStr"/>
+      <c r="F316" s="11" t="inlineStr"/>
+      <c r="G316" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H316" s="10" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="I316" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J316" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="10" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ФОРЕСТ ДОРС»</t>
+        </is>
+      </c>
+      <c r="C317" s="12" t="inlineStr">
+        <is>
+          <t>7820045700</t>
+        </is>
+      </c>
+      <c r="D317" s="13" t="inlineStr"/>
+      <c r="E317" s="11" t="inlineStr"/>
+      <c r="F317" s="11" t="inlineStr"/>
+      <c r="G317" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H317" s="10" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="I317" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J317" s="10" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="10" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ФОРТИС»</t>
+        </is>
+      </c>
+      <c r="C318" s="12" t="inlineStr">
+        <is>
+          <t>7817119800</t>
+        </is>
+      </c>
+      <c r="D318" s="13" t="inlineStr"/>
+      <c r="E318" s="11" t="inlineStr"/>
+      <c r="F318" s="11" t="inlineStr"/>
+      <c r="G318" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H318" s="10" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="I318" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J318" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="10" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Холодпроф»</t>
+        </is>
+      </c>
+      <c r="C319" s="12" t="inlineStr">
+        <is>
+          <t>7842418360</t>
+        </is>
+      </c>
+      <c r="D319" s="13" t="inlineStr"/>
+      <c r="E319" s="11" t="inlineStr"/>
+      <c r="F319" s="11" t="inlineStr"/>
+      <c r="G319" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H319" s="10" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="I319" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J319" s="10" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="10" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C320" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D320" s="13" t="inlineStr"/>
+      <c r="E320" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F320" s="11" t="inlineStr"/>
+      <c r="G320" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H320" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I320" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J320" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦИКЛОН»</t>
+        </is>
+      </c>
+      <c r="C321" s="12" t="inlineStr">
+        <is>
+          <t>7801225591</t>
+        </is>
+      </c>
+      <c r="D321" s="13" t="inlineStr"/>
+      <c r="E321" s="11" t="inlineStr"/>
+      <c r="F321" s="11" t="inlineStr"/>
+      <c r="G321" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H321" s="10" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="I321" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J321" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="10" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦИТАДЕЛЬ»</t>
+        </is>
+      </c>
+      <c r="C322" s="12" t="inlineStr">
+        <is>
+          <t>7817122190</t>
+        </is>
+      </c>
+      <c r="D322" s="13" t="inlineStr"/>
+      <c r="E322" s="11" t="inlineStr"/>
+      <c r="F322" s="11" t="inlineStr"/>
+      <c r="G322" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H322" s="10" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="I322" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J322" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="10" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C323" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D323" s="13" t="inlineStr"/>
+      <c r="E323" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F323" s="11" t="inlineStr"/>
+      <c r="G323" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H323" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I323" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J323" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="10" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C324" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D324" s="13" t="inlineStr"/>
+      <c r="E324" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F324" s="11" t="inlineStr"/>
+      <c r="G324" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H324" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I324" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J324" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="10" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энерго Альянс»</t>
+        </is>
+      </c>
+      <c r="C325" s="12" t="inlineStr">
+        <is>
+          <t>7813579997</t>
+        </is>
+      </c>
+      <c r="D325" s="13" t="inlineStr"/>
+      <c r="E325" s="11" t="inlineStr"/>
+      <c r="F325" s="11" t="inlineStr"/>
+      <c r="G325" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H325" s="10" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="I325" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J325" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="10" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЭнергоИнвест»</t>
+        </is>
+      </c>
+      <c r="C326" s="12" t="inlineStr">
+        <is>
+          <t>7841378040</t>
+        </is>
+      </c>
+      <c r="D326" s="13" t="inlineStr"/>
+      <c r="E326" s="11" t="inlineStr"/>
+      <c r="F326" s="11" t="inlineStr"/>
+      <c r="G326" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H326" s="10" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="I326" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J326" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="10" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C327" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D327" s="13" t="inlineStr"/>
+      <c r="E327" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F327" s="11" t="inlineStr"/>
+      <c r="G327" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H327" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I327" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J327" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="10" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C328" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D328" s="13" t="inlineStr"/>
+      <c r="E328" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F328" s="11" t="inlineStr"/>
+      <c r="G328" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H328" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I328" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J328" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="10" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C329" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D329" s="13" t="inlineStr"/>
+      <c r="E329" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F329" s="11" t="inlineStr"/>
+      <c r="G329" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H329" s="10" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="I329" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J329" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="10" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="11" t="inlineStr">
+        <is>
+          <t>ООО ПСМ «Спутник»</t>
+        </is>
+      </c>
+      <c r="C330" s="12" t="inlineStr">
+        <is>
+          <t>7810765071</t>
+        </is>
+      </c>
+      <c r="D330" s="13" t="inlineStr"/>
+      <c r="E330" s="11" t="inlineStr"/>
+      <c r="F330" s="11" t="inlineStr"/>
+      <c r="G330" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H330" s="10" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="I330" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J330" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="10" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="11" t="inlineStr">
+        <is>
+          <t>ООО СК «Аврора-Строй»</t>
+        </is>
+      </c>
+      <c r="C331" s="12" t="inlineStr">
+        <is>
+          <t>7801700173</t>
+        </is>
+      </c>
+      <c r="D331" s="13" t="inlineStr"/>
+      <c r="E331" s="11" t="inlineStr"/>
+      <c r="F331" s="11" t="inlineStr"/>
+      <c r="G331" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H331" s="10" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="I313" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J313" s="10" t="inlineStr">
+      <c r="I331" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J331" s="10" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J313"/>
+  <autoFilter ref="A1:J331"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13497,7 +14201,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8">
@@ -13517,7 +14221,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>267</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$363</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J347"/>
+  <dimension ref="A1:J363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5313,20 +5313,16 @@
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>ООО «АС Инжиниринг»</t>
+          <t>ООО «АРТстрой»</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>7810318651</t>
+          <t>7743830854</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr"/>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
-        </is>
-      </c>
+      <c r="E109" s="11" t="inlineStr"/>
       <c r="F109" s="11" t="inlineStr"/>
       <c r="G109" s="11" t="inlineStr">
         <is>
@@ -5335,7 +5331,7 @@
       </c>
       <c r="H109" s="10" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr">
@@ -5345,7 +5341,7 @@
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5355,12 +5351,12 @@
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>ООО «АС»</t>
+          <t>ООО «АРХЕТИП Девелопмент»</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>7810972487</t>
+          <t>7841100165</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr"/>
@@ -5373,7 +5369,7 @@
       </c>
       <c r="H110" s="10" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr">
@@ -5393,16 +5389,20 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>ООО «АСК «ПАРАДИГМА»</t>
+          <t>ООО «АС Инжиниринг»</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>7802838520</t>
+          <t>7810318651</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr"/>
-      <c r="E111" s="11" t="inlineStr"/>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Варшавская 6к2с1 кв.551; ОГРН 1047815011474; ген.дир. Подольский А.Ю.</t>
+        </is>
+      </c>
       <c r="F111" s="11" t="inlineStr"/>
       <c r="G111" s="11" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H111" s="10" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="J111" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>ООО «АТС»</t>
+          <t>ООО «АС-ИНЖ»</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>7841019066</t>
+          <t>7810531884</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr"/>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="H112" s="10" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>795</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>ООО «Аверс Наследие»</t>
+          <t>ООО «АС-Строй»</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>7801743219</t>
+          <t>7802954614</t>
         </is>
       </c>
       <c r="D113" s="13" t="inlineStr"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="H113" s="10" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>ООО «АвиаПроСвет»</t>
+          <t>ООО «АС»</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>7811714538</t>
+          <t>7810972487</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr"/>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>ООО «Айстарт»</t>
+          <t>ООО «АСИС»</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>7841061413</t>
+          <t>7838113781</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr"/>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr">
@@ -5583,12 +5583,12 @@
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>ООО «Академия Фасадов»</t>
+          <t>ООО «АСК «ПАРАДИГМА»</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>7814848410</t>
+          <t>7802838520</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr"/>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>412</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr">
@@ -5621,25 +5621,29 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>ООО «Аквадор»</t>
+          <t>ООО «АСКОМТЕЛ»</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>7811508912</t>
+          <t>7816597867</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr"/>
-      <c r="E117" s="11" t="inlineStr"/>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Воскресенская наб. 12А пом.2-Н оф.101; ОГРН 1147847376930; ген.дир. Шкабара А.С.; электромонтаж</t>
+        </is>
+      </c>
       <c r="F117" s="11" t="inlineStr"/>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>492</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr">
@@ -5659,12 +5663,12 @@
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>ООО «Аквил»</t>
+          <t>ООО «АСОТ»</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>7804425944</t>
+          <t>7814503172</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr"/>
@@ -5677,7 +5681,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>453</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -5697,12 +5701,12 @@
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>ООО «Акканто»</t>
+          <t>ООО «АССЭ»</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>7811815920</t>
+          <t>7802832084</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr"/>
@@ -5715,7 +5719,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>448</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -5735,12 +5739,12 @@
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>ООО «Актика»</t>
+          <t>ООО «АСТА-технологии»</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>7838430325</t>
+          <t>7839445420</t>
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr"/>
@@ -5753,7 +5757,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -5773,33 +5777,29 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>ООО «Алисард»</t>
+          <t>ООО «АСТРАКОМ»</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>7814713356</t>
+          <t>7804085896</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr"/>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
-        </is>
-      </c>
-      <c r="F121" s="11" t="inlineStr">
-        <is>
-          <t>alisard.com</t>
-        </is>
-      </c>
+          <t>191123 СПб, ул.Шпалерная 24А пом.1-Н каб.6,7; ОГРН 1027802483972; рук. Баранов А.И.; связная аппаратура</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr"/>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть e-mail и сайт)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>215</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="J121" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альфа»</t>
+          <t>ООО «АСФ-Групп»</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>7802594841</t>
+          <t>7842393644</t>
         </is>
       </c>
       <c r="D122" s="13" t="inlineStr"/>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>411</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="J122" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5857,29 +5857,25 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>ООО «АТС»</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7841019066</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr"/>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
-        </is>
-      </c>
+      <c r="E123" s="11" t="inlineStr"/>
       <c r="F123" s="11" t="inlineStr"/>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -5889,7 +5885,7 @@
       </c>
       <c r="J123" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -5899,12 +5895,12 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>ООО «Аверс Наследие»</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>7708532710</t>
+          <t>7801743219</t>
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr"/>
@@ -5917,7 +5913,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -5937,20 +5933,16 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>ООО «Анва-Сервис»</t>
+          <t>ООО «АвиаПроСвет»</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>7805721872</t>
+          <t>7811714538</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Кронштадтская 3к4 пом.6-Н оф.8.2; ОГРН 1187847032560; ген.дир. Васильев В.В.</t>
-        </is>
-      </c>
+      <c r="E125" s="11" t="inlineStr"/>
       <c r="F125" s="11" t="inlineStr"/>
       <c r="G125" s="11" t="inlineStr">
         <is>
@@ -5959,7 +5951,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>929</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -5979,12 +5971,12 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>ООО «Антарес»</t>
+          <t>ООО «Айстарт»</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>7802937023</t>
+          <t>7841061413</t>
         </is>
       </c>
       <c r="D126" s="13" t="inlineStr"/>
@@ -5997,7 +5989,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>452</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
@@ -6017,29 +6009,25 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>ООО «Антей»</t>
+          <t>ООО «Академия Фасадов»</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>4708011991</t>
+          <t>7814848410</t>
         </is>
       </c>
       <c r="D127" s="13" t="inlineStr"/>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
-        </is>
-      </c>
+      <c r="E127" s="11" t="inlineStr"/>
       <c r="F127" s="11" t="inlineStr"/>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
@@ -6049,7 +6037,7 @@
       </c>
       <c r="J127" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6059,12 +6047,12 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>ООО «Арестак-Строй»</t>
+          <t>ООО «Аквадор»</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>7807286304</t>
+          <t>7811508912</t>
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr"/>
@@ -6077,7 +6065,7 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr">
@@ -6097,12 +6085,12 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>ООО «АркаСтрой»</t>
+          <t>ООО «Аквил»</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>7810504390</t>
+          <t>7804425944</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr"/>
@@ -6115,7 +6103,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>229</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
@@ -6125,7 +6113,7 @@
       </c>
       <c r="J129" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6135,20 +6123,16 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>ООО «Арман»</t>
+          <t>ООО «Акканто»</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>7805298463</t>
+          <t>7811815920</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr"/>
-      <c r="E130" s="11" t="inlineStr">
-        <is>
-          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
-        </is>
-      </c>
+      <c r="E130" s="11" t="inlineStr"/>
       <c r="F130" s="11" t="inlineStr"/>
       <c r="G130" s="11" t="inlineStr">
         <is>
@@ -6157,7 +6141,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr">
@@ -6167,7 +6151,7 @@
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6177,12 +6161,12 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлантис»</t>
+          <t>ООО «Актика»</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>7810914904</t>
+          <t>7838430325</t>
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr"/>
@@ -6195,7 +6179,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>419</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
@@ -6205,7 +6189,7 @@
       </c>
       <c r="J131" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6215,29 +6199,33 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАРК»</t>
+          <t>ООО «Алисард»</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>7804462262</t>
+          <t>7814713356</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr"/>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
-        </is>
-      </c>
-      <c r="F132" s="11" t="inlineStr"/>
+          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>alisard.com</t>
+        </is>
+      </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть e-mail и сайт)</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>575</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr">
@@ -6257,20 +6245,16 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
+          <t>ООО «Альфа»</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>7804634666</t>
+          <t>7802594841</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr"/>
-      <c r="E133" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
-        </is>
-      </c>
+      <c r="E133" s="11" t="inlineStr"/>
       <c r="F133" s="11" t="inlineStr"/>
       <c r="G133" s="11" t="inlineStr">
         <is>
@@ -6279,7 +6263,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
@@ -6299,29 +6283,29 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>ООО «БЕЛНЕВА»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>7839489314</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr"/>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr"/>
       <c r="G134" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr">
@@ -6331,7 +6315,7 @@
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -6341,20 +6325,16 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7708532710</t>
         </is>
       </c>
       <c r="D135" s="13" t="inlineStr"/>
-      <c r="E135" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E135" s="11" t="inlineStr"/>
       <c r="F135" s="11" t="inlineStr"/>
       <c r="G135" s="11" t="inlineStr">
         <is>
@@ -6363,7 +6343,7 @@
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
@@ -6373,7 +6353,7 @@
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6363,20 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>ООО «Анва-Сервис»</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7805721872</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr"/>
-      <c r="E136" s="11" t="inlineStr"/>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кронштадтская 3к4 пом.6-Н оф.8.2; ОГРН 1187847032560; ген.дир. Васильев В.В.</t>
+        </is>
+      </c>
       <c r="F136" s="11" t="inlineStr"/>
       <c r="G136" s="11" t="inlineStr">
         <is>
@@ -6401,7 +6385,7 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr">
@@ -6411,7 +6395,7 @@
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6421,29 +6405,25 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>ООО «БРАЗСТРОЙ»</t>
+          <t>ООО «Антарес»</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>2630050808</t>
+          <t>7802937023</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr"/>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
-        </is>
-      </c>
+      <c r="E137" s="11" t="inlineStr"/>
       <c r="F137" s="11" t="inlineStr"/>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
@@ -6453,7 +6433,7 @@
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6463,25 +6443,29 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>ООО «Балтийский альянс»</t>
+          <t>ООО «Антей»</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>7838020706</t>
+          <t>4708011991</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr"/>
-      <c r="E138" s="11" t="inlineStr"/>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
+        </is>
+      </c>
       <c r="F138" s="11" t="inlineStr"/>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr">
@@ -6491,7 +6475,7 @@
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6501,29 +6485,25 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>ООО «БелькаРус»</t>
+          <t>ООО «Арестак-Строй»</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>7801665024</t>
+          <t>7807286304</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr"/>
-      <c r="E139" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
-        </is>
-      </c>
+      <c r="E139" s="11" t="inlineStr"/>
       <c r="F139" s="11" t="inlineStr"/>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
@@ -6533,7 +6513,7 @@
       </c>
       <c r="J139" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6543,29 +6523,25 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>ООО «БиАр»</t>
+          <t>ООО «АркаСтрой»</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>7802738910</t>
+          <t>7810504390</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr"/>
-      <c r="E140" s="11" t="inlineStr">
-        <is>
-          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
-        </is>
-      </c>
+      <c r="E140" s="11" t="inlineStr"/>
       <c r="F140" s="11" t="inlineStr"/>
       <c r="G140" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>542</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr">
@@ -6575,7 +6551,7 @@
       </c>
       <c r="J140" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -6585,18 +6561,18 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>ООО «Бобёр»</t>
+          <t>ООО «Арман»</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>7801632702</t>
+          <t>7805298463</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr"/>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
+          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -6607,7 +6583,7 @@
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>586</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
@@ -6627,29 +6603,25 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЕРТЕК»</t>
+          <t>ООО «Архитектурные Решения»</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>7806317711</t>
+          <t>7810918306</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr"/>
-      <c r="E142" s="11" t="inlineStr">
-        <is>
-          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
-        </is>
-      </c>
+      <c r="E142" s="11" t="inlineStr"/>
       <c r="F142" s="11" t="inlineStr"/>
       <c r="G142" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="I142" s="10" t="inlineStr">
@@ -6659,7 +6631,7 @@
       </c>
       <c r="J142" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6641,12 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИП»</t>
+          <t>ООО «АтРес»</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>7802742070</t>
+          <t>7813687270</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr"/>
@@ -6687,7 +6659,7 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
@@ -6697,7 +6669,7 @@
       </c>
       <c r="J143" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6707,29 +6679,25 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИРА»</t>
+          <t>ООО «Атлант»</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>7839139655</t>
+          <t>7838082413</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr"/>
-      <c r="E144" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
-        </is>
-      </c>
+      <c r="E144" s="11" t="inlineStr"/>
       <c r="F144" s="11" t="inlineStr"/>
       <c r="G144" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I144" s="10" t="inlineStr">
@@ -6739,7 +6707,7 @@
       </c>
       <c r="J144" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6717,12 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК»</t>
+          <t>ООО «Атлантис»</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>3525411380</t>
+          <t>7810914904</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr"/>
@@ -6767,7 +6735,7 @@
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
@@ -6787,12 +6755,12 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК» (Военно-строительная компания)</t>
+          <t>ООО «Атлас групп»</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>7804018392</t>
+          <t>7811587054</t>
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr"/>
@@ -6805,7 +6773,7 @@
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr">
@@ -6815,7 +6783,7 @@
       </c>
       <c r="J146" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6825,12 +6793,12 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЭС»</t>
+          <t>ООО «Атлас»</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>7839121496</t>
+          <t>7804667213</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr"/>
@@ -6843,7 +6811,7 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
@@ -6853,7 +6821,7 @@
       </c>
       <c r="J147" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6863,18 +6831,18 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «БАРК»</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7804462262</t>
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr"/>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr"/>
@@ -6885,7 +6853,7 @@
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
@@ -6895,7 +6863,7 @@
       </c>
       <c r="J148" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6905,16 +6873,20 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>ООО «Восток-Техника»</t>
+          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>7820049077</t>
+          <t>7804634666</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr"/>
-      <c r="E149" s="11" t="inlineStr"/>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
+        </is>
+      </c>
       <c r="F149" s="11" t="inlineStr"/>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -6923,7 +6895,7 @@
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
@@ -6933,7 +6905,7 @@
       </c>
       <c r="J149" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6943,29 +6915,29 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>ООО «БЕЛНЕВА»</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7839489314</t>
         </is>
       </c>
       <c r="D150" s="13" t="inlineStr"/>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr"/>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>457</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr">
@@ -6975,7 +6947,7 @@
       </c>
       <c r="J150" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6985,16 +6957,20 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>7603054270</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D151" s="13" t="inlineStr"/>
-      <c r="E151" s="11" t="inlineStr"/>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+        </is>
+      </c>
       <c r="F151" s="11" t="inlineStr"/>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -7003,7 +6979,7 @@
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
@@ -7013,7 +6989,7 @@
       </c>
       <c r="J151" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -7023,20 +6999,16 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D152" s="13" t="inlineStr"/>
-      <c r="E152" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
-        </is>
-      </c>
+      <c r="E152" s="11" t="inlineStr"/>
       <c r="F152" s="11" t="inlineStr"/>
       <c r="G152" s="11" t="inlineStr">
         <is>
@@ -7045,7 +7017,7 @@
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr">
@@ -7065,25 +7037,29 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГК «СТИ»</t>
+          <t>ООО «БРАЗСТРОЙ»</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>7814797620</t>
+          <t>2630050808</t>
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr"/>
-      <c r="E153" s="11" t="inlineStr"/>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
+        </is>
+      </c>
       <c r="F153" s="11" t="inlineStr"/>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
@@ -7103,29 +7079,25 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «Балтийский альянс»</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7838020706</t>
         </is>
       </c>
       <c r="D154" s="13" t="inlineStr"/>
-      <c r="E154" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
-        </is>
-      </c>
+      <c r="E154" s="11" t="inlineStr"/>
       <c r="F154" s="11" t="inlineStr"/>
       <c r="G154" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>768</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr">
@@ -7135,7 +7107,7 @@
       </c>
       <c r="J154" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -7145,18 +7117,18 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «БелькаРус»</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7801665024</t>
         </is>
       </c>
       <c r="D155" s="13" t="inlineStr"/>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
@@ -7167,7 +7139,7 @@
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
@@ -7177,7 +7149,7 @@
       </c>
       <c r="J155" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7187,25 +7159,29 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гелиос»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>7804608994</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D156" s="13" t="inlineStr"/>
-      <c r="E156" s="11" t="inlineStr"/>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
+        </is>
+      </c>
       <c r="F156" s="11" t="inlineStr"/>
       <c r="G156" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I156" s="10" t="inlineStr">
@@ -7215,7 +7191,7 @@
       </c>
       <c r="J156" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -7225,29 +7201,29 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «Бобёр»</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7801632702</t>
         </is>
       </c>
       <c r="D157" s="13" t="inlineStr"/>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
+          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr"/>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
@@ -7257,7 +7233,7 @@
       </c>
       <c r="J157" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7267,25 +7243,29 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>ООО «ДСК РЕГИОН»</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>7816487198</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D158" s="13" t="inlineStr"/>
-      <c r="E158" s="11" t="inlineStr"/>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+        </is>
+      </c>
       <c r="F158" s="11" t="inlineStr"/>
       <c r="G158" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I158" s="10" t="inlineStr">
@@ -7295,7 +7275,7 @@
       </c>
       <c r="J158" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -7305,12 +7285,12 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>ООО «Двеста»</t>
+          <t>ООО «ВИП»</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>0100042992</t>
+          <t>7802742070</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr"/>
@@ -7323,7 +7303,7 @@
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>226</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
@@ -7333,7 +7313,7 @@
       </c>
       <c r="J159" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7343,25 +7323,29 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>ООО «Дорожник СПб»</t>
+          <t>ООО «ВИРА»</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>7806421624</t>
+          <t>7839139655</t>
         </is>
       </c>
       <c r="D160" s="13" t="inlineStr"/>
-      <c r="E160" s="11" t="inlineStr"/>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
+        </is>
+      </c>
       <c r="F160" s="11" t="inlineStr"/>
       <c r="G160" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I160" s="10" t="inlineStr">
@@ -7381,29 +7365,25 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «ВСК»</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>3525411380</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr"/>
-      <c r="E161" s="11" t="inlineStr">
-        <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
-        </is>
-      </c>
+      <c r="E161" s="11" t="inlineStr"/>
       <c r="F161" s="11" t="inlineStr"/>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
@@ -7413,7 +7393,7 @@
       </c>
       <c r="J161" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7423,20 +7403,16 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «ВСК» (Военно-строительная компания)</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7804018392</t>
         </is>
       </c>
       <c r="D162" s="13" t="inlineStr"/>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
-        </is>
-      </c>
+      <c r="E162" s="11" t="inlineStr"/>
       <c r="F162" s="11" t="inlineStr"/>
       <c r="G162" s="11" t="inlineStr">
         <is>
@@ -7445,7 +7421,7 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>670</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr">
@@ -7455,7 +7431,7 @@
       </c>
       <c r="J162" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7441,12 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЗИТЕК»</t>
+          <t>ООО «ВЭС»</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>7814691303</t>
+          <t>7839121496</t>
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr"/>
@@ -7483,7 +7459,7 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>828</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
@@ -7503,16 +7479,20 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>ООО «Зодчий»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
-          <t>7810477235</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D164" s="13" t="inlineStr"/>
-      <c r="E164" s="11" t="inlineStr"/>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+        </is>
+      </c>
       <c r="F164" s="11" t="inlineStr"/>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7521,7 +7501,7 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr">
@@ -7531,7 +7511,7 @@
       </c>
       <c r="J164" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -7541,20 +7521,16 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «Восток-Техника»</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7820049077</t>
         </is>
       </c>
       <c r="D165" s="13" t="inlineStr"/>
-      <c r="E165" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
-        </is>
-      </c>
+      <c r="E165" s="11" t="inlineStr"/>
       <c r="F165" s="11" t="inlineStr"/>
       <c r="G165" s="11" t="inlineStr">
         <is>
@@ -7563,7 +7539,7 @@
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>538</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
@@ -7573,7 +7549,7 @@
       </c>
       <c r="J165" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -7583,25 +7559,29 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D166" s="13" t="inlineStr"/>
-      <c r="E166" s="11" t="inlineStr"/>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+        </is>
+      </c>
       <c r="F166" s="11" t="inlineStr"/>
       <c r="G166" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I166" s="10" t="inlineStr">
@@ -7621,12 +7601,12 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК «Петротрасса»</t>
+          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>7804572970</t>
+          <t>7603054270</t>
         </is>
       </c>
       <c r="D167" s="13" t="inlineStr"/>
@@ -7639,7 +7619,7 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
@@ -7659,16 +7639,20 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ИнТехПро»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>9810000213</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr"/>
-      <c r="E168" s="11" t="inlineStr"/>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+        </is>
+      </c>
       <c r="F168" s="11" t="inlineStr"/>
       <c r="G168" s="11" t="inlineStr">
         <is>
@@ -7677,7 +7661,7 @@
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I168" s="10" t="inlineStr">
@@ -7687,7 +7671,7 @@
       </c>
       <c r="J168" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7681,12 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
+          <t>ООО «ГК «СТИ»</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>7710910159</t>
+          <t>7814797620</t>
         </is>
       </c>
       <c r="D169" s="13" t="inlineStr"/>
@@ -7715,7 +7699,7 @@
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>847</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
@@ -7735,18 +7719,18 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D170" s="13" t="inlineStr"/>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr"/>
@@ -7757,7 +7741,7 @@
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I170" s="10" t="inlineStr">
@@ -7767,7 +7751,7 @@
       </c>
       <c r="J170" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -7777,25 +7761,29 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНСИ»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>7839398890</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D171" s="13" t="inlineStr"/>
-      <c r="E171" s="11" t="inlineStr"/>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+        </is>
+      </c>
       <c r="F171" s="11" t="inlineStr"/>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
@@ -7805,7 +7793,7 @@
       </c>
       <c r="J171" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7815,12 +7803,12 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИСБ-СЕРВИС»</t>
+          <t>ООО «Гелиос»</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>7811462471</t>
+          <t>7804608994</t>
         </is>
       </c>
       <c r="D172" s="13" t="inlineStr"/>
@@ -7833,7 +7821,7 @@
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>565</t>
         </is>
       </c>
       <c r="I172" s="10" t="inlineStr">
@@ -7853,29 +7841,29 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D173" s="13" t="inlineStr"/>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr"/>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
@@ -7885,7 +7873,7 @@
       </c>
       <c r="J173" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -7895,12 +7883,12 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>ООО «Импульс»</t>
+          <t>ООО «ДСК РЕГИОН»</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>7839473240</t>
+          <t>7816487198</t>
         </is>
       </c>
       <c r="D174" s="13" t="inlineStr"/>
@@ -7913,7 +7901,7 @@
       </c>
       <c r="H174" s="10" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I174" s="10" t="inlineStr">
@@ -7933,29 +7921,25 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «Двеста»</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>0100042992</t>
         </is>
       </c>
       <c r="D175" s="13" t="inlineStr"/>
-      <c r="E175" s="11" t="inlineStr">
-        <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
-        </is>
-      </c>
+      <c r="E175" s="11" t="inlineStr"/>
       <c r="F175" s="11" t="inlineStr"/>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
@@ -7965,7 +7949,7 @@
       </c>
       <c r="J175" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -7975,12 +7959,12 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интер-Строй»</t>
+          <t>ООО «Дорожник СПб»</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>5505064975</t>
+          <t>7806421624</t>
         </is>
       </c>
       <c r="D176" s="13" t="inlineStr"/>
@@ -7993,7 +7977,7 @@
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>564</t>
         </is>
       </c>
       <c r="I176" s="10" t="inlineStr">
@@ -8013,25 +7997,29 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интерпром»</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>7805576110</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D177" s="13" t="inlineStr"/>
-      <c r="E177" s="11" t="inlineStr"/>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
+        </is>
+      </c>
       <c r="F177" s="11" t="inlineStr"/>
       <c r="G177" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
@@ -8041,7 +8029,7 @@
       </c>
       <c r="J177" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8051,16 +8039,20 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>ООО «КС-Инжиниринг»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>7801615217</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D178" s="13" t="inlineStr"/>
-      <c r="E178" s="11" t="inlineStr"/>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+        </is>
+      </c>
       <c r="F178" s="11" t="inlineStr"/>
       <c r="G178" s="11" t="inlineStr">
         <is>
@@ -8069,7 +8061,7 @@
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I178" s="10" t="inlineStr">
@@ -8079,7 +8071,7 @@
       </c>
       <c r="J178" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -8089,20 +8081,16 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «ЗИТЕК»</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7814691303</t>
         </is>
       </c>
       <c r="D179" s="13" t="inlineStr"/>
-      <c r="E179" s="11" t="inlineStr">
-        <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
-        </is>
-      </c>
+      <c r="E179" s="11" t="inlineStr"/>
       <c r="F179" s="11" t="inlineStr"/>
       <c r="G179" s="11" t="inlineStr">
         <is>
@@ -8111,7 +8099,7 @@
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
@@ -8121,7 +8109,7 @@
       </c>
       <c r="J179" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8131,20 +8119,16 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>ООО «Компания КОМПЛИТ»</t>
+          <t>ООО «Зодчий»</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>7810793872</t>
+          <t>7810477235</t>
         </is>
       </c>
       <c r="D180" s="13" t="inlineStr"/>
-      <c r="E180" s="11" t="inlineStr">
-        <is>
-          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
-        </is>
-      </c>
+      <c r="E180" s="11" t="inlineStr"/>
       <c r="F180" s="11" t="inlineStr"/>
       <c r="G180" s="11" t="inlineStr">
         <is>
@@ -8153,7 +8137,7 @@
       </c>
       <c r="H180" s="10" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I180" s="10" t="inlineStr">
@@ -8173,16 +8157,20 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>ООО «Комфорт ЛСТК»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>7838428816</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D181" s="13" t="inlineStr"/>
-      <c r="E181" s="11" t="inlineStr"/>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+        </is>
+      </c>
       <c r="F181" s="11" t="inlineStr"/>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8191,7 +8179,7 @@
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
@@ -8201,7 +8189,7 @@
       </c>
       <c r="J181" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8211,20 +8199,16 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>ООО «Концерн «Питер»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>7826108410</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D182" s="13" t="inlineStr"/>
-      <c r="E182" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Ефимова 3С пом.417; ОГРН 1027810246750; ген.дир. Петров М.Ю.; застройщик</t>
-        </is>
-      </c>
+      <c r="E182" s="11" t="inlineStr"/>
       <c r="F182" s="11" t="inlineStr"/>
       <c r="G182" s="11" t="inlineStr">
         <is>
@@ -8233,7 +8217,7 @@
       </c>
       <c r="H182" s="10" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I182" s="10" t="inlineStr">
@@ -8243,7 +8227,7 @@
       </c>
       <c r="J182" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8237,12 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>ООО «Корнелиус»</t>
+          <t>ООО «ИК «Петротрасса»</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>7802611335</t>
+          <t>7804572970</t>
         </is>
       </c>
       <c r="D183" s="13" t="inlineStr"/>
@@ -8271,7 +8255,7 @@
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>712</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr">
@@ -8291,12 +8275,12 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>ООО «Красный Квадрат»</t>
+          <t>ООО «ИК ИнТехПро»</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>7802567950</t>
+          <t>9810000213</t>
         </is>
       </c>
       <c r="D184" s="13" t="inlineStr"/>
@@ -8309,7 +8293,7 @@
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I184" s="10" t="inlineStr">
@@ -8329,12 +8313,12 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЛС-Групп»</t>
+          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>7842036949</t>
+          <t>7710910159</t>
         </is>
       </c>
       <c r="D185" s="13" t="inlineStr"/>
@@ -8347,7 +8331,7 @@
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>940</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr">
@@ -8367,18 +8351,18 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D186" s="13" t="inlineStr"/>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr"/>
@@ -8389,7 +8373,7 @@
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I186" s="10" t="inlineStr">
@@ -8409,20 +8393,16 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «ИНСИ»</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7839398890</t>
         </is>
       </c>
       <c r="D187" s="13" t="inlineStr"/>
-      <c r="E187" s="11" t="inlineStr">
-        <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
-        </is>
-      </c>
+      <c r="E187" s="11" t="inlineStr"/>
       <c r="F187" s="11" t="inlineStr"/>
       <c r="G187" s="11" t="inlineStr">
         <is>
@@ -8431,7 +8411,7 @@
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr">
@@ -8441,7 +8421,7 @@
       </c>
       <c r="J187" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8451,12 +8431,12 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЛидерСервис»</t>
+          <t>ООО «ИСБ-СЕРВИС»</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>7805304438</t>
+          <t>7811462471</t>
         </is>
       </c>
       <c r="D188" s="13" t="inlineStr"/>
@@ -8469,7 +8449,7 @@
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>295</t>
         </is>
       </c>
       <c r="I188" s="10" t="inlineStr">
@@ -8489,16 +8469,20 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>ООО «М-ГРУПП»</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>3128105475</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D189" s="13" t="inlineStr"/>
-      <c r="E189" s="11" t="inlineStr"/>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+        </is>
+      </c>
       <c r="F189" s="11" t="inlineStr"/>
       <c r="G189" s="11" t="inlineStr">
         <is>
@@ -8507,7 +8491,7 @@
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I189" s="10" t="inlineStr">
@@ -8517,7 +8501,7 @@
       </c>
       <c r="J189" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8527,12 +8511,12 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>ООО «М-Сервис»</t>
+          <t>ООО «Импульс»</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>7842429918</t>
+          <t>7839473240</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr"/>
@@ -8545,7 +8529,7 @@
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr">
@@ -8565,25 +8549,29 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>ООО «МАН»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>7840404386</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D191" s="13" t="inlineStr"/>
-      <c r="E191" s="11" t="inlineStr"/>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
+        </is>
+      </c>
       <c r="F191" s="11" t="inlineStr"/>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I191" s="10" t="inlineStr">
@@ -8593,7 +8581,7 @@
       </c>
       <c r="J191" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8591,12 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>ООО «МАТИС»</t>
+          <t>ООО «Интер-Строй»</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>7820023103</t>
+          <t>5505064975</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr"/>
@@ -8621,7 +8609,7 @@
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr">
@@ -8641,12 +8629,12 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>ООО «МК БАМ»</t>
+          <t>ООО «Интерпром»</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>7536059295</t>
+          <t>7805576110</t>
         </is>
       </c>
       <c r="D193" s="13" t="inlineStr"/>
@@ -8659,7 +8647,7 @@
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I193" s="10" t="inlineStr">
@@ -8679,29 +8667,25 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «КС-Инжиниринг»</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>7801615217</t>
         </is>
       </c>
       <c r="D194" s="13" t="inlineStr"/>
-      <c r="E194" s="11" t="inlineStr">
-        <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
-        </is>
-      </c>
+      <c r="E194" s="11" t="inlineStr"/>
       <c r="F194" s="11" t="inlineStr"/>
       <c r="G194" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H194" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>695</t>
         </is>
       </c>
       <c r="I194" s="10" t="inlineStr">
@@ -8711,7 +8695,7 @@
       </c>
       <c r="J194" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8721,16 +8705,20 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>ООО «МСС СЗ»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>7804372114</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D195" s="13" t="inlineStr"/>
-      <c r="E195" s="11" t="inlineStr"/>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
+        </is>
+      </c>
       <c r="F195" s="11" t="inlineStr"/>
       <c r="G195" s="11" t="inlineStr">
         <is>
@@ -8739,7 +8727,7 @@
       </c>
       <c r="H195" s="10" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I195" s="10" t="inlineStr">
@@ -8749,7 +8737,7 @@
       </c>
       <c r="J195" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -8759,18 +8747,18 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «Компания КОМПЛИТ»</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7810793872</t>
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr"/>
       <c r="E196" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
+          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
         </is>
       </c>
       <c r="F196" s="11" t="inlineStr"/>
@@ -8781,7 +8769,7 @@
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>143</t>
         </is>
       </c>
       <c r="I196" s="10" t="inlineStr">
@@ -8791,7 +8779,7 @@
       </c>
       <c r="J196" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8801,29 +8789,25 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>ООО «Мелстон Инжиниринг»</t>
+          <t>ООО «Комфорт ЛСТК»</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>7813248219</t>
+          <t>7838428816</t>
         </is>
       </c>
       <c r="D197" s="13" t="inlineStr"/>
-      <c r="E197" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
-        </is>
-      </c>
+      <c r="E197" s="11" t="inlineStr"/>
       <c r="F197" s="11" t="inlineStr"/>
       <c r="G197" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>693</t>
         </is>
       </c>
       <c r="I197" s="10" t="inlineStr">
@@ -8843,18 +8827,18 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «Концерн «Питер»</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>7826108410</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr"/>
       <c r="E198" s="11" t="inlineStr">
         <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+          <t>СПб, ул.Ефимова 3С пом.417; ОГРН 1027810246750; ген.дир. Петров М.Ю.; застройщик</t>
         </is>
       </c>
       <c r="F198" s="11" t="inlineStr"/>
@@ -8865,7 +8849,7 @@
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>739</t>
         </is>
       </c>
       <c r="I198" s="10" t="inlineStr">
@@ -8875,7 +8859,7 @@
       </c>
       <c r="J198" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -8885,20 +8869,16 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>ООО «МонтажСтрой-М» (МСМ)</t>
+          <t>ООО «Корнелиус»</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>7811447071</t>
+          <t>7802611335</t>
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr"/>
-      <c r="E199" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
-        </is>
-      </c>
+      <c r="E199" s="11" t="inlineStr"/>
       <c r="F199" s="11" t="inlineStr"/>
       <c r="G199" s="11" t="inlineStr">
         <is>
@@ -8907,7 +8887,7 @@
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I199" s="10" t="inlineStr">
@@ -8917,7 +8897,7 @@
       </c>
       <c r="J199" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8927,12 +8907,12 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО «НАСТ»</t>
+          <t>ООО «Красный Квадрат»</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>7810172762</t>
+          <t>7802567950</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr"/>
@@ -8945,7 +8925,7 @@
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="I200" s="10" t="inlineStr">
@@ -8965,12 +8945,12 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО «Процесс»</t>
+          <t>ООО «ЛС-Групп»</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>7806468037</t>
+          <t>7842036949</t>
         </is>
       </c>
       <c r="D201" s="13" t="inlineStr"/>
@@ -8983,7 +8963,7 @@
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>509</t>
         </is>
       </c>
       <c r="I201" s="10" t="inlineStr">
@@ -9003,25 +8983,29 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО ПЭМЗ»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>7813361648</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D202" s="13" t="inlineStr"/>
-      <c r="E202" s="11" t="inlineStr"/>
+      <c r="E202" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
+        </is>
+      </c>
       <c r="F202" s="11" t="inlineStr"/>
       <c r="G202" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I202" s="10" t="inlineStr">
@@ -9031,7 +9015,7 @@
       </c>
       <c r="J202" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9041,18 +9025,18 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПП «Путьсервис»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>7810216184</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D203" s="13" t="inlineStr"/>
       <c r="E203" s="11" t="inlineStr">
         <is>
-          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F203" s="11" t="inlineStr"/>
@@ -9063,7 +9047,7 @@
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I203" s="10" t="inlineStr">
@@ -9073,7 +9057,7 @@
       </c>
       <c r="J203" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9083,20 +9067,16 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «ЛидерСервис»</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7805304438</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr"/>
-      <c r="E204" s="11" t="inlineStr">
-        <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
-        </is>
-      </c>
+      <c r="E204" s="11" t="inlineStr"/>
       <c r="F204" s="11" t="inlineStr"/>
       <c r="G204" s="11" t="inlineStr">
         <is>
@@ -9105,7 +9085,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>902</t>
         </is>
       </c>
       <c r="I204" s="10" t="inlineStr">
@@ -9115,7 +9095,7 @@
       </c>
       <c r="J204" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9125,12 +9105,12 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПХК «Ремстройкомплекс»</t>
+          <t>ООО «М-ГРУПП»</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>7826000423</t>
+          <t>3128105475</t>
         </is>
       </c>
       <c r="D205" s="13" t="inlineStr"/>
@@ -9143,7 +9123,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr">
@@ -9163,29 +9143,25 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «М-Сервис»</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7842429918</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr"/>
-      <c r="E206" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
-        </is>
-      </c>
+      <c r="E206" s="11" t="inlineStr"/>
       <c r="F206" s="11" t="inlineStr"/>
       <c r="G206" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>722</t>
         </is>
       </c>
       <c r="I206" s="10" t="inlineStr">
@@ -9195,7 +9171,7 @@
       </c>
       <c r="J206" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9181,12 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСР»</t>
+          <t>ООО «МАН»</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>7801727376</t>
+          <t>7840404386</t>
         </is>
       </c>
       <c r="D207" s="13" t="inlineStr"/>
@@ -9223,7 +9199,7 @@
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>510</t>
         </is>
       </c>
       <c r="I207" s="10" t="inlineStr">
@@ -9243,29 +9219,25 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «МАТИС»</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7820023103</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr"/>
-      <c r="E208" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
-        </is>
-      </c>
+      <c r="E208" s="11" t="inlineStr"/>
       <c r="F208" s="11" t="inlineStr"/>
       <c r="G208" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H208" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>616</t>
         </is>
       </c>
       <c r="I208" s="10" t="inlineStr">
@@ -9275,7 +9247,7 @@
       </c>
       <c r="J208" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9285,20 +9257,16 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «МК БАМ»</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7536059295</t>
         </is>
       </c>
       <c r="D209" s="13" t="inlineStr"/>
-      <c r="E209" s="11" t="inlineStr">
-        <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
-        </is>
-      </c>
+      <c r="E209" s="11" t="inlineStr"/>
       <c r="F209" s="11" t="inlineStr"/>
       <c r="G209" s="11" t="inlineStr">
         <is>
@@ -9307,7 +9275,7 @@
       </c>
       <c r="H209" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>668</t>
         </is>
       </c>
       <c r="I209" s="10" t="inlineStr">
@@ -9317,7 +9285,7 @@
       </c>
       <c r="J209" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9327,25 +9295,29 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОСА - Север»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>7801574480</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr"/>
-      <c r="E210" s="11" t="inlineStr"/>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
+        </is>
+      </c>
       <c r="F210" s="11" t="inlineStr"/>
       <c r="G210" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H210" s="10" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I210" s="10" t="inlineStr">
@@ -9355,7 +9327,7 @@
       </c>
       <c r="J210" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9365,12 +9337,12 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОблСервис»</t>
+          <t>ООО «МСС СЗ»</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>4712024087</t>
+          <t>7804372114</t>
         </is>
       </c>
       <c r="D211" s="13" t="inlineStr"/>
@@ -9383,7 +9355,7 @@
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>741</t>
         </is>
       </c>
       <c r="I211" s="10" t="inlineStr">
@@ -9393,7 +9365,7 @@
       </c>
       <c r="J211" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -9403,16 +9375,20 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОлАн»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>7827004614</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr"/>
-      <c r="E212" s="11" t="inlineStr"/>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
+        </is>
+      </c>
       <c r="F212" s="11" t="inlineStr"/>
       <c r="G212" s="11" t="inlineStr">
         <is>
@@ -9421,7 +9397,7 @@
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I212" s="10" t="inlineStr">
@@ -9431,7 +9407,7 @@
       </c>
       <c r="J212" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9441,25 +9417,29 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>ООО «Олимп-Строй»</t>
+          <t>ООО «Мелстон Инжиниринг»</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>7820315709</t>
+          <t>7813248219</t>
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr"/>
-      <c r="E213" s="11" t="inlineStr"/>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
+        </is>
+      </c>
       <c r="F213" s="11" t="inlineStr"/>
       <c r="G213" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>669</t>
         </is>
       </c>
       <c r="I213" s="10" t="inlineStr">
@@ -9479,18 +9459,18 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr"/>
       <c r="E214" s="11" t="inlineStr">
         <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
         </is>
       </c>
       <c r="F214" s="11" t="inlineStr"/>
@@ -9501,7 +9481,7 @@
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I214" s="10" t="inlineStr">
@@ -9521,16 +9501,20 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омни Структуре Санкт-Петербург»</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>7801641792</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr"/>
-      <c r="E215" s="11" t="inlineStr"/>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
+        </is>
+      </c>
       <c r="F215" s="11" t="inlineStr"/>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -9539,7 +9523,7 @@
       </c>
       <c r="H215" s="10" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I215" s="10" t="inlineStr">
@@ -9549,7 +9533,7 @@
       </c>
       <c r="J215" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -9559,12 +9543,12 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>ООО «Основание»</t>
+          <t>ООО «НПО «НАСТ»</t>
         </is>
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>7840083527</t>
+          <t>7810172762</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr"/>
@@ -9577,7 +9561,7 @@
       </c>
       <c r="H216" s="10" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>273</t>
         </is>
       </c>
       <c r="I216" s="10" t="inlineStr">
@@ -9597,29 +9581,25 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
+          <t>ООО «НПО «Процесс»</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>7825382561</t>
+          <t>7806468037</t>
         </is>
       </c>
       <c r="D217" s="13" t="inlineStr"/>
-      <c r="E217" s="11" t="inlineStr">
-        <is>
-          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
-        </is>
-      </c>
+      <c r="E217" s="11" t="inlineStr"/>
       <c r="F217" s="11" t="inlineStr"/>
       <c r="G217" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H217" s="10" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="I217" s="10" t="inlineStr">
@@ -9629,7 +9609,7 @@
       </c>
       <c r="J217" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9619,12 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПВВ Продукт»</t>
+          <t>ООО «НПО ПЭМЗ»</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>7840501541</t>
+          <t>7813361648</t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr"/>
@@ -9657,7 +9637,7 @@
       </c>
       <c r="H218" s="10" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="I218" s="10" t="inlineStr">
@@ -9677,16 +9657,20 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПВЦ «Восток»</t>
+          <t>ООО «НПП «Путьсервис»</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>7802203054</t>
+          <t>7810216184</t>
         </is>
       </c>
       <c r="D219" s="13" t="inlineStr"/>
-      <c r="E219" s="11" t="inlineStr"/>
+      <c r="E219" s="11" t="inlineStr">
+        <is>
+          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
+        </is>
+      </c>
       <c r="F219" s="11" t="inlineStr"/>
       <c r="G219" s="11" t="inlineStr">
         <is>
@@ -9695,7 +9679,7 @@
       </c>
       <c r="H219" s="10" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>733</t>
         </is>
       </c>
       <c r="I219" s="10" t="inlineStr">
@@ -9715,29 +9699,29 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr"/>
       <c r="E220" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
         </is>
       </c>
       <c r="F220" s="11" t="inlineStr"/>
       <c r="G220" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I220" s="10" t="inlineStr">
@@ -9747,7 +9731,7 @@
       </c>
       <c r="J220" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -9757,12 +9741,12 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕГАЗ»</t>
+          <t>ООО «НПХК «Ремстройкомплекс»</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>7804700982</t>
+          <t>7826000423</t>
         </is>
       </c>
       <c r="D221" s="13" t="inlineStr"/>
@@ -9775,7 +9759,7 @@
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I221" s="10" t="inlineStr">
@@ -9795,25 +9779,29 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОТОРГ»</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>7810518322</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr"/>
-      <c r="E222" s="11" t="inlineStr"/>
+      <c r="E222" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+        </is>
+      </c>
       <c r="F222" s="11" t="inlineStr"/>
       <c r="G222" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H222" s="10" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I222" s="10" t="inlineStr">
@@ -9823,7 +9811,7 @@
       </c>
       <c r="J222" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -9833,29 +9821,25 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «НСР»</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7801727376</t>
         </is>
       </c>
       <c r="D223" s="13" t="inlineStr"/>
-      <c r="E223" s="11" t="inlineStr">
-        <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
-        </is>
-      </c>
+      <c r="E223" s="11" t="inlineStr"/>
       <c r="F223" s="11" t="inlineStr"/>
       <c r="G223" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H223" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="I223" s="10" t="inlineStr">
@@ -9865,7 +9849,7 @@
       </c>
       <c r="J223" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9875,29 +9859,29 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>7810685806</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr"/>
       <c r="E224" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, Ярославский пр.</t>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
         </is>
       </c>
       <c r="F224" s="11" t="inlineStr"/>
       <c r="G224" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I224" s="10" t="inlineStr">
@@ -9907,7 +9891,7 @@
       </c>
       <c r="J224" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9917,33 +9901,29 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>7841469072</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D225" s="13" t="inlineStr"/>
       <c r="E225" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
-        </is>
-      </c>
-      <c r="F225" s="11" t="inlineStr">
-        <is>
-          <t>saby.ru/profile/7841469072-783901001</t>
-        </is>
-      </c>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+        </is>
+      </c>
+      <c r="F225" s="11" t="inlineStr"/>
       <c r="G225" s="11" t="inlineStr">
         <is>
-          <t>нет данных (найден только белорусский номер — под вопросом)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H225" s="10" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I225" s="10" t="inlineStr">
@@ -9953,7 +9933,7 @@
       </c>
       <c r="J225" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -9963,12 +9943,12 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСК «Реставрация»</t>
+          <t>ООО «ОСА - Север»</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>7839085696</t>
+          <t>7801574480</t>
         </is>
       </c>
       <c r="D226" s="13" t="inlineStr"/>
@@ -9981,7 +9961,7 @@
       </c>
       <c r="H226" s="10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>834</t>
         </is>
       </c>
       <c r="I226" s="10" t="inlineStr">
@@ -10001,20 +9981,16 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «ОблСервис»</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>4712024087</t>
         </is>
       </c>
       <c r="D227" s="13" t="inlineStr"/>
-      <c r="E227" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
-        </is>
-      </c>
+      <c r="E227" s="11" t="inlineStr"/>
       <c r="F227" s="11" t="inlineStr"/>
       <c r="G227" s="11" t="inlineStr">
         <is>
@@ -10023,7 +9999,7 @@
       </c>
       <c r="H227" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="I227" s="10" t="inlineStr">
@@ -10033,7 +10009,7 @@
       </c>
       <c r="J227" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10043,20 +10019,16 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «ОлАн»</t>
         </is>
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7827004614</t>
         </is>
       </c>
       <c r="D228" s="13" t="inlineStr"/>
-      <c r="E228" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
-        </is>
-      </c>
+      <c r="E228" s="11" t="inlineStr"/>
       <c r="F228" s="11" t="inlineStr"/>
       <c r="G228" s="11" t="inlineStr">
         <is>
@@ -10065,7 +10037,7 @@
       </c>
       <c r="H228" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>685</t>
         </is>
       </c>
       <c r="I228" s="10" t="inlineStr">
@@ -10075,7 +10047,7 @@
       </c>
       <c r="J228" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -10085,12 +10057,12 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «Олимп-Строй»</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>7820315709</t>
         </is>
       </c>
       <c r="D229" s="13" t="inlineStr"/>
@@ -10103,7 +10075,7 @@
       </c>
       <c r="H229" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>689</t>
         </is>
       </c>
       <c r="I229" s="10" t="inlineStr">
@@ -10113,7 +10085,7 @@
       </c>
       <c r="J229" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10123,16 +10095,20 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТО Сервис»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>7839334494</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D230" s="13" t="inlineStr"/>
-      <c r="E230" s="11" t="inlineStr"/>
+      <c r="E230" s="11" t="inlineStr">
+        <is>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+        </is>
+      </c>
       <c r="F230" s="11" t="inlineStr"/>
       <c r="G230" s="11" t="inlineStr">
         <is>
@@ -10141,7 +10117,7 @@
       </c>
       <c r="H230" s="10" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I230" s="10" t="inlineStr">
@@ -10151,7 +10127,7 @@
       </c>
       <c r="J230" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10161,12 +10137,12 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТФ «КонСис»</t>
+          <t>ООО «Омни Структуре Санкт-Петербург»</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>7805068406</t>
+          <t>7801641792</t>
         </is>
       </c>
       <c r="D231" s="13" t="inlineStr"/>
@@ -10179,7 +10155,7 @@
       </c>
       <c r="H231" s="10" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>562</t>
         </is>
       </c>
       <c r="I231" s="10" t="inlineStr">
@@ -10199,12 +10175,12 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЭС»</t>
+          <t>ООО «Основание»</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>7814677411</t>
+          <t>7840083527</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr"/>
@@ -10217,7 +10193,7 @@
       </c>
       <c r="H232" s="10" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="I232" s="10" t="inlineStr">
@@ -10237,25 +10213,29 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>ООО «Паритет Плюс»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>7806471030</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D233" s="13" t="inlineStr"/>
-      <c r="E233" s="11" t="inlineStr"/>
+      <c r="E233" s="11" t="inlineStr">
+        <is>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
+        </is>
+      </c>
       <c r="F233" s="11" t="inlineStr"/>
       <c r="G233" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H233" s="10" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I233" s="10" t="inlineStr">
@@ -10265,7 +10245,7 @@
       </c>
       <c r="J233" s="10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10255,12 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПетроТрейд-инжиниринг»</t>
+          <t>ООО «ПВВ Продукт»</t>
         </is>
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>7802490056</t>
+          <t>7840501541</t>
         </is>
       </c>
       <c r="D234" s="13" t="inlineStr"/>
@@ -10293,7 +10273,7 @@
       </c>
       <c r="H234" s="10" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>454</t>
         </is>
       </c>
       <c r="I234" s="10" t="inlineStr">
@@ -10313,12 +10293,12 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>ООО «Портмарин Инжиниринг»</t>
+          <t>ООО «ПВЦ «Восток»</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>7811777680</t>
+          <t>7802203054</t>
         </is>
       </c>
       <c r="D235" s="13" t="inlineStr"/>
@@ -10331,7 +10311,7 @@
       </c>
       <c r="H235" s="10" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>534</t>
         </is>
       </c>
       <c r="I235" s="10" t="inlineStr">
@@ -10351,25 +10331,29 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрогрессСтрой»</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>7811604013</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr"/>
-      <c r="E236" s="11" t="inlineStr"/>
+      <c r="E236" s="11" t="inlineStr">
+        <is>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+        </is>
+      </c>
       <c r="F236" s="11" t="inlineStr"/>
       <c r="G236" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H236" s="10" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I236" s="10" t="inlineStr">
@@ -10379,7 +10363,7 @@
       </c>
       <c r="J236" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10389,12 +10373,12 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПромИнвест»</t>
+          <t>ООО «ПЕГАЗ»</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>7841439543</t>
+          <t>7804700982</t>
         </is>
       </c>
       <c r="D237" s="13" t="inlineStr"/>
@@ -10407,7 +10391,7 @@
       </c>
       <c r="H237" s="10" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="I237" s="10" t="inlineStr">
@@ -10427,12 +10411,12 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПромСтрой»</t>
+          <t>ООО «ПЕТРОТОРГ»</t>
         </is>
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>7806156944</t>
+          <t>7810518322</t>
         </is>
       </c>
       <c r="D238" s="13" t="inlineStr"/>
@@ -10445,7 +10429,7 @@
       </c>
       <c r="H238" s="10" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>751</t>
         </is>
       </c>
       <c r="I238" s="10" t="inlineStr">
@@ -10455,7 +10439,7 @@
       </c>
       <c r="J238" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -10465,29 +10449,29 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D239" s="13" t="inlineStr"/>
       <c r="E239" s="11" t="inlineStr">
         <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
         </is>
       </c>
       <c r="F239" s="11" t="inlineStr"/>
       <c r="G239" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H239" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I239" s="10" t="inlineStr">
@@ -10497,7 +10481,7 @@
       </c>
       <c r="J239" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -10507,16 +10491,20 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстройинжиниринг»</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>7814349756</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr"/>
-      <c r="E240" s="11" t="inlineStr"/>
+      <c r="E240" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, Ярославский пр.</t>
+        </is>
+      </c>
       <c r="F240" s="11" t="inlineStr"/>
       <c r="G240" s="11" t="inlineStr">
         <is>
@@ -10525,7 +10513,7 @@
       </c>
       <c r="H240" s="10" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I240" s="10" t="inlineStr">
@@ -10535,7 +10523,7 @@
       </c>
       <c r="J240" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -10545,25 +10533,33 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрофСтрой-И»</t>
+          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>7810682530</t>
+          <t>7841469072</t>
         </is>
       </c>
       <c r="D241" s="13" t="inlineStr"/>
-      <c r="E241" s="11" t="inlineStr"/>
-      <c r="F241" s="11" t="inlineStr"/>
+      <c r="E241" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
+        </is>
+      </c>
+      <c r="F241" s="11" t="inlineStr">
+        <is>
+          <t>saby.ru/profile/7841469072-783901001</t>
+        </is>
+      </c>
       <c r="G241" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (найден только белорусский номер — под вопросом)</t>
         </is>
       </c>
       <c r="H241" s="10" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>595</t>
         </is>
       </c>
       <c r="I241" s="10" t="inlineStr">
@@ -10583,12 +10579,12 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрофСтройАльянс»</t>
+          <t>ООО «ПСК «Реставрация»</t>
         </is>
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>7842504114</t>
+          <t>7839085696</t>
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr"/>
@@ -10601,7 +10597,7 @@
       </c>
       <c r="H242" s="10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I242" s="10" t="inlineStr">
@@ -10621,18 +10617,18 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7811659380</t>
         </is>
       </c>
       <c r="D243" s="13" t="inlineStr"/>
       <c r="E243" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
         </is>
       </c>
       <c r="F243" s="11" t="inlineStr"/>
@@ -10643,7 +10639,7 @@
       </c>
       <c r="H243" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>607</t>
         </is>
       </c>
       <c r="I243" s="10" t="inlineStr">
@@ -10653,7 +10649,7 @@
       </c>
       <c r="J243" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10663,16 +10659,20 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>ООО «РД»</t>
+          <t>ООО «ПСТ»</t>
         </is>
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>7810062946</t>
+          <t>7813448257</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr"/>
-      <c r="E244" s="11" t="inlineStr"/>
+      <c r="E244" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+        </is>
+      </c>
       <c r="F244" s="11" t="inlineStr"/>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="H244" s="10" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>876</t>
         </is>
       </c>
       <c r="I244" s="10" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="J244" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10701,20 +10701,16 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «ПТГ»</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>5013050270</t>
         </is>
       </c>
       <c r="D245" s="13" t="inlineStr"/>
-      <c r="E245" s="11" t="inlineStr">
-        <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
-        </is>
-      </c>
+      <c r="E245" s="11" t="inlineStr"/>
       <c r="F245" s="11" t="inlineStr"/>
       <c r="G245" s="11" t="inlineStr">
         <is>
@@ -10723,7 +10719,7 @@
       </c>
       <c r="H245" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="I245" s="10" t="inlineStr">
@@ -10743,12 +10739,12 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>ООО «РИАРДЕН»</t>
+          <t>ООО «ПТО Сервис»</t>
         </is>
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>7814794789</t>
+          <t>7839334494</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr"/>
@@ -10761,7 +10757,7 @@
       </c>
       <c r="H246" s="10" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I246" s="10" t="inlineStr">
@@ -10771,7 +10767,7 @@
       </c>
       <c r="J246" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10777,12 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>ООО «РК ДЕВЕЛОПМЕНТ»</t>
+          <t>ООО «ПТФ «КонСис»</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>7814800834</t>
+          <t>7805068406</t>
         </is>
       </c>
       <c r="D247" s="13" t="inlineStr"/>
@@ -10799,7 +10795,7 @@
       </c>
       <c r="H247" s="10" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>642</t>
         </is>
       </c>
       <c r="I247" s="10" t="inlineStr">
@@ -10809,7 +10805,7 @@
       </c>
       <c r="J247" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -10819,20 +10815,16 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «ПЭС»</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7814677411</t>
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr"/>
-      <c r="E248" s="11" t="inlineStr">
-        <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
-        </is>
-      </c>
+      <c r="E248" s="11" t="inlineStr"/>
       <c r="F248" s="11" t="inlineStr"/>
       <c r="G248" s="11" t="inlineStr">
         <is>
@@ -10841,7 +10833,7 @@
       </c>
       <c r="H248" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>654</t>
         </is>
       </c>
       <c r="I248" s="10" t="inlineStr">
@@ -10851,7 +10843,7 @@
       </c>
       <c r="J248" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10853,12 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>ООО «РОНИС»</t>
+          <t>ООО «Паритет Плюс»</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>7840475549</t>
+          <t>7806471030</t>
         </is>
       </c>
       <c r="D249" s="13" t="inlineStr"/>
@@ -10879,7 +10871,7 @@
       </c>
       <c r="H249" s="10" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I249" s="10" t="inlineStr">
@@ -10889,7 +10881,7 @@
       </c>
       <c r="J249" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
@@ -10899,12 +10891,12 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>ООО «РОСТРА северо-запад»</t>
+          <t>ООО «ПетроТрейд-инжиниринг»</t>
         </is>
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>7805234942</t>
+          <t>7802490056</t>
         </is>
       </c>
       <c r="D250" s="13" t="inlineStr"/>
@@ -10917,7 +10909,7 @@
       </c>
       <c r="H250" s="10" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>771</t>
         </is>
       </c>
       <c r="I250" s="10" t="inlineStr">
@@ -10937,12 +10929,12 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСК «ОРДЕР» (реставрационно-строительная)</t>
+          <t>ООО «Портмарин Инжиниринг»</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>7801585837</t>
+          <t>7811777680</t>
         </is>
       </c>
       <c r="D251" s="13" t="inlineStr"/>
@@ -10955,7 +10947,7 @@
       </c>
       <c r="H251" s="10" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="I251" s="10" t="inlineStr">
@@ -10975,12 +10967,12 @@
       </c>
       <c r="B252" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСК «ТехноСтрой»</t>
+          <t>ООО «ПрогрессСтрой»</t>
         </is>
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>7838061420</t>
+          <t>7811604013</t>
         </is>
       </c>
       <c r="D252" s="13" t="inlineStr"/>
@@ -10993,7 +10985,7 @@
       </c>
       <c r="H252" s="10" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="I252" s="10" t="inlineStr">
@@ -11013,12 +11005,12 @@
       </c>
       <c r="B253" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСУ-9»</t>
+          <t>ООО «ПромИнвест»</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>7814785030</t>
+          <t>7841439543</t>
         </is>
       </c>
       <c r="D253" s="13" t="inlineStr"/>
@@ -11031,7 +11023,7 @@
       </c>
       <c r="H253" s="10" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I253" s="10" t="inlineStr">
@@ -11051,20 +11043,16 @@
       </c>
       <c r="B254" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСФ «Водолей плюс»</t>
+          <t>ООО «ПромСтрой»</t>
         </is>
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>7826040578</t>
+          <t>7806156944</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr"/>
-      <c r="E254" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Б.Сампсониевский пр. 60И; ОГРН 1027810321659; ген.дир. Колосовская П.В.</t>
-        </is>
-      </c>
+      <c r="E254" s="11" t="inlineStr"/>
       <c r="F254" s="11" t="inlineStr"/>
       <c r="G254" s="11" t="inlineStr">
         <is>
@@ -11073,7 +11061,7 @@
       </c>
       <c r="H254" s="10" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I254" s="10" t="inlineStr">
@@ -11093,29 +11081,29 @@
       </c>
       <c r="B255" s="11" t="inlineStr">
         <is>
-          <t>ООО «РестСтройГрупп»</t>
+          <t>ООО «Промстрой»</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>7839099924</t>
+          <t>7814656860</t>
         </is>
       </c>
       <c r="D255" s="13" t="inlineStr"/>
       <c r="E255" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
         </is>
       </c>
       <c r="F255" s="11" t="inlineStr"/>
       <c r="G255" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H255" s="10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>516</t>
         </is>
       </c>
       <c r="I255" s="10" t="inlineStr">
@@ -11125,7 +11113,7 @@
       </c>
       <c r="J255" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -11135,12 +11123,12 @@
       </c>
       <c r="B256" s="11" t="inlineStr">
         <is>
-          <t>ООО «СВМ - Групп»</t>
+          <t>ООО «Промстройинжиниринг»</t>
         </is>
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>7843014240</t>
+          <t>7814349756</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr"/>
@@ -11153,7 +11141,7 @@
       </c>
       <c r="H256" s="10" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>797</t>
         </is>
       </c>
       <c r="I256" s="10" t="inlineStr">
@@ -11173,12 +11161,12 @@
       </c>
       <c r="B257" s="11" t="inlineStr">
         <is>
-          <t>ООО «СГИ»</t>
+          <t>ООО «ПрофСтрой-И»</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>7816654829</t>
+          <t>7810682530</t>
         </is>
       </c>
       <c r="D257" s="13" t="inlineStr"/>
@@ -11191,7 +11179,7 @@
       </c>
       <c r="H257" s="10" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I257" s="10" t="inlineStr">
@@ -11211,12 +11199,12 @@
       </c>
       <c r="B258" s="11" t="inlineStr">
         <is>
-          <t>ООО «СДК Лидер-Строй»</t>
+          <t>ООО «ПрофСтройАльянс»</t>
         </is>
       </c>
       <c r="C258" s="12" t="inlineStr">
         <is>
-          <t>7806299036</t>
+          <t>7842504114</t>
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr"/>
@@ -11229,7 +11217,7 @@
       </c>
       <c r="H258" s="10" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I258" s="10" t="inlineStr">
@@ -11249,16 +11237,20 @@
       </c>
       <c r="B259" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЗ «Загородная, 71»</t>
+          <t>ООО «Профиль»</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>7817328112</t>
+          <t>7802182380</t>
         </is>
       </c>
       <c r="D259" s="13" t="inlineStr"/>
-      <c r="E259" s="11" t="inlineStr"/>
+      <c r="E259" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+        </is>
+      </c>
       <c r="F259" s="11" t="inlineStr"/>
       <c r="G259" s="11" t="inlineStr">
         <is>
@@ -11267,7 +11259,7 @@
       </c>
       <c r="H259" s="10" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>572</t>
         </is>
       </c>
       <c r="I259" s="10" t="inlineStr">
@@ -11277,7 +11269,7 @@
       </c>
       <c r="J259" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -11287,20 +11279,16 @@
       </c>
       <c r="B260" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Алстрой»</t>
+          <t>ООО «РД»</t>
         </is>
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>7813417675</t>
+          <t>7810062946</t>
         </is>
       </c>
       <c r="D260" s="13" t="inlineStr"/>
-      <c r="E260" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
-        </is>
-      </c>
+      <c r="E260" s="11" t="inlineStr"/>
       <c r="F260" s="11" t="inlineStr"/>
       <c r="G260" s="11" t="inlineStr">
         <is>
@@ -11309,7 +11297,7 @@
       </c>
       <c r="H260" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>365</t>
         </is>
       </c>
       <c r="I260" s="10" t="inlineStr">
@@ -11319,7 +11307,7 @@
       </c>
       <c r="J260" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11329,18 +11317,18 @@
       </c>
       <c r="B261" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Дальпитерстрой»</t>
+          <t>ООО «РЕССТРОЙ»</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>7842021879</t>
+          <t>7820012849</t>
         </is>
       </c>
       <c r="D261" s="13" t="inlineStr"/>
       <c r="E261" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.16Н; ОГРН 1157847026402; дир. Скоров М.А.</t>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
         </is>
       </c>
       <c r="F261" s="11" t="inlineStr"/>
@@ -11351,7 +11339,7 @@
       </c>
       <c r="H261" s="10" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="I261" s="10" t="inlineStr">
@@ -11361,7 +11349,7 @@
       </c>
       <c r="J261" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11371,12 +11359,12 @@
       </c>
       <c r="B262" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Орион»</t>
+          <t>ООО «РИАРДЕН»</t>
         </is>
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>7816699026</t>
+          <t>7814794789</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr"/>
@@ -11389,7 +11377,7 @@
       </c>
       <c r="H262" s="10" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>975</t>
         </is>
       </c>
       <c r="I262" s="10" t="inlineStr">
@@ -11409,20 +11397,16 @@
       </c>
       <c r="B263" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «РК ДЕВЕЛОПМЕНТ»</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7814800834</t>
         </is>
       </c>
       <c r="D263" s="13" t="inlineStr"/>
-      <c r="E263" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
-        </is>
-      </c>
+      <c r="E263" s="11" t="inlineStr"/>
       <c r="F263" s="11" t="inlineStr"/>
       <c r="G263" s="11" t="inlineStr">
         <is>
@@ -11431,7 +11415,7 @@
       </c>
       <c r="H263" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>861</t>
         </is>
       </c>
       <c r="I263" s="10" t="inlineStr">
@@ -11441,7 +11425,7 @@
       </c>
       <c r="J263" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11451,16 +11435,20 @@
       </c>
       <c r="B264" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «СтальСтрой»</t>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
         </is>
       </c>
       <c r="C264" s="12" t="inlineStr">
         <is>
-          <t>7841052031</t>
+          <t>7826123721</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr"/>
-      <c r="E264" s="11" t="inlineStr"/>
+      <c r="E264" s="11" t="inlineStr">
+        <is>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+        </is>
+      </c>
       <c r="F264" s="11" t="inlineStr"/>
       <c r="G264" s="11" t="inlineStr">
         <is>
@@ -11469,7 +11457,7 @@
       </c>
       <c r="H264" s="10" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>515</t>
         </is>
       </c>
       <c r="I264" s="10" t="inlineStr">
@@ -11479,7 +11467,7 @@
       </c>
       <c r="J264" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11489,12 +11477,12 @@
       </c>
       <c r="B265" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «СтиФ»</t>
+          <t>ООО «РОНИС»</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>7825475600</t>
+          <t>7840475549</t>
         </is>
       </c>
       <c r="D265" s="13" t="inlineStr"/>
@@ -11507,7 +11495,7 @@
       </c>
       <c r="H265" s="10" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I265" s="10" t="inlineStr">
@@ -11517,7 +11505,7 @@
       </c>
       <c r="J265" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11527,12 +11515,12 @@
       </c>
       <c r="B266" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Стройнорд»</t>
+          <t>ООО «РОСТРА северо-запад»</t>
         </is>
       </c>
       <c r="C266" s="12" t="inlineStr">
         <is>
-          <t>7811571992</t>
+          <t>7805234942</t>
         </is>
       </c>
       <c r="D266" s="13" t="inlineStr"/>
@@ -11545,7 +11533,7 @@
       </c>
       <c r="H266" s="10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>714</t>
         </is>
       </c>
       <c r="I266" s="10" t="inlineStr">
@@ -11565,20 +11553,16 @@
       </c>
       <c r="B267" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «РСК «ОРДЕР» (реставрационно-строительная)</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7801585837</t>
         </is>
       </c>
       <c r="D267" s="13" t="inlineStr"/>
-      <c r="E267" s="11" t="inlineStr">
-        <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
-        </is>
-      </c>
+      <c r="E267" s="11" t="inlineStr"/>
       <c r="F267" s="11" t="inlineStr"/>
       <c r="G267" s="11" t="inlineStr">
         <is>
@@ -11587,7 +11571,7 @@
       </c>
       <c r="H267" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>603</t>
         </is>
       </c>
       <c r="I267" s="10" t="inlineStr">
@@ -11597,7 +11581,7 @@
       </c>
       <c r="J267" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11607,12 +11591,12 @@
       </c>
       <c r="B268" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Меркурий»</t>
+          <t>ООО «РСК «ТехноСтрой»</t>
         </is>
       </c>
       <c r="C268" s="12" t="inlineStr">
         <is>
-          <t>7819046339</t>
+          <t>7838061420</t>
         </is>
       </c>
       <c r="D268" s="13" t="inlineStr"/>
@@ -11625,7 +11609,7 @@
       </c>
       <c r="H268" s="10" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I268" s="10" t="inlineStr">
@@ -11645,12 +11629,12 @@
       </c>
       <c r="B269" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПРАГМА СТРОЙ»</t>
+          <t>ООО «РСУ-9»</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>7802313956</t>
+          <t>7814785030</t>
         </is>
       </c>
       <c r="D269" s="13" t="inlineStr"/>
@@ -11663,7 +11647,7 @@
       </c>
       <c r="H269" s="10" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>799</t>
         </is>
       </c>
       <c r="I269" s="10" t="inlineStr">
@@ -11673,7 +11657,7 @@
       </c>
       <c r="J269" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11683,18 +11667,18 @@
       </c>
       <c r="B270" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «РСФ «Водолей плюс»</t>
         </is>
       </c>
       <c r="C270" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7826040578</t>
         </is>
       </c>
       <c r="D270" s="13" t="inlineStr"/>
       <c r="E270" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+          <t>СПб, Б.Сампсониевский пр. 60И; ОГРН 1027810321659; ген.дир. Колосовская П.В.</t>
         </is>
       </c>
       <c r="F270" s="11" t="inlineStr"/>
@@ -11705,7 +11689,7 @@
       </c>
       <c r="H270" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>582</t>
         </is>
       </c>
       <c r="I270" s="10" t="inlineStr">
@@ -11715,7 +11699,7 @@
       </c>
       <c r="J270" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11725,25 +11709,29 @@
       </c>
       <c r="B271" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Профиль групп»</t>
+          <t>ООО «РестСтройГрупп»</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>7802593414</t>
+          <t>7839099924</t>
         </is>
       </c>
       <c r="D271" s="13" t="inlineStr"/>
-      <c r="E271" s="11" t="inlineStr"/>
+      <c r="E271" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+        </is>
+      </c>
       <c r="F271" s="11" t="inlineStr"/>
       <c r="G271" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H271" s="10" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>673</t>
         </is>
       </c>
       <c r="I271" s="10" t="inlineStr">
@@ -11753,7 +11741,7 @@
       </c>
       <c r="J271" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11763,12 +11751,12 @@
       </c>
       <c r="B272" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК СФЕРА»</t>
+          <t>ООО «СВМ - Групп»</t>
         </is>
       </c>
       <c r="C272" s="12" t="inlineStr">
         <is>
-          <t>9715445653</t>
+          <t>7843014240</t>
         </is>
       </c>
       <c r="D272" s="13" t="inlineStr"/>
@@ -11781,7 +11769,7 @@
       </c>
       <c r="H272" s="10" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I272" s="10" t="inlineStr">
@@ -11801,12 +11789,12 @@
       </c>
       <c r="B273" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Стройкомплект»</t>
+          <t>ООО «СГИ»</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>7806133873</t>
+          <t>7816654829</t>
         </is>
       </c>
       <c r="D273" s="13" t="inlineStr"/>
@@ -11819,7 +11807,7 @@
       </c>
       <c r="H273" s="10" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="I273" s="10" t="inlineStr">
@@ -11829,7 +11817,7 @@
       </c>
       <c r="J273" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11839,12 +11827,12 @@
       </c>
       <c r="B274" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ТТ»</t>
+          <t>ООО «СДК Лидер-Строй»</t>
         </is>
       </c>
       <c r="C274" s="12" t="inlineStr">
         <is>
-          <t>7813676373</t>
+          <t>7806299036</t>
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr"/>
@@ -11857,7 +11845,7 @@
       </c>
       <c r="H274" s="10" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="I274" s="10" t="inlineStr">
@@ -11877,12 +11865,12 @@
       </c>
       <c r="B275" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКМ»</t>
+          <t>ООО «СЗ «Загородная, 71»</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>7807239583</t>
+          <t>7817328112</t>
         </is>
       </c>
       <c r="D275" s="13" t="inlineStr"/>
@@ -11895,7 +11883,7 @@
       </c>
       <c r="H275" s="10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="I275" s="10" t="inlineStr">
@@ -11915,16 +11903,20 @@
       </c>
       <c r="B276" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКН НВК»</t>
+          <t>ООО «СК «Алстрой»</t>
         </is>
       </c>
       <c r="C276" s="12" t="inlineStr">
         <is>
-          <t>7838057216</t>
+          <t>7813417675</t>
         </is>
       </c>
       <c r="D276" s="13" t="inlineStr"/>
-      <c r="E276" s="11" t="inlineStr"/>
+      <c r="E276" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+        </is>
+      </c>
       <c r="F276" s="11" t="inlineStr"/>
       <c r="G276" s="11" t="inlineStr">
         <is>
@@ -11933,7 +11925,7 @@
       </c>
       <c r="H276" s="10" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>590</t>
         </is>
       </c>
       <c r="I276" s="10" t="inlineStr">
@@ -11943,7 +11935,7 @@
       </c>
       <c r="J276" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -11953,16 +11945,20 @@
       </c>
       <c r="B277" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКП»</t>
+          <t>ООО «СК «Дальпитерстрой»</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>7806619896</t>
+          <t>7842021879</t>
         </is>
       </c>
       <c r="D277" s="13" t="inlineStr"/>
-      <c r="E277" s="11" t="inlineStr"/>
+      <c r="E277" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.16Н; ОГРН 1157847026402; дир. Скоров М.А.</t>
+        </is>
+      </c>
       <c r="F277" s="11" t="inlineStr"/>
       <c r="G277" s="11" t="inlineStr">
         <is>
@@ -11971,7 +11967,7 @@
       </c>
       <c r="H277" s="10" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>622</t>
         </is>
       </c>
       <c r="I277" s="10" t="inlineStr">
@@ -11981,7 +11977,7 @@
       </c>
       <c r="J277" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11991,12 +11987,12 @@
       </c>
       <c r="B278" s="11" t="inlineStr">
         <is>
-          <t>ООО «СМУ 8»</t>
+          <t>ООО «СК «Орион»</t>
         </is>
       </c>
       <c r="C278" s="12" t="inlineStr">
         <is>
-          <t>7810531355</t>
+          <t>7816699026</t>
         </is>
       </c>
       <c r="D278" s="13" t="inlineStr"/>
@@ -12009,7 +12005,7 @@
       </c>
       <c r="H278" s="10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>969</t>
         </is>
       </c>
       <c r="I278" s="10" t="inlineStr">
@@ -12029,16 +12025,20 @@
       </c>
       <c r="B279" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПМК - 18»</t>
+          <t>ООО «СК «Потенциал»</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>7814624120</t>
+          <t>7814558855</t>
         </is>
       </c>
       <c r="D279" s="13" t="inlineStr"/>
-      <c r="E279" s="11" t="inlineStr"/>
+      <c r="E279" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
       <c r="F279" s="11" t="inlineStr"/>
       <c r="G279" s="11" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="H279" s="10" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>675</t>
         </is>
       </c>
       <c r="I279" s="10" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="J279" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1700000</t>
         </is>
       </c>
     </row>
@@ -12067,20 +12067,16 @@
       </c>
       <c r="B280" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «СК «СтальСтрой»</t>
         </is>
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7841052031</t>
         </is>
       </c>
       <c r="D280" s="13" t="inlineStr"/>
-      <c r="E280" s="11" t="inlineStr">
-        <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
-        </is>
-      </c>
+      <c r="E280" s="11" t="inlineStr"/>
       <c r="F280" s="11" t="inlineStr"/>
       <c r="G280" s="11" t="inlineStr">
         <is>
@@ -12089,7 +12085,7 @@
       </c>
       <c r="H280" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>439</t>
         </is>
       </c>
       <c r="I280" s="10" t="inlineStr">
@@ -12099,7 +12095,7 @@
       </c>
       <c r="J280" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12109,12 +12105,12 @@
       </c>
       <c r="B281" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОИТЕЛЬ»</t>
+          <t>ООО «СК «СтиФ»</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>7804338561</t>
+          <t>7825475600</t>
         </is>
       </c>
       <c r="D281" s="13" t="inlineStr"/>
@@ -12127,7 +12123,7 @@
       </c>
       <c r="H281" s="10" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>581</t>
         </is>
       </c>
       <c r="I281" s="10" t="inlineStr">
@@ -12147,12 +12143,12 @@
       </c>
       <c r="B282" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙ КОРПУС»</t>
+          <t>ООО «СК «Стройнорд»</t>
         </is>
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>7804553054</t>
+          <t>7811571992</t>
         </is>
       </c>
       <c r="D282" s="13" t="inlineStr"/>
@@ -12165,7 +12161,7 @@
       </c>
       <c r="H282" s="10" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>549</t>
         </is>
       </c>
       <c r="I282" s="10" t="inlineStr">
@@ -12185,16 +12181,20 @@
       </c>
       <c r="B283" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙГРАД РСУ»</t>
+          <t>ООО «СК Гарант»</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>7802703995</t>
+          <t>7806380022</t>
         </is>
       </c>
       <c r="D283" s="13" t="inlineStr"/>
-      <c r="E283" s="11" t="inlineStr"/>
+      <c r="E283" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+        </is>
+      </c>
       <c r="F283" s="11" t="inlineStr"/>
       <c r="G283" s="11" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="H283" s="10" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I283" s="10" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="J283" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -12223,20 +12223,16 @@
       </c>
       <c r="B284" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «СК Меркурий»</t>
         </is>
       </c>
       <c r="C284" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7819046339</t>
         </is>
       </c>
       <c r="D284" s="13" t="inlineStr"/>
-      <c r="E284" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
-        </is>
-      </c>
+      <c r="E284" s="11" t="inlineStr"/>
       <c r="F284" s="11" t="inlineStr"/>
       <c r="G284" s="11" t="inlineStr">
         <is>
@@ -12245,7 +12241,7 @@
       </c>
       <c r="H284" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>983</t>
         </is>
       </c>
       <c r="I284" s="10" t="inlineStr">
@@ -12255,7 +12251,7 @@
       </c>
       <c r="J284" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12265,12 +12261,12 @@
       </c>
       <c r="B285" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОНСУЛЬТ»</t>
+          <t>ООО «СК ПРАГМА СТРОЙ»</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>7810289545</t>
+          <t>7802313956</t>
         </is>
       </c>
       <c r="D285" s="13" t="inlineStr"/>
@@ -12283,7 +12279,7 @@
       </c>
       <c r="H285" s="10" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>737</t>
         </is>
       </c>
       <c r="I285" s="10" t="inlineStr">
@@ -12303,18 +12299,18 @@
       </c>
       <c r="B286" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «СК ПСП»</t>
         </is>
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7810502379</t>
         </is>
       </c>
       <c r="D286" s="13" t="inlineStr"/>
       <c r="E286" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
         </is>
       </c>
       <c r="F286" s="11" t="inlineStr"/>
@@ -12325,7 +12321,7 @@
       </c>
       <c r="H286" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>527</t>
         </is>
       </c>
       <c r="I286" s="10" t="inlineStr">
@@ -12335,7 +12331,7 @@
       </c>
       <c r="J286" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -12345,20 +12341,16 @@
       </c>
       <c r="B287" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «СК Профиль групп»</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7802593414</t>
         </is>
       </c>
       <c r="D287" s="13" t="inlineStr"/>
-      <c r="E287" s="11" t="inlineStr">
-        <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
-        </is>
-      </c>
+      <c r="E287" s="11" t="inlineStr"/>
       <c r="F287" s="11" t="inlineStr"/>
       <c r="G287" s="11" t="inlineStr">
         <is>
@@ -12367,7 +12359,7 @@
       </c>
       <c r="H287" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>576</t>
         </is>
       </c>
       <c r="I287" s="10" t="inlineStr">
@@ -12377,7 +12369,7 @@
       </c>
       <c r="J287" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12387,20 +12379,16 @@
       </c>
       <c r="B288" s="11" t="inlineStr">
         <is>
-          <t>ООО «СФ «Новэк»</t>
+          <t>ООО «СК СФЕРА»</t>
         </is>
       </c>
       <c r="C288" s="12" t="inlineStr">
         <is>
-          <t>7825128540</t>
+          <t>9715445653</t>
         </is>
       </c>
       <c r="D288" s="13" t="inlineStr"/>
-      <c r="E288" s="11" t="inlineStr">
-        <is>
-          <t>194352 СПб, ул.Кустодиева 17А; ОГРН 1027809227907; ген.дир. Смирнов Д.И.</t>
-        </is>
-      </c>
+      <c r="E288" s="11" t="inlineStr"/>
       <c r="F288" s="11" t="inlineStr"/>
       <c r="G288" s="11" t="inlineStr">
         <is>
@@ -12409,7 +12397,7 @@
       </c>
       <c r="H288" s="10" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="I288" s="10" t="inlineStr">
@@ -12429,29 +12417,25 @@
       </c>
       <c r="B289" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «СК Стройкомплект»</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7806133873</t>
         </is>
       </c>
       <c r="D289" s="13" t="inlineStr"/>
-      <c r="E289" s="11" t="inlineStr">
-        <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
-        </is>
-      </c>
+      <c r="E289" s="11" t="inlineStr"/>
       <c r="F289" s="11" t="inlineStr"/>
       <c r="G289" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H289" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>641</t>
         </is>
       </c>
       <c r="I289" s="10" t="inlineStr">
@@ -12461,7 +12445,7 @@
       </c>
       <c r="J289" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -12471,12 +12455,12 @@
       </c>
       <c r="B290" s="11" t="inlineStr">
         <is>
-          <t>ООО «Свой Дом»</t>
+          <t>ООО «СК ТТ»</t>
         </is>
       </c>
       <c r="C290" s="12" t="inlineStr">
         <is>
-          <t>7813322254</t>
+          <t>7813676373</t>
         </is>
       </c>
       <c r="D290" s="13" t="inlineStr"/>
@@ -12489,7 +12473,7 @@
       </c>
       <c r="H290" s="10" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="I290" s="10" t="inlineStr">
@@ -12499,7 +12483,7 @@
       </c>
       <c r="J290" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12509,29 +12493,25 @@
       </c>
       <c r="B291" s="11" t="inlineStr">
         <is>
-          <t>ООО «СиФ»</t>
+          <t>ООО «СКМ»</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>7801075307</t>
+          <t>7807239583</t>
         </is>
       </c>
       <c r="D291" s="13" t="inlineStr"/>
-      <c r="E291" s="11" t="inlineStr">
-        <is>
-          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
-        </is>
-      </c>
+      <c r="E291" s="11" t="inlineStr"/>
       <c r="F291" s="11" t="inlineStr"/>
       <c r="G291" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H291" s="10" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I291" s="10" t="inlineStr">
@@ -12551,12 +12531,12 @@
       </c>
       <c r="B292" s="11" t="inlineStr">
         <is>
-          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
+          <t>ООО «СКН НВК»</t>
         </is>
       </c>
       <c r="C292" s="12" t="inlineStr">
         <is>
-          <t>7810691246</t>
+          <t>7838057216</t>
         </is>
       </c>
       <c r="D292" s="13" t="inlineStr"/>
@@ -12569,7 +12549,7 @@
       </c>
       <c r="H292" s="10" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="I292" s="10" t="inlineStr">
@@ -12589,12 +12569,12 @@
       </c>
       <c r="B293" s="11" t="inlineStr">
         <is>
-          <t>ООО «Синергия»</t>
+          <t>ООО «СКП»</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>7841100278</t>
+          <t>7806619896</t>
         </is>
       </c>
       <c r="D293" s="13" t="inlineStr"/>
@@ -12607,7 +12587,7 @@
       </c>
       <c r="H293" s="10" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="I293" s="10" t="inlineStr">
@@ -12627,29 +12607,25 @@
       </c>
       <c r="B294" s="11" t="inlineStr">
         <is>
-          <t>ООО «СносСтройИнвест»</t>
+          <t>ООО «СМУ 8»</t>
         </is>
       </c>
       <c r="C294" s="12" t="inlineStr">
         <is>
-          <t>7805239355</t>
+          <t>7810531355</t>
         </is>
       </c>
       <c r="D294" s="13" t="inlineStr"/>
-      <c r="E294" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E294" s="11" t="inlineStr"/>
       <c r="F294" s="11" t="inlineStr"/>
       <c r="G294" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H294" s="10" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>367</t>
         </is>
       </c>
       <c r="I294" s="10" t="inlineStr">
@@ -12669,12 +12645,12 @@
       </c>
       <c r="B295" s="11" t="inlineStr">
         <is>
-          <t>ООО «СпецСтрой»</t>
+          <t>ООО «СПМК - 18»</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>7802753883</t>
+          <t>7814624120</t>
         </is>
       </c>
       <c r="D295" s="13" t="inlineStr"/>
@@ -12687,7 +12663,7 @@
       </c>
       <c r="H295" s="10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>537</t>
         </is>
       </c>
       <c r="I295" s="10" t="inlineStr">
@@ -12697,7 +12673,7 @@
       </c>
       <c r="J295" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -12707,16 +12683,20 @@
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>ООО «СпецТехнологии»</t>
+          <t>ООО «СПбЭК-Майнинг»</t>
         </is>
       </c>
       <c r="C296" s="12" t="inlineStr">
         <is>
-          <t>7839332955</t>
+          <t>7820326027</t>
         </is>
       </c>
       <c r="D296" s="13" t="inlineStr"/>
-      <c r="E296" s="11" t="inlineStr"/>
+      <c r="E296" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
       <c r="F296" s="11" t="inlineStr"/>
       <c r="G296" s="11" t="inlineStr">
         <is>
@@ -12725,7 +12705,7 @@
       </c>
       <c r="H296" s="10" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>548</t>
         </is>
       </c>
       <c r="I296" s="10" t="inlineStr">
@@ -12735,7 +12715,7 @@
       </c>
       <c r="J296" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -12745,12 +12725,12 @@
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецмонтаж»</t>
+          <t>ООО «СТРОИТЕЛЬ»</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>7806403311</t>
+          <t>7804338561</t>
         </is>
       </c>
       <c r="D297" s="13" t="inlineStr"/>
@@ -12763,7 +12743,7 @@
       </c>
       <c r="H297" s="10" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>678</t>
         </is>
       </c>
       <c r="I297" s="10" t="inlineStr">
@@ -12783,12 +12763,12 @@
       </c>
       <c r="B298" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецстрой»</t>
+          <t>ООО «СТРОЙ КОРПУС»</t>
         </is>
       </c>
       <c r="C298" s="12" t="inlineStr">
         <is>
-          <t>7802182340</t>
+          <t>7804553054</t>
         </is>
       </c>
       <c r="D298" s="13" t="inlineStr"/>
@@ -12801,7 +12781,7 @@
       </c>
       <c r="H298" s="10" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>679</t>
         </is>
       </c>
       <c r="I298" s="10" t="inlineStr">
@@ -12811,7 +12791,7 @@
       </c>
       <c r="J298" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12821,20 +12801,16 @@
       </c>
       <c r="B299" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецстроймонтаж»</t>
+          <t>ООО «СТРОЙГРАД РСУ»</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>7826156798</t>
+          <t>7802703995</t>
         </is>
       </c>
       <c r="D299" s="13" t="inlineStr"/>
-      <c r="E299" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E299" s="11" t="inlineStr"/>
       <c r="F299" s="11" t="inlineStr"/>
       <c r="G299" s="11" t="inlineStr">
         <is>
@@ -12843,7 +12819,7 @@
       </c>
       <c r="H299" s="10" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>877</t>
         </is>
       </c>
       <c r="I299" s="10" t="inlineStr">
@@ -12863,16 +12839,20 @@
       </c>
       <c r="B300" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительная компания «ДМ»</t>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
         </is>
       </c>
       <c r="C300" s="12" t="inlineStr">
         <is>
-          <t>4703058442</t>
+          <t>7825055370</t>
         </is>
       </c>
       <c r="D300" s="13" t="inlineStr"/>
-      <c r="E300" s="11" t="inlineStr"/>
+      <c r="E300" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
       <c r="F300" s="11" t="inlineStr"/>
       <c r="G300" s="11" t="inlineStr">
         <is>
@@ -12881,7 +12861,7 @@
       </c>
       <c r="H300" s="10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>573</t>
         </is>
       </c>
       <c r="I300" s="10" t="inlineStr">
@@ -12891,7 +12871,7 @@
       </c>
       <c r="J300" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12881,12 @@
       </c>
       <c r="B301" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительное дело-СГ»</t>
+          <t>ООО «СТРОЙКОНСУЛЬТ»</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>7826005559</t>
+          <t>7810289545</t>
         </is>
       </c>
       <c r="D301" s="13" t="inlineStr"/>
@@ -12919,7 +12899,7 @@
       </c>
       <c r="H301" s="10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>672</t>
         </is>
       </c>
       <c r="I301" s="10" t="inlineStr">
@@ -12929,7 +12909,7 @@
       </c>
       <c r="J301" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -12939,16 +12919,20 @@
       </c>
       <c r="B302" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные решения»</t>
+          <t>ООО «СУ-17»</t>
         </is>
       </c>
       <c r="C302" s="12" t="inlineStr">
         <is>
-          <t>7840099703</t>
+          <t>7807028906</t>
         </is>
       </c>
       <c r="D302" s="13" t="inlineStr"/>
-      <c r="E302" s="11" t="inlineStr"/>
+      <c r="E302" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
       <c r="F302" s="11" t="inlineStr"/>
       <c r="G302" s="11" t="inlineStr">
         <is>
@@ -12957,7 +12941,7 @@
       </c>
       <c r="H302" s="10" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>747</t>
         </is>
       </c>
       <c r="I302" s="10" t="inlineStr">
@@ -12967,7 +12951,7 @@
       </c>
       <c r="J302" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2300000</t>
         </is>
       </c>
     </row>
@@ -12977,18 +12961,18 @@
       </c>
       <c r="B303" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «СУАР-Групп»</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7802270195</t>
         </is>
       </c>
       <c r="D303" s="13" t="inlineStr"/>
       <c r="E303" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
         </is>
       </c>
       <c r="F303" s="11" t="inlineStr"/>
@@ -12999,7 +12983,7 @@
       </c>
       <c r="H303" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>518</t>
         </is>
       </c>
       <c r="I303" s="10" t="inlineStr">
@@ -13009,7 +12993,7 @@
       </c>
       <c r="J303" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -13019,16 +13003,20 @@
       </c>
       <c r="B304" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «СФ «Новэк»</t>
         </is>
       </c>
       <c r="C304" s="12" t="inlineStr">
         <is>
-          <t>7802880338</t>
+          <t>7825128540</t>
         </is>
       </c>
       <c r="D304" s="13" t="inlineStr"/>
-      <c r="E304" s="11" t="inlineStr"/>
+      <c r="E304" s="11" t="inlineStr">
+        <is>
+          <t>194352 СПб, ул.Кустодиева 17А; ОГРН 1027809227907; ген.дир. Смирнов Д.И.</t>
+        </is>
+      </c>
       <c r="F304" s="11" t="inlineStr"/>
       <c r="G304" s="11" t="inlineStr">
         <is>
@@ -13037,7 +13025,7 @@
       </c>
       <c r="H304" s="10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>512</t>
         </is>
       </c>
       <c r="I304" s="10" t="inlineStr">
@@ -13057,25 +13045,29 @@
       </c>
       <c r="B305" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительный Цех»</t>
+          <t>ООО «СЭМ»</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>7842391502</t>
+          <t>7810201646</t>
         </is>
       </c>
       <c r="D305" s="13" t="inlineStr"/>
-      <c r="E305" s="11" t="inlineStr"/>
+      <c r="E305" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
       <c r="F305" s="11" t="inlineStr"/>
       <c r="G305" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H305" s="10" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>700</t>
         </is>
       </c>
       <c r="I305" s="10" t="inlineStr">
@@ -13085,7 +13077,7 @@
       </c>
       <c r="J305" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -13095,29 +13087,25 @@
       </c>
       <c r="B306" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй центр»</t>
+          <t>ООО «Свой Дом»</t>
         </is>
       </c>
       <c r="C306" s="12" t="inlineStr">
         <is>
-          <t>7804538240</t>
+          <t>7813322254</t>
         </is>
       </c>
       <c r="D306" s="13" t="inlineStr"/>
-      <c r="E306" s="11" t="inlineStr">
-        <is>
-          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
-        </is>
-      </c>
+      <c r="E306" s="11" t="inlineStr"/>
       <c r="F306" s="11" t="inlineStr"/>
       <c r="G306" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H306" s="10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>591</t>
         </is>
       </c>
       <c r="I306" s="10" t="inlineStr">
@@ -13127,7 +13115,7 @@
       </c>
       <c r="J306" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13137,25 +13125,29 @@
       </c>
       <c r="B307" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй-Импульс»</t>
+          <t>ООО «СиФ»</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>7806313724</t>
+          <t>7801075307</t>
         </is>
       </c>
       <c r="D307" s="13" t="inlineStr"/>
-      <c r="E307" s="11" t="inlineStr"/>
+      <c r="E307" s="11" t="inlineStr">
+        <is>
+          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
+        </is>
+      </c>
       <c r="F307" s="11" t="inlineStr"/>
       <c r="G307" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H307" s="10" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I307" s="10" t="inlineStr">
@@ -13175,12 +13167,12 @@
       </c>
       <c r="B308" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй-С»</t>
+          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
         </is>
       </c>
       <c r="C308" s="12" t="inlineStr">
         <is>
-          <t>7802373183</t>
+          <t>7810691246</t>
         </is>
       </c>
       <c r="D308" s="13" t="inlineStr"/>
@@ -13193,7 +13185,7 @@
       </c>
       <c r="H308" s="10" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>588</t>
         </is>
       </c>
       <c r="I308" s="10" t="inlineStr">
@@ -13213,12 +13205,12 @@
       </c>
       <c r="B309" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «Синергия»</t>
         </is>
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7841100278</t>
         </is>
       </c>
       <c r="D309" s="13" t="inlineStr"/>
@@ -13231,7 +13223,7 @@
       </c>
       <c r="H309" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="I309" s="10" t="inlineStr">
@@ -13241,7 +13233,7 @@
       </c>
       <c r="J309" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13251,25 +13243,29 @@
       </c>
       <c r="B310" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройКом»</t>
+          <t>ООО «СносСтройИнвест»</t>
         </is>
       </c>
       <c r="C310" s="12" t="inlineStr">
         <is>
-          <t>7811469780</t>
+          <t>7805239355</t>
         </is>
       </c>
       <c r="D310" s="13" t="inlineStr"/>
-      <c r="E310" s="11" t="inlineStr"/>
+      <c r="E310" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
+        </is>
+      </c>
       <c r="F310" s="11" t="inlineStr"/>
       <c r="G310" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H310" s="10" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>351</t>
         </is>
       </c>
       <c r="I310" s="10" t="inlineStr">
@@ -13289,12 +13285,12 @@
       </c>
       <c r="B311" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройПроект»</t>
+          <t>ООО «СпецСтрой»</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>7804554072</t>
+          <t>7802753883</t>
         </is>
       </c>
       <c r="D311" s="13" t="inlineStr"/>
@@ -13307,7 +13303,7 @@
       </c>
       <c r="H311" s="10" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>267</t>
         </is>
       </c>
       <c r="I311" s="10" t="inlineStr">
@@ -13327,12 +13323,12 @@
       </c>
       <c r="B312" s="11" t="inlineStr">
         <is>
-          <t>ООО «Стройперспектива»</t>
+          <t>ООО «СпецТехнологии»</t>
         </is>
       </c>
       <c r="C312" s="12" t="inlineStr">
         <is>
-          <t>7810740278</t>
+          <t>7839332955</t>
         </is>
       </c>
       <c r="D312" s="13" t="inlineStr"/>
@@ -13345,7 +13341,7 @@
       </c>
       <c r="H312" s="10" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>680</t>
         </is>
       </c>
       <c r="I312" s="10" t="inlineStr">
@@ -13355,7 +13351,7 @@
       </c>
       <c r="J312" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13365,12 +13361,12 @@
       </c>
       <c r="B313" s="11" t="inlineStr">
         <is>
-          <t>ООО «СулуС»</t>
+          <t>ООО «Спецмонтаж»</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>7801369120</t>
+          <t>7806403311</t>
         </is>
       </c>
       <c r="D313" s="13" t="inlineStr"/>
@@ -13383,7 +13379,7 @@
       </c>
       <c r="H313" s="10" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>526</t>
         </is>
       </c>
       <c r="I313" s="10" t="inlineStr">
@@ -13393,7 +13389,7 @@
       </c>
       <c r="J313" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13403,20 +13399,16 @@
       </c>
       <c r="B314" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «Спецстрой»</t>
         </is>
       </c>
       <c r="C314" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7802182340</t>
         </is>
       </c>
       <c r="D314" s="13" t="inlineStr"/>
-      <c r="E314" s="11" t="inlineStr">
-        <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
-        </is>
-      </c>
+      <c r="E314" s="11" t="inlineStr"/>
       <c r="F314" s="11" t="inlineStr"/>
       <c r="G314" s="11" t="inlineStr">
         <is>
@@ -13425,7 +13417,7 @@
       </c>
       <c r="H314" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>521</t>
         </is>
       </c>
       <c r="I314" s="10" t="inlineStr">
@@ -13435,7 +13427,7 @@
       </c>
       <c r="J314" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13445,18 +13437,18 @@
       </c>
       <c r="B315" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТАЛИОН»</t>
+          <t>ООО «Спецстроймонтаж»</t>
         </is>
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>7801569190</t>
+          <t>7826156798</t>
         </is>
       </c>
       <c r="D315" s="13" t="inlineStr"/>
       <c r="E315" s="11" t="inlineStr">
         <is>
-          <t>197229 СПб, ул.Новая 51к1 пом.7-Н; ОГРН 1127847128639; ген.дир. Марков А.А.; техконтроль/испытания</t>
+          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
         </is>
       </c>
       <c r="F315" s="11" t="inlineStr"/>
@@ -13467,7 +13459,7 @@
       </c>
       <c r="H315" s="10" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>505</t>
         </is>
       </c>
       <c r="I315" s="10" t="inlineStr">
@@ -13487,12 +13479,12 @@
       </c>
       <c r="B316" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТД «Буревестник»</t>
+          <t>ООО «Строительная компания «ДМ»</t>
         </is>
       </c>
       <c r="C316" s="12" t="inlineStr">
         <is>
-          <t>4705075034</t>
+          <t>4703058442</t>
         </is>
       </c>
       <c r="D316" s="13" t="inlineStr"/>
@@ -13505,7 +13497,7 @@
       </c>
       <c r="H316" s="10" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>252</t>
         </is>
       </c>
       <c r="I316" s="10" t="inlineStr">
@@ -13525,29 +13517,25 @@
       </c>
       <c r="B317" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕЗИС»</t>
+          <t>ООО «Строительное дело-СГ»</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>7804441209</t>
+          <t>7826005559</t>
         </is>
       </c>
       <c r="D317" s="13" t="inlineStr"/>
-      <c r="E317" s="11" t="inlineStr">
-        <is>
-          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
-        </is>
-      </c>
+      <c r="E317" s="11" t="inlineStr"/>
       <c r="F317" s="11" t="inlineStr"/>
       <c r="G317" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H317" s="10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>242</t>
         </is>
       </c>
       <c r="I317" s="10" t="inlineStr">
@@ -13557,7 +13545,7 @@
       </c>
       <c r="J317" s="10" t="inlineStr">
         <is>
-          <t>700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13567,12 +13555,12 @@
       </c>
       <c r="B318" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕХНОТРАНССТРОЙ»</t>
+          <t>ООО «Строительные решения»</t>
         </is>
       </c>
       <c r="C318" s="12" t="inlineStr">
         <is>
-          <t>5190067514</t>
+          <t>7840099703</t>
         </is>
       </c>
       <c r="D318" s="13" t="inlineStr"/>
@@ -13585,7 +13573,7 @@
       </c>
       <c r="H318" s="10" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="I318" s="10" t="inlineStr">
@@ -13605,18 +13593,18 @@
       </c>
       <c r="B319" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7813680179</t>
         </is>
       </c>
       <c r="D319" s="13" t="inlineStr"/>
       <c r="E319" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
         </is>
       </c>
       <c r="F319" s="11" t="inlineStr"/>
@@ -13627,7 +13615,7 @@
       </c>
       <c r="H319" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="I319" s="10" t="inlineStr">
@@ -13647,12 +13635,12 @@
       </c>
       <c r="B320" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТМС»</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C320" s="12" t="inlineStr">
         <is>
-          <t>7801629643</t>
+          <t>7802880338</t>
         </is>
       </c>
       <c r="D320" s="13" t="inlineStr"/>
@@ -13665,7 +13653,7 @@
       </c>
       <c r="H320" s="10" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>239</t>
         </is>
       </c>
       <c r="I320" s="10" t="inlineStr">
@@ -13685,12 +13673,12 @@
       </c>
       <c r="B321" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТСК «ОЛИМП»</t>
+          <t>ООО «Строительный Цех»</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>4205310949</t>
+          <t>7842391502</t>
         </is>
       </c>
       <c r="D321" s="13" t="inlineStr"/>
@@ -13703,7 +13691,7 @@
       </c>
       <c r="H321" s="10" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>554</t>
         </is>
       </c>
       <c r="I321" s="10" t="inlineStr">
@@ -13713,7 +13701,7 @@
       </c>
       <c r="J321" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13723,29 +13711,29 @@
       </c>
       <c r="B322" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «Строй центр»</t>
         </is>
       </c>
       <c r="C322" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7804538240</t>
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr"/>
       <c r="E322" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
         </is>
       </c>
       <c r="F322" s="11" t="inlineStr"/>
       <c r="G322" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H322" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>732</t>
         </is>
       </c>
       <c r="I322" s="10" t="inlineStr">
@@ -13755,7 +13743,7 @@
       </c>
       <c r="J322" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -13765,12 +13753,12 @@
       </c>
       <c r="B323" s="11" t="inlineStr">
         <is>
-          <t>ООО «Текманн»</t>
+          <t>ООО «Строй-Импульс»</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
         <is>
-          <t>7842508750</t>
+          <t>7806313724</t>
         </is>
       </c>
       <c r="D323" s="13" t="inlineStr"/>
@@ -13783,7 +13771,7 @@
       </c>
       <c r="H323" s="10" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="I323" s="10" t="inlineStr">
@@ -13803,12 +13791,12 @@
       </c>
       <c r="B324" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТехЭнерго»</t>
+          <t>ООО «Строй-С»</t>
         </is>
       </c>
       <c r="C324" s="12" t="inlineStr">
         <is>
-          <t>7816531513</t>
+          <t>7802373183</t>
         </is>
       </c>
       <c r="D324" s="13" t="inlineStr"/>
@@ -13821,7 +13809,7 @@
       </c>
       <c r="H324" s="10" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>599</t>
         </is>
       </c>
       <c r="I324" s="10" t="inlineStr">
@@ -13831,7 +13819,7 @@
       </c>
       <c r="J324" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13841,12 +13829,12 @@
       </c>
       <c r="B325" s="11" t="inlineStr">
         <is>
-          <t>ООО «Технические Системы»</t>
+          <t>ООО «СтройГрад»</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>7807345648</t>
+          <t>7813692632</t>
         </is>
       </c>
       <c r="D325" s="13" t="inlineStr"/>
@@ -13859,7 +13847,7 @@
       </c>
       <c r="H325" s="10" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="I325" s="10" t="inlineStr">
@@ -13869,7 +13857,7 @@
       </c>
       <c r="J325" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -13879,12 +13867,12 @@
       </c>
       <c r="B326" s="11" t="inlineStr">
         <is>
-          <t>ООО «Техно Эйр Групп»</t>
+          <t>ООО «СтройКом»</t>
         </is>
       </c>
       <c r="C326" s="12" t="inlineStr">
         <is>
-          <t>7816594954</t>
+          <t>7811469780</t>
         </is>
       </c>
       <c r="D326" s="13" t="inlineStr"/>
@@ -13897,7 +13885,7 @@
       </c>
       <c r="H326" s="10" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>602</t>
         </is>
       </c>
       <c r="I326" s="10" t="inlineStr">
@@ -13917,20 +13905,16 @@
       </c>
       <c r="B327" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «СтройПроект»</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7804554072</t>
         </is>
       </c>
       <c r="D327" s="13" t="inlineStr"/>
-      <c r="E327" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
-        </is>
-      </c>
+      <c r="E327" s="11" t="inlineStr"/>
       <c r="F327" s="11" t="inlineStr"/>
       <c r="G327" s="11" t="inlineStr">
         <is>
@@ -13939,7 +13923,7 @@
       </c>
       <c r="H327" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>291</t>
         </is>
       </c>
       <c r="I327" s="10" t="inlineStr">
@@ -13949,7 +13933,7 @@
       </c>
       <c r="J327" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13959,20 +13943,16 @@
       </c>
       <c r="B328" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трест «Сантехмонтаж-1»</t>
+          <t>ООО «Стройперспектива»</t>
         </is>
       </c>
       <c r="C328" s="12" t="inlineStr">
         <is>
-          <t>4706050882</t>
+          <t>7810740278</t>
         </is>
       </c>
       <c r="D328" s="13" t="inlineStr"/>
-      <c r="E328" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Мытнинская 12/44А пом.13н оф.14; ОГРН 1224700013230; сантехмонтаж, вентиляция, ИТП</t>
-        </is>
-      </c>
+      <c r="E328" s="11" t="inlineStr"/>
       <c r="F328" s="11" t="inlineStr"/>
       <c r="G328" s="11" t="inlineStr">
         <is>
@@ -13981,7 +13961,7 @@
       </c>
       <c r="H328" s="10" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>932</t>
         </is>
       </c>
       <c r="I328" s="10" t="inlineStr">
@@ -14001,20 +13981,16 @@
       </c>
       <c r="B329" s="11" t="inlineStr">
         <is>
-          <t>ООО «УМ «Эталон»</t>
+          <t>ООО «СулуС»</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>7810048170</t>
+          <t>7801369120</t>
         </is>
       </c>
       <c r="D329" s="13" t="inlineStr"/>
-      <c r="E329" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Богатырский пр. 2А каб.0.09; ОГРН 1057813303767; ген.дир. Харитонов О.В.; башенные краны; УК 463 млн</t>
-        </is>
-      </c>
+      <c r="E329" s="11" t="inlineStr"/>
       <c r="F329" s="11" t="inlineStr"/>
       <c r="G329" s="11" t="inlineStr">
         <is>
@@ -14023,7 +13999,7 @@
       </c>
       <c r="H329" s="10" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>754</t>
         </is>
       </c>
       <c r="I329" s="10" t="inlineStr">
@@ -14033,7 +14009,7 @@
       </c>
       <c r="J329" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14043,16 +14019,20 @@
       </c>
       <c r="B330" s="11" t="inlineStr">
         <is>
-          <t>ООО «УМ-11»</t>
+          <t>ООО «Сфера»</t>
         </is>
       </c>
       <c r="C330" s="12" t="inlineStr">
         <is>
-          <t>7805802232</t>
+          <t>2311308786</t>
         </is>
       </c>
       <c r="D330" s="13" t="inlineStr"/>
-      <c r="E330" s="11" t="inlineStr"/>
+      <c r="E330" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
       <c r="F330" s="11" t="inlineStr"/>
       <c r="G330" s="11" t="inlineStr">
         <is>
@@ -14061,7 +14041,7 @@
       </c>
       <c r="H330" s="10" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="I330" s="10" t="inlineStr">
@@ -14071,7 +14051,7 @@
       </c>
       <c r="J330" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -14081,16 +14061,20 @@
       </c>
       <c r="B331" s="11" t="inlineStr">
         <is>
-          <t>ООО «УСН»</t>
+          <t>ООО «ТАЛИОН»</t>
         </is>
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>7819306040</t>
+          <t>7801569190</t>
         </is>
       </c>
       <c r="D331" s="13" t="inlineStr"/>
-      <c r="E331" s="11" t="inlineStr"/>
+      <c r="E331" s="11" t="inlineStr">
+        <is>
+          <t>197229 СПб, ул.Новая 51к1 пом.7-Н; ОГРН 1127847128639; ген.дир. Марков А.А.; техконтроль/испытания</t>
+        </is>
+      </c>
       <c r="F331" s="11" t="inlineStr"/>
       <c r="G331" s="11" t="inlineStr">
         <is>
@@ -14099,7 +14083,7 @@
       </c>
       <c r="H331" s="10" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="I331" s="10" t="inlineStr">
@@ -14119,12 +14103,12 @@
       </c>
       <c r="B332" s="11" t="inlineStr">
         <is>
-          <t>ООО «Универсалстрой»</t>
+          <t>ООО «ТД «Буревестник»</t>
         </is>
       </c>
       <c r="C332" s="12" t="inlineStr">
         <is>
-          <t>7801227091</t>
+          <t>4705075034</t>
         </is>
       </c>
       <c r="D332" s="13" t="inlineStr"/>
@@ -14137,7 +14121,7 @@
       </c>
       <c r="H332" s="10" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="I332" s="10" t="inlineStr">
@@ -14157,25 +14141,29 @@
       </c>
       <c r="B333" s="11" t="inlineStr">
         <is>
-          <t>ООО «ФОРЕСТ ДОРС»</t>
+          <t>ООО «ТЕЗИС»</t>
         </is>
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>7820045700</t>
+          <t>7804441209</t>
         </is>
       </c>
       <c r="D333" s="13" t="inlineStr"/>
-      <c r="E333" s="11" t="inlineStr"/>
+      <c r="E333" s="11" t="inlineStr">
+        <is>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+        </is>
+      </c>
       <c r="F333" s="11" t="inlineStr"/>
       <c r="G333" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H333" s="10" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>674</t>
         </is>
       </c>
       <c r="I333" s="10" t="inlineStr">
@@ -14185,7 +14173,7 @@
       </c>
       <c r="J333" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>700000</t>
         </is>
       </c>
     </row>
@@ -14195,12 +14183,12 @@
       </c>
       <c r="B334" s="11" t="inlineStr">
         <is>
-          <t>ООО «ФОРТИС»</t>
+          <t>ООО «ТЕХНОТРАНССТРОЙ»</t>
         </is>
       </c>
       <c r="C334" s="12" t="inlineStr">
         <is>
-          <t>7817119800</t>
+          <t>5190067514</t>
         </is>
       </c>
       <c r="D334" s="13" t="inlineStr"/>
@@ -14213,7 +14201,7 @@
       </c>
       <c r="H334" s="10" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>787</t>
         </is>
       </c>
       <c r="I334" s="10" t="inlineStr">
@@ -14233,16 +14221,20 @@
       </c>
       <c r="B335" s="11" t="inlineStr">
         <is>
-          <t>ООО «Холодпроф»</t>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
         </is>
       </c>
       <c r="C335" s="12" t="inlineStr">
         <is>
-          <t>7842418360</t>
+          <t>7814612968</t>
         </is>
       </c>
       <c r="D335" s="13" t="inlineStr"/>
-      <c r="E335" s="11" t="inlineStr"/>
+      <c r="E335" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
       <c r="F335" s="11" t="inlineStr"/>
       <c r="G335" s="11" t="inlineStr">
         <is>
@@ -14251,7 +14243,7 @@
       </c>
       <c r="H335" s="10" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>335</t>
         </is>
       </c>
       <c r="I335" s="10" t="inlineStr">
@@ -14261,7 +14253,7 @@
       </c>
       <c r="J335" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -14271,20 +14263,16 @@
       </c>
       <c r="B336" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «ТМС»</t>
         </is>
       </c>
       <c r="C336" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>7801629643</t>
         </is>
       </c>
       <c r="D336" s="13" t="inlineStr"/>
-      <c r="E336" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
-        </is>
-      </c>
+      <c r="E336" s="11" t="inlineStr"/>
       <c r="F336" s="11" t="inlineStr"/>
       <c r="G336" s="11" t="inlineStr">
         <is>
@@ -14293,7 +14281,7 @@
       </c>
       <c r="H336" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I336" s="10" t="inlineStr">
@@ -14303,7 +14291,7 @@
       </c>
       <c r="J336" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14313,12 +14301,12 @@
       </c>
       <c r="B337" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦИКЛОН»</t>
+          <t>ООО «ТСК «ОЛИМП»</t>
         </is>
       </c>
       <c r="C337" s="12" t="inlineStr">
         <is>
-          <t>7801225591</t>
+          <t>4205310949</t>
         </is>
       </c>
       <c r="D337" s="13" t="inlineStr"/>
@@ -14331,7 +14319,7 @@
       </c>
       <c r="H337" s="10" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>244</t>
         </is>
       </c>
       <c r="I337" s="10" t="inlineStr">
@@ -14351,16 +14339,20 @@
       </c>
       <c r="B338" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦИТАДЕЛЬ»</t>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
         </is>
       </c>
       <c r="C338" s="12" t="inlineStr">
         <is>
-          <t>7817122190</t>
+          <t>7839061021</t>
         </is>
       </c>
       <c r="D338" s="13" t="inlineStr"/>
-      <c r="E338" s="11" t="inlineStr"/>
+      <c r="E338" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
       <c r="F338" s="11" t="inlineStr"/>
       <c r="G338" s="11" t="inlineStr">
         <is>
@@ -14369,7 +14361,7 @@
       </c>
       <c r="H338" s="10" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I338" s="10" t="inlineStr">
@@ -14379,7 +14371,7 @@
       </c>
       <c r="J338" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -14389,20 +14381,16 @@
       </c>
       <c r="B339" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «Текманн»</t>
         </is>
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7842508750</t>
         </is>
       </c>
       <c r="D339" s="13" t="inlineStr"/>
-      <c r="E339" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
-        </is>
-      </c>
+      <c r="E339" s="11" t="inlineStr"/>
       <c r="F339" s="11" t="inlineStr"/>
       <c r="G339" s="11" t="inlineStr">
         <is>
@@ -14411,7 +14399,7 @@
       </c>
       <c r="H339" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>694</t>
         </is>
       </c>
       <c r="I339" s="10" t="inlineStr">
@@ -14421,7 +14409,7 @@
       </c>
       <c r="J339" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14431,29 +14419,25 @@
       </c>
       <c r="B340" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «ТехЭнерго»</t>
         </is>
       </c>
       <c r="C340" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7816531513</t>
         </is>
       </c>
       <c r="D340" s="13" t="inlineStr"/>
-      <c r="E340" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
-        </is>
-      </c>
+      <c r="E340" s="11" t="inlineStr"/>
       <c r="F340" s="11" t="inlineStr"/>
       <c r="G340" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H340" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I340" s="10" t="inlineStr">
@@ -14463,7 +14447,7 @@
       </c>
       <c r="J340" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14457,12 @@
       </c>
       <c r="B341" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энерго Альянс»</t>
+          <t>ООО «Технические Системы»</t>
         </is>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>7813579997</t>
+          <t>7807345648</t>
         </is>
       </c>
       <c r="D341" s="13" t="inlineStr"/>
@@ -14491,7 +14475,7 @@
       </c>
       <c r="H341" s="10" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>511</t>
         </is>
       </c>
       <c r="I341" s="10" t="inlineStr">
@@ -14511,12 +14495,12 @@
       </c>
       <c r="B342" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЭнергоИнвест»</t>
+          <t>ООО «Техно Эйр Групп»</t>
         </is>
       </c>
       <c r="C342" s="12" t="inlineStr">
         <is>
-          <t>7841378040</t>
+          <t>7816594954</t>
         </is>
       </c>
       <c r="D342" s="13" t="inlineStr"/>
@@ -14529,7 +14513,7 @@
       </c>
       <c r="H342" s="10" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>661</t>
         </is>
       </c>
       <c r="I342" s="10" t="inlineStr">
@@ -14549,18 +14533,18 @@
       </c>
       <c r="B343" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Трамплин-строй»</t>
         </is>
       </c>
       <c r="C343" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7802207193</t>
         </is>
       </c>
       <c r="D343" s="13" t="inlineStr"/>
       <c r="E343" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
         </is>
       </c>
       <c r="F343" s="11" t="inlineStr"/>
@@ -14571,7 +14555,7 @@
       </c>
       <c r="H343" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>726</t>
         </is>
       </c>
       <c r="I343" s="10" t="inlineStr">
@@ -14581,7 +14565,7 @@
       </c>
       <c r="J343" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -14591,18 +14575,18 @@
       </c>
       <c r="B344" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «Трест «Сантехмонтаж-1»</t>
         </is>
       </c>
       <c r="C344" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>4706050882</t>
         </is>
       </c>
       <c r="D344" s="13" t="inlineStr"/>
       <c r="E344" s="11" t="inlineStr">
         <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+          <t>СПб, ул.Мытнинская 12/44А пом.13н оф.14; ОГРН 1224700013230; сантехмонтаж, вентиляция, ИТП</t>
         </is>
       </c>
       <c r="F344" s="11" t="inlineStr"/>
@@ -14613,7 +14597,7 @@
       </c>
       <c r="H344" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="I344" s="10" t="inlineStr">
@@ -14623,7 +14607,7 @@
       </c>
       <c r="J344" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14633,29 +14617,29 @@
       </c>
       <c r="B345" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «УМ «Эталон»</t>
         </is>
       </c>
       <c r="C345" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7810048170</t>
         </is>
       </c>
       <c r="D345" s="13" t="inlineStr"/>
       <c r="E345" s="11" t="inlineStr">
         <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+          <t>СПб, Богатырский пр. 2А каб.0.09; ОГРН 1057813303767; ген.дир. Харитонов О.В.; башенные краны; УК 463 млн</t>
         </is>
       </c>
       <c r="F345" s="11" t="inlineStr"/>
       <c r="G345" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H345" s="10" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>701</t>
         </is>
       </c>
       <c r="I345" s="10" t="inlineStr">
@@ -14665,7 +14649,7 @@
       </c>
       <c r="J345" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -14675,12 +14659,12 @@
       </c>
       <c r="B346" s="11" t="inlineStr">
         <is>
-          <t>ООО ПСМ «Спутник»</t>
+          <t>ООО «УМ-11»</t>
         </is>
       </c>
       <c r="C346" s="12" t="inlineStr">
         <is>
-          <t>7810765071</t>
+          <t>7805802232</t>
         </is>
       </c>
       <c r="D346" s="13" t="inlineStr"/>
@@ -14693,7 +14677,7 @@
       </c>
       <c r="H346" s="10" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="I346" s="10" t="inlineStr">
@@ -14713,12 +14697,12 @@
       </c>
       <c r="B347" s="11" t="inlineStr">
         <is>
-          <t>ООО СК «Аврора-Строй»</t>
+          <t>ООО «УСН»</t>
         </is>
       </c>
       <c r="C347" s="12" t="inlineStr">
         <is>
-          <t>7801700173</t>
+          <t>7819306040</t>
         </is>
       </c>
       <c r="D347" s="13" t="inlineStr"/>
@@ -14731,22 +14715,654 @@
       </c>
       <c r="H347" s="10" t="inlineStr">
         <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="I347" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J347" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="10" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Универсалстрой»</t>
+        </is>
+      </c>
+      <c r="C348" s="12" t="inlineStr">
+        <is>
+          <t>7801227091</t>
+        </is>
+      </c>
+      <c r="D348" s="13" t="inlineStr"/>
+      <c r="E348" s="11" t="inlineStr"/>
+      <c r="F348" s="11" t="inlineStr"/>
+      <c r="G348" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H348" s="10" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="I348" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J348" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="10" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ФОРЕСТ ДОРС»</t>
+        </is>
+      </c>
+      <c r="C349" s="12" t="inlineStr">
+        <is>
+          <t>7820045700</t>
+        </is>
+      </c>
+      <c r="D349" s="13" t="inlineStr"/>
+      <c r="E349" s="11" t="inlineStr"/>
+      <c r="F349" s="11" t="inlineStr"/>
+      <c r="G349" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H349" s="10" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="I349" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J349" s="10" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="10" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ФОРТИС»</t>
+        </is>
+      </c>
+      <c r="C350" s="12" t="inlineStr">
+        <is>
+          <t>7817119800</t>
+        </is>
+      </c>
+      <c r="D350" s="13" t="inlineStr"/>
+      <c r="E350" s="11" t="inlineStr"/>
+      <c r="F350" s="11" t="inlineStr"/>
+      <c r="G350" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H350" s="10" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="I350" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J350" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Холодпроф»</t>
+        </is>
+      </c>
+      <c r="C351" s="12" t="inlineStr">
+        <is>
+          <t>7842418360</t>
+        </is>
+      </c>
+      <c r="D351" s="13" t="inlineStr"/>
+      <c r="E351" s="11" t="inlineStr"/>
+      <c r="F351" s="11" t="inlineStr"/>
+      <c r="G351" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H351" s="10" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="I351" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J351" s="10" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="10" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C352" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D352" s="13" t="inlineStr"/>
+      <c r="E352" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F352" s="11" t="inlineStr"/>
+      <c r="G352" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H352" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I352" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J352" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="10" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦИКЛОН»</t>
+        </is>
+      </c>
+      <c r="C353" s="12" t="inlineStr">
+        <is>
+          <t>7801225591</t>
+        </is>
+      </c>
+      <c r="D353" s="13" t="inlineStr"/>
+      <c r="E353" s="11" t="inlineStr"/>
+      <c r="F353" s="11" t="inlineStr"/>
+      <c r="G353" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H353" s="10" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="I353" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J353" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="10" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦИТАДЕЛЬ»</t>
+        </is>
+      </c>
+      <c r="C354" s="12" t="inlineStr">
+        <is>
+          <t>7817122190</t>
+        </is>
+      </c>
+      <c r="D354" s="13" t="inlineStr"/>
+      <c r="E354" s="11" t="inlineStr"/>
+      <c r="F354" s="11" t="inlineStr"/>
+      <c r="G354" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H354" s="10" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="I354" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J354" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="10" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C355" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D355" s="13" t="inlineStr"/>
+      <c r="E355" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F355" s="11" t="inlineStr"/>
+      <c r="G355" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H355" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I355" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J355" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="10" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C356" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D356" s="13" t="inlineStr"/>
+      <c r="E356" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F356" s="11" t="inlineStr"/>
+      <c r="G356" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H356" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I356" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J356" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="10" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энерго Альянс»</t>
+        </is>
+      </c>
+      <c r="C357" s="12" t="inlineStr">
+        <is>
+          <t>7813579997</t>
+        </is>
+      </c>
+      <c r="D357" s="13" t="inlineStr"/>
+      <c r="E357" s="11" t="inlineStr"/>
+      <c r="F357" s="11" t="inlineStr"/>
+      <c r="G357" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H357" s="10" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="I357" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J357" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="10" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЭнергоИнвест»</t>
+        </is>
+      </c>
+      <c r="C358" s="12" t="inlineStr">
+        <is>
+          <t>7841378040</t>
+        </is>
+      </c>
+      <c r="D358" s="13" t="inlineStr"/>
+      <c r="E358" s="11" t="inlineStr"/>
+      <c r="F358" s="11" t="inlineStr"/>
+      <c r="G358" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H358" s="10" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="I358" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J358" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="10" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C359" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D359" s="13" t="inlineStr"/>
+      <c r="E359" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F359" s="11" t="inlineStr"/>
+      <c r="G359" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H359" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I359" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J359" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="10" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C360" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D360" s="13" t="inlineStr"/>
+      <c r="E360" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F360" s="11" t="inlineStr"/>
+      <c r="G360" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H360" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I360" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J360" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="10" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C361" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D361" s="13" t="inlineStr"/>
+      <c r="E361" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F361" s="11" t="inlineStr"/>
+      <c r="G361" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H361" s="10" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="I361" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J361" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="10" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="11" t="inlineStr">
+        <is>
+          <t>ООО ПСМ «Спутник»</t>
+        </is>
+      </c>
+      <c r="C362" s="12" t="inlineStr">
+        <is>
+          <t>7810765071</t>
+        </is>
+      </c>
+      <c r="D362" s="13" t="inlineStr"/>
+      <c r="E362" s="11" t="inlineStr"/>
+      <c r="F362" s="11" t="inlineStr"/>
+      <c r="G362" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H362" s="10" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="I362" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J362" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="10" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="11" t="inlineStr">
+        <is>
+          <t>ООО СК «Аврора-Строй»</t>
+        </is>
+      </c>
+      <c r="C363" s="12" t="inlineStr">
+        <is>
+          <t>7801700173</t>
+        </is>
+      </c>
+      <c r="D363" s="13" t="inlineStr"/>
+      <c r="E363" s="11" t="inlineStr"/>
+      <c r="F363" s="11" t="inlineStr"/>
+      <c r="G363" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H363" s="10" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="I347" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J347" s="10" t="inlineStr">
+      <c r="I363" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J363" s="10" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J347"/>
+  <autoFilter ref="A1:J363"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14829,7 +15445,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>346</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8">
@@ -14849,7 +15465,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Телефоны СРО-410'!$A$1:$J$379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J363"/>
+  <dimension ref="A1:J379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>ООО «АТС»</t>
+          <t>ООО «АТЛОН ФМ СЕВЕР»</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>7841019066</t>
+          <t>7802931945</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr"/>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>ООО «Аверс Наследие»</t>
+          <t>ООО «АТМ-Монтаж»</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>7801743219</t>
+          <t>7807075536</t>
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr"/>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>985</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>ООО «АвиаПроСвет»</t>
+          <t>ООО «АТОМ»</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>7811714538</t>
+          <t>7813531723</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>ООО «Айстарт»</t>
+          <t>ООО «АТС»</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>7841061413</t>
+          <t>7841019066</t>
         </is>
       </c>
       <c r="D126" s="13" t="inlineStr"/>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>ООО «Академия Фасадов»</t>
+          <t>ООО «Аверс Наследие»</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>7814848410</t>
+          <t>7801743219</t>
         </is>
       </c>
       <c r="D127" s="13" t="inlineStr"/>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>ООО «Аквадор»</t>
+          <t>ООО «АвиаПроСвет»</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>7811508912</t>
+          <t>7811714538</t>
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr"/>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>929</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>ООО «Аквил»</t>
+          <t>ООО «Айстарт»</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>7804425944</t>
+          <t>7841061413</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr"/>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>452</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>ООО «Акканто»</t>
+          <t>ООО «Академия Фасадов»</t>
         </is>
       </c>
       <c r="C130" s="12" t="inlineStr">
         <is>
-          <t>7811815920</t>
+          <t>7814848410</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr"/>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>ООО «Актика»</t>
+          <t>ООО «Аквадор»</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>7838430325</t>
+          <t>7811508912</t>
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="H131" s="10" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr">
@@ -6199,33 +6199,25 @@
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>ООО «Алисард»</t>
+          <t>ООО «Аквил»</t>
         </is>
       </c>
       <c r="C132" s="12" t="inlineStr">
         <is>
-          <t>7814713356</t>
+          <t>7804425944</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr"/>
-      <c r="E132" s="11" t="inlineStr">
-        <is>
-          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
-        </is>
-      </c>
-      <c r="F132" s="11" t="inlineStr">
-        <is>
-          <t>alisard.com</t>
-        </is>
-      </c>
+      <c r="E132" s="11" t="inlineStr"/>
+      <c r="F132" s="11" t="inlineStr"/>
       <c r="G132" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть e-mail и сайт)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>229</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr">
@@ -6235,7 +6227,7 @@
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6245,12 +6237,12 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альфа»</t>
+          <t>ООО «Акканто»</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>7802594841</t>
+          <t>7811815920</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr"/>
@@ -6263,7 +6255,7 @@
       </c>
       <c r="H133" s="10" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr">
@@ -6273,7 +6265,7 @@
       </c>
       <c r="J133" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6283,29 +6275,25 @@
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>ООО «Актика»</t>
         </is>
       </c>
       <c r="C134" s="12" t="inlineStr">
         <is>
-          <t>7814300662</t>
+          <t>7838430325</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr"/>
-      <c r="E134" s="11" t="inlineStr">
-        <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
-        </is>
-      </c>
+      <c r="E134" s="11" t="inlineStr"/>
       <c r="F134" s="11" t="inlineStr"/>
       <c r="G134" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>419</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr">
@@ -6315,7 +6303,7 @@
       </c>
       <c r="J134" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6325,25 +6313,33 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>ООО «Альянс»</t>
+          <t>ООО «Алисард»</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>7708532710</t>
+          <t>7814713356</t>
         </is>
       </c>
       <c r="D135" s="13" t="inlineStr"/>
-      <c r="E135" s="11" t="inlineStr"/>
-      <c r="F135" s="11" t="inlineStr"/>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>197375 СПб, Вербная ул. 27А пом.5-н оф.419; ОГРН 1177847380248; e-mail info@alisard.com; сайт alisard.com</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>alisard.com</t>
+        </is>
+      </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть e-mail и сайт)</t>
         </is>
       </c>
       <c r="H135" s="10" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>575</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr">
@@ -6353,7 +6349,7 @@
       </c>
       <c r="J135" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6363,20 +6359,16 @@
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>ООО «Анва-Сервис»</t>
+          <t>ООО «Альфа»</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
         <is>
-          <t>7805721872</t>
+          <t>7802594841</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr"/>
-      <c r="E136" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Кронштадтская 3к4 пом.6-Н оф.8.2; ОГРН 1187847032560; ген.дир. Васильев В.В.</t>
-        </is>
-      </c>
+      <c r="E136" s="11" t="inlineStr"/>
       <c r="F136" s="11" t="inlineStr"/>
       <c r="G136" s="11" t="inlineStr">
         <is>
@@ -6385,7 +6377,7 @@
       </c>
       <c r="H136" s="10" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr">
@@ -6395,7 +6387,7 @@
       </c>
       <c r="J136" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6405,25 +6397,29 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>ООО «Антарес»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>7802937023</t>
+          <t>7814300662</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr"/>
-      <c r="E137" s="11" t="inlineStr"/>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1047855002436; ген.дир. Милованцев А.А.</t>
+        </is>
+      </c>
       <c r="F137" s="11" t="inlineStr"/>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H137" s="10" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr">
@@ -6433,7 +6429,7 @@
       </c>
       <c r="J137" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -6443,29 +6439,25 @@
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>ООО «Антей»</t>
+          <t>ООО «Альянс»</t>
         </is>
       </c>
       <c r="C138" s="12" t="inlineStr">
         <is>
-          <t>4708011991</t>
+          <t>7708532710</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr"/>
-      <c r="E138" s="11" t="inlineStr">
-        <is>
-          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
-        </is>
-      </c>
+      <c r="E138" s="11" t="inlineStr"/>
       <c r="F138" s="11" t="inlineStr"/>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr">
@@ -6475,7 +6467,7 @@
       </c>
       <c r="J138" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6485,16 +6477,20 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>ООО «Арестак-Строй»</t>
+          <t>ООО «Анва-Сервис»</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>7807286304</t>
+          <t>7805721872</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr"/>
-      <c r="E139" s="11" t="inlineStr"/>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кронштадтская 3к4 пом.6-Н оф.8.2; ОГРН 1187847032560; ген.дир. Васильев В.В.</t>
+        </is>
+      </c>
       <c r="F139" s="11" t="inlineStr"/>
       <c r="G139" s="11" t="inlineStr">
         <is>
@@ -6503,7 +6499,7 @@
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr">
@@ -6523,12 +6519,12 @@
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>ООО «АркаСтрой»</t>
+          <t>ООО «Антарес»</t>
         </is>
       </c>
       <c r="C140" s="12" t="inlineStr">
         <is>
-          <t>7810504390</t>
+          <t>7802937023</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr"/>
@@ -6541,7 +6537,7 @@
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr">
@@ -6551,7 +6547,7 @@
       </c>
       <c r="J140" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6561,29 +6557,29 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>ООО «Арман»</t>
+          <t>ООО «Антей»</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>7805298463</t>
+          <t>4708011991</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr"/>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
+          <t>Лен.обл., г.Кириши, пр.Победы 30; ген.дир. Дряхлов В.В.; электромонтаж</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr">
@@ -6603,12 +6599,12 @@
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>ООО «Архитектурные Решения»</t>
+          <t>ООО «Арестак-Строй»</t>
         </is>
       </c>
       <c r="C142" s="12" t="inlineStr">
         <is>
-          <t>7810918306</t>
+          <t>7807286304</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr"/>
@@ -6621,7 +6617,7 @@
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="I142" s="10" t="inlineStr">
@@ -6641,12 +6637,12 @@
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>ООО «АтРес»</t>
+          <t>ООО «АркаСтрой»</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>7813687270</t>
+          <t>7810504390</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr"/>
@@ -6659,7 +6655,7 @@
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>542</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr">
@@ -6669,7 +6665,7 @@
       </c>
       <c r="J143" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -6679,16 +6675,20 @@
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлант»</t>
+          <t>ООО «Арман»</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>7838082413</t>
+          <t>7805298463</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr"/>
-      <c r="E144" s="11" t="inlineStr"/>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>198152 СПб, Краснопутиловская ул. 69А пом.17н; ОГРН 1047808016937; управляющая — ООО «АРМАН ГРУПП»; выручка 4,2 млрд</t>
+        </is>
+      </c>
       <c r="F144" s="11" t="inlineStr"/>
       <c r="G144" s="11" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>586</t>
         </is>
       </c>
       <c r="I144" s="10" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="J144" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -6717,12 +6717,12 @@
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлантис»</t>
+          <t>ООО «Архитектурные Решения»</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>7810914904</t>
+          <t>7810918306</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr"/>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="J145" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлас групп»</t>
+          <t>ООО «АтРес»</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>7811587054</t>
+          <t>7813687270</t>
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr"/>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>ООО «Атлас»</t>
+          <t>ООО «Атлант»</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>7804667213</t>
+          <t>7838082413</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr"/>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr">
@@ -6831,20 +6831,16 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАРК»</t>
+          <t>ООО «Атлантис»</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>7804462262</t>
+          <t>7810914904</t>
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr"/>
-      <c r="E148" s="11" t="inlineStr">
-        <is>
-          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
-        </is>
-      </c>
+      <c r="E148" s="11" t="inlineStr"/>
       <c r="F148" s="11" t="inlineStr"/>
       <c r="G148" s="11" t="inlineStr">
         <is>
@@ -6853,7 +6849,7 @@
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
@@ -6873,20 +6869,16 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
+          <t>ООО «Атлас групп»</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>7804634666</t>
+          <t>7811587054</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr"/>
-      <c r="E149" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
-        </is>
-      </c>
+      <c r="E149" s="11" t="inlineStr"/>
       <c r="F149" s="11" t="inlineStr"/>
       <c r="G149" s="11" t="inlineStr">
         <is>
@@ -6895,7 +6887,7 @@
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr">
@@ -6905,7 +6897,7 @@
       </c>
       <c r="J149" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6915,20 +6907,16 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>ООО «БЕЛНЕВА»</t>
+          <t>ООО «Атлас»</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>7839489314</t>
+          <t>7804667213</t>
         </is>
       </c>
       <c r="D150" s="13" t="inlineStr"/>
-      <c r="E150" s="11" t="inlineStr">
-        <is>
-          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
-        </is>
-      </c>
+      <c r="E150" s="11" t="inlineStr"/>
       <c r="F150" s="11" t="inlineStr"/>
       <c r="G150" s="11" t="inlineStr">
         <is>
@@ -6937,7 +6925,7 @@
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr">
@@ -6947,7 +6935,7 @@
       </c>
       <c r="J150" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6957,20 +6945,16 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК-Монолит»</t>
+          <t>ООО «Атриум»</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>7840321242</t>
+          <t>7814794281</t>
         </is>
       </c>
       <c r="D151" s="13" t="inlineStr"/>
-      <c r="E151" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E151" s="11" t="inlineStr"/>
       <c r="F151" s="11" t="inlineStr"/>
       <c r="G151" s="11" t="inlineStr">
         <is>
@@ -6979,7 +6963,7 @@
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr">
@@ -6989,7 +6973,7 @@
       </c>
       <c r="J151" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6983,12 @@
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>ООО «БИК»</t>
+          <t>ООО «БАЗИС»</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>7801336654</t>
+          <t>7801719664</t>
         </is>
       </c>
       <c r="D152" s="13" t="inlineStr"/>
@@ -7017,7 +7001,7 @@
       </c>
       <c r="H152" s="10" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr">
@@ -7027,7 +7011,7 @@
       </c>
       <c r="J152" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7037,29 +7021,25 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>ООО «БРАЗСТРОЙ»</t>
+          <t>ООО «БАЛТПРОЕКТ»</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>2630050808</t>
+          <t>7838330169</t>
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr"/>
-      <c r="E153" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
-        </is>
-      </c>
+      <c r="E153" s="11" t="inlineStr"/>
       <c r="F153" s="11" t="inlineStr"/>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>159</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr">
@@ -7069,7 +7049,7 @@
       </c>
       <c r="J153" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7079,16 +7059,20 @@
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>ООО «Балтийский альянс»</t>
+          <t>ООО «БАРК»</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>7838020706</t>
+          <t>7804462262</t>
         </is>
       </c>
       <c r="D154" s="13" t="inlineStr"/>
-      <c r="E154" s="11" t="inlineStr"/>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>СПб, г.Пушкин, ш.Подбельского 9А пом.615; ОГРН 1117847202428; ген.дир. Мантуров И.А.; автодороги</t>
+        </is>
+      </c>
       <c r="F154" s="11" t="inlineStr"/>
       <c r="G154" s="11" t="inlineStr">
         <is>
@@ -7097,7 +7081,7 @@
       </c>
       <c r="H154" s="10" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr">
@@ -7107,7 +7091,7 @@
       </c>
       <c r="J154" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7117,29 +7101,29 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>ООО «БелькаРус»</t>
+          <t>ООО «БАС» (Бюро архитектуры и строительства)</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>7801665024</t>
+          <t>7804634666</t>
         </is>
       </c>
       <c r="D155" s="13" t="inlineStr"/>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
+          <t>СПб, ул.Большая Пушкарская 25А пом.4-Н; ОГРН 1187847389443; ген.дир. Солопов С.Н.</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
       <c r="G155" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H155" s="10" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr">
@@ -7159,29 +7143,25 @@
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>ООО «БиАр»</t>
+          <t>ООО «БГК»</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>7802738910</t>
+          <t>7813211931</t>
         </is>
       </c>
       <c r="D156" s="13" t="inlineStr"/>
-      <c r="E156" s="11" t="inlineStr">
-        <is>
-          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
-        </is>
-      </c>
+      <c r="E156" s="11" t="inlineStr"/>
       <c r="F156" s="11" t="inlineStr"/>
       <c r="G156" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>310</t>
         </is>
       </c>
       <c r="I156" s="10" t="inlineStr">
@@ -7191,7 +7171,7 @@
       </c>
       <c r="J156" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7201,20 +7181,16 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>ООО «Бобёр»</t>
+          <t>ООО «БД»</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>7801632702</t>
+          <t>7806561614</t>
         </is>
       </c>
       <c r="D157" s="13" t="inlineStr"/>
-      <c r="E157" s="11" t="inlineStr">
-        <is>
-          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
-        </is>
-      </c>
+      <c r="E157" s="11" t="inlineStr"/>
       <c r="F157" s="11" t="inlineStr"/>
       <c r="G157" s="11" t="inlineStr">
         <is>
@@ -7223,7 +7199,7 @@
       </c>
       <c r="H157" s="10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>974</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr">
@@ -7233,7 +7209,7 @@
       </c>
       <c r="J157" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7243,29 +7219,29 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЕРТЕК»</t>
+          <t>ООО «БЕЛНЕВА»</t>
         </is>
       </c>
       <c r="C158" s="12" t="inlineStr">
         <is>
-          <t>7806317711</t>
+          <t>7839489314</t>
         </is>
       </c>
       <c r="D158" s="13" t="inlineStr"/>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+          <t>198152 СПб, Автовская ул. 16 каб.401; ОГРН 1137847492001; малярные работы</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr"/>
       <c r="G158" s="11" t="inlineStr">
         <is>
-          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H158" s="10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>457</t>
         </is>
       </c>
       <c r="I158" s="10" t="inlineStr">
@@ -7275,7 +7251,7 @@
       </c>
       <c r="J158" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7285,16 +7261,20 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИП»</t>
+          <t>ООО «БИК-Монолит»</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>7802742070</t>
+          <t>7840321242</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr"/>
-      <c r="E159" s="11" t="inlineStr"/>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Петергофское ш. 73У оф.517-1; ОГРН 1057811690243; ген.дир. Плавник Д.Е.; снос зданий</t>
+        </is>
+      </c>
       <c r="F159" s="11" t="inlineStr"/>
       <c r="G159" s="11" t="inlineStr">
         <is>
@@ -7303,7 +7283,7 @@
       </c>
       <c r="H159" s="10" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>656</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr">
@@ -7313,7 +7293,7 @@
       </c>
       <c r="J159" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -7323,29 +7303,25 @@
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИРА»</t>
+          <t>ООО «БИК»</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>7839139655</t>
+          <t>7801336654</t>
         </is>
       </c>
       <c r="D160" s="13" t="inlineStr"/>
-      <c r="E160" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
-        </is>
-      </c>
+      <c r="E160" s="11" t="inlineStr"/>
       <c r="F160" s="11" t="inlineStr"/>
       <c r="G160" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>530</t>
         </is>
       </c>
       <c r="I160" s="10" t="inlineStr">
@@ -7355,7 +7331,7 @@
       </c>
       <c r="J160" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -7365,25 +7341,29 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК»</t>
+          <t>ООО «БРАЗСТРОЙ»</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>3525411380</t>
+          <t>2630050808</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr"/>
-      <c r="E161" s="11" t="inlineStr"/>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Ленинский пр. 82к1 кв.1117; ОГРН 1192651015468; ген.дир. Бразевич И.С.</t>
+        </is>
+      </c>
       <c r="F161" s="11" t="inlineStr"/>
       <c r="G161" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H161" s="10" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr">
@@ -7403,12 +7383,12 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВСК» (Военно-строительная компания)</t>
+          <t>ООО «БалтИнжиниринг»</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>7804018392</t>
+          <t>7804429402</t>
         </is>
       </c>
       <c r="D162" s="13" t="inlineStr"/>
@@ -7421,7 +7401,7 @@
       </c>
       <c r="H162" s="10" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>979</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr">
@@ -7431,7 +7411,7 @@
       </c>
       <c r="J162" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7421,12 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВЭС»</t>
+          <t>ООО «БалтСтрой»</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>7839121496</t>
+          <t>7806250383</t>
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr"/>
@@ -7459,7 +7439,7 @@
       </c>
       <c r="H163" s="10" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr">
@@ -7469,7 +7449,7 @@
       </c>
       <c r="J163" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7479,20 +7459,16 @@
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>ООО «Вертикаль»</t>
+          <t>ООО «БалтСтройСервис»</t>
         </is>
       </c>
       <c r="C164" s="12" t="inlineStr">
         <is>
-          <t>7810855374</t>
+          <t>7811588523</t>
         </is>
       </c>
       <c r="D164" s="13" t="inlineStr"/>
-      <c r="E164" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
-        </is>
-      </c>
+      <c r="E164" s="11" t="inlineStr"/>
       <c r="F164" s="11" t="inlineStr"/>
       <c r="G164" s="11" t="inlineStr">
         <is>
@@ -7501,7 +7477,7 @@
       </c>
       <c r="H164" s="10" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>462</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr">
@@ -7511,7 +7487,7 @@
       </c>
       <c r="J164" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7521,12 +7497,12 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>ООО «Восток-Техника»</t>
+          <t>ООО «БалтТехМонтаж»</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>7820049077</t>
+          <t>7810383690</t>
         </is>
       </c>
       <c r="D165" s="13" t="inlineStr"/>
@@ -7539,7 +7515,7 @@
       </c>
       <c r="H165" s="10" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr">
@@ -7549,7 +7525,7 @@
       </c>
       <c r="J165" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7559,29 +7535,29 @@
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕ Газ Инжиниринг»</t>
+          <t>ООО «Балтийская Строительная Компания»</t>
         </is>
       </c>
       <c r="C166" s="12" t="inlineStr">
         <is>
-          <t>7810956319</t>
+          <t>7806278300</t>
         </is>
       </c>
       <c r="D166" s="13" t="inlineStr"/>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+          <t>СПб, Индустриальный пр. 44к2А пом.309А; ОГРН 1177847260381; ген.дир. Султанбеков Р.К.</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr"/>
       <c r="G166" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H166" s="10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>786</t>
         </is>
       </c>
       <c r="I166" s="10" t="inlineStr">
@@ -7591,7 +7567,7 @@
       </c>
       <c r="J166" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7601,12 +7577,12 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
+          <t>ООО «Балтийский альянс»</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>7603054270</t>
+          <t>7838020706</t>
         </is>
       </c>
       <c r="D167" s="13" t="inlineStr"/>
@@ -7619,7 +7595,7 @@
       </c>
       <c r="H167" s="10" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>768</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr">
@@ -7629,7 +7605,7 @@
       </c>
       <c r="J167" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -7639,20 +7615,16 @@
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГЕО-ПРОЕКТ»</t>
+          <t>ООО «Балтпетрострой»</t>
         </is>
       </c>
       <c r="C168" s="12" t="inlineStr">
         <is>
-          <t>7839418049</t>
+          <t>7805390814</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr"/>
-      <c r="E168" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
-        </is>
-      </c>
+      <c r="E168" s="11" t="inlineStr"/>
       <c r="F168" s="11" t="inlineStr"/>
       <c r="G168" s="11" t="inlineStr">
         <is>
@@ -7661,7 +7633,7 @@
       </c>
       <c r="H168" s="10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I168" s="10" t="inlineStr">
@@ -7671,7 +7643,7 @@
       </c>
       <c r="J168" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7681,25 +7653,29 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГК «СТИ»</t>
+          <t>ООО «Балтспецфлот»</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>7814797620</t>
+          <t>7838016570</t>
         </is>
       </c>
       <c r="D169" s="13" t="inlineStr"/>
-      <c r="E169" s="11" t="inlineStr"/>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Московский пр. 4А пом.19-Н оф.1; ОГРН 1047833003547; ген.дир. Шпигель А.И.; речные грузоперевозки</t>
+        </is>
+      </c>
       <c r="F169" s="11" t="inlineStr"/>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H169" s="10" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr">
@@ -7709,7 +7685,7 @@
       </c>
       <c r="J169" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7719,29 +7695,25 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГП Большая Лахта»</t>
+          <t>ООО «Балтстрой Инжиниринг»</t>
         </is>
       </c>
       <c r="C170" s="12" t="inlineStr">
         <is>
-          <t>7814858513</t>
+          <t>7816327927</t>
         </is>
       </c>
       <c r="D170" s="13" t="inlineStr"/>
-      <c r="E170" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
-        </is>
-      </c>
+      <c r="E170" s="11" t="inlineStr"/>
       <c r="F170" s="11" t="inlineStr"/>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H170" s="10" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>321</t>
         </is>
       </c>
       <c r="I170" s="10" t="inlineStr">
@@ -7751,7 +7723,7 @@
       </c>
       <c r="J170" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -7761,18 +7733,18 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
+          <t>ООО «БелькаРус»</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>7810447671</t>
+          <t>7801665024</t>
         </is>
       </c>
       <c r="D171" s="13" t="inlineStr"/>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+          <t>СПб, Богатырский пр. 18к2А пом.769; ОГРН 1197847115025; ген.дир. Никитина А.А.</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr"/>
@@ -7783,7 +7755,7 @@
       </c>
       <c r="H171" s="10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr">
@@ -7793,7 +7765,7 @@
       </c>
       <c r="J171" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7803,25 +7775,29 @@
       </c>
       <c r="B172" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гелиос»</t>
+          <t>ООО «БиАр»</t>
         </is>
       </c>
       <c r="C172" s="12" t="inlineStr">
         <is>
-          <t>7804608994</t>
+          <t>7802738910</t>
         </is>
       </c>
       <c r="D172" s="13" t="inlineStr"/>
-      <c r="E172" s="11" t="inlineStr"/>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>190020 СПб, ул.Бумажная 17А пом.1502; ОГРН 1117847026604; ген.дир. Власов А.В.</t>
+        </is>
+      </c>
       <c r="F172" s="11" t="inlineStr"/>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H172" s="10" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>652</t>
         </is>
       </c>
       <c r="I172" s="10" t="inlineStr">
@@ -7831,7 +7807,7 @@
       </c>
       <c r="J172" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -7841,29 +7817,29 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>ООО «Гидротэкс Рус»</t>
+          <t>ООО «Бобёр»</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>7801470868</t>
+          <t>7801632702</t>
         </is>
       </c>
       <c r="D173" s="13" t="inlineStr"/>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
+          <t>193091 СПб, Октябрьская наб. 10к1 пом.11-н оф.1; ОГРН 1147847220311; ген.дир. Сотков С.А.</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr"/>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H173" s="10" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr">
@@ -7873,7 +7849,7 @@
       </c>
       <c r="J173" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7883,25 +7859,29 @@
       </c>
       <c r="B174" s="11" t="inlineStr">
         <is>
-          <t>ООО «ДСК РЕГИОН»</t>
+          <t>ООО «ВЕРТЕК»</t>
         </is>
       </c>
       <c r="C174" s="12" t="inlineStr">
         <is>
-          <t>7816487198</t>
+          <t>7806317711</t>
         </is>
       </c>
       <c r="D174" s="13" t="inlineStr"/>
-      <c r="E174" s="11" t="inlineStr"/>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>192019 СПб, ул.Профессора Качалова 7А пом.11-Н оф.211; ОГРН 1057811091117; ген.дир. Жиров А.Г.; сайт vertek.ru</t>
+        </is>
+      </c>
       <c r="F174" s="11" t="inlineStr"/>
       <c r="G174" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (есть сайт vertek.ru — телефон смотреть там)</t>
         </is>
       </c>
       <c r="H174" s="10" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>659</t>
         </is>
       </c>
       <c r="I174" s="10" t="inlineStr">
@@ -7911,7 +7891,7 @@
       </c>
       <c r="J174" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7901,12 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>ООО «Двеста»</t>
+          <t>ООО «ВИП»</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>0100042992</t>
+          <t>7802742070</t>
         </is>
       </c>
       <c r="D175" s="13" t="inlineStr"/>
@@ -7939,7 +7919,7 @@
       </c>
       <c r="H175" s="10" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>226</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr">
@@ -7949,7 +7929,7 @@
       </c>
       <c r="J175" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -7959,25 +7939,29 @@
       </c>
       <c r="B176" s="11" t="inlineStr">
         <is>
-          <t>ООО «Дорожник СПб»</t>
+          <t>ООО «ВИРА»</t>
         </is>
       </c>
       <c r="C176" s="12" t="inlineStr">
         <is>
-          <t>7806421624</t>
+          <t>7839139655</t>
         </is>
       </c>
       <c r="D176" s="13" t="inlineStr"/>
-      <c r="E176" s="11" t="inlineStr"/>
+      <c r="E176" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 4А пом.8-Н оф.309; ОГРН 1217800056935; ген.дир. Целобёнок А.С.</t>
+        </is>
+      </c>
       <c r="F176" s="11" t="inlineStr"/>
       <c r="G176" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H176" s="10" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I176" s="10" t="inlineStr">
@@ -7997,29 +7981,25 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
+          <t>ООО «ВСК»</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>7804692788</t>
+          <t>3525411380</t>
         </is>
       </c>
       <c r="D177" s="13" t="inlineStr"/>
-      <c r="E177" s="11" t="inlineStr">
-        <is>
-          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
-        </is>
-      </c>
+      <c r="E177" s="11" t="inlineStr"/>
       <c r="F177" s="11" t="inlineStr"/>
       <c r="G177" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr">
@@ -8029,7 +8009,7 @@
       </c>
       <c r="J177" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8039,20 +8019,16 @@
       </c>
       <c r="B178" s="11" t="inlineStr">
         <is>
-          <t>ООО «Европейская Столица»</t>
+          <t>ООО «ВСК» (Военно-строительная компания)</t>
         </is>
       </c>
       <c r="C178" s="12" t="inlineStr">
         <is>
-          <t>7802202491</t>
+          <t>7804018392</t>
         </is>
       </c>
       <c r="D178" s="13" t="inlineStr"/>
-      <c r="E178" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
-        </is>
-      </c>
+      <c r="E178" s="11" t="inlineStr"/>
       <c r="F178" s="11" t="inlineStr"/>
       <c r="G178" s="11" t="inlineStr">
         <is>
@@ -8061,7 +8037,7 @@
       </c>
       <c r="H178" s="10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>670</t>
         </is>
       </c>
       <c r="I178" s="10" t="inlineStr">
@@ -8071,7 +8047,7 @@
       </c>
       <c r="J178" s="10" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8081,12 +8057,12 @@
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЗИТЕК»</t>
+          <t>ООО «ВЭС»</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>7814691303</t>
+          <t>7839121496</t>
         </is>
       </c>
       <c r="D179" s="13" t="inlineStr"/>
@@ -8099,7 +8075,7 @@
       </c>
       <c r="H179" s="10" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>828</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr">
@@ -8119,16 +8095,20 @@
       </c>
       <c r="B180" s="11" t="inlineStr">
         <is>
-          <t>ООО «Зодчий»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C180" s="12" t="inlineStr">
         <is>
-          <t>7810477235</t>
+          <t>7810855374</t>
         </is>
       </c>
       <c r="D180" s="13" t="inlineStr"/>
-      <c r="E180" s="11" t="inlineStr"/>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Выборгская ул. 5 пом.23-н; ОГРН 1127847045138; ген.дир. Гавриш А.В.</t>
+        </is>
+      </c>
       <c r="F180" s="11" t="inlineStr"/>
       <c r="G180" s="11" t="inlineStr">
         <is>
@@ -8137,7 +8117,7 @@
       </c>
       <c r="H180" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>596</t>
         </is>
       </c>
       <c r="I180" s="10" t="inlineStr">
@@ -8147,7 +8127,7 @@
       </c>
       <c r="J180" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -8157,20 +8137,16 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГ «Северо-Запад»</t>
+          <t>ООО «Восток-Техника»</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>7804599718</t>
+          <t>7820049077</t>
         </is>
       </c>
       <c r="D181" s="13" t="inlineStr"/>
-      <c r="E181" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
-        </is>
-      </c>
+      <c r="E181" s="11" t="inlineStr"/>
       <c r="F181" s="11" t="inlineStr"/>
       <c r="G181" s="11" t="inlineStr">
         <is>
@@ -8179,7 +8155,7 @@
       </c>
       <c r="H181" s="10" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>538</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr">
@@ -8189,7 +8165,7 @@
       </c>
       <c r="J181" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -8199,25 +8175,29 @@
       </c>
       <c r="B182" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИГС»</t>
+          <t>ООО «ГЕ Газ Инжиниринг»</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>7723568655</t>
+          <t>7810956319</t>
         </is>
       </c>
       <c r="D182" s="13" t="inlineStr"/>
-      <c r="E182" s="11" t="inlineStr"/>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кубинская 82к2с1; ОГРН 1227800133593; профиль на b2b-center.ru</t>
+        </is>
+      </c>
       <c r="F182" s="11" t="inlineStr"/>
       <c r="G182" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H182" s="10" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="I182" s="10" t="inlineStr">
@@ -8237,12 +8217,12 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК «Петротрасса»</t>
+          <t>ООО «ГЕНДЕЛЬ Инжиниринг»</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>7804572970</t>
+          <t>7603054270</t>
         </is>
       </c>
       <c r="D183" s="13" t="inlineStr"/>
@@ -8255,7 +8235,7 @@
       </c>
       <c r="H183" s="10" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr">
@@ -8275,16 +8255,20 @@
       </c>
       <c r="B184" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ИнТехПро»</t>
+          <t>ООО «ГЕО-ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>9810000213</t>
+          <t>7839418049</t>
         </is>
       </c>
       <c r="D184" s="13" t="inlineStr"/>
-      <c r="E184" s="11" t="inlineStr"/>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Рентгена 7А пом.1-Н; ОГРН 1107847026231; ген.дир. Артемьев М.Ю.</t>
+        </is>
+      </c>
       <c r="F184" s="11" t="inlineStr"/>
       <c r="G184" s="11" t="inlineStr">
         <is>
@@ -8293,7 +8277,7 @@
       </c>
       <c r="H184" s="10" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I184" s="10" t="inlineStr">
@@ -8303,7 +8287,7 @@
       </c>
       <c r="J184" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8313,12 +8297,12 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
+          <t>ООО «ГК «СТИ»</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>7710910159</t>
+          <t>7814797620</t>
         </is>
       </c>
       <c r="D185" s="13" t="inlineStr"/>
@@ -8331,7 +8315,7 @@
       </c>
       <c r="H185" s="10" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>847</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr">
@@ -8351,18 +8335,18 @@
       </c>
       <c r="B186" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
+          <t>ООО «ГП Большая Лахта»</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>7810714581</t>
+          <t>7814858513</t>
         </is>
       </c>
       <c r="D186" s="13" t="inlineStr"/>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
+          <t>СПб, ул.Савушкина 126Б пом.80нс; ОГРН 1257800110040; ген.дир. Краснов И.В.; рег. 08.12.2025</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr"/>
@@ -8373,7 +8357,7 @@
       </c>
       <c r="H186" s="10" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I186" s="10" t="inlineStr">
@@ -8383,7 +8367,7 @@
       </c>
       <c r="J186" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -8393,25 +8377,29 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИНСИ»</t>
+          <t>ООО «ГТНС» (Глобальные технологии новационных систем)</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>7839398890</t>
+          <t>7810447671</t>
         </is>
       </c>
       <c r="D187" s="13" t="inlineStr"/>
-      <c r="E187" s="11" t="inlineStr"/>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гапсальская 5А оф.508; ОГРН 1137847261705; ген.дир. Ревякин А.Ю.</t>
+        </is>
+      </c>
       <c r="F187" s="11" t="inlineStr"/>
       <c r="G187" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H187" s="10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>313</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr">
@@ -8421,7 +8409,7 @@
       </c>
       <c r="J187" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8431,12 +8419,12 @@
       </c>
       <c r="B188" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИСБ-СЕРВИС»</t>
+          <t>ООО «Гелиос»</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>7811462471</t>
+          <t>7804608994</t>
         </is>
       </c>
       <c r="D188" s="13" t="inlineStr"/>
@@ -8449,7 +8437,7 @@
       </c>
       <c r="H188" s="10" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>565</t>
         </is>
       </c>
       <c r="I188" s="10" t="inlineStr">
@@ -8469,29 +8457,29 @@
       </c>
       <c r="B189" s="11" t="inlineStr">
         <is>
-          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
+          <t>ООО «Гидротэкс Рус»</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>7802002333</t>
+          <t>7801470868</t>
         </is>
       </c>
       <c r="D189" s="13" t="inlineStr"/>
       <c r="E189" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+          <t>199178 СПб, 18-я линия В.О. 47А оф.1; ОГРН 1089847220165; ген.дир. Пронин Д.Е.</t>
         </is>
       </c>
       <c r="F189" s="11" t="inlineStr"/>
       <c r="G189" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H189" s="10" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I189" s="10" t="inlineStr">
@@ -8501,7 +8489,7 @@
       </c>
       <c r="J189" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -8511,12 +8499,12 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>ООО «Импульс»</t>
+          <t>ООО «ДСК РЕГИОН»</t>
         </is>
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>7839473240</t>
+          <t>7816487198</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr"/>
@@ -8529,7 +8517,7 @@
       </c>
       <c r="H190" s="10" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr">
@@ -8549,29 +8537,25 @@
       </c>
       <c r="B191" s="11" t="inlineStr">
         <is>
-          <t>ООО «Институт Теплоэнергетики»</t>
+          <t>ООО «Двеста»</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>7839134583</t>
+          <t>0100042992</t>
         </is>
       </c>
       <c r="D191" s="13" t="inlineStr"/>
-      <c r="E191" s="11" t="inlineStr">
-        <is>
-          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
-        </is>
-      </c>
+      <c r="E191" s="11" t="inlineStr"/>
       <c r="F191" s="11" t="inlineStr"/>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>805</t>
         </is>
       </c>
       <c r="I191" s="10" t="inlineStr">
@@ -8581,7 +8565,7 @@
       </c>
       <c r="J191" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8575,12 @@
       </c>
       <c r="B192" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интер-Строй»</t>
+          <t>ООО «Дорожник СПб»</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>5505064975</t>
+          <t>7806421624</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr"/>
@@ -8609,7 +8593,7 @@
       </c>
       <c r="H192" s="10" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>564</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr">
@@ -8629,25 +8613,29 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>ООО «Интерпром»</t>
+          <t>ООО «ЕТК» (Единая теплосетевая компания)</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>7805576110</t>
+          <t>7804692788</t>
         </is>
       </c>
       <c r="D193" s="13" t="inlineStr"/>
-      <c r="E193" s="11" t="inlineStr"/>
+      <c r="E193" s="11" t="inlineStr">
+        <is>
+          <t>195221 СПб, ул.Антоновская 14к2А оф.13; ОГРН 1227800055845; ген.дир. Мозговой О.А.</t>
+        </is>
+      </c>
       <c r="F193" s="11" t="inlineStr"/>
       <c r="G193" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H193" s="10" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="I193" s="10" t="inlineStr">
@@ -8657,7 +8645,7 @@
       </c>
       <c r="J193" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8667,16 +8655,20 @@
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>ООО «КС-Инжиниринг»</t>
+          <t>ООО «Европейская Столица»</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>7801615217</t>
+          <t>7802202491</t>
         </is>
       </c>
       <c r="D194" s="13" t="inlineStr"/>
-      <c r="E194" s="11" t="inlineStr"/>
+      <c r="E194" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Б.Сампсониевский пр. 68Н пом.2Н; ОГРН 1027801563965; ген.дир. Иванов А.П.; автодороги</t>
+        </is>
+      </c>
       <c r="F194" s="11" t="inlineStr"/>
       <c r="G194" s="11" t="inlineStr">
         <is>
@@ -8685,7 +8677,7 @@
       </c>
       <c r="H194" s="10" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I194" s="10" t="inlineStr">
@@ -8695,7 +8687,7 @@
       </c>
       <c r="J194" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
@@ -8705,20 +8697,16 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>ООО «Каппа»</t>
+          <t>ООО «ЗИТЕК»</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>7804593787</t>
+          <t>7814691303</t>
         </is>
       </c>
       <c r="D195" s="13" t="inlineStr"/>
-      <c r="E195" s="11" t="inlineStr">
-        <is>
-          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
-        </is>
-      </c>
+      <c r="E195" s="11" t="inlineStr"/>
       <c r="F195" s="11" t="inlineStr"/>
       <c r="G195" s="11" t="inlineStr">
         <is>
@@ -8727,7 +8715,7 @@
       </c>
       <c r="H195" s="10" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="I195" s="10" t="inlineStr">
@@ -8737,7 +8725,7 @@
       </c>
       <c r="J195" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -8747,20 +8735,16 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>ООО «Компания КОМПЛИТ»</t>
+          <t>ООО «Зодчий»</t>
         </is>
       </c>
       <c r="C196" s="12" t="inlineStr">
         <is>
-          <t>7810793872</t>
+          <t>7810477235</t>
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr"/>
-      <c r="E196" s="11" t="inlineStr">
-        <is>
-          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
-        </is>
-      </c>
+      <c r="E196" s="11" t="inlineStr"/>
       <c r="F196" s="11" t="inlineStr"/>
       <c r="G196" s="11" t="inlineStr">
         <is>
@@ -8769,7 +8753,7 @@
       </c>
       <c r="H196" s="10" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I196" s="10" t="inlineStr">
@@ -8789,16 +8773,20 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>ООО «Комфорт ЛСТК»</t>
+          <t>ООО «ИГ «Северо-Запад»</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>7838428816</t>
+          <t>7804599718</t>
         </is>
       </c>
       <c r="D197" s="13" t="inlineStr"/>
-      <c r="E197" s="11" t="inlineStr"/>
+      <c r="E197" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Кондратьевский пр. 15к3И оф.202-Ю; ОГРН 1177847190795; ген.дир. Назаров Д.Л.</t>
+        </is>
+      </c>
       <c r="F197" s="11" t="inlineStr"/>
       <c r="G197" s="11" t="inlineStr">
         <is>
@@ -8807,7 +8795,7 @@
       </c>
       <c r="H197" s="10" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>571</t>
         </is>
       </c>
       <c r="I197" s="10" t="inlineStr">
@@ -8817,7 +8805,7 @@
       </c>
       <c r="J197" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8827,20 +8815,16 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>ООО «Концерн «Питер»</t>
+          <t>ООО «ИГС»</t>
         </is>
       </c>
       <c r="C198" s="12" t="inlineStr">
         <is>
-          <t>7826108410</t>
+          <t>7723568655</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr"/>
-      <c r="E198" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Ефимова 3С пом.417; ОГРН 1027810246750; ген.дир. Петров М.Ю.; застройщик</t>
-        </is>
-      </c>
+      <c r="E198" s="11" t="inlineStr"/>
       <c r="F198" s="11" t="inlineStr"/>
       <c r="G198" s="11" t="inlineStr">
         <is>
@@ -8849,7 +8833,7 @@
       </c>
       <c r="H198" s="10" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="I198" s="10" t="inlineStr">
@@ -8859,7 +8843,7 @@
       </c>
       <c r="J198" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -8869,12 +8853,12 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>ООО «Корнелиус»</t>
+          <t>ООО «ИК «Петротрасса»</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>7802611335</t>
+          <t>7804572970</t>
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr"/>
@@ -8887,7 +8871,7 @@
       </c>
       <c r="H199" s="10" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>712</t>
         </is>
       </c>
       <c r="I199" s="10" t="inlineStr">
@@ -8907,12 +8891,12 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>ООО «Красный Квадрат»</t>
+          <t>ООО «ИК ИнТехПро»</t>
         </is>
       </c>
       <c r="C200" s="12" t="inlineStr">
         <is>
-          <t>7802567950</t>
+          <t>9810000213</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr"/>
@@ -8925,7 +8909,7 @@
       </c>
       <c r="H200" s="10" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I200" s="10" t="inlineStr">
@@ -8945,12 +8929,12 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЛС-Групп»</t>
+          <t>ООО «ИК ОЗНА-ГазИнтерАвто»</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>7842036949</t>
+          <t>7710910159</t>
         </is>
       </c>
       <c r="D201" s="13" t="inlineStr"/>
@@ -8963,7 +8947,7 @@
       </c>
       <c r="H201" s="10" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>940</t>
         </is>
       </c>
       <c r="I201" s="10" t="inlineStr">
@@ -8983,18 +8967,18 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лартех Телеком»</t>
+          <t>ООО «ИНЖИНИРИНГОВОЕ УПРАВЛЕНИЕ»</t>
         </is>
       </c>
       <c r="C202" s="12" t="inlineStr">
         <is>
-          <t>7838046461</t>
+          <t>7810714581</t>
         </is>
       </c>
       <c r="D202" s="13" t="inlineStr"/>
       <c r="E202" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
+          <t>196084 СПб, ул.Коли Томчака 12-14А пом.15; ОГРН 1177847372746; ген.дир. Мирошников Н.Н.</t>
         </is>
       </c>
       <c r="F202" s="11" t="inlineStr"/>
@@ -9005,7 +8989,7 @@
       </c>
       <c r="H202" s="10" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>278</t>
         </is>
       </c>
       <c r="I202" s="10" t="inlineStr">
@@ -9025,20 +9009,16 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>ООО «Лен-сити»</t>
+          <t>ООО «ИНСИ»</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>7804499590</t>
+          <t>7839398890</t>
         </is>
       </c>
       <c r="D203" s="13" t="inlineStr"/>
-      <c r="E203" s="11" t="inlineStr">
-        <is>
-          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
-        </is>
-      </c>
+      <c r="E203" s="11" t="inlineStr"/>
       <c r="F203" s="11" t="inlineStr"/>
       <c r="G203" s="11" t="inlineStr">
         <is>
@@ -9047,7 +9027,7 @@
       </c>
       <c r="H203" s="10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I203" s="10" t="inlineStr">
@@ -9057,7 +9037,7 @@
       </c>
       <c r="J203" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9047,12 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЛидерСервис»</t>
+          <t>ООО «ИСБ-СЕРВИС»</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
         <is>
-          <t>7805304438</t>
+          <t>7811462471</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr"/>
@@ -9085,7 +9065,7 @@
       </c>
       <c r="H204" s="10" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>295</t>
         </is>
       </c>
       <c r="I204" s="10" t="inlineStr">
@@ -9105,16 +9085,20 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>ООО «М-ГРУПП»</t>
+          <t>ООО «ИТС СЗ» (ИТС Северо-Запад)</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>3128105475</t>
+          <t>7802002333</t>
         </is>
       </c>
       <c r="D205" s="13" t="inlineStr"/>
-      <c r="E205" s="11" t="inlineStr"/>
+      <c r="E205" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, пр.Тореза 102к4А пом.14-Н; ОГРН 1147847545680; ген.дир. Осенний С.О.; выручка ~667 млн</t>
+        </is>
+      </c>
       <c r="F205" s="11" t="inlineStr"/>
       <c r="G205" s="11" t="inlineStr">
         <is>
@@ -9123,7 +9107,7 @@
       </c>
       <c r="H205" s="10" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr">
@@ -9133,7 +9117,7 @@
       </c>
       <c r="J205" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9143,12 +9127,12 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>ООО «М-Сервис»</t>
+          <t>ООО «Импульс»</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>7842429918</t>
+          <t>7839473240</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr"/>
@@ -9161,7 +9145,7 @@
       </c>
       <c r="H206" s="10" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I206" s="10" t="inlineStr">
@@ -9181,25 +9165,29 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>ООО «МАН»</t>
+          <t>ООО «Институт Теплоэнергетики»</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>7840404386</t>
+          <t>7839134583</t>
         </is>
       </c>
       <c r="D207" s="13" t="inlineStr"/>
-      <c r="E207" s="11" t="inlineStr"/>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>190121 СПб, ул.Садовая 107А пом.9Н оф.6; ОГРН 1207800164550; ген.дир. Переверзев В.Л.</t>
+        </is>
+      </c>
       <c r="F207" s="11" t="inlineStr"/>
       <c r="G207" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H207" s="10" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>628</t>
         </is>
       </c>
       <c r="I207" s="10" t="inlineStr">
@@ -9209,7 +9197,7 @@
       </c>
       <c r="J207" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9219,12 +9207,12 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>ООО «МАТИС»</t>
+          <t>ООО «Интер-Строй»</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
         <is>
-          <t>7820023103</t>
+          <t>5505064975</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr"/>
@@ -9237,7 +9225,7 @@
       </c>
       <c r="H208" s="10" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="I208" s="10" t="inlineStr">
@@ -9257,12 +9245,12 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>ООО «МК БАМ»</t>
+          <t>ООО «Интерпром»</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>7536059295</t>
+          <t>7805576110</t>
         </is>
       </c>
       <c r="D209" s="13" t="inlineStr"/>
@@ -9275,7 +9263,7 @@
       </c>
       <c r="H209" s="10" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I209" s="10" t="inlineStr">
@@ -9295,29 +9283,25 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>ООО «МРГС» (Межрегионгидрострой)</t>
+          <t>ООО «КС-Инжиниринг»</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>7838103021</t>
+          <t>7801615217</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr"/>
-      <c r="E210" s="11" t="inlineStr">
-        <is>
-          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
-        </is>
-      </c>
+      <c r="E210" s="11" t="inlineStr"/>
       <c r="F210" s="11" t="inlineStr"/>
       <c r="G210" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H210" s="10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>695</t>
         </is>
       </c>
       <c r="I210" s="10" t="inlineStr">
@@ -9327,7 +9311,7 @@
       </c>
       <c r="J210" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9337,16 +9321,20 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>ООО «МСС СЗ»</t>
+          <t>ООО «Каппа»</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>7804372114</t>
+          <t>7804593787</t>
         </is>
       </c>
       <c r="D211" s="13" t="inlineStr"/>
-      <c r="E211" s="11" t="inlineStr"/>
+      <c r="E211" s="11" t="inlineStr">
+        <is>
+          <t>195273 СПб, ул.Руставели 13А пом.28н; ОГРН 1177847108581; ген.дир. Николаенко Д.А.</t>
+        </is>
+      </c>
       <c r="F211" s="11" t="inlineStr"/>
       <c r="G211" s="11" t="inlineStr">
         <is>
@@ -9355,7 +9343,7 @@
       </c>
       <c r="H211" s="10" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>709</t>
         </is>
       </c>
       <c r="I211" s="10" t="inlineStr">
@@ -9365,7 +9353,7 @@
       </c>
       <c r="J211" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -9375,18 +9363,18 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>ООО «МедСтрой»</t>
+          <t>ООО «Компания КОМПЛИТ»</t>
         </is>
       </c>
       <c r="C212" s="12" t="inlineStr">
         <is>
-          <t>7806163116</t>
+          <t>7810793872</t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr"/>
       <c r="E212" s="11" t="inlineStr">
         <is>
-          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
+          <t>197345 СПб, Яхтенная ул. 22к1А пом.553; ОГРН 1027804883094; рук. Клязника В.Н.</t>
         </is>
       </c>
       <c r="F212" s="11" t="inlineStr"/>
@@ -9397,7 +9385,7 @@
       </c>
       <c r="H212" s="10" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>143</t>
         </is>
       </c>
       <c r="I212" s="10" t="inlineStr">
@@ -9407,7 +9395,7 @@
       </c>
       <c r="J212" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9417,29 +9405,25 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>ООО «Мелстон Инжиниринг»</t>
+          <t>ООО «Комфорт ЛСТК»</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>7813248219</t>
+          <t>7838428816</t>
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr"/>
-      <c r="E213" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
-        </is>
-      </c>
+      <c r="E213" s="11" t="inlineStr"/>
       <c r="F213" s="11" t="inlineStr"/>
       <c r="G213" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H213" s="10" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>693</t>
         </is>
       </c>
       <c r="I213" s="10" t="inlineStr">
@@ -9459,18 +9443,18 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>ООО «Метаформа»</t>
+          <t>ООО «Концерн «Питер»</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>7838104240</t>
+          <t>7826108410</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr"/>
       <c r="E214" s="11" t="inlineStr">
         <is>
-          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
+          <t>СПб, ул.Ефимова 3С пом.417; ОГРН 1027810246750; ген.дир. Петров М.Ю.; застройщик</t>
         </is>
       </c>
       <c r="F214" s="11" t="inlineStr"/>
@@ -9481,7 +9465,7 @@
       </c>
       <c r="H214" s="10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>739</t>
         </is>
       </c>
       <c r="I214" s="10" t="inlineStr">
@@ -9491,7 +9475,7 @@
       </c>
       <c r="J214" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -9501,20 +9485,16 @@
       </c>
       <c r="B215" s="11" t="inlineStr">
         <is>
-          <t>ООО «МонтажСтрой-М» (МСМ)</t>
+          <t>ООО «Корнелиус»</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>7811447071</t>
+          <t>7802611335</t>
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr"/>
-      <c r="E215" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
-        </is>
-      </c>
+      <c r="E215" s="11" t="inlineStr"/>
       <c r="F215" s="11" t="inlineStr"/>
       <c r="G215" s="11" t="inlineStr">
         <is>
@@ -9523,7 +9503,7 @@
       </c>
       <c r="H215" s="10" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I215" s="10" t="inlineStr">
@@ -9533,7 +9513,7 @@
       </c>
       <c r="J215" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9543,12 +9523,12 @@
       </c>
       <c r="B216" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО «НАСТ»</t>
+          <t>ООО «Красный Квадрат»</t>
         </is>
       </c>
       <c r="C216" s="12" t="inlineStr">
         <is>
-          <t>7810172762</t>
+          <t>7802567950</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr"/>
@@ -9561,7 +9541,7 @@
       </c>
       <c r="H216" s="10" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="I216" s="10" t="inlineStr">
@@ -9581,12 +9561,12 @@
       </c>
       <c r="B217" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО «Процесс»</t>
+          <t>ООО «ЛС-Групп»</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>7806468037</t>
+          <t>7842036949</t>
         </is>
       </c>
       <c r="D217" s="13" t="inlineStr"/>
@@ -9599,7 +9579,7 @@
       </c>
       <c r="H217" s="10" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>509</t>
         </is>
       </c>
       <c r="I217" s="10" t="inlineStr">
@@ -9619,25 +9599,29 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПО ПЭМЗ»</t>
+          <t>ООО «Лартех Телеком»</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>7813361648</t>
+          <t>7838046461</t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr"/>
-      <c r="E218" s="11" t="inlineStr"/>
+      <c r="E218" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, наб.реки Карповки 5; ОГРН 1157847415890; ген.дир. Шириков В.А.</t>
+        </is>
+      </c>
       <c r="F218" s="11" t="inlineStr"/>
       <c r="G218" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H218" s="10" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="I218" s="10" t="inlineStr">
@@ -9647,7 +9631,7 @@
       </c>
       <c r="J218" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9657,18 +9641,18 @@
       </c>
       <c r="B219" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПП «Путьсервис»</t>
+          <t>ООО «Лен-сити»</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>7810216184</t>
+          <t>7804499590</t>
         </is>
       </c>
       <c r="D219" s="13" t="inlineStr"/>
       <c r="E219" s="11" t="inlineStr">
         <is>
-          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
+          <t>199004 СПб, Средний пр. В.О. 4; ОГРН 1129847019092; ген.дир. Ройзман М.А.</t>
         </is>
       </c>
       <c r="F219" s="11" t="inlineStr"/>
@@ -9679,7 +9663,7 @@
       </c>
       <c r="H219" s="10" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>649</t>
         </is>
       </c>
       <c r="I219" s="10" t="inlineStr">
@@ -9689,7 +9673,7 @@
       </c>
       <c r="J219" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9699,20 +9683,16 @@
       </c>
       <c r="B220" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПФ «Тест»</t>
+          <t>ООО «ЛидерСервис»</t>
         </is>
       </c>
       <c r="C220" s="12" t="inlineStr">
         <is>
-          <t>7805098168</t>
+          <t>7805304438</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr"/>
-      <c r="E220" s="11" t="inlineStr">
-        <is>
-          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
-        </is>
-      </c>
+      <c r="E220" s="11" t="inlineStr"/>
       <c r="F220" s="11" t="inlineStr"/>
       <c r="G220" s="11" t="inlineStr">
         <is>
@@ -9721,7 +9701,7 @@
       </c>
       <c r="H220" s="10" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>902</t>
         </is>
       </c>
       <c r="I220" s="10" t="inlineStr">
@@ -9731,7 +9711,7 @@
       </c>
       <c r="J220" s="10" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9741,12 +9721,12 @@
       </c>
       <c r="B221" s="11" t="inlineStr">
         <is>
-          <t>ООО «НПХК «Ремстройкомплекс»</t>
+          <t>ООО «М-ГРУПП»</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>7826000423</t>
+          <t>3128105475</t>
         </is>
       </c>
       <c r="D221" s="13" t="inlineStr"/>
@@ -9759,7 +9739,7 @@
       </c>
       <c r="H221" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="I221" s="10" t="inlineStr">
@@ -9779,29 +9759,25 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСК» (Невская строительная компания)</t>
+          <t>ООО «М-Сервис»</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>7805500513</t>
+          <t>7842429918</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr"/>
-      <c r="E222" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
-        </is>
-      </c>
+      <c r="E222" s="11" t="inlineStr"/>
       <c r="F222" s="11" t="inlineStr"/>
       <c r="G222" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H222" s="10" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>722</t>
         </is>
       </c>
       <c r="I222" s="10" t="inlineStr">
@@ -9811,7 +9787,7 @@
       </c>
       <c r="J222" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9821,12 +9797,12 @@
       </c>
       <c r="B223" s="11" t="inlineStr">
         <is>
-          <t>ООО «НСР»</t>
+          <t>ООО «МАН»</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>7801727376</t>
+          <t>7840404386</t>
         </is>
       </c>
       <c r="D223" s="13" t="inlineStr"/>
@@ -9839,7 +9815,7 @@
       </c>
       <c r="H223" s="10" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>510</t>
         </is>
       </c>
       <c r="I223" s="10" t="inlineStr">
@@ -9859,29 +9835,25 @@
       </c>
       <c r="B224" s="11" t="inlineStr">
         <is>
-          <t>ООО «Новый век»</t>
+          <t>ООО «МАТИС»</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>7806113612</t>
+          <t>7820023103</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr"/>
-      <c r="E224" s="11" t="inlineStr">
-        <is>
-          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
-        </is>
-      </c>
+      <c r="E224" s="11" t="inlineStr"/>
       <c r="F224" s="11" t="inlineStr"/>
       <c r="G224" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H224" s="10" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>616</t>
         </is>
       </c>
       <c r="I224" s="10" t="inlineStr">
@@ -9891,7 +9863,7 @@
       </c>
       <c r="J224" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9901,20 +9873,16 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>ООО «Нордик»</t>
+          <t>ООО «МК БАМ»</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>7804596040</t>
+          <t>7536059295</t>
         </is>
       </c>
       <c r="D225" s="13" t="inlineStr"/>
-      <c r="E225" s="11" t="inlineStr">
-        <is>
-          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
-        </is>
-      </c>
+      <c r="E225" s="11" t="inlineStr"/>
       <c r="F225" s="11" t="inlineStr"/>
       <c r="G225" s="11" t="inlineStr">
         <is>
@@ -9923,7 +9891,7 @@
       </c>
       <c r="H225" s="10" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>668</t>
         </is>
       </c>
       <c r="I225" s="10" t="inlineStr">
@@ -9933,7 +9901,7 @@
       </c>
       <c r="J225" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -9943,25 +9911,29 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОСА - Север»</t>
+          <t>ООО «МРГС» (Межрегионгидрострой)</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>7801574480</t>
+          <t>7838103021</t>
         </is>
       </c>
       <c r="D226" s="13" t="inlineStr"/>
-      <c r="E226" s="11" t="inlineStr"/>
+      <c r="E226" s="11" t="inlineStr">
+        <is>
+          <t>191119 СПб, наб.Обводного канала 93А оф.1304; ОГРН 1227800028543; ген.дир. Грицюк А.Г.</t>
+        </is>
+      </c>
       <c r="F226" s="11" t="inlineStr"/>
       <c r="G226" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H226" s="10" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>963</t>
         </is>
       </c>
       <c r="I226" s="10" t="inlineStr">
@@ -9971,7 +9943,7 @@
       </c>
       <c r="J226" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9953,12 @@
       </c>
       <c r="B227" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОблСервис»</t>
+          <t>ООО «МСС СЗ»</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>4712024087</t>
+          <t>7804372114</t>
         </is>
       </c>
       <c r="D227" s="13" t="inlineStr"/>
@@ -9999,7 +9971,7 @@
       </c>
       <c r="H227" s="10" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>741</t>
         </is>
       </c>
       <c r="I227" s="10" t="inlineStr">
@@ -10009,7 +9981,7 @@
       </c>
       <c r="J227" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -10019,16 +9991,20 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>ООО «ОлАн»</t>
+          <t>ООО «МедСтрой»</t>
         </is>
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>7827004614</t>
+          <t>7806163116</t>
         </is>
       </c>
       <c r="D228" s="13" t="inlineStr"/>
-      <c r="E228" s="11" t="inlineStr"/>
+      <c r="E228" s="11" t="inlineStr">
+        <is>
+          <t>195273 СПб, Пискарёвский пр. 63к2с1 пом.6-н; ОГРН 1157847126370; ген.дир. Липисвицкий О.В.</t>
+        </is>
+      </c>
       <c r="F228" s="11" t="inlineStr"/>
       <c r="G228" s="11" t="inlineStr">
         <is>
@@ -10037,7 +10013,7 @@
       </c>
       <c r="H228" s="10" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>724</t>
         </is>
       </c>
       <c r="I228" s="10" t="inlineStr">
@@ -10047,7 +10023,7 @@
       </c>
       <c r="J228" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10057,25 +10033,29 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>ООО «Олимп-Строй»</t>
+          <t>ООО «Мелстон Инжиниринг»</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>7820315709</t>
+          <t>7813248219</t>
         </is>
       </c>
       <c r="D229" s="13" t="inlineStr"/>
-      <c r="E229" s="11" t="inlineStr"/>
+      <c r="E229" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Аптекарская наб. 20А оф.802; ОГРН 1167847164242; ген.дир. Лапшин О.Н.; стройконтроль/технадзор</t>
+        </is>
+      </c>
       <c r="F229" s="11" t="inlineStr"/>
       <c r="G229" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H229" s="10" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>669</t>
         </is>
       </c>
       <c r="I229" s="10" t="inlineStr">
@@ -10095,18 +10075,18 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омега Строй»</t>
+          <t>ООО «Метаформа»</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>7802711097</t>
+          <t>7838104240</t>
         </is>
       </c>
       <c r="D230" s="13" t="inlineStr"/>
       <c r="E230" s="11" t="inlineStr">
         <is>
-          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+          <t>СПб; ОГРН 1227800051929; дир. Ткаченко А.В.</t>
         </is>
       </c>
       <c r="F230" s="11" t="inlineStr"/>
@@ -10117,7 +10097,7 @@
       </c>
       <c r="H230" s="10" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="I230" s="10" t="inlineStr">
@@ -10137,16 +10117,20 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>ООО «Омни Структуре Санкт-Петербург»</t>
+          <t>ООО «МонтажСтрой-М» (МСМ)</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>7801641792</t>
+          <t>7811447071</t>
         </is>
       </c>
       <c r="D231" s="13" t="inlineStr"/>
-      <c r="E231" s="11" t="inlineStr"/>
+      <c r="E231" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Лёни Голикова 35А пом.1Н; ОГРН 1097847291376; ген.дир. Смирнов А.В.</t>
+        </is>
+      </c>
       <c r="F231" s="11" t="inlineStr"/>
       <c r="G231" s="11" t="inlineStr">
         <is>
@@ -10155,7 +10139,7 @@
       </c>
       <c r="H231" s="10" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I231" s="10" t="inlineStr">
@@ -10165,7 +10149,7 @@
       </c>
       <c r="J231" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10159,12 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>ООО «Основание»</t>
+          <t>ООО «НПО «НАСТ»</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>7840083527</t>
+          <t>7810172762</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr"/>
@@ -10193,7 +10177,7 @@
       </c>
       <c r="H232" s="10" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>273</t>
         </is>
       </c>
       <c r="I232" s="10" t="inlineStr">
@@ -10213,29 +10197,25 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
+          <t>ООО «НПО «Процесс»</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>7825382561</t>
+          <t>7806468037</t>
         </is>
       </c>
       <c r="D233" s="13" t="inlineStr"/>
-      <c r="E233" s="11" t="inlineStr">
-        <is>
-          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
-        </is>
-      </c>
+      <c r="E233" s="11" t="inlineStr"/>
       <c r="F233" s="11" t="inlineStr"/>
       <c r="G233" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H233" s="10" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="I233" s="10" t="inlineStr">
@@ -10245,7 +10225,7 @@
       </c>
       <c r="J233" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10255,12 +10235,12 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПВВ Продукт»</t>
+          <t>ООО «НПО ПЭМЗ»</t>
         </is>
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>7840501541</t>
+          <t>7813361648</t>
         </is>
       </c>
       <c r="D234" s="13" t="inlineStr"/>
@@ -10273,7 +10253,7 @@
       </c>
       <c r="H234" s="10" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="I234" s="10" t="inlineStr">
@@ -10293,16 +10273,20 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПВЦ «Восток»</t>
+          <t>ООО «НПП «Путьсервис»</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>7802203054</t>
+          <t>7810216184</t>
         </is>
       </c>
       <c r="D235" s="13" t="inlineStr"/>
-      <c r="E235" s="11" t="inlineStr"/>
+      <c r="E235" s="11" t="inlineStr">
+        <is>
+          <t>196128 СПб, ул.Кузнецовская 19А пом.10н; ОГРН 1027804861314; ген.дир. Алехин Л.И.; ж/д и метро</t>
+        </is>
+      </c>
       <c r="F235" s="11" t="inlineStr"/>
       <c r="G235" s="11" t="inlineStr">
         <is>
@@ -10311,7 +10295,7 @@
       </c>
       <c r="H235" s="10" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>733</t>
         </is>
       </c>
       <c r="I235" s="10" t="inlineStr">
@@ -10331,29 +10315,29 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПГИ» (Промгазиндустрия)</t>
+          <t>ООО «НПФ «Тест»</t>
         </is>
       </c>
       <c r="C236" s="12" t="inlineStr">
         <is>
-          <t>7814822228</t>
+          <t>7805098168</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr"/>
       <c r="E236" s="11" t="inlineStr">
         <is>
-          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+          <t>СПб, 8-я Красноармейская 6А/5; ОГРН 1027802761898; ген.дир. Зенкин С.В.</t>
         </is>
       </c>
       <c r="F236" s="11" t="inlineStr"/>
       <c r="G236" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H236" s="10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>604</t>
         </is>
       </c>
       <c r="I236" s="10" t="inlineStr">
@@ -10363,7 +10347,7 @@
       </c>
       <c r="J236" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -10373,12 +10357,12 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕГАЗ»</t>
+          <t>ООО «НПХК «Ремстройкомплекс»</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>7804700982</t>
+          <t>7826000423</t>
         </is>
       </c>
       <c r="D237" s="13" t="inlineStr"/>
@@ -10391,7 +10375,7 @@
       </c>
       <c r="H237" s="10" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>551</t>
         </is>
       </c>
       <c r="I237" s="10" t="inlineStr">
@@ -10411,25 +10395,29 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОТОРГ»</t>
+          <t>ООО «НСК» (Невская строительная компания)</t>
         </is>
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>7810518322</t>
+          <t>7805500513</t>
         </is>
       </c>
       <c r="D238" s="13" t="inlineStr"/>
-      <c r="E238" s="11" t="inlineStr"/>
+      <c r="E238" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Таврическая 45А пом.9-Н; ОГРН 1097847266186; ген.дир. Гукасян А.А.</t>
+        </is>
+      </c>
       <c r="F238" s="11" t="inlineStr"/>
       <c r="G238" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H238" s="10" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I238" s="10" t="inlineStr">
@@ -10439,7 +10427,7 @@
       </c>
       <c r="J238" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -10449,29 +10437,25 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
+          <t>ООО «НСР»</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>7804384374</t>
+          <t>7801727376</t>
         </is>
       </c>
       <c r="D239" s="13" t="inlineStr"/>
-      <c r="E239" s="11" t="inlineStr">
-        <is>
-          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
-        </is>
-      </c>
+      <c r="E239" s="11" t="inlineStr"/>
       <c r="F239" s="11" t="inlineStr"/>
       <c r="G239" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H239" s="10" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="I239" s="10" t="inlineStr">
@@ -10481,7 +10465,7 @@
       </c>
       <c r="J239" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10491,29 +10475,29 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
+          <t>ООО «Новый век»</t>
         </is>
       </c>
       <c r="C240" s="12" t="inlineStr">
         <is>
-          <t>7810685806</t>
+          <t>7806113612</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr"/>
       <c r="E240" s="11" t="inlineStr">
         <is>
-          <t>194017 СПб, Ярославский пр.</t>
+          <t>199178 СПб, 12-я линия В.О. 13А пом.18н оф.30; ОГРН 1037816012398; ген.дир. Николаев С.Л.</t>
         </is>
       </c>
       <c r="F240" s="11" t="inlineStr"/>
       <c r="G240" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H240" s="10" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>547</t>
         </is>
       </c>
       <c r="I240" s="10" t="inlineStr">
@@ -10523,7 +10507,7 @@
       </c>
       <c r="J240" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10533,33 +10517,29 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
+          <t>ООО «Нордик»</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>7841469072</t>
+          <t>7804596040</t>
         </is>
       </c>
       <c r="D241" s="13" t="inlineStr"/>
       <c r="E241" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
-        </is>
-      </c>
-      <c r="F241" s="11" t="inlineStr">
-        <is>
-          <t>saby.ru/profile/7841469072-783901001</t>
-        </is>
-      </c>
+          <t>195220 СПб, пр.Непокорённых 17к4В; ОГРН 1177847139095; ген.дир. Барабанщиков А.Д.</t>
+        </is>
+      </c>
+      <c r="F241" s="11" t="inlineStr"/>
       <c r="G241" s="11" t="inlineStr">
         <is>
-          <t>нет данных (найден только белорусский номер — под вопросом)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H241" s="10" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>706</t>
         </is>
       </c>
       <c r="I241" s="10" t="inlineStr">
@@ -10569,7 +10549,7 @@
       </c>
       <c r="J241" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -10579,12 +10559,12 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСК «Реставрация»</t>
+          <t>ООО «ОСА - Север»</t>
         </is>
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>7839085696</t>
+          <t>7801574480</t>
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr"/>
@@ -10597,7 +10577,7 @@
       </c>
       <c r="H242" s="10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>834</t>
         </is>
       </c>
       <c r="I242" s="10" t="inlineStr">
@@ -10617,20 +10597,16 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
+          <t>ООО «ОблСервис»</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>7811659380</t>
+          <t>4712024087</t>
         </is>
       </c>
       <c r="D243" s="13" t="inlineStr"/>
-      <c r="E243" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
-        </is>
-      </c>
+      <c r="E243" s="11" t="inlineStr"/>
       <c r="F243" s="11" t="inlineStr"/>
       <c r="G243" s="11" t="inlineStr">
         <is>
@@ -10639,7 +10615,7 @@
       </c>
       <c r="H243" s="10" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="I243" s="10" t="inlineStr">
@@ -10649,7 +10625,7 @@
       </c>
       <c r="J243" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10659,20 +10635,16 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПСТ»</t>
+          <t>ООО «ОлАн»</t>
         </is>
       </c>
       <c r="C244" s="12" t="inlineStr">
         <is>
-          <t>7813448257</t>
+          <t>7827004614</t>
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr"/>
-      <c r="E244" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
-        </is>
-      </c>
+      <c r="E244" s="11" t="inlineStr"/>
       <c r="F244" s="11" t="inlineStr"/>
       <c r="G244" s="11" t="inlineStr">
         <is>
@@ -10681,7 +10653,7 @@
       </c>
       <c r="H244" s="10" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>685</t>
         </is>
       </c>
       <c r="I244" s="10" t="inlineStr">
@@ -10691,7 +10663,7 @@
       </c>
       <c r="J244" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -10701,12 +10673,12 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТГ»</t>
+          <t>ООО «Олимп-Строй»</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>5013050270</t>
+          <t>7820315709</t>
         </is>
       </c>
       <c r="D245" s="13" t="inlineStr"/>
@@ -10719,7 +10691,7 @@
       </c>
       <c r="H245" s="10" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>689</t>
         </is>
       </c>
       <c r="I245" s="10" t="inlineStr">
@@ -10729,7 +10701,7 @@
       </c>
       <c r="J245" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -10739,16 +10711,20 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТО Сервис»</t>
+          <t>ООО «Омега Строй»</t>
         </is>
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t>7839334494</t>
+          <t>7802711097</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr"/>
-      <c r="E246" s="11" t="inlineStr"/>
+      <c r="E246" s="11" t="inlineStr">
+        <is>
+          <t>195269 СПб, ул.Учительская 18к3 пом.10Н; ОГРН 1107847122459; ген.дир. Каленов П.А.</t>
+        </is>
+      </c>
       <c r="F246" s="11" t="inlineStr"/>
       <c r="G246" s="11" t="inlineStr">
         <is>
@@ -10757,7 +10733,7 @@
       </c>
       <c r="H246" s="10" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>632</t>
         </is>
       </c>
       <c r="I246" s="10" t="inlineStr">
@@ -10767,7 +10743,7 @@
       </c>
       <c r="J246" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -10777,12 +10753,12 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПТФ «КонСис»</t>
+          <t>ООО «Омни Структуре Санкт-Петербург»</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>7805068406</t>
+          <t>7801641792</t>
         </is>
       </c>
       <c r="D247" s="13" t="inlineStr"/>
@@ -10795,7 +10771,7 @@
       </c>
       <c r="H247" s="10" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>562</t>
         </is>
       </c>
       <c r="I247" s="10" t="inlineStr">
@@ -10815,12 +10791,12 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПЭС»</t>
+          <t>ООО «Основание»</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>7814677411</t>
+          <t>7840083527</t>
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr"/>
@@ -10833,7 +10809,7 @@
       </c>
       <c r="H248" s="10" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="I248" s="10" t="inlineStr">
@@ -10853,25 +10829,29 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>ООО «Паритет Плюс»</t>
+          <t>ООО «ПЁТР ВЕЛИКИЙ»</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>7806471030</t>
+          <t>7825382561</t>
         </is>
       </c>
       <c r="D249" s="13" t="inlineStr"/>
-      <c r="E249" s="11" t="inlineStr"/>
+      <c r="E249" s="11" t="inlineStr">
+        <is>
+          <t>191023 СПб, наб.реки Фонтанки 51-53А пом.24-н; ОГРН 1027809212133; ген.дир. Блашкевич В.А.</t>
+        </is>
+      </c>
       <c r="F249" s="11" t="inlineStr"/>
       <c r="G249" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H249" s="10" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>651</t>
         </is>
       </c>
       <c r="I249" s="10" t="inlineStr">
@@ -10881,7 +10861,7 @@
       </c>
       <c r="J249" s="10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10871,12 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПетроТрейд-инжиниринг»</t>
+          <t>ООО «ПВВ Продукт»</t>
         </is>
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>7802490056</t>
+          <t>7840501541</t>
         </is>
       </c>
       <c r="D250" s="13" t="inlineStr"/>
@@ -10909,7 +10889,7 @@
       </c>
       <c r="H250" s="10" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>454</t>
         </is>
       </c>
       <c r="I250" s="10" t="inlineStr">
@@ -10929,12 +10909,12 @@
       </c>
       <c r="B251" s="11" t="inlineStr">
         <is>
-          <t>ООО «Портмарин Инжиниринг»</t>
+          <t>ООО «ПВЦ «Восток»</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>7811777680</t>
+          <t>7802203054</t>
         </is>
       </c>
       <c r="D251" s="13" t="inlineStr"/>
@@ -10947,7 +10927,7 @@
       </c>
       <c r="H251" s="10" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>534</t>
         </is>
       </c>
       <c r="I251" s="10" t="inlineStr">
@@ -10967,25 +10947,29 @@
       </c>
       <c r="B252" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрогрессСтрой»</t>
+          <t>ООО «ПГИ» (Промгазиндустрия)</t>
         </is>
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>7811604013</t>
+          <t>7814822228</t>
         </is>
       </c>
       <c r="D252" s="13" t="inlineStr"/>
-      <c r="E252" s="11" t="inlineStr"/>
+      <c r="E252" s="11" t="inlineStr">
+        <is>
+          <t>197198 СПб, Петровская коса 1к1с1 пом.6Н оф.3022; ОГРН 1237800050135; ген.дир. Белецкий Д.С.</t>
+        </is>
+      </c>
       <c r="F252" s="11" t="inlineStr"/>
       <c r="G252" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H252" s="10" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="I252" s="10" t="inlineStr">
@@ -10995,7 +10979,7 @@
       </c>
       <c r="J252" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11005,12 +10989,12 @@
       </c>
       <c r="B253" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПромИнвест»</t>
+          <t>ООО «ПЕГАЗ»</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>7841439543</t>
+          <t>7804700982</t>
         </is>
       </c>
       <c r="D253" s="13" t="inlineStr"/>
@@ -11023,7 +11007,7 @@
       </c>
       <c r="H253" s="10" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="I253" s="10" t="inlineStr">
@@ -11043,12 +11027,12 @@
       </c>
       <c r="B254" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПромСтрой»</t>
+          <t>ООО «ПЕТРОТОРГ»</t>
         </is>
       </c>
       <c r="C254" s="12" t="inlineStr">
         <is>
-          <t>7806156944</t>
+          <t>7810518322</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr"/>
@@ -11061,7 +11045,7 @@
       </c>
       <c r="H254" s="10" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>751</t>
         </is>
       </c>
       <c r="I254" s="10" t="inlineStr">
@@ -11071,7 +11055,7 @@
       </c>
       <c r="J254" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11081,29 +11065,29 @@
       </c>
       <c r="B255" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстрой»</t>
+          <t>ООО «ПЕТРОЭКОЛОГИЯ Северо-Запад»</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>7814656860</t>
+          <t>7804384374</t>
         </is>
       </c>
       <c r="D255" s="13" t="inlineStr"/>
       <c r="E255" s="11" t="inlineStr">
         <is>
-          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
+          <t>СПб, о.Канонерский 24А оф.3а; ОГРН 1089847084073; рук. Бродский Л.Л.</t>
         </is>
       </c>
       <c r="F255" s="11" t="inlineStr"/>
       <c r="G255" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H255" s="10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>209</t>
         </is>
       </c>
       <c r="I255" s="10" t="inlineStr">
@@ -11113,7 +11097,7 @@
       </c>
       <c r="J255" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -11123,16 +11107,20 @@
       </c>
       <c r="B256" s="11" t="inlineStr">
         <is>
-          <t>ООО «Промстройинжиниринг»</t>
+          <t>ООО «ПРОМРЕКОНСТРУКЦИЯ»</t>
         </is>
       </c>
       <c r="C256" s="12" t="inlineStr">
         <is>
-          <t>7814349756</t>
+          <t>7810685806</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr"/>
-      <c r="E256" s="11" t="inlineStr"/>
+      <c r="E256" s="11" t="inlineStr">
+        <is>
+          <t>194017 СПб, Ярославский пр.</t>
+        </is>
+      </c>
       <c r="F256" s="11" t="inlineStr"/>
       <c r="G256" s="11" t="inlineStr">
         <is>
@@ -11141,7 +11129,7 @@
       </c>
       <c r="H256" s="10" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>753</t>
         </is>
       </c>
       <c r="I256" s="10" t="inlineStr">
@@ -11151,7 +11139,7 @@
       </c>
       <c r="J256" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -11161,25 +11149,33 @@
       </c>
       <c r="B257" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрофСтрой-И»</t>
+          <t>ООО «ПРОМТЕПЛОЭНЕРГОМОНТАЖ»</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>7810682530</t>
+          <t>7841469072</t>
         </is>
       </c>
       <c r="D257" s="13" t="inlineStr"/>
-      <c r="E257" s="11" t="inlineStr"/>
-      <c r="F257" s="11" t="inlineStr"/>
+      <c r="E257" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Дровяная 9А пом.10-Н оф.11-2; ОГРН 1127847433317; ген.дир. Бескубский Д.Ю. | В источнике указан +375 17 500-28-39 — это БЕЛОРУССКИЙ номер (Минск). Для петербургской компании нетипично, в телефоны не внесён, требует проверки</t>
+        </is>
+      </c>
+      <c r="F257" s="11" t="inlineStr">
+        <is>
+          <t>saby.ru/profile/7841469072-783901001</t>
+        </is>
+      </c>
       <c r="G257" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (найден только белорусский номер — под вопросом)</t>
         </is>
       </c>
       <c r="H257" s="10" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>595</t>
         </is>
       </c>
       <c r="I257" s="10" t="inlineStr">
@@ -11199,12 +11195,12 @@
       </c>
       <c r="B258" s="11" t="inlineStr">
         <is>
-          <t>ООО «ПрофСтройАльянс»</t>
+          <t>ООО «ПСК «Реставрация»</t>
         </is>
       </c>
       <c r="C258" s="12" t="inlineStr">
         <is>
-          <t>7842504114</t>
+          <t>7839085696</t>
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr"/>
@@ -11217,7 +11213,7 @@
       </c>
       <c r="H258" s="10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I258" s="10" t="inlineStr">
@@ -11237,18 +11233,18 @@
       </c>
       <c r="B259" s="11" t="inlineStr">
         <is>
-          <t>ООО «Профиль»</t>
+          <t>ООО «ПСО «ЛЕНОБЛСТРОЙ»</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>7802182380</t>
+          <t>7811659380</t>
         </is>
       </c>
       <c r="D259" s="13" t="inlineStr"/>
       <c r="E259" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+          <t>СПб, ул.Седова 1к2Б оф.2; ОГРН 1177847274770; ген.дир. Сидоров А.В.</t>
         </is>
       </c>
       <c r="F259" s="11" t="inlineStr"/>
@@ -11259,7 +11255,7 @@
       </c>
       <c r="H259" s="10" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>607</t>
         </is>
       </c>
       <c r="I259" s="10" t="inlineStr">
@@ -11269,7 +11265,7 @@
       </c>
       <c r="J259" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11279,16 +11275,20 @@
       </c>
       <c r="B260" s="11" t="inlineStr">
         <is>
-          <t>ООО «РД»</t>
+          <t>ООО «ПСТ»</t>
         </is>
       </c>
       <c r="C260" s="12" t="inlineStr">
         <is>
-          <t>7810062946</t>
+          <t>7813448257</t>
         </is>
       </c>
       <c r="D260" s="13" t="inlineStr"/>
-      <c r="E260" s="11" t="inlineStr"/>
+      <c r="E260" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, ул.Профессора Попова 23В оф.300; ОГРН 1097847197623; ген.дир. Смуглянов С.А.</t>
+        </is>
+      </c>
       <c r="F260" s="11" t="inlineStr"/>
       <c r="G260" s="11" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="H260" s="10" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>876</t>
         </is>
       </c>
       <c r="I260" s="10" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="J260" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11317,20 +11317,16 @@
       </c>
       <c r="B261" s="11" t="inlineStr">
         <is>
-          <t>ООО «РЕССТРОЙ»</t>
+          <t>ООО «ПТГ»</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>7820012849</t>
+          <t>5013050270</t>
         </is>
       </c>
       <c r="D261" s="13" t="inlineStr"/>
-      <c r="E261" s="11" t="inlineStr">
-        <is>
-          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
-        </is>
-      </c>
+      <c r="E261" s="11" t="inlineStr"/>
       <c r="F261" s="11" t="inlineStr"/>
       <c r="G261" s="11" t="inlineStr">
         <is>
@@ -11339,7 +11335,7 @@
       </c>
       <c r="H261" s="10" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="I261" s="10" t="inlineStr">
@@ -11359,12 +11355,12 @@
       </c>
       <c r="B262" s="11" t="inlineStr">
         <is>
-          <t>ООО «РИАРДЕН»</t>
+          <t>ООО «ПТО Сервис»</t>
         </is>
       </c>
       <c r="C262" s="12" t="inlineStr">
         <is>
-          <t>7814794789</t>
+          <t>7839334494</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr"/>
@@ -11377,7 +11373,7 @@
       </c>
       <c r="H262" s="10" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>558</t>
         </is>
       </c>
       <c r="I262" s="10" t="inlineStr">
@@ -11387,7 +11383,7 @@
       </c>
       <c r="J262" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11397,12 +11393,12 @@
       </c>
       <c r="B263" s="11" t="inlineStr">
         <is>
-          <t>ООО «РК ДЕВЕЛОПМЕНТ»</t>
+          <t>ООО «ПТФ «КонСис»</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>7814800834</t>
+          <t>7805068406</t>
         </is>
       </c>
       <c r="D263" s="13" t="inlineStr"/>
@@ -11415,7 +11411,7 @@
       </c>
       <c r="H263" s="10" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>642</t>
         </is>
       </c>
       <c r="I263" s="10" t="inlineStr">
@@ -11425,7 +11421,7 @@
       </c>
       <c r="J263" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -11435,20 +11431,16 @@
       </c>
       <c r="B264" s="11" t="inlineStr">
         <is>
-          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
+          <t>ООО «ПЭС»</t>
         </is>
       </c>
       <c r="C264" s="12" t="inlineStr">
         <is>
-          <t>7826123721</t>
+          <t>7814677411</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr"/>
-      <c r="E264" s="11" t="inlineStr">
-        <is>
-          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
-        </is>
-      </c>
+      <c r="E264" s="11" t="inlineStr"/>
       <c r="F264" s="11" t="inlineStr"/>
       <c r="G264" s="11" t="inlineStr">
         <is>
@@ -11457,7 +11449,7 @@
       </c>
       <c r="H264" s="10" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>654</t>
         </is>
       </c>
       <c r="I264" s="10" t="inlineStr">
@@ -11467,7 +11459,7 @@
       </c>
       <c r="J264" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11477,12 +11469,12 @@
       </c>
       <c r="B265" s="11" t="inlineStr">
         <is>
-          <t>ООО «РОНИС»</t>
+          <t>ООО «Паритет Плюс»</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>7840475549</t>
+          <t>7806471030</t>
         </is>
       </c>
       <c r="D265" s="13" t="inlineStr"/>
@@ -11495,7 +11487,7 @@
       </c>
       <c r="H265" s="10" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I265" s="10" t="inlineStr">
@@ -11505,7 +11497,7 @@
       </c>
       <c r="J265" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
@@ -11515,12 +11507,12 @@
       </c>
       <c r="B266" s="11" t="inlineStr">
         <is>
-          <t>ООО «РОСТРА северо-запад»</t>
+          <t>ООО «ПетроТрейд-инжиниринг»</t>
         </is>
       </c>
       <c r="C266" s="12" t="inlineStr">
         <is>
-          <t>7805234942</t>
+          <t>7802490056</t>
         </is>
       </c>
       <c r="D266" s="13" t="inlineStr"/>
@@ -11533,7 +11525,7 @@
       </c>
       <c r="H266" s="10" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>771</t>
         </is>
       </c>
       <c r="I266" s="10" t="inlineStr">
@@ -11553,12 +11545,12 @@
       </c>
       <c r="B267" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСК «ОРДЕР» (реставрационно-строительная)</t>
+          <t>ООО «Портмарин Инжиниринг»</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>7801585837</t>
+          <t>7811777680</t>
         </is>
       </c>
       <c r="D267" s="13" t="inlineStr"/>
@@ -11571,7 +11563,7 @@
       </c>
       <c r="H267" s="10" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="I267" s="10" t="inlineStr">
@@ -11591,12 +11583,12 @@
       </c>
       <c r="B268" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСК «ТехноСтрой»</t>
+          <t>ООО «ПрогрессСтрой»</t>
         </is>
       </c>
       <c r="C268" s="12" t="inlineStr">
         <is>
-          <t>7838061420</t>
+          <t>7811604013</t>
         </is>
       </c>
       <c r="D268" s="13" t="inlineStr"/>
@@ -11609,7 +11601,7 @@
       </c>
       <c r="H268" s="10" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="I268" s="10" t="inlineStr">
@@ -11629,12 +11621,12 @@
       </c>
       <c r="B269" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСУ-9»</t>
+          <t>ООО «ПромИнвест»</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>7814785030</t>
+          <t>7841439543</t>
         </is>
       </c>
       <c r="D269" s="13" t="inlineStr"/>
@@ -11647,7 +11639,7 @@
       </c>
       <c r="H269" s="10" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I269" s="10" t="inlineStr">
@@ -11667,20 +11659,16 @@
       </c>
       <c r="B270" s="11" t="inlineStr">
         <is>
-          <t>ООО «РСФ «Водолей плюс»</t>
+          <t>ООО «ПромСтрой»</t>
         </is>
       </c>
       <c r="C270" s="12" t="inlineStr">
         <is>
-          <t>7826040578</t>
+          <t>7806156944</t>
         </is>
       </c>
       <c r="D270" s="13" t="inlineStr"/>
-      <c r="E270" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Б.Сампсониевский пр. 60И; ОГРН 1027810321659; ген.дир. Колосовская П.В.</t>
-        </is>
-      </c>
+      <c r="E270" s="11" t="inlineStr"/>
       <c r="F270" s="11" t="inlineStr"/>
       <c r="G270" s="11" t="inlineStr">
         <is>
@@ -11689,7 +11677,7 @@
       </c>
       <c r="H270" s="10" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I270" s="10" t="inlineStr">
@@ -11709,29 +11697,29 @@
       </c>
       <c r="B271" s="11" t="inlineStr">
         <is>
-          <t>ООО «РестСтройГрупп»</t>
+          <t>ООО «Промстрой»</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>7839099924</t>
+          <t>7814656860</t>
         </is>
       </c>
       <c r="D271" s="13" t="inlineStr"/>
       <c r="E271" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+          <t>197348 СПб, Богатырский пр. 2А каб.3.23; ОГРН 1167847280006</t>
         </is>
       </c>
       <c r="F271" s="11" t="inlineStr"/>
       <c r="G271" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H271" s="10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>516</t>
         </is>
       </c>
       <c r="I271" s="10" t="inlineStr">
@@ -11741,7 +11729,7 @@
       </c>
       <c r="J271" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -11751,12 +11739,12 @@
       </c>
       <c r="B272" s="11" t="inlineStr">
         <is>
-          <t>ООО «СВМ - Групп»</t>
+          <t>ООО «Промстройинжиниринг»</t>
         </is>
       </c>
       <c r="C272" s="12" t="inlineStr">
         <is>
-          <t>7843014240</t>
+          <t>7814349756</t>
         </is>
       </c>
       <c r="D272" s="13" t="inlineStr"/>
@@ -11769,7 +11757,7 @@
       </c>
       <c r="H272" s="10" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>797</t>
         </is>
       </c>
       <c r="I272" s="10" t="inlineStr">
@@ -11789,12 +11777,12 @@
       </c>
       <c r="B273" s="11" t="inlineStr">
         <is>
-          <t>ООО «СГИ»</t>
+          <t>ООО «ПрофСтрой-И»</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>7816654829</t>
+          <t>7810682530</t>
         </is>
       </c>
       <c r="D273" s="13" t="inlineStr"/>
@@ -11807,7 +11795,7 @@
       </c>
       <c r="H273" s="10" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I273" s="10" t="inlineStr">
@@ -11827,12 +11815,12 @@
       </c>
       <c r="B274" s="11" t="inlineStr">
         <is>
-          <t>ООО «СДК Лидер-Строй»</t>
+          <t>ООО «ПрофСтройАльянс»</t>
         </is>
       </c>
       <c r="C274" s="12" t="inlineStr">
         <is>
-          <t>7806299036</t>
+          <t>7842504114</t>
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr"/>
@@ -11845,7 +11833,7 @@
       </c>
       <c r="H274" s="10" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I274" s="10" t="inlineStr">
@@ -11865,16 +11853,20 @@
       </c>
       <c r="B275" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЗ «Загородная, 71»</t>
+          <t>ООО «Профиль»</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>7817328112</t>
+          <t>7802182380</t>
         </is>
       </c>
       <c r="D275" s="13" t="inlineStr"/>
-      <c r="E275" s="11" t="inlineStr"/>
+      <c r="E275" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Чугунная 4А оф.500; ОГРН 1037804035851; ген.дир. Сальников Д.В.</t>
+        </is>
+      </c>
       <c r="F275" s="11" t="inlineStr"/>
       <c r="G275" s="11" t="inlineStr">
         <is>
@@ -11883,7 +11875,7 @@
       </c>
       <c r="H275" s="10" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>572</t>
         </is>
       </c>
       <c r="I275" s="10" t="inlineStr">
@@ -11893,7 +11885,7 @@
       </c>
       <c r="J275" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -11903,20 +11895,16 @@
       </c>
       <c r="B276" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Алстрой»</t>
+          <t>ООО «РД»</t>
         </is>
       </c>
       <c r="C276" s="12" t="inlineStr">
         <is>
-          <t>7813417675</t>
+          <t>7810062946</t>
         </is>
       </c>
       <c r="D276" s="13" t="inlineStr"/>
-      <c r="E276" s="11" t="inlineStr">
-        <is>
-          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
-        </is>
-      </c>
+      <c r="E276" s="11" t="inlineStr"/>
       <c r="F276" s="11" t="inlineStr"/>
       <c r="G276" s="11" t="inlineStr">
         <is>
@@ -11925,7 +11913,7 @@
       </c>
       <c r="H276" s="10" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>365</t>
         </is>
       </c>
       <c r="I276" s="10" t="inlineStr">
@@ -11935,7 +11923,7 @@
       </c>
       <c r="J276" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -11945,18 +11933,18 @@
       </c>
       <c r="B277" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Дальпитерстрой»</t>
+          <t>ООО «РЕССТРОЙ»</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>7842021879</t>
+          <t>7820012849</t>
         </is>
       </c>
       <c r="D277" s="13" t="inlineStr"/>
       <c r="E277" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.16Н; ОГРН 1157847026402; дир. Скоров М.А.</t>
+          <t>СПб, г.Пушкин, Софийский б-р; ОГРН 1037842000943; ген.дир. Бачой Д.В.</t>
         </is>
       </c>
       <c r="F277" s="11" t="inlineStr"/>
@@ -11967,7 +11955,7 @@
       </c>
       <c r="H277" s="10" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>713</t>
         </is>
       </c>
       <c r="I277" s="10" t="inlineStr">
@@ -11977,7 +11965,7 @@
       </c>
       <c r="J277" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11975,12 @@
       </c>
       <c r="B278" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Орион»</t>
+          <t>ООО «РИАРДЕН»</t>
         </is>
       </c>
       <c r="C278" s="12" t="inlineStr">
         <is>
-          <t>7816699026</t>
+          <t>7814794789</t>
         </is>
       </c>
       <c r="D278" s="13" t="inlineStr"/>
@@ -12005,7 +11993,7 @@
       </c>
       <c r="H278" s="10" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>975</t>
         </is>
       </c>
       <c r="I278" s="10" t="inlineStr">
@@ -12025,20 +12013,16 @@
       </c>
       <c r="B279" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Потенциал»</t>
+          <t>ООО «РК ДЕВЕЛОПМЕНТ»</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>7814558855</t>
+          <t>7814800834</t>
         </is>
       </c>
       <c r="D279" s="13" t="inlineStr"/>
-      <c r="E279" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
-        </is>
-      </c>
+      <c r="E279" s="11" t="inlineStr"/>
       <c r="F279" s="11" t="inlineStr"/>
       <c r="G279" s="11" t="inlineStr">
         <is>
@@ -12047,7 +12031,7 @@
       </c>
       <c r="H279" s="10" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>861</t>
         </is>
       </c>
       <c r="I279" s="10" t="inlineStr">
@@ -12057,7 +12041,7 @@
       </c>
       <c r="J279" s="10" t="inlineStr">
         <is>
-          <t>1700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12067,16 +12051,20 @@
       </c>
       <c r="B280" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «СтальСтрой»</t>
+          <t>ООО «РМ «Наследие» (Реставрационная мастерская)</t>
         </is>
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>7841052031</t>
+          <t>7826123721</t>
         </is>
       </c>
       <c r="D280" s="13" t="inlineStr"/>
-      <c r="E280" s="11" t="inlineStr"/>
+      <c r="E280" s="11" t="inlineStr">
+        <is>
+          <t>191187 СПб, ул.Оружейника Фёдорова 5А пом.1н; ОГРН 1027810317633; ген.дир. Щедров Ю.С.</t>
+        </is>
+      </c>
       <c r="F280" s="11" t="inlineStr"/>
       <c r="G280" s="11" t="inlineStr">
         <is>
@@ -12085,7 +12073,7 @@
       </c>
       <c r="H280" s="10" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>515</t>
         </is>
       </c>
       <c r="I280" s="10" t="inlineStr">
@@ -12095,7 +12083,7 @@
       </c>
       <c r="J280" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12093,12 @@
       </c>
       <c r="B281" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «СтиФ»</t>
+          <t>ООО «РОНИС»</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>7825475600</t>
+          <t>7840475549</t>
         </is>
       </c>
       <c r="D281" s="13" t="inlineStr"/>
@@ -12123,7 +12111,7 @@
       </c>
       <c r="H281" s="10" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I281" s="10" t="inlineStr">
@@ -12133,7 +12121,7 @@
       </c>
       <c r="J281" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12143,12 +12131,12 @@
       </c>
       <c r="B282" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК «Стройнорд»</t>
+          <t>ООО «РОСТРА северо-запад»</t>
         </is>
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>7811571992</t>
+          <t>7805234942</t>
         </is>
       </c>
       <c r="D282" s="13" t="inlineStr"/>
@@ -12161,7 +12149,7 @@
       </c>
       <c r="H282" s="10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>714</t>
         </is>
       </c>
       <c r="I282" s="10" t="inlineStr">
@@ -12181,20 +12169,16 @@
       </c>
       <c r="B283" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Гарант»</t>
+          <t>ООО «РСК «ОРДЕР» (реставрационно-строительная)</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>7806380022</t>
+          <t>7801585837</t>
         </is>
       </c>
       <c r="D283" s="13" t="inlineStr"/>
-      <c r="E283" s="11" t="inlineStr">
-        <is>
-          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
-        </is>
-      </c>
+      <c r="E283" s="11" t="inlineStr"/>
       <c r="F283" s="11" t="inlineStr"/>
       <c r="G283" s="11" t="inlineStr">
         <is>
@@ -12203,7 +12187,7 @@
       </c>
       <c r="H283" s="10" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>603</t>
         </is>
       </c>
       <c r="I283" s="10" t="inlineStr">
@@ -12213,7 +12197,7 @@
       </c>
       <c r="J283" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12223,12 +12207,12 @@
       </c>
       <c r="B284" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Меркурий»</t>
+          <t>ООО «РСК «ТехноСтрой»</t>
         </is>
       </c>
       <c r="C284" s="12" t="inlineStr">
         <is>
-          <t>7819046339</t>
+          <t>7838061420</t>
         </is>
       </c>
       <c r="D284" s="13" t="inlineStr"/>
@@ -12241,7 +12225,7 @@
       </c>
       <c r="H284" s="10" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I284" s="10" t="inlineStr">
@@ -12261,12 +12245,12 @@
       </c>
       <c r="B285" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПРАГМА СТРОЙ»</t>
+          <t>ООО «РСУ-9»</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>7802313956</t>
+          <t>7814785030</t>
         </is>
       </c>
       <c r="D285" s="13" t="inlineStr"/>
@@ -12279,7 +12263,7 @@
       </c>
       <c r="H285" s="10" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>799</t>
         </is>
       </c>
       <c r="I285" s="10" t="inlineStr">
@@ -12289,7 +12273,7 @@
       </c>
       <c r="J285" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12299,18 +12283,18 @@
       </c>
       <c r="B286" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ПСП»</t>
+          <t>ООО «РСФ «Водолей плюс»</t>
         </is>
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>7810502379</t>
+          <t>7826040578</t>
         </is>
       </c>
       <c r="D286" s="13" t="inlineStr"/>
       <c r="E286" s="11" t="inlineStr">
         <is>
-          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
+          <t>СПб, Б.Сампсониевский пр. 60И; ОГРН 1027810321659; ген.дир. Колосовская П.В.</t>
         </is>
       </c>
       <c r="F286" s="11" t="inlineStr"/>
@@ -12321,7 +12305,7 @@
       </c>
       <c r="H286" s="10" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>582</t>
         </is>
       </c>
       <c r="I286" s="10" t="inlineStr">
@@ -12331,7 +12315,7 @@
       </c>
       <c r="J286" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12341,25 +12325,29 @@
       </c>
       <c r="B287" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Профиль групп»</t>
+          <t>ООО «РестСтройГрупп»</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>7802593414</t>
+          <t>7839099924</t>
         </is>
       </c>
       <c r="D287" s="13" t="inlineStr"/>
-      <c r="E287" s="11" t="inlineStr"/>
+      <c r="E287" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Гагаринская 6/1А пом.11-Н; ОГРН 1187847092905; ген.дир. Чертищев А.Ю.</t>
+        </is>
+      </c>
       <c r="F287" s="11" t="inlineStr"/>
       <c r="G287" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H287" s="10" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>673</t>
         </is>
       </c>
       <c r="I287" s="10" t="inlineStr">
@@ -12369,7 +12357,7 @@
       </c>
       <c r="J287" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12367,12 @@
       </c>
       <c r="B288" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК СФЕРА»</t>
+          <t>ООО «СВМ - Групп»</t>
         </is>
       </c>
       <c r="C288" s="12" t="inlineStr">
         <is>
-          <t>9715445653</t>
+          <t>7843014240</t>
         </is>
       </c>
       <c r="D288" s="13" t="inlineStr"/>
@@ -12397,7 +12385,7 @@
       </c>
       <c r="H288" s="10" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I288" s="10" t="inlineStr">
@@ -12417,12 +12405,12 @@
       </c>
       <c r="B289" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК Стройкомплект»</t>
+          <t>ООО «СГИ»</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>7806133873</t>
+          <t>7816654829</t>
         </is>
       </c>
       <c r="D289" s="13" t="inlineStr"/>
@@ -12435,7 +12423,7 @@
       </c>
       <c r="H289" s="10" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="I289" s="10" t="inlineStr">
@@ -12445,7 +12433,7 @@
       </c>
       <c r="J289" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12455,12 +12443,12 @@
       </c>
       <c r="B290" s="11" t="inlineStr">
         <is>
-          <t>ООО «СК ТТ»</t>
+          <t>ООО «СДК Лидер-Строй»</t>
         </is>
       </c>
       <c r="C290" s="12" t="inlineStr">
         <is>
-          <t>7813676373</t>
+          <t>7806299036</t>
         </is>
       </c>
       <c r="D290" s="13" t="inlineStr"/>
@@ -12473,7 +12461,7 @@
       </c>
       <c r="H290" s="10" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="I290" s="10" t="inlineStr">
@@ -12493,12 +12481,12 @@
       </c>
       <c r="B291" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКМ»</t>
+          <t>ООО «СЗ «Загородная, 71»</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>7807239583</t>
+          <t>7817328112</t>
         </is>
       </c>
       <c r="D291" s="13" t="inlineStr"/>
@@ -12511,7 +12499,7 @@
       </c>
       <c r="H291" s="10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="I291" s="10" t="inlineStr">
@@ -12531,16 +12519,20 @@
       </c>
       <c r="B292" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКН НВК»</t>
+          <t>ООО «СК «Алстрой»</t>
         </is>
       </c>
       <c r="C292" s="12" t="inlineStr">
         <is>
-          <t>7838057216</t>
+          <t>7813417675</t>
         </is>
       </c>
       <c r="D292" s="13" t="inlineStr"/>
-      <c r="E292" s="11" t="inlineStr"/>
+      <c r="E292" s="11" t="inlineStr">
+        <is>
+          <t>197022 СПб, Аптекарский пр. 6/4А; ОГРН 1089847245894; ген.дир. Тихомирова Г.Ю.</t>
+        </is>
+      </c>
       <c r="F292" s="11" t="inlineStr"/>
       <c r="G292" s="11" t="inlineStr">
         <is>
@@ -12549,7 +12541,7 @@
       </c>
       <c r="H292" s="10" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>590</t>
         </is>
       </c>
       <c r="I292" s="10" t="inlineStr">
@@ -12559,7 +12551,7 @@
       </c>
       <c r="J292" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -12569,16 +12561,20 @@
       </c>
       <c r="B293" s="11" t="inlineStr">
         <is>
-          <t>ООО «СКП»</t>
+          <t>ООО «СК «Дальпитерстрой»</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>7806619896</t>
+          <t>7842021879</t>
         </is>
       </c>
       <c r="D293" s="13" t="inlineStr"/>
-      <c r="E293" s="11" t="inlineStr"/>
+      <c r="E293" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.16Н; ОГРН 1157847026402; дир. Скоров М.А.</t>
+        </is>
+      </c>
       <c r="F293" s="11" t="inlineStr"/>
       <c r="G293" s="11" t="inlineStr">
         <is>
@@ -12587,7 +12583,7 @@
       </c>
       <c r="H293" s="10" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>622</t>
         </is>
       </c>
       <c r="I293" s="10" t="inlineStr">
@@ -12597,7 +12593,7 @@
       </c>
       <c r="J293" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -12607,12 +12603,12 @@
       </c>
       <c r="B294" s="11" t="inlineStr">
         <is>
-          <t>ООО «СМУ 8»</t>
+          <t>ООО «СК «Орион»</t>
         </is>
       </c>
       <c r="C294" s="12" t="inlineStr">
         <is>
-          <t>7810531355</t>
+          <t>7816699026</t>
         </is>
       </c>
       <c r="D294" s="13" t="inlineStr"/>
@@ -12625,7 +12621,7 @@
       </c>
       <c r="H294" s="10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>969</t>
         </is>
       </c>
       <c r="I294" s="10" t="inlineStr">
@@ -12645,16 +12641,20 @@
       </c>
       <c r="B295" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПМК - 18»</t>
+          <t>ООО «СК «Потенциал»</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>7814624120</t>
+          <t>7814558855</t>
         </is>
       </c>
       <c r="D295" s="13" t="inlineStr"/>
-      <c r="E295" s="11" t="inlineStr"/>
+      <c r="E295" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Репищева 14АД; ОГРН 1129847030807; ген.дир. Бахарев А.С.</t>
+        </is>
+      </c>
       <c r="F295" s="11" t="inlineStr"/>
       <c r="G295" s="11" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="H295" s="10" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>675</t>
         </is>
       </c>
       <c r="I295" s="10" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="J295" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1700000</t>
         </is>
       </c>
     </row>
@@ -12683,20 +12683,16 @@
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>ООО «СПбЭК-Майнинг»</t>
+          <t>ООО «СК «СтальСтрой»</t>
         </is>
       </c>
       <c r="C296" s="12" t="inlineStr">
         <is>
-          <t>7820326027</t>
+          <t>7841052031</t>
         </is>
       </c>
       <c r="D296" s="13" t="inlineStr"/>
-      <c r="E296" s="11" t="inlineStr">
-        <is>
-          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
-        </is>
-      </c>
+      <c r="E296" s="11" t="inlineStr"/>
       <c r="F296" s="11" t="inlineStr"/>
       <c r="G296" s="11" t="inlineStr">
         <is>
@@ -12705,7 +12701,7 @@
       </c>
       <c r="H296" s="10" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>439</t>
         </is>
       </c>
       <c r="I296" s="10" t="inlineStr">
@@ -12715,7 +12711,7 @@
       </c>
       <c r="J296" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12725,12 +12721,12 @@
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОИТЕЛЬ»</t>
+          <t>ООО «СК «СтиФ»</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>7804338561</t>
+          <t>7825475600</t>
         </is>
       </c>
       <c r="D297" s="13" t="inlineStr"/>
@@ -12743,7 +12739,7 @@
       </c>
       <c r="H297" s="10" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>581</t>
         </is>
       </c>
       <c r="I297" s="10" t="inlineStr">
@@ -12763,12 +12759,12 @@
       </c>
       <c r="B298" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙ КОРПУС»</t>
+          <t>ООО «СК «Стройнорд»</t>
         </is>
       </c>
       <c r="C298" s="12" t="inlineStr">
         <is>
-          <t>7804553054</t>
+          <t>7811571992</t>
         </is>
       </c>
       <c r="D298" s="13" t="inlineStr"/>
@@ -12781,7 +12777,7 @@
       </c>
       <c r="H298" s="10" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>549</t>
         </is>
       </c>
       <c r="I298" s="10" t="inlineStr">
@@ -12801,16 +12797,20 @@
       </c>
       <c r="B299" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙГРАД РСУ»</t>
+          <t>ООО «СК Гарант»</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>7802703995</t>
+          <t>7806380022</t>
         </is>
       </c>
       <c r="D299" s="13" t="inlineStr"/>
-      <c r="E299" s="11" t="inlineStr"/>
+      <c r="E299" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, Перевозный пер. 19к1; рег. 08.02.2008; малое предприятие</t>
+        </is>
+      </c>
       <c r="F299" s="11" t="inlineStr"/>
       <c r="G299" s="11" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="H299" s="10" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>600</t>
         </is>
       </c>
       <c r="I299" s="10" t="inlineStr">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="J299" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -12839,20 +12839,16 @@
       </c>
       <c r="B300" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОМПЛЕКС»</t>
+          <t>ООО «СК Меркурий»</t>
         </is>
       </c>
       <c r="C300" s="12" t="inlineStr">
         <is>
-          <t>7825055370</t>
+          <t>7819046339</t>
         </is>
       </c>
       <c r="D300" s="13" t="inlineStr"/>
-      <c r="E300" s="11" t="inlineStr">
-        <is>
-          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
-        </is>
-      </c>
+      <c r="E300" s="11" t="inlineStr"/>
       <c r="F300" s="11" t="inlineStr"/>
       <c r="G300" s="11" t="inlineStr">
         <is>
@@ -12861,7 +12857,7 @@
       </c>
       <c r="H300" s="10" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>983</t>
         </is>
       </c>
       <c r="I300" s="10" t="inlineStr">
@@ -12871,7 +12867,7 @@
       </c>
       <c r="J300" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -12881,12 +12877,12 @@
       </c>
       <c r="B301" s="11" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙКОНСУЛЬТ»</t>
+          <t>ООО «СК ПРАГМА СТРОЙ»</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>7810289545</t>
+          <t>7802313956</t>
         </is>
       </c>
       <c r="D301" s="13" t="inlineStr"/>
@@ -12899,7 +12895,7 @@
       </c>
       <c r="H301" s="10" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>737</t>
         </is>
       </c>
       <c r="I301" s="10" t="inlineStr">
@@ -12919,18 +12915,18 @@
       </c>
       <c r="B302" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУ-17»</t>
+          <t>ООО «СК ПСП»</t>
         </is>
       </c>
       <c r="C302" s="12" t="inlineStr">
         <is>
-          <t>7807028906</t>
+          <t>7810502379</t>
         </is>
       </c>
       <c r="D302" s="13" t="inlineStr"/>
       <c r="E302" s="11" t="inlineStr">
         <is>
-          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+          <t>196084 СПб, Цветочная ул. 18А пом.8-н; ОГРН 1089847014586; ген.дир. Плавник И.Е.</t>
         </is>
       </c>
       <c r="F302" s="11" t="inlineStr"/>
@@ -12941,7 +12937,7 @@
       </c>
       <c r="H302" s="10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>527</t>
         </is>
       </c>
       <c r="I302" s="10" t="inlineStr">
@@ -12951,7 +12947,7 @@
       </c>
       <c r="J302" s="10" t="inlineStr">
         <is>
-          <t>2300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -12961,20 +12957,16 @@
       </c>
       <c r="B303" s="11" t="inlineStr">
         <is>
-          <t>ООО «СУАР-Групп»</t>
+          <t>ООО «СК Профиль групп»</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>7802270195</t>
+          <t>7802593414</t>
         </is>
       </c>
       <c r="D303" s="13" t="inlineStr"/>
-      <c r="E303" s="11" t="inlineStr">
-        <is>
-          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
-        </is>
-      </c>
+      <c r="E303" s="11" t="inlineStr"/>
       <c r="F303" s="11" t="inlineStr"/>
       <c r="G303" s="11" t="inlineStr">
         <is>
@@ -12983,7 +12975,7 @@
       </c>
       <c r="H303" s="10" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>576</t>
         </is>
       </c>
       <c r="I303" s="10" t="inlineStr">
@@ -12993,7 +12985,7 @@
       </c>
       <c r="J303" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13003,20 +12995,16 @@
       </c>
       <c r="B304" s="11" t="inlineStr">
         <is>
-          <t>ООО «СФ «Новэк»</t>
+          <t>ООО «СК СФЕРА»</t>
         </is>
       </c>
       <c r="C304" s="12" t="inlineStr">
         <is>
-          <t>7825128540</t>
+          <t>9715445653</t>
         </is>
       </c>
       <c r="D304" s="13" t="inlineStr"/>
-      <c r="E304" s="11" t="inlineStr">
-        <is>
-          <t>194352 СПб, ул.Кустодиева 17А; ОГРН 1027809227907; ген.дир. Смирнов Д.И.</t>
-        </is>
-      </c>
+      <c r="E304" s="11" t="inlineStr"/>
       <c r="F304" s="11" t="inlineStr"/>
       <c r="G304" s="11" t="inlineStr">
         <is>
@@ -13025,7 +13013,7 @@
       </c>
       <c r="H304" s="10" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="I304" s="10" t="inlineStr">
@@ -13045,29 +13033,25 @@
       </c>
       <c r="B305" s="11" t="inlineStr">
         <is>
-          <t>ООО «СЭМ»</t>
+          <t>ООО «СК Стройкомплект»</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>7810201646</t>
+          <t>7806133873</t>
         </is>
       </c>
       <c r="D305" s="13" t="inlineStr"/>
-      <c r="E305" s="11" t="inlineStr">
-        <is>
-          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
-        </is>
-      </c>
+      <c r="E305" s="11" t="inlineStr"/>
       <c r="F305" s="11" t="inlineStr"/>
       <c r="G305" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H305" s="10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>641</t>
         </is>
       </c>
       <c r="I305" s="10" t="inlineStr">
@@ -13077,7 +13061,7 @@
       </c>
       <c r="J305" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13087,12 +13071,12 @@
       </c>
       <c r="B306" s="11" t="inlineStr">
         <is>
-          <t>ООО «Свой Дом»</t>
+          <t>ООО «СК ТТ»</t>
         </is>
       </c>
       <c r="C306" s="12" t="inlineStr">
         <is>
-          <t>7813322254</t>
+          <t>7813676373</t>
         </is>
       </c>
       <c r="D306" s="13" t="inlineStr"/>
@@ -13105,7 +13089,7 @@
       </c>
       <c r="H306" s="10" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="I306" s="10" t="inlineStr">
@@ -13115,7 +13099,7 @@
       </c>
       <c r="J306" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13125,29 +13109,25 @@
       </c>
       <c r="B307" s="11" t="inlineStr">
         <is>
-          <t>ООО «СиФ»</t>
+          <t>ООО «СКМ»</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>7801075307</t>
+          <t>7807239583</t>
         </is>
       </c>
       <c r="D307" s="13" t="inlineStr"/>
-      <c r="E307" s="11" t="inlineStr">
-        <is>
-          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
-        </is>
-      </c>
+      <c r="E307" s="11" t="inlineStr"/>
       <c r="F307" s="11" t="inlineStr"/>
       <c r="G307" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H307" s="10" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I307" s="10" t="inlineStr">
@@ -13167,12 +13147,12 @@
       </c>
       <c r="B308" s="11" t="inlineStr">
         <is>
-          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
+          <t>ООО «СКН НВК»</t>
         </is>
       </c>
       <c r="C308" s="12" t="inlineStr">
         <is>
-          <t>7810691246</t>
+          <t>7838057216</t>
         </is>
       </c>
       <c r="D308" s="13" t="inlineStr"/>
@@ -13185,7 +13165,7 @@
       </c>
       <c r="H308" s="10" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>629</t>
         </is>
       </c>
       <c r="I308" s="10" t="inlineStr">
@@ -13205,12 +13185,12 @@
       </c>
       <c r="B309" s="11" t="inlineStr">
         <is>
-          <t>ООО «Синергия»</t>
+          <t>ООО «СКП»</t>
         </is>
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>7841100278</t>
+          <t>7806619896</t>
         </is>
       </c>
       <c r="D309" s="13" t="inlineStr"/>
@@ -13223,7 +13203,7 @@
       </c>
       <c r="H309" s="10" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="I309" s="10" t="inlineStr">
@@ -13243,29 +13223,25 @@
       </c>
       <c r="B310" s="11" t="inlineStr">
         <is>
-          <t>ООО «СносСтройИнвест»</t>
+          <t>ООО «СМУ 8»</t>
         </is>
       </c>
       <c r="C310" s="12" t="inlineStr">
         <is>
-          <t>7805239355</t>
+          <t>7810531355</t>
         </is>
       </c>
       <c r="D310" s="13" t="inlineStr"/>
-      <c r="E310" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E310" s="11" t="inlineStr"/>
       <c r="F310" s="11" t="inlineStr"/>
       <c r="G310" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H310" s="10" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>367</t>
         </is>
       </c>
       <c r="I310" s="10" t="inlineStr">
@@ -13285,12 +13261,12 @@
       </c>
       <c r="B311" s="11" t="inlineStr">
         <is>
-          <t>ООО «СпецСтрой»</t>
+          <t>ООО «СПМК - 18»</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>7802753883</t>
+          <t>7814624120</t>
         </is>
       </c>
       <c r="D311" s="13" t="inlineStr"/>
@@ -13303,7 +13279,7 @@
       </c>
       <c r="H311" s="10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>537</t>
         </is>
       </c>
       <c r="I311" s="10" t="inlineStr">
@@ -13313,7 +13289,7 @@
       </c>
       <c r="J311" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13323,16 +13299,20 @@
       </c>
       <c r="B312" s="11" t="inlineStr">
         <is>
-          <t>ООО «СпецТехнологии»</t>
+          <t>ООО «СПбЭК-Майнинг»</t>
         </is>
       </c>
       <c r="C312" s="12" t="inlineStr">
         <is>
-          <t>7839332955</t>
+          <t>7820326027</t>
         </is>
       </c>
       <c r="D312" s="13" t="inlineStr"/>
-      <c r="E312" s="11" t="inlineStr"/>
+      <c r="E312" s="11" t="inlineStr">
+        <is>
+          <t>196605 СПб, Пулковское, Кокколевская ул. 1с1 пом.45-н; ОГРН 1117847356417; ген.дир. Иконников С.В.</t>
+        </is>
+      </c>
       <c r="F312" s="11" t="inlineStr"/>
       <c r="G312" s="11" t="inlineStr">
         <is>
@@ -13341,7 +13321,7 @@
       </c>
       <c r="H312" s="10" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>548</t>
         </is>
       </c>
       <c r="I312" s="10" t="inlineStr">
@@ -13351,7 +13331,7 @@
       </c>
       <c r="J312" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -13361,12 +13341,12 @@
       </c>
       <c r="B313" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецмонтаж»</t>
+          <t>ООО «СТРОИТЕЛЬ»</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>7806403311</t>
+          <t>7804338561</t>
         </is>
       </c>
       <c r="D313" s="13" t="inlineStr"/>
@@ -13379,7 +13359,7 @@
       </c>
       <c r="H313" s="10" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>678</t>
         </is>
       </c>
       <c r="I313" s="10" t="inlineStr">
@@ -13399,12 +13379,12 @@
       </c>
       <c r="B314" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецстрой»</t>
+          <t>ООО «СТРОЙ КОРПУС»</t>
         </is>
       </c>
       <c r="C314" s="12" t="inlineStr">
         <is>
-          <t>7802182340</t>
+          <t>7804553054</t>
         </is>
       </c>
       <c r="D314" s="13" t="inlineStr"/>
@@ -13417,7 +13397,7 @@
       </c>
       <c r="H314" s="10" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>679</t>
         </is>
       </c>
       <c r="I314" s="10" t="inlineStr">
@@ -13427,7 +13407,7 @@
       </c>
       <c r="J314" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13437,20 +13417,16 @@
       </c>
       <c r="B315" s="11" t="inlineStr">
         <is>
-          <t>ООО «Спецстроймонтаж»</t>
+          <t>ООО «СТРОЙГРАД РСУ»</t>
         </is>
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>7826156798</t>
+          <t>7802703995</t>
         </is>
       </c>
       <c r="D315" s="13" t="inlineStr"/>
-      <c r="E315" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
-        </is>
-      </c>
+      <c r="E315" s="11" t="inlineStr"/>
       <c r="F315" s="11" t="inlineStr"/>
       <c r="G315" s="11" t="inlineStr">
         <is>
@@ -13459,7 +13435,7 @@
       </c>
       <c r="H315" s="10" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>877</t>
         </is>
       </c>
       <c r="I315" s="10" t="inlineStr">
@@ -13479,16 +13455,20 @@
       </c>
       <c r="B316" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительная компания «ДМ»</t>
+          <t>ООО «СТРОЙКОМПЛЕКС»</t>
         </is>
       </c>
       <c r="C316" s="12" t="inlineStr">
         <is>
-          <t>4703058442</t>
+          <t>7825055370</t>
         </is>
       </c>
       <c r="D316" s="13" t="inlineStr"/>
-      <c r="E316" s="11" t="inlineStr"/>
+      <c r="E316" s="11" t="inlineStr">
+        <is>
+          <t>198095 СПб, ул.Шкапина 32-34А пом.502,503; ОГРН 1037843028662; ген.дир. Шапошников В.Т.</t>
+        </is>
+      </c>
       <c r="F316" s="11" t="inlineStr"/>
       <c r="G316" s="11" t="inlineStr">
         <is>
@@ -13497,7 +13477,7 @@
       </c>
       <c r="H316" s="10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>573</t>
         </is>
       </c>
       <c r="I316" s="10" t="inlineStr">
@@ -13507,7 +13487,7 @@
       </c>
       <c r="J316" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13497,12 @@
       </c>
       <c r="B317" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительное дело-СГ»</t>
+          <t>ООО «СТРОЙКОНСУЛЬТ»</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>7826005559</t>
+          <t>7810289545</t>
         </is>
       </c>
       <c r="D317" s="13" t="inlineStr"/>
@@ -13535,7 +13515,7 @@
       </c>
       <c r="H317" s="10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>672</t>
         </is>
       </c>
       <c r="I317" s="10" t="inlineStr">
@@ -13545,7 +13525,7 @@
       </c>
       <c r="J317" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13555,16 +13535,20 @@
       </c>
       <c r="B318" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные решения»</t>
+          <t>ООО «СУ-17»</t>
         </is>
       </c>
       <c r="C318" s="12" t="inlineStr">
         <is>
-          <t>7840099703</t>
+          <t>7807028906</t>
         </is>
       </c>
       <c r="D318" s="13" t="inlineStr"/>
-      <c r="E318" s="11" t="inlineStr"/>
+      <c r="E318" s="11" t="inlineStr">
+        <is>
+          <t>195197 СПб, Полюстровский пр. 59Ф оф.388; ОГРН 1027804605069; управляющий Гордиенко Д.Б.</t>
+        </is>
+      </c>
       <c r="F318" s="11" t="inlineStr"/>
       <c r="G318" s="11" t="inlineStr">
         <is>
@@ -13573,7 +13557,7 @@
       </c>
       <c r="H318" s="10" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>747</t>
         </is>
       </c>
       <c r="I318" s="10" t="inlineStr">
@@ -13583,7 +13567,7 @@
       </c>
       <c r="J318" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2300000</t>
         </is>
       </c>
     </row>
@@ -13593,18 +13577,18 @@
       </c>
       <c r="B319" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «СУАР-Групп»</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>7813680179</t>
+          <t>7802270195</t>
         </is>
       </c>
       <c r="D319" s="13" t="inlineStr"/>
       <c r="E319" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
+          <t>192012 СПб, пр.Обуховской Обороны 112к2И пом.204; ОГРН 1157847052956; ген.дир. Мкртчян А.М.</t>
         </is>
       </c>
       <c r="F319" s="11" t="inlineStr"/>
@@ -13615,7 +13599,7 @@
       </c>
       <c r="H319" s="10" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>518</t>
         </is>
       </c>
       <c r="I319" s="10" t="inlineStr">
@@ -13625,7 +13609,7 @@
       </c>
       <c r="J319" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -13635,16 +13619,20 @@
       </c>
       <c r="B320" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительные технологии»</t>
+          <t>ООО «СФ «Новэк»</t>
         </is>
       </c>
       <c r="C320" s="12" t="inlineStr">
         <is>
-          <t>7802880338</t>
+          <t>7825128540</t>
         </is>
       </c>
       <c r="D320" s="13" t="inlineStr"/>
-      <c r="E320" s="11" t="inlineStr"/>
+      <c r="E320" s="11" t="inlineStr">
+        <is>
+          <t>194352 СПб, ул.Кустодиева 17А; ОГРН 1027809227907; ген.дир. Смирнов Д.И.</t>
+        </is>
+      </c>
       <c r="F320" s="11" t="inlineStr"/>
       <c r="G320" s="11" t="inlineStr">
         <is>
@@ -13653,7 +13641,7 @@
       </c>
       <c r="H320" s="10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>512</t>
         </is>
       </c>
       <c r="I320" s="10" t="inlineStr">
@@ -13673,25 +13661,29 @@
       </c>
       <c r="B321" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строительный Цех»</t>
+          <t>ООО «СЭМ»</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>7842391502</t>
+          <t>7810201646</t>
         </is>
       </c>
       <c r="D321" s="13" t="inlineStr"/>
-      <c r="E321" s="11" t="inlineStr"/>
+      <c r="E321" s="11" t="inlineStr">
+        <is>
+          <t>СПб, наб.Обводного канала 199-201Ф пом.409Н; ОГРН 1027804903070; ген.дир. Мартынов А.Н.</t>
+        </is>
+      </c>
       <c r="F321" s="11" t="inlineStr"/>
       <c r="G321" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H321" s="10" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>700</t>
         </is>
       </c>
       <c r="I321" s="10" t="inlineStr">
@@ -13701,7 +13693,7 @@
       </c>
       <c r="J321" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -13711,29 +13703,25 @@
       </c>
       <c r="B322" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй центр»</t>
+          <t>ООО «Свой Дом»</t>
         </is>
       </c>
       <c r="C322" s="12" t="inlineStr">
         <is>
-          <t>7804538240</t>
+          <t>7813322254</t>
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr"/>
-      <c r="E322" s="11" t="inlineStr">
-        <is>
-          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
-        </is>
-      </c>
+      <c r="E322" s="11" t="inlineStr"/>
       <c r="F322" s="11" t="inlineStr"/>
       <c r="G322" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H322" s="10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>591</t>
         </is>
       </c>
       <c r="I322" s="10" t="inlineStr">
@@ -13743,7 +13731,7 @@
       </c>
       <c r="J322" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13753,25 +13741,29 @@
       </c>
       <c r="B323" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй-Импульс»</t>
+          <t>ООО «СиФ»</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
         <is>
-          <t>7806313724</t>
+          <t>7801075307</t>
         </is>
       </c>
       <c r="D323" s="13" t="inlineStr"/>
-      <c r="E323" s="11" t="inlineStr"/>
+      <c r="E323" s="11" t="inlineStr">
+        <is>
+          <t>193091 СПб, Октябрьская наб. 6; ОГРН 1027800558170; ген.дир. Левин А.Ю.; заказчик-застройщик/генподряд</t>
+        </is>
+      </c>
       <c r="F323" s="11" t="inlineStr"/>
       <c r="G323" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H323" s="10" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I323" s="10" t="inlineStr">
@@ -13791,12 +13783,12 @@
       </c>
       <c r="B324" s="11" t="inlineStr">
         <is>
-          <t>ООО «Строй-С»</t>
+          <t>ООО «СиЭсБиАй АйТи-Сервис»</t>
         </is>
       </c>
       <c r="C324" s="12" t="inlineStr">
         <is>
-          <t>7802373183</t>
+          <t>7810691246</t>
         </is>
       </c>
       <c r="D324" s="13" t="inlineStr"/>
@@ -13809,7 +13801,7 @@
       </c>
       <c r="H324" s="10" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>588</t>
         </is>
       </c>
       <c r="I324" s="10" t="inlineStr">
@@ -13829,12 +13821,12 @@
       </c>
       <c r="B325" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройГрад»</t>
+          <t>ООО «Синергия»</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>7813692632</t>
+          <t>7841100278</t>
         </is>
       </c>
       <c r="D325" s="13" t="inlineStr"/>
@@ -13847,7 +13839,7 @@
       </c>
       <c r="H325" s="10" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="I325" s="10" t="inlineStr">
@@ -13857,7 +13849,7 @@
       </c>
       <c r="J325" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -13867,25 +13859,29 @@
       </c>
       <c r="B326" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройКом»</t>
+          <t>ООО «СносСтройИнвест»</t>
         </is>
       </c>
       <c r="C326" s="12" t="inlineStr">
         <is>
-          <t>7811469780</t>
+          <t>7805239355</t>
         </is>
       </c>
       <c r="D326" s="13" t="inlineStr"/>
-      <c r="E326" s="11" t="inlineStr"/>
+      <c r="E326" s="11" t="inlineStr">
+        <is>
+          <t>СПб, пр.Народного Ополчения 10А оф.26,31; ОГРН 1027802725554; ген.дир. Герилович С.П.; снос зданий</t>
+        </is>
+      </c>
       <c r="F326" s="11" t="inlineStr"/>
       <c r="G326" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H326" s="10" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>351</t>
         </is>
       </c>
       <c r="I326" s="10" t="inlineStr">
@@ -13905,12 +13901,12 @@
       </c>
       <c r="B327" s="11" t="inlineStr">
         <is>
-          <t>ООО «СтройПроект»</t>
+          <t>ООО «СпецСтрой»</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>7804554072</t>
+          <t>7802753883</t>
         </is>
       </c>
       <c r="D327" s="13" t="inlineStr"/>
@@ -13923,7 +13919,7 @@
       </c>
       <c r="H327" s="10" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>267</t>
         </is>
       </c>
       <c r="I327" s="10" t="inlineStr">
@@ -13943,12 +13939,12 @@
       </c>
       <c r="B328" s="11" t="inlineStr">
         <is>
-          <t>ООО «Стройперспектива»</t>
+          <t>ООО «СпецТехнологии»</t>
         </is>
       </c>
       <c r="C328" s="12" t="inlineStr">
         <is>
-          <t>7810740278</t>
+          <t>7839332955</t>
         </is>
       </c>
       <c r="D328" s="13" t="inlineStr"/>
@@ -13961,7 +13957,7 @@
       </c>
       <c r="H328" s="10" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>680</t>
         </is>
       </c>
       <c r="I328" s="10" t="inlineStr">
@@ -13971,7 +13967,7 @@
       </c>
       <c r="J328" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -13981,12 +13977,12 @@
       </c>
       <c r="B329" s="11" t="inlineStr">
         <is>
-          <t>ООО «СулуС»</t>
+          <t>ООО «Спецмонтаж»</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>7801369120</t>
+          <t>7806403311</t>
         </is>
       </c>
       <c r="D329" s="13" t="inlineStr"/>
@@ -13999,7 +13995,7 @@
       </c>
       <c r="H329" s="10" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>526</t>
         </is>
       </c>
       <c r="I329" s="10" t="inlineStr">
@@ -14009,7 +14005,7 @@
       </c>
       <c r="J329" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -14019,20 +14015,16 @@
       </c>
       <c r="B330" s="11" t="inlineStr">
         <is>
-          <t>ООО «Сфера»</t>
+          <t>ООО «Спецстрой»</t>
         </is>
       </c>
       <c r="C330" s="12" t="inlineStr">
         <is>
-          <t>2311308786</t>
+          <t>7802182340</t>
         </is>
       </c>
       <c r="D330" s="13" t="inlineStr"/>
-      <c r="E330" s="11" t="inlineStr">
-        <is>
-          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
-        </is>
-      </c>
+      <c r="E330" s="11" t="inlineStr"/>
       <c r="F330" s="11" t="inlineStr"/>
       <c r="G330" s="11" t="inlineStr">
         <is>
@@ -14041,7 +14033,7 @@
       </c>
       <c r="H330" s="10" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>521</t>
         </is>
       </c>
       <c r="I330" s="10" t="inlineStr">
@@ -14051,7 +14043,7 @@
       </c>
       <c r="J330" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -14061,18 +14053,18 @@
       </c>
       <c r="B331" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТАЛИОН»</t>
+          <t>ООО «Спецстроймонтаж»</t>
         </is>
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>7801569190</t>
+          <t>7826156798</t>
         </is>
       </c>
       <c r="D331" s="13" t="inlineStr"/>
       <c r="E331" s="11" t="inlineStr">
         <is>
-          <t>197229 СПб, ул.Новая 51к1 пом.7-Н; ОГРН 1127847128639; ген.дир. Марков А.А.; техконтроль/испытания</t>
+          <t>СПб, ул.Володи Ермака 17А пом.2-н; ОГРН 1027810307315; ген.дир. Свиженко В.С.; снос зданий</t>
         </is>
       </c>
       <c r="F331" s="11" t="inlineStr"/>
@@ -14083,7 +14075,7 @@
       </c>
       <c r="H331" s="10" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>505</t>
         </is>
       </c>
       <c r="I331" s="10" t="inlineStr">
@@ -14103,12 +14095,12 @@
       </c>
       <c r="B332" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТД «Буревестник»</t>
+          <t>ООО «Строительная компания «ДМ»</t>
         </is>
       </c>
       <c r="C332" s="12" t="inlineStr">
         <is>
-          <t>4705075034</t>
+          <t>4703058442</t>
         </is>
       </c>
       <c r="D332" s="13" t="inlineStr"/>
@@ -14121,7 +14113,7 @@
       </c>
       <c r="H332" s="10" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>252</t>
         </is>
       </c>
       <c r="I332" s="10" t="inlineStr">
@@ -14141,29 +14133,25 @@
       </c>
       <c r="B333" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕЗИС»</t>
+          <t>ООО «Строительное дело-СГ»</t>
         </is>
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>7804441209</t>
+          <t>7826005559</t>
         </is>
       </c>
       <c r="D333" s="13" t="inlineStr"/>
-      <c r="E333" s="11" t="inlineStr">
-        <is>
-          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
-        </is>
-      </c>
+      <c r="E333" s="11" t="inlineStr"/>
       <c r="F333" s="11" t="inlineStr"/>
       <c r="G333" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H333" s="10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>242</t>
         </is>
       </c>
       <c r="I333" s="10" t="inlineStr">
@@ -14173,7 +14161,7 @@
       </c>
       <c r="J333" s="10" t="inlineStr">
         <is>
-          <t>700000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14183,12 +14171,12 @@
       </c>
       <c r="B334" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЕХНОТРАНССТРОЙ»</t>
+          <t>ООО «Строительные решения»</t>
         </is>
       </c>
       <c r="C334" s="12" t="inlineStr">
         <is>
-          <t>5190067514</t>
+          <t>7840099703</t>
         </is>
       </c>
       <c r="D334" s="13" t="inlineStr"/>
@@ -14201,7 +14189,7 @@
       </c>
       <c r="H334" s="10" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="I334" s="10" t="inlineStr">
@@ -14221,18 +14209,18 @@
       </c>
       <c r="B335" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТК-ЭнергоСтрой»</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C335" s="12" t="inlineStr">
         <is>
-          <t>7814612968</t>
+          <t>7813680179</t>
         </is>
       </c>
       <c r="D335" s="13" t="inlineStr"/>
       <c r="E335" s="11" t="inlineStr">
         <is>
-          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+          <t>СПб, ул.Воскова 8/5А пом.8-Н; ОГРН 1247800052917; рег. 28.05.2024</t>
         </is>
       </c>
       <c r="F335" s="11" t="inlineStr"/>
@@ -14243,7 +14231,7 @@
       </c>
       <c r="H335" s="10" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="I335" s="10" t="inlineStr">
@@ -14263,12 +14251,12 @@
       </c>
       <c r="B336" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТМС»</t>
+          <t>ООО «Строительные технологии»</t>
         </is>
       </c>
       <c r="C336" s="12" t="inlineStr">
         <is>
-          <t>7801629643</t>
+          <t>7802880338</t>
         </is>
       </c>
       <c r="D336" s="13" t="inlineStr"/>
@@ -14281,7 +14269,7 @@
       </c>
       <c r="H336" s="10" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>239</t>
         </is>
       </c>
       <c r="I336" s="10" t="inlineStr">
@@ -14301,12 +14289,12 @@
       </c>
       <c r="B337" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТСК «ОЛИМП»</t>
+          <t>ООО «Строительный Цех»</t>
         </is>
       </c>
       <c r="C337" s="12" t="inlineStr">
         <is>
-          <t>4205310949</t>
+          <t>7842391502</t>
         </is>
       </c>
       <c r="D337" s="13" t="inlineStr"/>
@@ -14319,7 +14307,7 @@
       </c>
       <c r="H337" s="10" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>554</t>
         </is>
       </c>
       <c r="I337" s="10" t="inlineStr">
@@ -14329,7 +14317,7 @@
       </c>
       <c r="J337" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -14339,29 +14327,29 @@
       </c>
       <c r="B338" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
+          <t>ООО «Строй центр»</t>
         </is>
       </c>
       <c r="C338" s="12" t="inlineStr">
         <is>
-          <t>7839061021</t>
+          <t>7804538240</t>
         </is>
       </c>
       <c r="D338" s="13" t="inlineStr"/>
       <c r="E338" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+          <t>195009 СПб, ул.Бобруйская 7с1 пом.72 1Н; ОГРН 1147847273650; ген.дир. Прокопец В.П.</t>
         </is>
       </c>
       <c r="F338" s="11" t="inlineStr"/>
       <c r="G338" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H338" s="10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>732</t>
         </is>
       </c>
       <c r="I338" s="10" t="inlineStr">
@@ -14371,7 +14359,7 @@
       </c>
       <c r="J338" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -14381,12 +14369,12 @@
       </c>
       <c r="B339" s="11" t="inlineStr">
         <is>
-          <t>ООО «Текманн»</t>
+          <t>ООО «Строй-Импульс»</t>
         </is>
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
-          <t>7842508750</t>
+          <t>7806313724</t>
         </is>
       </c>
       <c r="D339" s="13" t="inlineStr"/>
@@ -14399,7 +14387,7 @@
       </c>
       <c r="H339" s="10" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="I339" s="10" t="inlineStr">
@@ -14419,12 +14407,12 @@
       </c>
       <c r="B340" s="11" t="inlineStr">
         <is>
-          <t>ООО «ТехЭнерго»</t>
+          <t>ООО «Строй-С»</t>
         </is>
       </c>
       <c r="C340" s="12" t="inlineStr">
         <is>
-          <t>7816531513</t>
+          <t>7802373183</t>
         </is>
       </c>
       <c r="D340" s="13" t="inlineStr"/>
@@ -14437,7 +14425,7 @@
       </c>
       <c r="H340" s="10" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>599</t>
         </is>
       </c>
       <c r="I340" s="10" t="inlineStr">
@@ -14447,7 +14435,7 @@
       </c>
       <c r="J340" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14457,12 +14445,12 @@
       </c>
       <c r="B341" s="11" t="inlineStr">
         <is>
-          <t>ООО «Технические Системы»</t>
+          <t>ООО «СтройГрад»</t>
         </is>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>7807345648</t>
+          <t>7813692632</t>
         </is>
       </c>
       <c r="D341" s="13" t="inlineStr"/>
@@ -14475,7 +14463,7 @@
       </c>
       <c r="H341" s="10" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="I341" s="10" t="inlineStr">
@@ -14485,7 +14473,7 @@
       </c>
       <c r="J341" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -14495,12 +14483,12 @@
       </c>
       <c r="B342" s="11" t="inlineStr">
         <is>
-          <t>ООО «Техно Эйр Групп»</t>
+          <t>ООО «СтройКом»</t>
         </is>
       </c>
       <c r="C342" s="12" t="inlineStr">
         <is>
-          <t>7816594954</t>
+          <t>7811469780</t>
         </is>
       </c>
       <c r="D342" s="13" t="inlineStr"/>
@@ -14513,7 +14501,7 @@
       </c>
       <c r="H342" s="10" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>602</t>
         </is>
       </c>
       <c r="I342" s="10" t="inlineStr">
@@ -14533,20 +14521,16 @@
       </c>
       <c r="B343" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трамплин-строй»</t>
+          <t>ООО «СтройПроект»</t>
         </is>
       </c>
       <c r="C343" s="12" t="inlineStr">
         <is>
-          <t>7802207193</t>
+          <t>7804554072</t>
         </is>
       </c>
       <c r="D343" s="13" t="inlineStr"/>
-      <c r="E343" s="11" t="inlineStr">
-        <is>
-          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
-        </is>
-      </c>
+      <c r="E343" s="11" t="inlineStr"/>
       <c r="F343" s="11" t="inlineStr"/>
       <c r="G343" s="11" t="inlineStr">
         <is>
@@ -14555,7 +14539,7 @@
       </c>
       <c r="H343" s="10" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>291</t>
         </is>
       </c>
       <c r="I343" s="10" t="inlineStr">
@@ -14565,7 +14549,7 @@
       </c>
       <c r="J343" s="10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14575,20 +14559,16 @@
       </c>
       <c r="B344" s="11" t="inlineStr">
         <is>
-          <t>ООО «Трест «Сантехмонтаж-1»</t>
+          <t>ООО «Стройперспектива»</t>
         </is>
       </c>
       <c r="C344" s="12" t="inlineStr">
         <is>
-          <t>4706050882</t>
+          <t>7810740278</t>
         </is>
       </c>
       <c r="D344" s="13" t="inlineStr"/>
-      <c r="E344" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Мытнинская 12/44А пом.13н оф.14; ОГРН 1224700013230; сантехмонтаж, вентиляция, ИТП</t>
-        </is>
-      </c>
+      <c r="E344" s="11" t="inlineStr"/>
       <c r="F344" s="11" t="inlineStr"/>
       <c r="G344" s="11" t="inlineStr">
         <is>
@@ -14597,7 +14577,7 @@
       </c>
       <c r="H344" s="10" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>932</t>
         </is>
       </c>
       <c r="I344" s="10" t="inlineStr">
@@ -14617,20 +14597,16 @@
       </c>
       <c r="B345" s="11" t="inlineStr">
         <is>
-          <t>ООО «УМ «Эталон»</t>
+          <t>ООО «СулуС»</t>
         </is>
       </c>
       <c r="C345" s="12" t="inlineStr">
         <is>
-          <t>7810048170</t>
+          <t>7801369120</t>
         </is>
       </c>
       <c r="D345" s="13" t="inlineStr"/>
-      <c r="E345" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Богатырский пр. 2А каб.0.09; ОГРН 1057813303767; ген.дир. Харитонов О.В.; башенные краны; УК 463 млн</t>
-        </is>
-      </c>
+      <c r="E345" s="11" t="inlineStr"/>
       <c r="F345" s="11" t="inlineStr"/>
       <c r="G345" s="11" t="inlineStr">
         <is>
@@ -14639,7 +14615,7 @@
       </c>
       <c r="H345" s="10" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>754</t>
         </is>
       </c>
       <c r="I345" s="10" t="inlineStr">
@@ -14649,7 +14625,7 @@
       </c>
       <c r="J345" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14659,16 +14635,20 @@
       </c>
       <c r="B346" s="11" t="inlineStr">
         <is>
-          <t>ООО «УМ-11»</t>
+          <t>ООО «Сфера»</t>
         </is>
       </c>
       <c r="C346" s="12" t="inlineStr">
         <is>
-          <t>7805802232</t>
+          <t>2311308786</t>
         </is>
       </c>
       <c r="D346" s="13" t="inlineStr"/>
-      <c r="E346" s="11" t="inlineStr"/>
+      <c r="E346" s="11" t="inlineStr">
+        <is>
+          <t>199106 СПб, 26-я линия В.О. 5к4Д оф.106/1; ОГРН 1202300046277; ген.дир. Дубс В.И.</t>
+        </is>
+      </c>
       <c r="F346" s="11" t="inlineStr"/>
       <c r="G346" s="11" t="inlineStr">
         <is>
@@ -14677,7 +14657,7 @@
       </c>
       <c r="H346" s="10" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="I346" s="10" t="inlineStr">
@@ -14687,7 +14667,7 @@
       </c>
       <c r="J346" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -14697,16 +14677,20 @@
       </c>
       <c r="B347" s="11" t="inlineStr">
         <is>
-          <t>ООО «УСН»</t>
+          <t>ООО «ТАЛИОН»</t>
         </is>
       </c>
       <c r="C347" s="12" t="inlineStr">
         <is>
-          <t>7819306040</t>
+          <t>7801569190</t>
         </is>
       </c>
       <c r="D347" s="13" t="inlineStr"/>
-      <c r="E347" s="11" t="inlineStr"/>
+      <c r="E347" s="11" t="inlineStr">
+        <is>
+          <t>197229 СПб, ул.Новая 51к1 пом.7-Н; ОГРН 1127847128639; ген.дир. Марков А.А.; техконтроль/испытания</t>
+        </is>
+      </c>
       <c r="F347" s="11" t="inlineStr"/>
       <c r="G347" s="11" t="inlineStr">
         <is>
@@ -14715,7 +14699,7 @@
       </c>
       <c r="H347" s="10" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="I347" s="10" t="inlineStr">
@@ -14735,12 +14719,12 @@
       </c>
       <c r="B348" s="11" t="inlineStr">
         <is>
-          <t>ООО «Универсалстрой»</t>
+          <t>ООО «ТД «Буревестник»</t>
         </is>
       </c>
       <c r="C348" s="12" t="inlineStr">
         <is>
-          <t>7801227091</t>
+          <t>4705075034</t>
         </is>
       </c>
       <c r="D348" s="13" t="inlineStr"/>
@@ -14753,7 +14737,7 @@
       </c>
       <c r="H348" s="10" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="I348" s="10" t="inlineStr">
@@ -14773,25 +14757,29 @@
       </c>
       <c r="B349" s="11" t="inlineStr">
         <is>
-          <t>ООО «ФОРЕСТ ДОРС»</t>
+          <t>ООО «ТЕЗИС»</t>
         </is>
       </c>
       <c r="C349" s="12" t="inlineStr">
         <is>
-          <t>7820045700</t>
+          <t>7804441209</t>
         </is>
       </c>
       <c r="D349" s="13" t="inlineStr"/>
-      <c r="E349" s="11" t="inlineStr"/>
+      <c r="E349" s="11" t="inlineStr">
+        <is>
+          <t>195067 СПб, ул.Маршала Тухачевского 22А оф.315; ОГРН 1107847212472; ген.дир. Илюшин А.К.</t>
+        </is>
+      </c>
       <c r="F349" s="11" t="inlineStr"/>
       <c r="G349" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H349" s="10" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>674</t>
         </is>
       </c>
       <c r="I349" s="10" t="inlineStr">
@@ -14801,7 +14789,7 @@
       </c>
       <c r="J349" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>700000</t>
         </is>
       </c>
     </row>
@@ -14811,12 +14799,12 @@
       </c>
       <c r="B350" s="11" t="inlineStr">
         <is>
-          <t>ООО «ФОРТИС»</t>
+          <t>ООО «ТЕХНОТРАНССТРОЙ»</t>
         </is>
       </c>
       <c r="C350" s="12" t="inlineStr">
         <is>
-          <t>7817119800</t>
+          <t>5190067514</t>
         </is>
       </c>
       <c r="D350" s="13" t="inlineStr"/>
@@ -14829,7 +14817,7 @@
       </c>
       <c r="H350" s="10" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>787</t>
         </is>
       </c>
       <c r="I350" s="10" t="inlineStr">
@@ -14849,16 +14837,20 @@
       </c>
       <c r="B351" s="11" t="inlineStr">
         <is>
-          <t>ООО «Холодпроф»</t>
+          <t>ООО «ТК-ЭнергоСтрой»</t>
         </is>
       </c>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>7842418360</t>
+          <t>7814612968</t>
         </is>
       </c>
       <c r="D351" s="13" t="inlineStr"/>
-      <c r="E351" s="11" t="inlineStr"/>
+      <c r="E351" s="11" t="inlineStr">
+        <is>
+          <t>195112 СПб, пл.Карла Фаберже 8А пом.8-н; ОГРН 1147847188609; ген.дир. Кучерской А.А.</t>
+        </is>
+      </c>
       <c r="F351" s="11" t="inlineStr"/>
       <c r="G351" s="11" t="inlineStr">
         <is>
@@ -14867,7 +14859,7 @@
       </c>
       <c r="H351" s="10" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>335</t>
         </is>
       </c>
       <c r="I351" s="10" t="inlineStr">
@@ -14877,7 +14869,7 @@
       </c>
       <c r="J351" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -14887,20 +14879,16 @@
       </c>
       <c r="B352" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+          <t>ООО «ТМС»</t>
         </is>
       </c>
       <c r="C352" s="12" t="inlineStr">
         <is>
-          <t>7820055440</t>
+          <t>7801629643</t>
         </is>
       </c>
       <c r="D352" s="13" t="inlineStr"/>
-      <c r="E352" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
-        </is>
-      </c>
+      <c r="E352" s="11" t="inlineStr"/>
       <c r="F352" s="11" t="inlineStr"/>
       <c r="G352" s="11" t="inlineStr">
         <is>
@@ -14909,7 +14897,7 @@
       </c>
       <c r="H352" s="10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I352" s="10" t="inlineStr">
@@ -14919,7 +14907,7 @@
       </c>
       <c r="J352" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -14929,12 +14917,12 @@
       </c>
       <c r="B353" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦИКЛОН»</t>
+          <t>ООО «ТСК «ОЛИМП»</t>
         </is>
       </c>
       <c r="C353" s="12" t="inlineStr">
         <is>
-          <t>7801225591</t>
+          <t>4205310949</t>
         </is>
       </c>
       <c r="D353" s="13" t="inlineStr"/>
@@ -14947,7 +14935,7 @@
       </c>
       <c r="H353" s="10" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>244</t>
         </is>
       </c>
       <c r="I353" s="10" t="inlineStr">
@@ -14967,16 +14955,20 @@
       </c>
       <c r="B354" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЦИТАДЕЛЬ»</t>
+          <t>ООО «ТЭС И» (ТЭС Инновации)</t>
         </is>
       </c>
       <c r="C354" s="12" t="inlineStr">
         <is>
-          <t>7817122190</t>
+          <t>7839061021</t>
         </is>
       </c>
       <c r="D354" s="13" t="inlineStr"/>
-      <c r="E354" s="11" t="inlineStr"/>
+      <c r="E354" s="11" t="inlineStr">
+        <is>
+          <t>190005 СПб, наб.Обводного канала 118аЖ оф.12; ОГРН 1167847142341; ген.дир. Николаев И.А.</t>
+        </is>
+      </c>
       <c r="F354" s="11" t="inlineStr"/>
       <c r="G354" s="11" t="inlineStr">
         <is>
@@ -14985,7 +14977,7 @@
       </c>
       <c r="H354" s="10" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I354" s="10" t="inlineStr">
@@ -14995,7 +14987,7 @@
       </c>
       <c r="J354" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -15005,20 +14997,16 @@
       </c>
       <c r="B355" s="11" t="inlineStr">
         <is>
-          <t>ООО «Центр-Инвест-Строй»</t>
+          <t>ООО «Текманн»</t>
         </is>
       </c>
       <c r="C355" s="12" t="inlineStr">
         <is>
-          <t>7825483746</t>
+          <t>7842508750</t>
         </is>
       </c>
       <c r="D355" s="13" t="inlineStr"/>
-      <c r="E355" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
-        </is>
-      </c>
+      <c r="E355" s="11" t="inlineStr"/>
       <c r="F355" s="11" t="inlineStr"/>
       <c r="G355" s="11" t="inlineStr">
         <is>
@@ -15027,7 +15015,7 @@
       </c>
       <c r="H355" s="10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>694</t>
         </is>
       </c>
       <c r="I355" s="10" t="inlineStr">
@@ -15037,7 +15025,7 @@
       </c>
       <c r="J355" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -15047,29 +15035,25 @@
       </c>
       <c r="B356" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергетическое Строительство»</t>
+          <t>ООО «ТехЭнерго»</t>
         </is>
       </c>
       <c r="C356" s="12" t="inlineStr">
         <is>
-          <t>7813548237</t>
+          <t>7816531513</t>
         </is>
       </c>
       <c r="D356" s="13" t="inlineStr"/>
-      <c r="E356" s="11" t="inlineStr">
-        <is>
-          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
-        </is>
-      </c>
+      <c r="E356" s="11" t="inlineStr"/>
       <c r="F356" s="11" t="inlineStr"/>
       <c r="G356" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H356" s="10" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I356" s="10" t="inlineStr">
@@ -15079,7 +15063,7 @@
       </c>
       <c r="J356" s="10" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -15089,12 +15073,12 @@
       </c>
       <c r="B357" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энерго Альянс»</t>
+          <t>ООО «Технические Системы»</t>
         </is>
       </c>
       <c r="C357" s="12" t="inlineStr">
         <is>
-          <t>7813579997</t>
+          <t>7807345648</t>
         </is>
       </c>
       <c r="D357" s="13" t="inlineStr"/>
@@ -15107,7 +15091,7 @@
       </c>
       <c r="H357" s="10" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>511</t>
         </is>
       </c>
       <c r="I357" s="10" t="inlineStr">
@@ -15127,12 +15111,12 @@
       </c>
       <c r="B358" s="11" t="inlineStr">
         <is>
-          <t>ООО «ЭнергоИнвест»</t>
+          <t>ООО «Техно Эйр Групп»</t>
         </is>
       </c>
       <c r="C358" s="12" t="inlineStr">
         <is>
-          <t>7841378040</t>
+          <t>7816594954</t>
         </is>
       </c>
       <c r="D358" s="13" t="inlineStr"/>
@@ -15145,7 +15129,7 @@
       </c>
       <c r="H358" s="10" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>661</t>
         </is>
       </c>
       <c r="I358" s="10" t="inlineStr">
@@ -15165,18 +15149,18 @@
       </c>
       <c r="B359" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергоком»</t>
+          <t>ООО «Трамплин-строй»</t>
         </is>
       </c>
       <c r="C359" s="12" t="inlineStr">
         <is>
-          <t>7841367514</t>
+          <t>7802207193</t>
         </is>
       </c>
       <c r="D359" s="13" t="inlineStr"/>
       <c r="E359" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+          <t>СПб, пр.Энгельса 33к1А пом.1-Н оф.307; ОГРН 1037804033211; ген.дир. Груздев Т.В.</t>
         </is>
       </c>
       <c r="F359" s="11" t="inlineStr"/>
@@ -15187,7 +15171,7 @@
       </c>
       <c r="H359" s="10" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>726</t>
         </is>
       </c>
       <c r="I359" s="10" t="inlineStr">
@@ -15197,7 +15181,7 @@
       </c>
       <c r="J359" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
@@ -15207,18 +15191,18 @@
       </c>
       <c r="B360" s="11" t="inlineStr">
         <is>
-          <t>ООО «Энергосервис»</t>
+          <t>ООО «Трест «Сантехмонтаж-1»</t>
         </is>
       </c>
       <c r="C360" s="12" t="inlineStr">
         <is>
-          <t>7811004224</t>
+          <t>4706050882</t>
         </is>
       </c>
       <c r="D360" s="13" t="inlineStr"/>
       <c r="E360" s="11" t="inlineStr">
         <is>
-          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+          <t>СПб, ул.Мытнинская 12/44А пом.13н оф.14; ОГРН 1224700013230; сантехмонтаж, вентиляция, ИТП</t>
         </is>
       </c>
       <c r="F360" s="11" t="inlineStr"/>
@@ -15229,7 +15213,7 @@
       </c>
       <c r="H360" s="10" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="I360" s="10" t="inlineStr">
@@ -15239,7 +15223,7 @@
       </c>
       <c r="J360" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -15249,29 +15233,29 @@
       </c>
       <c r="B361" s="11" t="inlineStr">
         <is>
-          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+          <t>ООО «УМ «Эталон»</t>
         </is>
       </c>
       <c r="C361" s="12" t="inlineStr">
         <is>
-          <t>7810721927</t>
+          <t>7810048170</t>
         </is>
       </c>
       <c r="D361" s="13" t="inlineStr"/>
       <c r="E361" s="11" t="inlineStr">
         <is>
-          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+          <t>СПб, Богатырский пр. 2А каб.0.09; ОГРН 1057813303767; ген.дир. Харитонов О.В.; башенные краны; УК 463 млн</t>
         </is>
       </c>
       <c r="F361" s="11" t="inlineStr"/>
       <c r="G361" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H361" s="10" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>701</t>
         </is>
       </c>
       <c r="I361" s="10" t="inlineStr">
@@ -15281,7 +15265,7 @@
       </c>
       <c r="J361" s="10" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -15291,12 +15275,12 @@
       </c>
       <c r="B362" s="11" t="inlineStr">
         <is>
-          <t>ООО ПСМ «Спутник»</t>
+          <t>ООО «УМ-11»</t>
         </is>
       </c>
       <c r="C362" s="12" t="inlineStr">
         <is>
-          <t>7810765071</t>
+          <t>7805802232</t>
         </is>
       </c>
       <c r="D362" s="13" t="inlineStr"/>
@@ -15309,7 +15293,7 @@
       </c>
       <c r="H362" s="10" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="I362" s="10" t="inlineStr">
@@ -15329,12 +15313,12 @@
       </c>
       <c r="B363" s="11" t="inlineStr">
         <is>
-          <t>ООО СК «Аврора-Строй»</t>
+          <t>ООО «УСН»</t>
         </is>
       </c>
       <c r="C363" s="12" t="inlineStr">
         <is>
-          <t>7801700173</t>
+          <t>7819306040</t>
         </is>
       </c>
       <c r="D363" s="13" t="inlineStr"/>
@@ -15347,22 +15331,654 @@
       </c>
       <c r="H363" s="10" t="inlineStr">
         <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="I363" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J363" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="10" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Универсалстрой»</t>
+        </is>
+      </c>
+      <c r="C364" s="12" t="inlineStr">
+        <is>
+          <t>7801227091</t>
+        </is>
+      </c>
+      <c r="D364" s="13" t="inlineStr"/>
+      <c r="E364" s="11" t="inlineStr"/>
+      <c r="F364" s="11" t="inlineStr"/>
+      <c r="G364" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H364" s="10" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="I364" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J364" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="10" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ФОРЕСТ ДОРС»</t>
+        </is>
+      </c>
+      <c r="C365" s="12" t="inlineStr">
+        <is>
+          <t>7820045700</t>
+        </is>
+      </c>
+      <c r="D365" s="13" t="inlineStr"/>
+      <c r="E365" s="11" t="inlineStr"/>
+      <c r="F365" s="11" t="inlineStr"/>
+      <c r="G365" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H365" s="10" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="I365" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J365" s="10" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="10" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ФОРТИС»</t>
+        </is>
+      </c>
+      <c r="C366" s="12" t="inlineStr">
+        <is>
+          <t>7817119800</t>
+        </is>
+      </c>
+      <c r="D366" s="13" t="inlineStr"/>
+      <c r="E366" s="11" t="inlineStr"/>
+      <c r="F366" s="11" t="inlineStr"/>
+      <c r="G366" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H366" s="10" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="I366" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J366" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="10" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Холодпроф»</t>
+        </is>
+      </c>
+      <c r="C367" s="12" t="inlineStr">
+        <is>
+          <t>7842418360</t>
+        </is>
+      </c>
+      <c r="D367" s="13" t="inlineStr"/>
+      <c r="E367" s="11" t="inlineStr"/>
+      <c r="F367" s="11" t="inlineStr"/>
+      <c r="G367" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H367" s="10" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="I367" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J367" s="10" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="10" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦДКИ» (Центр диагностики комплексной инфраструктуры)</t>
+        </is>
+      </c>
+      <c r="C368" s="12" t="inlineStr">
+        <is>
+          <t>7820055440</t>
+        </is>
+      </c>
+      <c r="D368" s="13" t="inlineStr"/>
+      <c r="E368" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Шушары, ул.Ростовская 6к4А кв.56; ОГРН 1167847454158; ген.дир. Гетманский С.А.</t>
+        </is>
+      </c>
+      <c r="F368" s="11" t="inlineStr"/>
+      <c r="G368" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H368" s="10" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="I368" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J368" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="10" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦИКЛОН»</t>
+        </is>
+      </c>
+      <c r="C369" s="12" t="inlineStr">
+        <is>
+          <t>7801225591</t>
+        </is>
+      </c>
+      <c r="D369" s="13" t="inlineStr"/>
+      <c r="E369" s="11" t="inlineStr"/>
+      <c r="F369" s="11" t="inlineStr"/>
+      <c r="G369" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H369" s="10" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="I369" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J369" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="10" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЦИТАДЕЛЬ»</t>
+        </is>
+      </c>
+      <c r="C370" s="12" t="inlineStr">
+        <is>
+          <t>7817122190</t>
+        </is>
+      </c>
+      <c r="D370" s="13" t="inlineStr"/>
+      <c r="E370" s="11" t="inlineStr"/>
+      <c r="F370" s="11" t="inlineStr"/>
+      <c r="G370" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H370" s="10" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="I370" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J370" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="10" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Центр-Инвест-Строй»</t>
+        </is>
+      </c>
+      <c r="C371" s="12" t="inlineStr">
+        <is>
+          <t>7825483746</t>
+        </is>
+      </c>
+      <c r="D371" s="13" t="inlineStr"/>
+      <c r="E371" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Невский пр. 117Б пом.6-н/7-н; ОГРН 1027809184798; ген.дир. Богуцкий А.А.</t>
+        </is>
+      </c>
+      <c r="F371" s="11" t="inlineStr"/>
+      <c r="G371" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H371" s="10" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="I371" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J371" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="10" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергетическое Строительство»</t>
+        </is>
+      </c>
+      <c r="C372" s="12" t="inlineStr">
+        <is>
+          <t>7813548237</t>
+        </is>
+      </c>
+      <c r="D372" s="13" t="inlineStr"/>
+      <c r="E372" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ул.Кропоткина 1И; ОГРН 1127847599439; ген.дир. Котельников И.Л.</t>
+        </is>
+      </c>
+      <c r="F372" s="11" t="inlineStr"/>
+      <c r="G372" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H372" s="10" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="I372" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J372" s="10" t="inlineStr">
+        <is>
+          <t>5000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="10" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энерго Альянс»</t>
+        </is>
+      </c>
+      <c r="C373" s="12" t="inlineStr">
+        <is>
+          <t>7813579997</t>
+        </is>
+      </c>
+      <c r="D373" s="13" t="inlineStr"/>
+      <c r="E373" s="11" t="inlineStr"/>
+      <c r="F373" s="11" t="inlineStr"/>
+      <c r="G373" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H373" s="10" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="I373" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J373" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="10" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="11" t="inlineStr">
+        <is>
+          <t>ООО «ЭнергоИнвест»</t>
+        </is>
+      </c>
+      <c r="C374" s="12" t="inlineStr">
+        <is>
+          <t>7841378040</t>
+        </is>
+      </c>
+      <c r="D374" s="13" t="inlineStr"/>
+      <c r="E374" s="11" t="inlineStr"/>
+      <c r="F374" s="11" t="inlineStr"/>
+      <c r="G374" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H374" s="10" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="I374" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J374" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="10" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергоком»</t>
+        </is>
+      </c>
+      <c r="C375" s="12" t="inlineStr">
+        <is>
+          <t>7841367514</t>
+        </is>
+      </c>
+      <c r="D375" s="13" t="inlineStr"/>
+      <c r="E375" s="11" t="inlineStr">
+        <is>
+          <t>СПб, Лиговский пр. 94к2А пом.25н; ОГРН 1077847536161; ген.дир. Боков В.Н.</t>
+        </is>
+      </c>
+      <c r="F375" s="11" t="inlineStr"/>
+      <c r="G375" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H375" s="10" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I375" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J375" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="10" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" s="11" t="inlineStr">
+        <is>
+          <t>ООО «Энергосервис»</t>
+        </is>
+      </c>
+      <c r="C376" s="12" t="inlineStr">
+        <is>
+          <t>7811004224</t>
+        </is>
+      </c>
+      <c r="D376" s="13" t="inlineStr"/>
+      <c r="E376" s="11" t="inlineStr">
+        <is>
+          <t>193079 СПб, Октябрьская наб. 104к31с1 пом.3-н; ОГРН 1027806083964; ген.дир. Смирнов С.А.</t>
+        </is>
+      </c>
+      <c r="F376" s="11" t="inlineStr"/>
+      <c r="G376" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H376" s="10" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I376" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J376" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="10" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" s="11" t="inlineStr">
+        <is>
+          <t>ООО БМПТ (Бюро морских проектов и технологий)</t>
+        </is>
+      </c>
+      <c r="C377" s="12" t="inlineStr">
+        <is>
+          <t>7810721927</t>
+        </is>
+      </c>
+      <c r="D377" s="13" t="inlineStr"/>
+      <c r="E377" s="11" t="inlineStr">
+        <is>
+          <t>196066 СПб, Московский пр. 212А оф.7017; ОГРН 1187847036750; рук. Якбаров В.В.</t>
+        </is>
+      </c>
+      <c r="F377" s="11" t="inlineStr"/>
+      <c r="G377" s="11" t="inlineStr">
+        <is>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H377" s="10" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="I377" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J377" s="10" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="10" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" s="11" t="inlineStr">
+        <is>
+          <t>ООО ПСМ «Спутник»</t>
+        </is>
+      </c>
+      <c r="C378" s="12" t="inlineStr">
+        <is>
+          <t>7810765071</t>
+        </is>
+      </c>
+      <c r="D378" s="13" t="inlineStr"/>
+      <c r="E378" s="11" t="inlineStr"/>
+      <c r="F378" s="11" t="inlineStr"/>
+      <c r="G378" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H378" s="10" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="I378" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J378" s="10" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="10" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" s="11" t="inlineStr">
+        <is>
+          <t>ООО СК «Аврора-Строй»</t>
+        </is>
+      </c>
+      <c r="C379" s="12" t="inlineStr">
+        <is>
+          <t>7801700173</t>
+        </is>
+      </c>
+      <c r="D379" s="13" t="inlineStr"/>
+      <c r="E379" s="11" t="inlineStr"/>
+      <c r="F379" s="11" t="inlineStr"/>
+      <c r="G379" s="11" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="H379" s="10" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="I363" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J363" s="10" t="inlineStr">
+      <c r="I379" s="10" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J379" s="10" t="inlineStr">
         <is>
           <t>500000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J363"/>
+  <autoFilter ref="A1:J379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15445,7 +16061,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>362</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8">
@@ -15465,7 +16081,7 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -2930,11 +2930,15 @@
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr"/>
-      <c r="E49" s="11" t="inlineStr"/>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -2968,11 +2972,15 @@
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr"/>
-      <c r="E50" s="11" t="inlineStr"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -3174,11 +3182,15 @@
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr"/>
-      <c r="E55" s="11" t="inlineStr"/>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -3254,11 +3266,15 @@
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr"/>
-      <c r="E57" s="11" t="inlineStr"/>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -3460,11 +3476,15 @@
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr"/>
-      <c r="E62" s="11" t="inlineStr"/>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F62" s="11" t="inlineStr"/>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -3540,11 +3560,15 @@
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr"/>
-      <c r="E64" s="11" t="inlineStr"/>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F64" s="11" t="inlineStr"/>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -3578,11 +3602,15 @@
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr"/>
-      <c r="E65" s="11" t="inlineStr"/>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F65" s="11" t="inlineStr"/>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -3616,11 +3644,19 @@
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr"/>
-      <c r="E66" s="11" t="inlineStr"/>
-      <c r="F66" s="11" t="inlineStr"/>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>карточка есть на list-org, но контакты в выдачу не попали; в СПб несколько ООО «СМУ-47» с другими ИНН</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>поиск выполнен</t>
+        </is>
+      </c>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -3654,11 +3690,15 @@
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr"/>
-      <c r="E67" s="11" t="inlineStr"/>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H67" s="10" t="inlineStr">
@@ -3776,11 +3816,15 @@
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr"/>
-      <c r="E70" s="11" t="inlineStr"/>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F70" s="11" t="inlineStr"/>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
@@ -3814,11 +3858,15 @@
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
-      <c r="E71" s="11" t="inlineStr"/>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -3894,11 +3942,15 @@
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
-      <c r="E73" s="11" t="inlineStr"/>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -3932,11 +3984,15 @@
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr"/>
-      <c r="E74" s="11" t="inlineStr"/>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F74" s="11" t="inlineStr"/>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -3970,11 +4026,15 @@
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr"/>
-      <c r="E75" s="11" t="inlineStr"/>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F75" s="11" t="inlineStr"/>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
@@ -4092,11 +4152,15 @@
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr"/>
-      <c r="E78" s="11" t="inlineStr"/>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F78" s="11" t="inlineStr"/>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
@@ -4130,11 +4194,15 @@
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr"/>
-      <c r="E79" s="11" t="inlineStr"/>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F79" s="11" t="inlineStr"/>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
@@ -4210,11 +4278,15 @@
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr"/>
-      <c r="E81" s="11" t="inlineStr"/>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F81" s="11" t="inlineStr"/>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -4248,11 +4320,15 @@
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr"/>
-      <c r="E82" s="11" t="inlineStr"/>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F82" s="11" t="inlineStr"/>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -4328,11 +4404,15 @@
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr"/>
-      <c r="E84" s="11" t="inlineStr"/>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F84" s="11" t="inlineStr"/>
       <c r="G84" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -4626,11 +4706,15 @@
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr"/>
-      <c r="E91" s="11" t="inlineStr"/>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H91" s="10" t="inlineStr">
@@ -4664,11 +4748,15 @@
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr"/>
-      <c r="E92" s="11" t="inlineStr"/>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F92" s="11" t="inlineStr"/>
       <c r="G92" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -4702,11 +4790,15 @@
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr"/>
-      <c r="E93" s="11" t="inlineStr"/>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H93" s="10" t="inlineStr">
@@ -4740,11 +4832,15 @@
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr"/>
-      <c r="E94" s="11" t="inlineStr"/>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F94" s="11" t="inlineStr"/>
       <c r="G94" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H94" s="10" t="inlineStr">
@@ -4778,11 +4874,15 @@
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr"/>
-      <c r="E95" s="11" t="inlineStr"/>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F95" s="11" t="inlineStr"/>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H95" s="10" t="inlineStr">
@@ -4816,11 +4916,15 @@
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr"/>
-      <c r="E96" s="11" t="inlineStr"/>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F96" s="11" t="inlineStr"/>
       <c r="G96" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H96" s="10" t="inlineStr">
@@ -4854,11 +4958,15 @@
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr"/>
-      <c r="E97" s="11" t="inlineStr"/>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F97" s="11" t="inlineStr"/>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H97" s="10" t="inlineStr">
@@ -4892,11 +5000,15 @@
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr"/>
-      <c r="E98" s="11" t="inlineStr"/>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F98" s="11" t="inlineStr"/>
       <c r="G98" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H98" s="10" t="inlineStr">
@@ -4930,11 +5042,15 @@
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr"/>
-      <c r="E99" s="11" t="inlineStr"/>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F99" s="11" t="inlineStr"/>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H99" s="10" t="inlineStr">
@@ -4968,11 +5084,15 @@
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr"/>
-      <c r="E100" s="11" t="inlineStr"/>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F100" s="11" t="inlineStr"/>
       <c r="G100" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H100" s="10" t="inlineStr">
@@ -5006,11 +5126,15 @@
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr"/>
-      <c r="E101" s="11" t="inlineStr"/>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F101" s="11" t="inlineStr"/>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H101" s="10" t="inlineStr">
@@ -5128,11 +5252,15 @@
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr"/>
-      <c r="E104" s="11" t="inlineStr"/>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F104" s="11" t="inlineStr"/>
       <c r="G104" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H104" s="10" t="inlineStr">
@@ -5166,11 +5294,15 @@
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr"/>
-      <c r="E105" s="11" t="inlineStr"/>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F105" s="11" t="inlineStr"/>
       <c r="G105" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H105" s="10" t="inlineStr">
@@ -5204,11 +5336,15 @@
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr"/>
-      <c r="E106" s="11" t="inlineStr"/>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F106" s="11" t="inlineStr"/>
       <c r="G106" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H106" s="10" t="inlineStr">
@@ -5284,11 +5420,15 @@
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr"/>
-      <c r="E108" s="11" t="inlineStr"/>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F108" s="11" t="inlineStr"/>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H108" s="10" t="inlineStr">
@@ -5322,11 +5462,15 @@
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr"/>
-      <c r="E109" s="11" t="inlineStr"/>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F109" s="11" t="inlineStr"/>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H109" s="10" t="inlineStr">
@@ -5360,11 +5504,15 @@
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr"/>
-      <c r="E110" s="11" t="inlineStr"/>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F110" s="11" t="inlineStr"/>
       <c r="G110" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H110" s="10" t="inlineStr">
@@ -5440,11 +5588,15 @@
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr"/>
-      <c r="E112" s="11" t="inlineStr"/>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F112" s="11" t="inlineStr"/>
       <c r="G112" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H112" s="10" t="inlineStr">
@@ -5478,11 +5630,15 @@
         </is>
       </c>
       <c r="D113" s="13" t="inlineStr"/>
-      <c r="E113" s="11" t="inlineStr"/>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F113" s="11" t="inlineStr"/>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H113" s="10" t="inlineStr">
@@ -5516,11 +5672,15 @@
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr"/>
-      <c r="E114" s="11" t="inlineStr"/>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F114" s="11" t="inlineStr"/>
       <c r="G114" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -5554,11 +5714,15 @@
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr"/>
-      <c r="E115" s="11" t="inlineStr"/>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F115" s="11" t="inlineStr"/>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H115" s="10" t="inlineStr">
@@ -5592,11 +5756,15 @@
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr"/>
-      <c r="E116" s="11" t="inlineStr"/>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F116" s="11" t="inlineStr"/>
       <c r="G116" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
@@ -5672,11 +5840,15 @@
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr"/>
-      <c r="E118" s="11" t="inlineStr"/>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F118" s="11" t="inlineStr"/>
       <c r="G118" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H118" s="10" t="inlineStr">
@@ -5710,11 +5882,15 @@
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr"/>
-      <c r="E119" s="11" t="inlineStr"/>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F119" s="11" t="inlineStr"/>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H119" s="10" t="inlineStr">
@@ -5748,11 +5924,15 @@
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr"/>
-      <c r="E120" s="11" t="inlineStr"/>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F120" s="11" t="inlineStr"/>
       <c r="G120" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H120" s="10" t="inlineStr">
@@ -5828,11 +6008,15 @@
         </is>
       </c>
       <c r="D122" s="13" t="inlineStr"/>
-      <c r="E122" s="11" t="inlineStr"/>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F122" s="11" t="inlineStr"/>
       <c r="G122" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
@@ -5866,11 +6050,15 @@
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr"/>
-      <c r="E123" s="11" t="inlineStr"/>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F123" s="11" t="inlineStr"/>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H123" s="10" t="inlineStr">
@@ -5904,11 +6092,15 @@
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr"/>
-      <c r="E124" s="11" t="inlineStr"/>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F124" s="11" t="inlineStr"/>
       <c r="G124" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H124" s="10" t="inlineStr">
@@ -5942,11 +6134,15 @@
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr"/>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F125" s="11" t="inlineStr"/>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H125" s="10" t="inlineStr">
@@ -5980,11 +6176,15 @@
         </is>
       </c>
       <c r="D126" s="13" t="inlineStr"/>
-      <c r="E126" s="11" t="inlineStr"/>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F126" s="11" t="inlineStr"/>
       <c r="G126" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H126" s="10" t="inlineStr">
@@ -6018,11 +6218,15 @@
         </is>
       </c>
       <c r="D127" s="13" t="inlineStr"/>
-      <c r="E127" s="11" t="inlineStr"/>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F127" s="11" t="inlineStr"/>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H127" s="10" t="inlineStr">
@@ -6056,11 +6260,15 @@
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr"/>
-      <c r="E128" s="11" t="inlineStr"/>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F128" s="11" t="inlineStr"/>
       <c r="G128" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H128" s="10" t="inlineStr">
@@ -6094,11 +6302,15 @@
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr"/>
-      <c r="E129" s="11" t="inlineStr"/>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F129" s="11" t="inlineStr"/>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H129" s="10" t="inlineStr">
@@ -6132,11 +6344,15 @@
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr"/>
-      <c r="E130" s="11" t="inlineStr"/>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F130" s="11" t="inlineStr"/>
       <c r="G130" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H130" s="10" t="inlineStr">
@@ -6170,11 +6386,15 @@
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr"/>
-      <c r="E131" s="11" t="inlineStr"/>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F131" s="11" t="inlineStr"/>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H131" s="10" t="inlineStr">
@@ -6208,11 +6428,15 @@
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr"/>
-      <c r="E132" s="11" t="inlineStr"/>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F132" s="11" t="inlineStr"/>
       <c r="G132" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -6246,11 +6470,15 @@
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr"/>
-      <c r="E133" s="11" t="inlineStr"/>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F133" s="11" t="inlineStr"/>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H133" s="10" t="inlineStr">
@@ -6284,11 +6512,15 @@
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr"/>
-      <c r="E134" s="11" t="inlineStr"/>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F134" s="11" t="inlineStr"/>
       <c r="G134" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H134" s="10" t="inlineStr">
@@ -6368,11 +6600,19 @@
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr"/>
-      <c r="E136" s="11" t="inlineStr"/>
-      <c r="F136" s="11" t="inlineStr"/>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>ИНН в выдаче не найден; в СПб много одноимённых ООО с другими ИНН</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>поиск выполнен</t>
+        </is>
+      </c>
       <c r="G136" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H136" s="10" t="inlineStr">
@@ -6448,11 +6688,15 @@
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr"/>
-      <c r="E138" s="11" t="inlineStr"/>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F138" s="11" t="inlineStr"/>
       <c r="G138" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H138" s="10" t="inlineStr">
@@ -6528,11 +6772,15 @@
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr"/>
-      <c r="E140" s="11" t="inlineStr"/>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F140" s="11" t="inlineStr"/>
       <c r="G140" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H140" s="10" t="inlineStr">
@@ -6608,11 +6856,15 @@
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr"/>
-      <c r="E142" s="11" t="inlineStr"/>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F142" s="11" t="inlineStr"/>
       <c r="G142" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H142" s="10" t="inlineStr">
@@ -6646,11 +6898,15 @@
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr"/>
-      <c r="E143" s="11" t="inlineStr"/>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F143" s="11" t="inlineStr"/>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H143" s="10" t="inlineStr">
@@ -6726,11 +6982,15 @@
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr"/>
-      <c r="E145" s="11" t="inlineStr"/>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F145" s="11" t="inlineStr"/>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H145" s="10" t="inlineStr">
@@ -6764,11 +7024,15 @@
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr"/>
-      <c r="E146" s="11" t="inlineStr"/>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F146" s="11" t="inlineStr"/>
       <c r="G146" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H146" s="10" t="inlineStr">
@@ -6802,11 +7066,15 @@
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr"/>
-      <c r="E147" s="11" t="inlineStr"/>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F147" s="11" t="inlineStr"/>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H147" s="10" t="inlineStr">
@@ -6840,11 +7108,19 @@
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr"/>
-      <c r="E148" s="11" t="inlineStr"/>
-      <c r="F148" s="11" t="inlineStr"/>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>ИНН в выдаче не найден; одноимённые ООО в СПб имеют другие ИНН</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>поиск выполнен</t>
+        </is>
+      </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H148" s="10" t="inlineStr">
@@ -6878,11 +7154,15 @@
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr"/>
-      <c r="E149" s="11" t="inlineStr"/>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F149" s="11" t="inlineStr"/>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H149" s="10" t="inlineStr">
@@ -6916,11 +7196,15 @@
         </is>
       </c>
       <c r="D150" s="13" t="inlineStr"/>
-      <c r="E150" s="11" t="inlineStr"/>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F150" s="11" t="inlineStr"/>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H150" s="10" t="inlineStr">
@@ -6954,11 +7238,15 @@
         </is>
       </c>
       <c r="D151" s="13" t="inlineStr"/>
-      <c r="E151" s="11" t="inlineStr"/>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F151" s="11" t="inlineStr"/>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H151" s="10" t="inlineStr">
@@ -6992,11 +7280,15 @@
         </is>
       </c>
       <c r="D152" s="13" t="inlineStr"/>
-      <c r="E152" s="11" t="inlineStr"/>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F152" s="11" t="inlineStr"/>
       <c r="G152" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H152" s="10" t="inlineStr">
@@ -7030,11 +7322,15 @@
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr"/>
-      <c r="E153" s="11" t="inlineStr"/>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F153" s="11" t="inlineStr"/>
       <c r="G153" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H153" s="10" t="inlineStr">
@@ -7152,11 +7448,15 @@
         </is>
       </c>
       <c r="D156" s="13" t="inlineStr"/>
-      <c r="E156" s="11" t="inlineStr"/>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F156" s="11" t="inlineStr"/>
       <c r="G156" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H156" s="10" t="inlineStr">
@@ -7190,11 +7490,15 @@
         </is>
       </c>
       <c r="D157" s="13" t="inlineStr"/>
-      <c r="E157" s="11" t="inlineStr"/>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F157" s="11" t="inlineStr"/>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H157" s="10" t="inlineStr">
@@ -7312,11 +7616,19 @@
         </is>
       </c>
       <c r="D160" s="13" t="inlineStr"/>
-      <c r="E160" s="11" t="inlineStr"/>
-      <c r="F160" s="11" t="inlineStr"/>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>в выдаче только другие ООО «БИК» с иными ИНН</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>поиск выполнен</t>
+        </is>
+      </c>
       <c r="G160" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H160" s="10" t="inlineStr">
@@ -7392,11 +7704,15 @@
         </is>
       </c>
       <c r="D162" s="13" t="inlineStr"/>
-      <c r="E162" s="11" t="inlineStr"/>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F162" s="11" t="inlineStr"/>
       <c r="G162" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H162" s="10" t="inlineStr">
@@ -7430,11 +7746,15 @@
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr"/>
-      <c r="E163" s="11" t="inlineStr"/>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F163" s="11" t="inlineStr"/>
       <c r="G163" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H163" s="10" t="inlineStr">
@@ -7468,11 +7788,15 @@
         </is>
       </c>
       <c r="D164" s="13" t="inlineStr"/>
-      <c r="E164" s="11" t="inlineStr"/>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F164" s="11" t="inlineStr"/>
       <c r="G164" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H164" s="10" t="inlineStr">
@@ -7506,11 +7830,15 @@
         </is>
       </c>
       <c r="D165" s="13" t="inlineStr"/>
-      <c r="E165" s="11" t="inlineStr"/>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F165" s="11" t="inlineStr"/>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H165" s="10" t="inlineStr">
@@ -7586,11 +7914,15 @@
         </is>
       </c>
       <c r="D167" s="13" t="inlineStr"/>
-      <c r="E167" s="11" t="inlineStr"/>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F167" s="11" t="inlineStr"/>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H167" s="10" t="inlineStr">
@@ -7624,11 +7956,15 @@
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr"/>
-      <c r="E168" s="11" t="inlineStr"/>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F168" s="11" t="inlineStr"/>
       <c r="G168" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H168" s="10" t="inlineStr">
@@ -7704,11 +8040,15 @@
         </is>
       </c>
       <c r="D170" s="13" t="inlineStr"/>
-      <c r="E170" s="11" t="inlineStr"/>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F170" s="11" t="inlineStr"/>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H170" s="10" t="inlineStr">
@@ -7901,7 +8241,7 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>ООО «ВИП»</t>
+          <t>ООО «ВИП» (Водяной и Партнёры)</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
@@ -7910,11 +8250,19 @@
         </is>
       </c>
       <c r="D175" s="13" t="inlineStr"/>
-      <c r="E175" s="11" t="inlineStr"/>
-      <c r="F175" s="11" t="inlineStr"/>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>СПб, ш.Революции 69А пом.68н оф.211; ОГРН 1117847065445; ген.дир. Потапов А.В.</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/5286143; companies.rbc.ru</t>
+        </is>
+      </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено, нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H175" s="10" t="inlineStr">
@@ -7990,11 +8338,15 @@
         </is>
       </c>
       <c r="D177" s="13" t="inlineStr"/>
-      <c r="E177" s="11" t="inlineStr"/>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F177" s="11" t="inlineStr"/>
       <c r="G177" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H177" s="10" t="inlineStr">
@@ -8028,11 +8380,15 @@
         </is>
       </c>
       <c r="D178" s="13" t="inlineStr"/>
-      <c r="E178" s="11" t="inlineStr"/>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F178" s="11" t="inlineStr"/>
       <c r="G178" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H178" s="10" t="inlineStr">
@@ -8066,11 +8422,15 @@
         </is>
       </c>
       <c r="D179" s="13" t="inlineStr"/>
-      <c r="E179" s="11" t="inlineStr"/>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F179" s="11" t="inlineStr"/>
       <c r="G179" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H179" s="10" t="inlineStr">
@@ -8146,11 +8506,15 @@
         </is>
       </c>
       <c r="D181" s="13" t="inlineStr"/>
-      <c r="E181" s="11" t="inlineStr"/>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F181" s="11" t="inlineStr"/>
       <c r="G181" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H181" s="10" t="inlineStr">
@@ -8226,11 +8590,15 @@
         </is>
       </c>
       <c r="D183" s="13" t="inlineStr"/>
-      <c r="E183" s="11" t="inlineStr"/>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F183" s="11" t="inlineStr"/>
       <c r="G183" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H183" s="10" t="inlineStr">
@@ -8306,11 +8674,15 @@
         </is>
       </c>
       <c r="D185" s="13" t="inlineStr"/>
-      <c r="E185" s="11" t="inlineStr"/>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F185" s="11" t="inlineStr"/>
       <c r="G185" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H185" s="10" t="inlineStr">
@@ -8428,11 +8800,15 @@
         </is>
       </c>
       <c r="D188" s="13" t="inlineStr"/>
-      <c r="E188" s="11" t="inlineStr"/>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F188" s="11" t="inlineStr"/>
       <c r="G188" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H188" s="10" t="inlineStr">
@@ -8508,11 +8884,15 @@
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr"/>
-      <c r="E190" s="11" t="inlineStr"/>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F190" s="11" t="inlineStr"/>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H190" s="10" t="inlineStr">
@@ -8546,11 +8926,15 @@
         </is>
       </c>
       <c r="D191" s="13" t="inlineStr"/>
-      <c r="E191" s="11" t="inlineStr"/>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F191" s="11" t="inlineStr"/>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H191" s="10" t="inlineStr">
@@ -8584,11 +8968,15 @@
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr"/>
-      <c r="E192" s="11" t="inlineStr"/>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F192" s="11" t="inlineStr"/>
       <c r="G192" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H192" s="10" t="inlineStr">
@@ -8706,11 +9094,15 @@
         </is>
       </c>
       <c r="D195" s="13" t="inlineStr"/>
-      <c r="E195" s="11" t="inlineStr"/>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F195" s="11" t="inlineStr"/>
       <c r="G195" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H195" s="10" t="inlineStr">
@@ -8744,11 +9136,15 @@
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr"/>
-      <c r="E196" s="11" t="inlineStr"/>
+      <c r="E196" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F196" s="11" t="inlineStr"/>
       <c r="G196" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H196" s="10" t="inlineStr">
@@ -8824,11 +9220,19 @@
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr"/>
-      <c r="E198" s="11" t="inlineStr"/>
-      <c r="F198" s="11" t="inlineStr"/>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>ИНН в выдаче не найден; в СПб есть другое ООО «ИГС» с ИНН 7813257950 — не тот контрагент</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>поиск выполнен</t>
+        </is>
+      </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H198" s="10" t="inlineStr">
@@ -8862,11 +9266,15 @@
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr"/>
-      <c r="E199" s="11" t="inlineStr"/>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F199" s="11" t="inlineStr"/>
       <c r="G199" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H199" s="10" t="inlineStr">
@@ -8900,11 +9308,15 @@
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr"/>
-      <c r="E200" s="11" t="inlineStr"/>
+      <c r="E200" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F200" s="11" t="inlineStr"/>
       <c r="G200" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H200" s="10" t="inlineStr">
@@ -8938,11 +9350,15 @@
         </is>
       </c>
       <c r="D201" s="13" t="inlineStr"/>
-      <c r="E201" s="11" t="inlineStr"/>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F201" s="11" t="inlineStr"/>
       <c r="G201" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H201" s="10" t="inlineStr">
@@ -9018,11 +9434,15 @@
         </is>
       </c>
       <c r="D203" s="13" t="inlineStr"/>
-      <c r="E203" s="11" t="inlineStr"/>
+      <c r="E203" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F203" s="11" t="inlineStr"/>
       <c r="G203" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H203" s="10" t="inlineStr">
@@ -9056,11 +9476,15 @@
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr"/>
-      <c r="E204" s="11" t="inlineStr"/>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F204" s="11" t="inlineStr"/>
       <c r="G204" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H204" s="10" t="inlineStr">
@@ -9136,11 +9560,15 @@
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr"/>
-      <c r="E206" s="11" t="inlineStr"/>
+      <c r="E206" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F206" s="11" t="inlineStr"/>
       <c r="G206" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H206" s="10" t="inlineStr">
@@ -9216,11 +9644,15 @@
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr"/>
-      <c r="E208" s="11" t="inlineStr"/>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F208" s="11" t="inlineStr"/>
       <c r="G208" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H208" s="10" t="inlineStr">
@@ -9254,11 +9686,15 @@
         </is>
       </c>
       <c r="D209" s="13" t="inlineStr"/>
-      <c r="E209" s="11" t="inlineStr"/>
+      <c r="E209" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F209" s="11" t="inlineStr"/>
       <c r="G209" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H209" s="10" t="inlineStr">
@@ -9292,11 +9728,15 @@
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr"/>
-      <c r="E210" s="11" t="inlineStr"/>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F210" s="11" t="inlineStr"/>
       <c r="G210" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H210" s="10" t="inlineStr">
@@ -9414,11 +9854,15 @@
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr"/>
-      <c r="E213" s="11" t="inlineStr"/>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F213" s="11" t="inlineStr"/>
       <c r="G213" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H213" s="10" t="inlineStr">
@@ -9494,11 +9938,15 @@
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr"/>
-      <c r="E215" s="11" t="inlineStr"/>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F215" s="11" t="inlineStr"/>
       <c r="G215" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H215" s="10" t="inlineStr">
@@ -9532,11 +9980,15 @@
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr"/>
-      <c r="E216" s="11" t="inlineStr"/>
+      <c r="E216" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F216" s="11" t="inlineStr"/>
       <c r="G216" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H216" s="10" t="inlineStr">
@@ -9570,11 +10022,15 @@
         </is>
       </c>
       <c r="D217" s="13" t="inlineStr"/>
-      <c r="E217" s="11" t="inlineStr"/>
+      <c r="E217" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F217" s="11" t="inlineStr"/>
       <c r="G217" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H217" s="10" t="inlineStr">
@@ -9692,11 +10148,15 @@
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr"/>
-      <c r="E220" s="11" t="inlineStr"/>
+      <c r="E220" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F220" s="11" t="inlineStr"/>
       <c r="G220" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H220" s="10" t="inlineStr">
@@ -9730,11 +10190,15 @@
         </is>
       </c>
       <c r="D221" s="13" t="inlineStr"/>
-      <c r="E221" s="11" t="inlineStr"/>
+      <c r="E221" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F221" s="11" t="inlineStr"/>
       <c r="G221" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H221" s="10" t="inlineStr">
@@ -9768,11 +10232,15 @@
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr"/>
-      <c r="E222" s="11" t="inlineStr"/>
+      <c r="E222" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F222" s="11" t="inlineStr"/>
       <c r="G222" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H222" s="10" t="inlineStr">
@@ -9806,11 +10274,15 @@
         </is>
       </c>
       <c r="D223" s="13" t="inlineStr"/>
-      <c r="E223" s="11" t="inlineStr"/>
+      <c r="E223" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F223" s="11" t="inlineStr"/>
       <c r="G223" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H223" s="10" t="inlineStr">
@@ -9844,11 +10316,15 @@
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr"/>
-      <c r="E224" s="11" t="inlineStr"/>
+      <c r="E224" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F224" s="11" t="inlineStr"/>
       <c r="G224" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H224" s="10" t="inlineStr">
@@ -9882,11 +10358,15 @@
         </is>
       </c>
       <c r="D225" s="13" t="inlineStr"/>
-      <c r="E225" s="11" t="inlineStr"/>
+      <c r="E225" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F225" s="11" t="inlineStr"/>
       <c r="G225" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H225" s="10" t="inlineStr">
@@ -9962,11 +10442,15 @@
         </is>
       </c>
       <c r="D227" s="13" t="inlineStr"/>
-      <c r="E227" s="11" t="inlineStr"/>
+      <c r="E227" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F227" s="11" t="inlineStr"/>
       <c r="G227" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H227" s="10" t="inlineStr">
@@ -10168,11 +10652,15 @@
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr"/>
-      <c r="E232" s="11" t="inlineStr"/>
+      <c r="E232" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F232" s="11" t="inlineStr"/>
       <c r="G232" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H232" s="10" t="inlineStr">
@@ -10206,11 +10694,15 @@
         </is>
       </c>
       <c r="D233" s="13" t="inlineStr"/>
-      <c r="E233" s="11" t="inlineStr"/>
+      <c r="E233" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F233" s="11" t="inlineStr"/>
       <c r="G233" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H233" s="10" t="inlineStr">
@@ -10244,11 +10736,15 @@
         </is>
       </c>
       <c r="D234" s="13" t="inlineStr"/>
-      <c r="E234" s="11" t="inlineStr"/>
+      <c r="E234" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F234" s="11" t="inlineStr"/>
       <c r="G234" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H234" s="10" t="inlineStr">
@@ -10366,11 +10862,15 @@
         </is>
       </c>
       <c r="D237" s="13" t="inlineStr"/>
-      <c r="E237" s="11" t="inlineStr"/>
+      <c r="E237" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F237" s="11" t="inlineStr"/>
       <c r="G237" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H237" s="10" t="inlineStr">
@@ -10446,11 +10946,15 @@
         </is>
       </c>
       <c r="D239" s="13" t="inlineStr"/>
-      <c r="E239" s="11" t="inlineStr"/>
+      <c r="E239" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F239" s="11" t="inlineStr"/>
       <c r="G239" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H239" s="10" t="inlineStr">
@@ -10568,11 +11072,15 @@
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr"/>
-      <c r="E242" s="11" t="inlineStr"/>
+      <c r="E242" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F242" s="11" t="inlineStr"/>
       <c r="G242" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H242" s="10" t="inlineStr">
@@ -10606,11 +11114,15 @@
         </is>
       </c>
       <c r="D243" s="13" t="inlineStr"/>
-      <c r="E243" s="11" t="inlineStr"/>
+      <c r="E243" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F243" s="11" t="inlineStr"/>
       <c r="G243" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H243" s="10" t="inlineStr">
@@ -10644,11 +11156,15 @@
         </is>
       </c>
       <c r="D244" s="13" t="inlineStr"/>
-      <c r="E244" s="11" t="inlineStr"/>
+      <c r="E244" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F244" s="11" t="inlineStr"/>
       <c r="G244" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H244" s="10" t="inlineStr">
@@ -10682,11 +11198,15 @@
         </is>
       </c>
       <c r="D245" s="13" t="inlineStr"/>
-      <c r="E245" s="11" t="inlineStr"/>
+      <c r="E245" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F245" s="11" t="inlineStr"/>
       <c r="G245" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H245" s="10" t="inlineStr">
@@ -10762,11 +11282,15 @@
         </is>
       </c>
       <c r="D247" s="13" t="inlineStr"/>
-      <c r="E247" s="11" t="inlineStr"/>
+      <c r="E247" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F247" s="11" t="inlineStr"/>
       <c r="G247" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H247" s="10" t="inlineStr">
@@ -10800,11 +11324,15 @@
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr"/>
-      <c r="E248" s="11" t="inlineStr"/>
+      <c r="E248" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F248" s="11" t="inlineStr"/>
       <c r="G248" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H248" s="10" t="inlineStr">
@@ -10880,11 +11408,15 @@
         </is>
       </c>
       <c r="D250" s="13" t="inlineStr"/>
-      <c r="E250" s="11" t="inlineStr"/>
+      <c r="E250" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F250" s="11" t="inlineStr"/>
       <c r="G250" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H250" s="10" t="inlineStr">
@@ -10918,11 +11450,15 @@
         </is>
       </c>
       <c r="D251" s="13" t="inlineStr"/>
-      <c r="E251" s="11" t="inlineStr"/>
+      <c r="E251" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F251" s="11" t="inlineStr"/>
       <c r="G251" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H251" s="10" t="inlineStr">
@@ -10998,11 +11534,15 @@
         </is>
       </c>
       <c r="D253" s="13" t="inlineStr"/>
-      <c r="E253" s="11" t="inlineStr"/>
+      <c r="E253" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F253" s="11" t="inlineStr"/>
       <c r="G253" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H253" s="10" t="inlineStr">
@@ -11036,11 +11576,15 @@
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr"/>
-      <c r="E254" s="11" t="inlineStr"/>
+      <c r="E254" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F254" s="11" t="inlineStr"/>
       <c r="G254" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H254" s="10" t="inlineStr">
@@ -11204,11 +11748,15 @@
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr"/>
-      <c r="E258" s="11" t="inlineStr"/>
+      <c r="E258" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F258" s="11" t="inlineStr"/>
       <c r="G258" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H258" s="10" t="inlineStr">
@@ -11326,11 +11874,19 @@
         </is>
       </c>
       <c r="D261" s="13" t="inlineStr"/>
-      <c r="E261" s="11" t="inlineStr"/>
-      <c r="F261" s="11" t="inlineStr"/>
+      <c r="E261" s="11" t="inlineStr">
+        <is>
+          <t>в выдаче только другие ООО «ПТГ» с иными ИНН</t>
+        </is>
+      </c>
+      <c r="F261" s="11" t="inlineStr">
+        <is>
+          <t>поиск выполнен</t>
+        </is>
+      </c>
       <c r="G261" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H261" s="10" t="inlineStr">
@@ -11364,11 +11920,15 @@
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr"/>
-      <c r="E262" s="11" t="inlineStr"/>
+      <c r="E262" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F262" s="11" t="inlineStr"/>
       <c r="G262" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H262" s="10" t="inlineStr">
@@ -11402,11 +11962,15 @@
         </is>
       </c>
       <c r="D263" s="13" t="inlineStr"/>
-      <c r="E263" s="11" t="inlineStr"/>
+      <c r="E263" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F263" s="11" t="inlineStr"/>
       <c r="G263" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H263" s="10" t="inlineStr">
@@ -11440,11 +12004,15 @@
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr"/>
-      <c r="E264" s="11" t="inlineStr"/>
+      <c r="E264" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F264" s="11" t="inlineStr"/>
       <c r="G264" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H264" s="10" t="inlineStr">
@@ -11478,11 +12046,15 @@
         </is>
       </c>
       <c r="D265" s="13" t="inlineStr"/>
-      <c r="E265" s="11" t="inlineStr"/>
+      <c r="E265" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F265" s="11" t="inlineStr"/>
       <c r="G265" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H265" s="10" t="inlineStr">
@@ -11516,11 +12088,15 @@
         </is>
       </c>
       <c r="D266" s="13" t="inlineStr"/>
-      <c r="E266" s="11" t="inlineStr"/>
+      <c r="E266" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F266" s="11" t="inlineStr"/>
       <c r="G266" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H266" s="10" t="inlineStr">
@@ -11554,11 +12130,15 @@
         </is>
       </c>
       <c r="D267" s="13" t="inlineStr"/>
-      <c r="E267" s="11" t="inlineStr"/>
+      <c r="E267" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F267" s="11" t="inlineStr"/>
       <c r="G267" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H267" s="10" t="inlineStr">
@@ -11592,11 +12172,15 @@
         </is>
       </c>
       <c r="D268" s="13" t="inlineStr"/>
-      <c r="E268" s="11" t="inlineStr"/>
+      <c r="E268" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F268" s="11" t="inlineStr"/>
       <c r="G268" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H268" s="10" t="inlineStr">
@@ -11630,11 +12214,15 @@
         </is>
       </c>
       <c r="D269" s="13" t="inlineStr"/>
-      <c r="E269" s="11" t="inlineStr"/>
+      <c r="E269" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F269" s="11" t="inlineStr"/>
       <c r="G269" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H269" s="10" t="inlineStr">
@@ -11668,11 +12256,15 @@
         </is>
       </c>
       <c r="D270" s="13" t="inlineStr"/>
-      <c r="E270" s="11" t="inlineStr"/>
+      <c r="E270" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F270" s="11" t="inlineStr"/>
       <c r="G270" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H270" s="10" t="inlineStr">
@@ -11748,11 +12340,15 @@
         </is>
       </c>
       <c r="D272" s="13" t="inlineStr"/>
-      <c r="E272" s="11" t="inlineStr"/>
+      <c r="E272" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F272" s="11" t="inlineStr"/>
       <c r="G272" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H272" s="10" t="inlineStr">
@@ -11786,11 +12382,15 @@
         </is>
       </c>
       <c r="D273" s="13" t="inlineStr"/>
-      <c r="E273" s="11" t="inlineStr"/>
+      <c r="E273" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F273" s="11" t="inlineStr"/>
       <c r="G273" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H273" s="10" t="inlineStr">
@@ -11824,11 +12424,15 @@
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr"/>
-      <c r="E274" s="11" t="inlineStr"/>
+      <c r="E274" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F274" s="11" t="inlineStr"/>
       <c r="G274" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H274" s="10" t="inlineStr">
@@ -11904,11 +12508,15 @@
         </is>
       </c>
       <c r="D276" s="13" t="inlineStr"/>
-      <c r="E276" s="11" t="inlineStr"/>
+      <c r="E276" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F276" s="11" t="inlineStr"/>
       <c r="G276" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H276" s="10" t="inlineStr">
@@ -11984,11 +12592,15 @@
         </is>
       </c>
       <c r="D278" s="13" t="inlineStr"/>
-      <c r="E278" s="11" t="inlineStr"/>
+      <c r="E278" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F278" s="11" t="inlineStr"/>
       <c r="G278" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H278" s="10" t="inlineStr">
@@ -12022,11 +12634,15 @@
         </is>
       </c>
       <c r="D279" s="13" t="inlineStr"/>
-      <c r="E279" s="11" t="inlineStr"/>
+      <c r="E279" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F279" s="11" t="inlineStr"/>
       <c r="G279" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H279" s="10" t="inlineStr">
@@ -12102,11 +12718,15 @@
         </is>
       </c>
       <c r="D281" s="13" t="inlineStr"/>
-      <c r="E281" s="11" t="inlineStr"/>
+      <c r="E281" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F281" s="11" t="inlineStr"/>
       <c r="G281" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H281" s="10" t="inlineStr">
@@ -12140,11 +12760,15 @@
         </is>
       </c>
       <c r="D282" s="13" t="inlineStr"/>
-      <c r="E282" s="11" t="inlineStr"/>
+      <c r="E282" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F282" s="11" t="inlineStr"/>
       <c r="G282" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H282" s="10" t="inlineStr">
@@ -12178,11 +12802,15 @@
         </is>
       </c>
       <c r="D283" s="13" t="inlineStr"/>
-      <c r="E283" s="11" t="inlineStr"/>
+      <c r="E283" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F283" s="11" t="inlineStr"/>
       <c r="G283" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H283" s="10" t="inlineStr">
@@ -12216,11 +12844,15 @@
         </is>
       </c>
       <c r="D284" s="13" t="inlineStr"/>
-      <c r="E284" s="11" t="inlineStr"/>
+      <c r="E284" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F284" s="11" t="inlineStr"/>
       <c r="G284" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H284" s="10" t="inlineStr">
@@ -12254,11 +12886,15 @@
         </is>
       </c>
       <c r="D285" s="13" t="inlineStr"/>
-      <c r="E285" s="11" t="inlineStr"/>
+      <c r="E285" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F285" s="11" t="inlineStr"/>
       <c r="G285" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H285" s="10" t="inlineStr">
@@ -12376,11 +13012,15 @@
         </is>
       </c>
       <c r="D288" s="13" t="inlineStr"/>
-      <c r="E288" s="11" t="inlineStr"/>
+      <c r="E288" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F288" s="11" t="inlineStr"/>
       <c r="G288" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H288" s="10" t="inlineStr">
@@ -12414,11 +13054,15 @@
         </is>
       </c>
       <c r="D289" s="13" t="inlineStr"/>
-      <c r="E289" s="11" t="inlineStr"/>
+      <c r="E289" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F289" s="11" t="inlineStr"/>
       <c r="G289" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H289" s="10" t="inlineStr">
@@ -12452,11 +13096,15 @@
         </is>
       </c>
       <c r="D290" s="13" t="inlineStr"/>
-      <c r="E290" s="11" t="inlineStr"/>
+      <c r="E290" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F290" s="11" t="inlineStr"/>
       <c r="G290" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H290" s="10" t="inlineStr">
@@ -12490,11 +13138,15 @@
         </is>
       </c>
       <c r="D291" s="13" t="inlineStr"/>
-      <c r="E291" s="11" t="inlineStr"/>
+      <c r="E291" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F291" s="11" t="inlineStr"/>
       <c r="G291" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H291" s="10" t="inlineStr">
@@ -12612,11 +13264,15 @@
         </is>
       </c>
       <c r="D294" s="13" t="inlineStr"/>
-      <c r="E294" s="11" t="inlineStr"/>
+      <c r="E294" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F294" s="11" t="inlineStr"/>
       <c r="G294" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H294" s="10" t="inlineStr">
@@ -12692,11 +13348,15 @@
         </is>
       </c>
       <c r="D296" s="13" t="inlineStr"/>
-      <c r="E296" s="11" t="inlineStr"/>
+      <c r="E296" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F296" s="11" t="inlineStr"/>
       <c r="G296" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H296" s="10" t="inlineStr">
@@ -12730,11 +13390,15 @@
         </is>
       </c>
       <c r="D297" s="13" t="inlineStr"/>
-      <c r="E297" s="11" t="inlineStr"/>
+      <c r="E297" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F297" s="11" t="inlineStr"/>
       <c r="G297" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H297" s="10" t="inlineStr">
@@ -12768,11 +13432,15 @@
         </is>
       </c>
       <c r="D298" s="13" t="inlineStr"/>
-      <c r="E298" s="11" t="inlineStr"/>
+      <c r="E298" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F298" s="11" t="inlineStr"/>
       <c r="G298" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H298" s="10" t="inlineStr">
@@ -12848,11 +13516,15 @@
         </is>
       </c>
       <c r="D300" s="13" t="inlineStr"/>
-      <c r="E300" s="11" t="inlineStr"/>
+      <c r="E300" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F300" s="11" t="inlineStr"/>
       <c r="G300" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H300" s="10" t="inlineStr">
@@ -12886,11 +13558,15 @@
         </is>
       </c>
       <c r="D301" s="13" t="inlineStr"/>
-      <c r="E301" s="11" t="inlineStr"/>
+      <c r="E301" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F301" s="11" t="inlineStr"/>
       <c r="G301" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H301" s="10" t="inlineStr">
@@ -12966,11 +13642,15 @@
         </is>
       </c>
       <c r="D303" s="13" t="inlineStr"/>
-      <c r="E303" s="11" t="inlineStr"/>
+      <c r="E303" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F303" s="11" t="inlineStr"/>
       <c r="G303" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H303" s="10" t="inlineStr">
@@ -13004,11 +13684,15 @@
         </is>
       </c>
       <c r="D304" s="13" t="inlineStr"/>
-      <c r="E304" s="11" t="inlineStr"/>
+      <c r="E304" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F304" s="11" t="inlineStr"/>
       <c r="G304" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H304" s="10" t="inlineStr">
@@ -13042,11 +13726,15 @@
         </is>
       </c>
       <c r="D305" s="13" t="inlineStr"/>
-      <c r="E305" s="11" t="inlineStr"/>
+      <c r="E305" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F305" s="11" t="inlineStr"/>
       <c r="G305" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H305" s="10" t="inlineStr">
@@ -13080,11 +13768,15 @@
         </is>
       </c>
       <c r="D306" s="13" t="inlineStr"/>
-      <c r="E306" s="11" t="inlineStr"/>
+      <c r="E306" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F306" s="11" t="inlineStr"/>
       <c r="G306" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H306" s="10" t="inlineStr">
@@ -13118,11 +13810,15 @@
         </is>
       </c>
       <c r="D307" s="13" t="inlineStr"/>
-      <c r="E307" s="11" t="inlineStr"/>
+      <c r="E307" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F307" s="11" t="inlineStr"/>
       <c r="G307" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H307" s="10" t="inlineStr">
@@ -13156,11 +13852,15 @@
         </is>
       </c>
       <c r="D308" s="13" t="inlineStr"/>
-      <c r="E308" s="11" t="inlineStr"/>
+      <c r="E308" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F308" s="11" t="inlineStr"/>
       <c r="G308" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H308" s="10" t="inlineStr">
@@ -13194,11 +13894,15 @@
         </is>
       </c>
       <c r="D309" s="13" t="inlineStr"/>
-      <c r="E309" s="11" t="inlineStr"/>
+      <c r="E309" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F309" s="11" t="inlineStr"/>
       <c r="G309" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H309" s="10" t="inlineStr">
@@ -13232,11 +13936,15 @@
         </is>
       </c>
       <c r="D310" s="13" t="inlineStr"/>
-      <c r="E310" s="11" t="inlineStr"/>
+      <c r="E310" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F310" s="11" t="inlineStr"/>
       <c r="G310" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H310" s="10" t="inlineStr">
@@ -13270,11 +13978,15 @@
         </is>
       </c>
       <c r="D311" s="13" t="inlineStr"/>
-      <c r="E311" s="11" t="inlineStr"/>
+      <c r="E311" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F311" s="11" t="inlineStr"/>
       <c r="G311" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H311" s="10" t="inlineStr">
@@ -13350,11 +14062,15 @@
         </is>
       </c>
       <c r="D313" s="13" t="inlineStr"/>
-      <c r="E313" s="11" t="inlineStr"/>
+      <c r="E313" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F313" s="11" t="inlineStr"/>
       <c r="G313" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H313" s="10" t="inlineStr">
@@ -13388,11 +14104,15 @@
         </is>
       </c>
       <c r="D314" s="13" t="inlineStr"/>
-      <c r="E314" s="11" t="inlineStr"/>
+      <c r="E314" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F314" s="11" t="inlineStr"/>
       <c r="G314" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H314" s="10" t="inlineStr">
@@ -13426,11 +14146,15 @@
         </is>
       </c>
       <c r="D315" s="13" t="inlineStr"/>
-      <c r="E315" s="11" t="inlineStr"/>
+      <c r="E315" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F315" s="11" t="inlineStr"/>
       <c r="G315" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H315" s="10" t="inlineStr">
@@ -13506,11 +14230,15 @@
         </is>
       </c>
       <c r="D317" s="13" t="inlineStr"/>
-      <c r="E317" s="11" t="inlineStr"/>
+      <c r="E317" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F317" s="11" t="inlineStr"/>
       <c r="G317" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H317" s="10" t="inlineStr">
@@ -13712,11 +14440,15 @@
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr"/>
-      <c r="E322" s="11" t="inlineStr"/>
+      <c r="E322" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F322" s="11" t="inlineStr"/>
       <c r="G322" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H322" s="10" t="inlineStr">
@@ -13792,11 +14524,15 @@
         </is>
       </c>
       <c r="D324" s="13" t="inlineStr"/>
-      <c r="E324" s="11" t="inlineStr"/>
+      <c r="E324" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F324" s="11" t="inlineStr"/>
       <c r="G324" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H324" s="10" t="inlineStr">
@@ -13830,11 +14566,15 @@
         </is>
       </c>
       <c r="D325" s="13" t="inlineStr"/>
-      <c r="E325" s="11" t="inlineStr"/>
+      <c r="E325" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F325" s="11" t="inlineStr"/>
       <c r="G325" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H325" s="10" t="inlineStr">
@@ -13910,11 +14650,15 @@
         </is>
       </c>
       <c r="D327" s="13" t="inlineStr"/>
-      <c r="E327" s="11" t="inlineStr"/>
+      <c r="E327" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F327" s="11" t="inlineStr"/>
       <c r="G327" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H327" s="10" t="inlineStr">
@@ -13948,11 +14692,15 @@
         </is>
       </c>
       <c r="D328" s="13" t="inlineStr"/>
-      <c r="E328" s="11" t="inlineStr"/>
+      <c r="E328" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F328" s="11" t="inlineStr"/>
       <c r="G328" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H328" s="10" t="inlineStr">
@@ -13986,11 +14734,15 @@
         </is>
       </c>
       <c r="D329" s="13" t="inlineStr"/>
-      <c r="E329" s="11" t="inlineStr"/>
+      <c r="E329" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F329" s="11" t="inlineStr"/>
       <c r="G329" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H329" s="10" t="inlineStr">
@@ -14024,11 +14776,15 @@
         </is>
       </c>
       <c r="D330" s="13" t="inlineStr"/>
-      <c r="E330" s="11" t="inlineStr"/>
+      <c r="E330" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F330" s="11" t="inlineStr"/>
       <c r="G330" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H330" s="10" t="inlineStr">
@@ -14104,11 +14860,15 @@
         </is>
       </c>
       <c r="D332" s="13" t="inlineStr"/>
-      <c r="E332" s="11" t="inlineStr"/>
+      <c r="E332" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F332" s="11" t="inlineStr"/>
       <c r="G332" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H332" s="10" t="inlineStr">
@@ -14142,11 +14902,15 @@
         </is>
       </c>
       <c r="D333" s="13" t="inlineStr"/>
-      <c r="E333" s="11" t="inlineStr"/>
+      <c r="E333" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F333" s="11" t="inlineStr"/>
       <c r="G333" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H333" s="10" t="inlineStr">
@@ -14180,11 +14944,15 @@
         </is>
       </c>
       <c r="D334" s="13" t="inlineStr"/>
-      <c r="E334" s="11" t="inlineStr"/>
+      <c r="E334" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F334" s="11" t="inlineStr"/>
       <c r="G334" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H334" s="10" t="inlineStr">
@@ -14260,11 +15028,15 @@
         </is>
       </c>
       <c r="D336" s="13" t="inlineStr"/>
-      <c r="E336" s="11" t="inlineStr"/>
+      <c r="E336" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F336" s="11" t="inlineStr"/>
       <c r="G336" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H336" s="10" t="inlineStr">
@@ -14298,11 +15070,15 @@
         </is>
       </c>
       <c r="D337" s="13" t="inlineStr"/>
-      <c r="E337" s="11" t="inlineStr"/>
+      <c r="E337" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F337" s="11" t="inlineStr"/>
       <c r="G337" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H337" s="10" t="inlineStr">
@@ -14378,11 +15154,15 @@
         </is>
       </c>
       <c r="D339" s="13" t="inlineStr"/>
-      <c r="E339" s="11" t="inlineStr"/>
+      <c r="E339" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F339" s="11" t="inlineStr"/>
       <c r="G339" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H339" s="10" t="inlineStr">
@@ -14416,11 +15196,15 @@
         </is>
       </c>
       <c r="D340" s="13" t="inlineStr"/>
-      <c r="E340" s="11" t="inlineStr"/>
+      <c r="E340" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F340" s="11" t="inlineStr"/>
       <c r="G340" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H340" s="10" t="inlineStr">
@@ -14454,11 +15238,19 @@
         </is>
       </c>
       <c r="D341" s="13" t="inlineStr"/>
-      <c r="E341" s="11" t="inlineStr"/>
-      <c r="F341" s="11" t="inlineStr"/>
+      <c r="E341" s="11" t="inlineStr">
+        <is>
+          <t>в выдаче только однофамильцы с другими ИНН; карточка по этому ИНН не раскрыта</t>
+        </is>
+      </c>
+      <c r="F341" s="11" t="inlineStr">
+        <is>
+          <t>поиск выполнен</t>
+        </is>
+      </c>
       <c r="G341" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H341" s="10" t="inlineStr">
@@ -14492,11 +15284,15 @@
         </is>
       </c>
       <c r="D342" s="13" t="inlineStr"/>
-      <c r="E342" s="11" t="inlineStr"/>
+      <c r="E342" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F342" s="11" t="inlineStr"/>
       <c r="G342" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H342" s="10" t="inlineStr">
@@ -14530,11 +15326,15 @@
         </is>
       </c>
       <c r="D343" s="13" t="inlineStr"/>
-      <c r="E343" s="11" t="inlineStr"/>
+      <c r="E343" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F343" s="11" t="inlineStr"/>
       <c r="G343" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H343" s="10" t="inlineStr">
@@ -14568,11 +15368,15 @@
         </is>
       </c>
       <c r="D344" s="13" t="inlineStr"/>
-      <c r="E344" s="11" t="inlineStr"/>
+      <c r="E344" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F344" s="11" t="inlineStr"/>
       <c r="G344" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H344" s="10" t="inlineStr">
@@ -14606,11 +15410,15 @@
         </is>
       </c>
       <c r="D345" s="13" t="inlineStr"/>
-      <c r="E345" s="11" t="inlineStr"/>
+      <c r="E345" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F345" s="11" t="inlineStr"/>
       <c r="G345" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H345" s="10" t="inlineStr">
@@ -14728,11 +15536,15 @@
         </is>
       </c>
       <c r="D348" s="13" t="inlineStr"/>
-      <c r="E348" s="11" t="inlineStr"/>
+      <c r="E348" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F348" s="11" t="inlineStr"/>
       <c r="G348" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H348" s="10" t="inlineStr">
@@ -14808,11 +15620,15 @@
         </is>
       </c>
       <c r="D350" s="13" t="inlineStr"/>
-      <c r="E350" s="11" t="inlineStr"/>
+      <c r="E350" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F350" s="11" t="inlineStr"/>
       <c r="G350" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H350" s="10" t="inlineStr">
@@ -14888,11 +15704,15 @@
         </is>
       </c>
       <c r="D352" s="13" t="inlineStr"/>
-      <c r="E352" s="11" t="inlineStr"/>
+      <c r="E352" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F352" s="11" t="inlineStr"/>
       <c r="G352" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H352" s="10" t="inlineStr">
@@ -14926,11 +15746,15 @@
         </is>
       </c>
       <c r="D353" s="13" t="inlineStr"/>
-      <c r="E353" s="11" t="inlineStr"/>
+      <c r="E353" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F353" s="11" t="inlineStr"/>
       <c r="G353" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H353" s="10" t="inlineStr">
@@ -15006,11 +15830,15 @@
         </is>
       </c>
       <c r="D355" s="13" t="inlineStr"/>
-      <c r="E355" s="11" t="inlineStr"/>
+      <c r="E355" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F355" s="11" t="inlineStr"/>
       <c r="G355" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H355" s="10" t="inlineStr">
@@ -15044,11 +15872,15 @@
         </is>
       </c>
       <c r="D356" s="13" t="inlineStr"/>
-      <c r="E356" s="11" t="inlineStr"/>
+      <c r="E356" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F356" s="11" t="inlineStr"/>
       <c r="G356" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H356" s="10" t="inlineStr">
@@ -15082,11 +15914,15 @@
         </is>
       </c>
       <c r="D357" s="13" t="inlineStr"/>
-      <c r="E357" s="11" t="inlineStr"/>
+      <c r="E357" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F357" s="11" t="inlineStr"/>
       <c r="G357" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H357" s="10" t="inlineStr">
@@ -15120,11 +15956,15 @@
         </is>
       </c>
       <c r="D358" s="13" t="inlineStr"/>
-      <c r="E358" s="11" t="inlineStr"/>
+      <c r="E358" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F358" s="11" t="inlineStr"/>
       <c r="G358" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H358" s="10" t="inlineStr">
@@ -15284,11 +16124,15 @@
         </is>
       </c>
       <c r="D362" s="13" t="inlineStr"/>
-      <c r="E362" s="11" t="inlineStr"/>
+      <c r="E362" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F362" s="11" t="inlineStr"/>
       <c r="G362" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H362" s="10" t="inlineStr">
@@ -15322,11 +16166,15 @@
         </is>
       </c>
       <c r="D363" s="13" t="inlineStr"/>
-      <c r="E363" s="11" t="inlineStr"/>
+      <c r="E363" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F363" s="11" t="inlineStr"/>
       <c r="G363" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H363" s="10" t="inlineStr">
@@ -15360,11 +16208,15 @@
         </is>
       </c>
       <c r="D364" s="13" t="inlineStr"/>
-      <c r="E364" s="11" t="inlineStr"/>
+      <c r="E364" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F364" s="11" t="inlineStr"/>
       <c r="G364" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H364" s="10" t="inlineStr">
@@ -15398,11 +16250,15 @@
         </is>
       </c>
       <c r="D365" s="13" t="inlineStr"/>
-      <c r="E365" s="11" t="inlineStr"/>
+      <c r="E365" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F365" s="11" t="inlineStr"/>
       <c r="G365" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H365" s="10" t="inlineStr">
@@ -15436,11 +16292,15 @@
         </is>
       </c>
       <c r="D366" s="13" t="inlineStr"/>
-      <c r="E366" s="11" t="inlineStr"/>
+      <c r="E366" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F366" s="11" t="inlineStr"/>
       <c r="G366" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H366" s="10" t="inlineStr">
@@ -15474,11 +16334,15 @@
         </is>
       </c>
       <c r="D367" s="13" t="inlineStr"/>
-      <c r="E367" s="11" t="inlineStr"/>
+      <c r="E367" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F367" s="11" t="inlineStr"/>
       <c r="G367" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H367" s="10" t="inlineStr">
@@ -15554,11 +16418,15 @@
         </is>
       </c>
       <c r="D369" s="13" t="inlineStr"/>
-      <c r="E369" s="11" t="inlineStr"/>
+      <c r="E369" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F369" s="11" t="inlineStr"/>
       <c r="G369" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H369" s="10" t="inlineStr">
@@ -15592,11 +16460,15 @@
         </is>
       </c>
       <c r="D370" s="13" t="inlineStr"/>
-      <c r="E370" s="11" t="inlineStr"/>
+      <c r="E370" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F370" s="11" t="inlineStr"/>
       <c r="G370" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H370" s="10" t="inlineStr">
@@ -15714,11 +16586,15 @@
         </is>
       </c>
       <c r="D373" s="13" t="inlineStr"/>
-      <c r="E373" s="11" t="inlineStr"/>
+      <c r="E373" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F373" s="11" t="inlineStr"/>
       <c r="G373" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H373" s="10" t="inlineStr">
@@ -15752,11 +16628,15 @@
         </is>
       </c>
       <c r="D374" s="13" t="inlineStr"/>
-      <c r="E374" s="11" t="inlineStr"/>
+      <c r="E374" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F374" s="11" t="inlineStr"/>
       <c r="G374" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H374" s="10" t="inlineStr">
@@ -15916,11 +16796,15 @@
         </is>
       </c>
       <c r="D378" s="13" t="inlineStr"/>
-      <c r="E378" s="11" t="inlineStr"/>
+      <c r="E378" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F378" s="11" t="inlineStr"/>
       <c r="G378" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H378" s="10" t="inlineStr">
@@ -15954,11 +16838,15 @@
         </is>
       </c>
       <c r="D379" s="13" t="inlineStr"/>
-      <c r="E379" s="11" t="inlineStr"/>
+      <c r="E379" s="11" t="inlineStr">
+        <is>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
       <c r="F379" s="11" t="inlineStr"/>
       <c r="G379" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H379" s="10" t="inlineStr">

--- a/Телефоны_СРО410_НОСТРОЙ.xlsx
+++ b/Телефоны_СРО410_НОСТРОЙ.xlsx
@@ -1524,52 +1524,52 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>ООО «Вертикаль»</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>7816500610</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 603-29-07</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>199106 СПб, пл.Морской Славы 1А пом.5069; ОГРН 1107847385040; ген.дир. Власенко А.В. | в источнике также обрывок «365-66-38» без кода города — уточнить</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/5307814; focus.kontur.ru; zachestnyibiznes.ru</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>1500000</t>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ВСК»</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>7804018392</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>+7 (812) 365-37-64</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>СПб, Лесной пр. 65к1 оф.ЛИТА; ОГРН 1027802492112; ген.дир. Цой П.В.; в ЕГРЮЛ телефона нет, номер из коммерческих источников</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/4213768; sbis.ru/contragents/7804018392/780201001</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, номер не из ЕГРЮЛ)</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1579,27 +1579,27 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>ООО «Газпромнефть ИТО»</t>
+          <t>ООО «Вертикаль»</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>8905032518</t>
+          <t>7816500610</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 493-25-63; +7 (3496) 37-20-89; +7 (495) 123-60-22</t>
+          <t>+7 (812) 603-29-07</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Московский пр. 60/129А пом.1-Н комн.195-207; ОГРН 1038900945995; 100% ПАО «Газпром нефть»; СПб-номер основной, остальные — Ноябрьск и Москва</t>
+          <t>199106 СПб, пл.Морской Славы 1А пом.5069; ОГРН 1107847385040; ген.дир. Власенко А.В. | в источнике также обрывок «365-66-38» без кода города — уточнить</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/470197; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru/id/5307814; focus.kontur.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>611</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -1629,27 +1629,27 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ООО «Графит»</t>
+          <t>ООО «Газпромнефть ИТО»</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>7841505154</t>
+          <t>8905032518</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 944-62-49</t>
+          <t>+7 (812) 493-25-63; +7 (3496) 37-20-89; +7 (495) 123-60-22</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
+          <t>190013 СПб, Московский пр. 60/129А пом.1-Н комн.195-207; ОГРН 1038900945995; 100% ПАО «Газпром нефть»; СПб-номер основной, остальные — Ноябрьск и Москва</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
+          <t>rusprofile.ru/id/470197; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>957</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1679,27 +1679,27 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>ООО «ИНТРА ПРОЕКТ»</t>
+          <t>ООО «Графит»</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>7806519718</t>
+          <t>7841505154</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
+          <t>+7 (812) 944-62-49</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
+          <t>СПб, наб.реки Мойки 75-79В пом.5-Н; ОГРН 1147847252849; ген.дир. Душкевич А.А.</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
+          <t>spark-interfax.ru; saby.ru/profile/7841505154-783801001; sbis.ru</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>441</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1729,37 +1729,37 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>ООО «ИРЕСТ СТРОЙ»</t>
+          <t>ООО «ДСК РЕГИОН»</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>7825134181</t>
+          <t>7816487198</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>+7 (812) 326-11-53</t>
+          <t>+7 (813) 612-04-70; +7 (921) 868-04-67</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
+          <t>192102 СПб, Волковский пр. 146 пом.6-Н комн.11/2; ОГРН 1107847130698; ген.дир. Сухарев М.В.; выручка 348 млн | код 813 — Ленобласть, не СПб: проверить</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>kanoner.com (данные 2013 г.)</t>
+          <t>rusprofile.ru/id/1858895; checko.ru; vsem-podryad.ru</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>средняя (ИНН совпал, но источник старый — сверить)</t>
+          <t>средняя (ИНН совпал, код города не петербургский)</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>759</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1800000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -1779,27 +1779,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ООО «ИСК» (Инженерно-строительная компания)</t>
+          <t>ООО «ИНТРА ПРОЕКТ»</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>7814519060</t>
+          <t>7806519718</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 244-98-97; +7 (921) 908-42-53</t>
+          <t>+7 (812) 313-50-92; +7 (921) 345-37-89</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>197350 СПб, Мебельная ул. 12к1А пом.14-Н; ОГРН 1117847529327; ген.дир. Мамедов Р.Т.</t>
+          <t>СПб, ш.Революции 3к1А оф.211.1; ОГРН 1147847048722; ген.дир. Можелис Я.С.</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru; sbis.ru/contragents/7814519060/781401001; companies.rbc.ru</t>
+          <t>rusprofile.ru/id/7174539; rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>514</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1819,57 +1819,57 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>ООО «Инженерный Дом»</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>7811474068</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 943-13-43</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>СПб, пр.Большевиков 81 кв.49; ОГРН 1107847321207; ген.дир. Климовский Р.А.</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>sbis.ru/contragents/7811474068/781101001; 2gis.ru/spb</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>500000</t>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ИРЕСТ СТРОЙ»</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>7825134181</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>+7 (812) 326-11-53</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>191015 СПб, Шпалерная ул. 52; ОГРН 1037843007212; факс 380-60-48; irest@list.ru; ireststroy.ru; рук. Нисумаа Юло</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>kanoner.com (данные 2013 г.)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но источник старый — сверить)</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>1800000</t>
         </is>
       </c>
     </row>
@@ -1879,27 +1879,27 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ООО «Капитель»</t>
+          <t>ООО «ИСК» (Инженерно-строительная компания)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>7816235786</t>
+          <t>7814519060</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 244-05-56; +7 (921) 942-96-99</t>
+          <t>+7 (812) 244-98-97; +7 (921) 908-42-53</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>192102 СПб, ул.Салова 27 оф.315; ОГРН 1097847259399; ген.дир. Кузнецов А.В.</t>
+          <t>197350 СПб, Мебельная ул. 12к1А пом.14-Н; ОГРН 1117847529327; ген.дир. Мамедов Р.Т.</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru; sbis.ru/contragents/7816235786/781601001</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7814519060/781401001; companies.rbc.ru</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>677</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1929,27 +1929,27 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>ООО «Люксэнергомонтаж»</t>
+          <t>ООО «Инженерный Дом»</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>7805413540</t>
+          <t>7811474068</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 346-54-68</t>
+          <t>+7 (812) 943-13-43</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>198097 СПб, пр.Стачек 47А пом.24Н; ОГРН 5067847562107; ген.дир. Кузин А.В.; электромонтаж</t>
+          <t>СПб, пр.Большевиков 81 кв.49; ОГРН 1107847321207; ген.дир. Климовский Р.А.</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>sbis.ru/contragents/7805413540/780501001; focus.kontur.ru; b2bsky.ru</t>
+          <t>sbis.ru/contragents/7811474068/781101001; 2gis.ru/spb</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>719</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1979,27 +1979,27 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ООО «Магистраль северной столицы»</t>
+          <t>ООО «Капитель»</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>7710884741</t>
+          <t>7816235786</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
+          <t>+7 (812) 244-05-56; +7 (921) 942-96-99</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
+          <t>192102 СПб, ул.Салова 27 оф.315; ОГРН 1097847259399; ген.дир. Кузнецов А.В.</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7816235786/781601001</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>332</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2029,27 +2029,27 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ООО «Мосты и инженерные проекты»</t>
+          <t>ООО «Люксэнергомонтаж»</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>7734396101</t>
+          <t>7805413540</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 987-56-15; +7 (916) 452-59-04</t>
+          <t>+7 (812) 346-54-68</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>СПб-офис; e-mail spb@mip.moscow; сайт mip.moscow; проектирование мостов</t>
+          <t>198097 СПб, пр.Стачек 47А пом.24Н; ОГРН 5067847562107; ген.дир. Кузин А.В.; электромонтаж</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru; mip.moscow</t>
+          <t>sbis.ru/contragents/7805413540/780501001; focus.kontur.ru; b2bsky.ru</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2079,27 +2079,27 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>ООО «НПО «АМБ»</t>
+          <t>ООО «Магистраль северной столицы»</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>7804516528</t>
+          <t>7710884741</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
+          <t>+7 (812) 645-40-04; +7 (812) 313-92-44</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
+          <t>СПб, ул.Некрасова 14А пом.20-Н; ОГРН 1117746182399; ген.дир. Никифоров А.В.; автодороги</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
+          <t>rusprofile.ru/id/5409176; checko.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>833</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -2129,27 +2129,27 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ООО «Невское РЭУ»</t>
+          <t>ООО «Мосты и инженерные проекты»</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>7810819552</t>
+          <t>7734396101</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 244-52-91</t>
+          <t>+7 (812) 987-56-15; +7 (916) 452-59-04</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>196084 СПб, ул.Заставская 33Ж оф.416; ОГРН 1117847459466; ген.дир. Соловьев М.Ю.</t>
+          <t>СПб-офис; e-mail spb@mip.moscow; сайт mip.moscow; проектирование мостов</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru; sbis.ru/contragents/7810819552/781001001</t>
+          <t>rusprofile.ru; mip.moscow</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>715</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2179,27 +2179,27 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПИТЕРСТРОЙСЕРВИС»</t>
+          <t>ООО «НПО «АМБ»</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>7810711975</t>
+          <t>7804516528</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 385-47-25</t>
+          <t>+7 (812) 243-92-98; +7 (812) 252-79-07; +7 (911) 950-40-25</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>196006 СПб, Заставская ул. 22к2А оф.229; ОГРН 1177847347150; ген.дир. Сорокин А.С.</t>
+          <t>191124 СПб, Синопская наб. 50аА пом.70/2 / Колпино, Северная 14к; ОГРН 1137847368295; ген.дир. Колесников П.Н.; teplovisor.ru</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru; sbis.ru/contragents/7810711975/781001001; companies.rbc.ru</t>
+          <t>rusprofile.ru/id/7279516; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2229,27 +2229,27 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПО «Энергосистема»</t>
+          <t>ООО «Невское РЭУ»</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>7805654520</t>
+          <t>7810819552</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
+          <t>+7 (812) 244-52-91</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
+          <t>196084 СПб, ул.Заставская 33Ж оф.416; ОГРН 1117847459466; ген.дир. Соловьев М.Ю.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7810819552/781001001</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2279,27 +2279,27 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ООО «ПСМ» (Промстроймонтаж)</t>
+          <t>ООО «ПИТЕРСТРОЙСЕРВИС»</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>7814118903</t>
+          <t>7810711975</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
+          <t>+7 (812) 385-47-25</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
+          <t>196006 СПб, Заставская ул. 22к2А оф.229; ОГРН 1177847347150; ген.дир. Сорокин А.С.</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7810711975/781001001; companies.rbc.ru</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>696</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>3000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2329,27 +2329,27 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>ООО «Розенберг Северо-Запад»</t>
+          <t>ООО «ПО «Энергосистема»</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>7816592450</t>
+          <t>7805654520</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+          <t>+7 (812) 101-68-28; +7 (911) 970-31-20; +7 (812) 449-39-69</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+          <t>СПб, Комендантский пр. 4А оф.609; ОГРН 1147847236492; ген.дир. Шевчук А.В.; 135 сотрудников</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+          <t>rusprofile.ru/id/7239673; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>336</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2379,27 +2379,27 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
+          <t>ООО «ПСМ» (Промстроймонтаж)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>7810206161</t>
+          <t>7814118903</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
+          <t>+7 (812) 954-30-97; +7 (812) 275-59-58; +7 (812) 332-14-45</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
+          <t>СПб, Коломяжский пр. 18А пом.106НС; ОГРН 1037832012591; ген.дир. Лущевич А.Ю.</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
+          <t>rusprofile.ru/id/232208; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>727</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2419,57 +2419,57 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>3000000</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>5609095128</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>1500000</t>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Розенберг Северо-Запад»</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>7816592450</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 255-76-41; +7 (964) 376-31-36</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.240; ОГРН 1147847280679; сайт rosenberg.ru; инж.изыскания/стройконтроль</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/7558159; synapsenet.ru; buhonline.ru</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
         </is>
       </c>
     </row>
@@ -2479,27 +2479,27 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
+          <t>ООО «СИК «СИНКО» (Строительная инжиниринговая компания)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>7801349149</t>
+          <t>7810206161</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
+          <t>+7 (812) 710-11-91; +7 (812) 316-27-33</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
+          <t>СПб, ул.Егорова 26А литера Б; ОГРН 1027804895216; ген.дир. Чубатюк А.И.</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
+          <t>synapsenet.ru; spark-interfax.ru; zachestnyibiznes.ru</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>241</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2524,50 +2524,50 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>ООО «Северный Альянс»</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>7805662306</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>высокая (ИНН совпал)</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>ООО «ССМ» (Стройсервисмонтаж)</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>5609095128</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>+7 (3532) 44-44-46; +7 (3532) 44-44-41</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>СПб, Апраксин пер. 8А оф.110; ОГРН 1145658007351; ВНИМАНИЕ: номера оренбургские (код 3532) — компания перерегистрирована из Оренбурга, актуальность уточнить</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; checko.ru/company/ssm-1145658007351</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>средняя (ИНН совпал, но номер иногороднего кода)</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
@@ -2579,27 +2579,27 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>ООО «Сити-ППА»</t>
+          <t>ООО «СТРОЙМОНТАЖКОМПЛЕКТ»</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7802940940</t>
+          <t>7801349149</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 985-53-55</t>
+          <t>+7 (812) 931-88-28; +7 (812) 321-71-86; +7 (812) 495-44-83</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>194292 СПб, 5-й Верхний пер. 12к2Б оф.11; ОГРН 1237800142380; ген.дир. Прокофьев А.В.</t>
+          <t>СПб, Ленинский пр. 153А пом.35-Н; ОГРН 1187847073424; ген.дир. Могила И.М.; stroycom192@yandex.ru; ж/д и метро</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru; sbis.ru/contragents/7802940940/780201001</t>
+          <t>rusprofile.ru/id/11379214; checko.ru; companium.ru</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>627</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2629,27 +2629,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>ООО «Спецтехкомплект»</t>
+          <t>ООО «Северный Альянс»</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7811127120</t>
+          <t>7805662306</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 362-09-21</t>
+          <t>+7 (812) 915-63-87; +7 (812) 943-96-88; +7 (911) 120-93-39</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
+          <t>197374 СПб, Приморский пр. 78к5с1 пом.1-Н; ОГРН 1147847371044; ген.дир. Лобиков В.В.</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
+          <t>rusprofile.ru/id/7559487; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2679,27 +2679,27 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>ООО «СтарКом»</t>
+          <t>ООО «Сити-ППА»</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>7841416641</t>
+          <t>7802940940</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
+          <t>+7 (812) 985-53-55</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
+          <t>194292 СПб, 5-й Верхний пер. 12к2Б оф.11; ОГРН 1237800142380; ген.дир. Прокофьев А.В.</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
+          <t>rusprofile.ru; sbis.ru/contragents/7802940940/780201001</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>5000000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -2729,27 +2729,27 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>ООО «ТМГ ГРУП»</t>
+          <t>ООО «Спецтехкомплект»</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>7705405168</t>
+          <t>7811127120</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 680-30-20</t>
+          <t>+7 (812) 362-09-21</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+          <t>СПб, Большой пр. В.О. 84А оф.19-Н 503; ОГРН 1027806058774; ген.дир. Павлов И.В.; tgvstk@mail.ru; spectk.ru</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+          <t>rusprofile.ru/id/3375038; sbis.ru/contragents/7811127120/780101001</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -2779,27 +2779,27 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>ООО «Транспромстрой»</t>
+          <t>ООО «СтарКом»</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>7804591155</t>
+          <t>7841416641</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 449-31-21</t>
+          <t>+7 (921) 395-80-39; +7 (812) 414-98-03</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>СПб, ул.Савушкина 83к3А оф.401-402; ОГРН 1177847074250; ген.дир. Аванесов Д.Б.; ~467 сотрудников</t>
+          <t>190000 СПб, ул.Чехова 18А пом.1нс; ОГРН 1099847000296; ген.дир. Шин В.В.</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>spark-interfax.ru; companies.rbc.ru; sbis.ru</t>
+          <t>rusprofile.ru/id/383255; companies.rbc.ru; saby.ru</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>508</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>5000000</t>
         </is>
       </c>
     </row>
@@ -2829,131 +2829,147 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
+          <t>ООО «ТМГ ГРУП»</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>7705405168</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 680-30-20</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>190013 СПб, Рузовская ул. 8Б оф.418,420; ОГРН 1037739198199; ген.дир. Тица Мирко</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>rusprofile.ru/id/2289794; companies.rbc.ru; ngee.ru</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Транспромстрой»</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>7804591155</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>+7 (812) 449-31-21</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>СПб, ул.Савушкина 83к3А оф.401-402; ОГРН 1177847074250; ген.дир. Аванесов Д.Б.; ~467 сотрудников</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>spark-interfax.ru; companies.rbc.ru; sbis.ru</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
           <t>ООО «ЭКОТЭП»</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>7802037985</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>+7 (812) 535-10-10; +7 (812) 535-88-62; +7 (812) 309-01-04</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>195220 СПб, ул.Гжатская 21к2А пом.18-Н; ОГРН 1027801581037; ген.дир. Свердлин Б.Л.; с 1992 г.</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>rusprofile.ru/id/4489918; companies.rbc.ru; checko.ru</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>высокая (ИНН совпал)</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>523</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Является членом</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>АНО «ВАЛААМ»</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>7839024647</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="inlineStr"/>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr"/>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>АНО «Промбезопасность-Северо-Запад»</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>7825489730</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="inlineStr"/>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr"/>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Является членом</t>
-        </is>
-      </c>
-      <c r="J49" s="10" t="inlineStr">
-        <is>
-          <t>100000</t>
         </is>
       </c>
     </row>
@@ -2963,29 +2979,29 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>АО «АТЭК»</t>
+          <t>АНО «ВАЛААМ»</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>7826135558</t>
+          <t>7839024647</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr"/>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>СПб, Нарвский пр. 1/29; ОГРН 1157800000544; ген.дир. Щеколдин В.А.</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2995,7 +3011,7 @@
       </c>
       <c r="J50" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3005,29 +3021,29 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>АО «Абсолют»</t>
+          <t>АНО «Промбезопасность-Северо-Запад»</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>7825663795</t>
+          <t>7825489730</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr"/>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -3037,7 +3053,7 @@
       </c>
       <c r="J51" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -3047,29 +3063,29 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>АО «Аспект Северо-Запад»</t>
+          <t>АО «АТЭК»</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>7810143306</t>
+          <t>7826135558</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr"/>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>482</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -3079,7 +3095,7 @@
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -3089,18 +3105,18 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>АО «Балтийская инжиниринговая компания»</t>
+          <t>АО «Абсолют»</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>7810255553</t>
+          <t>7825663795</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr"/>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
+          <t>192288 СПб, Бухарестская ул. 118к1А пом.70н; ОГРН 1037843017684; ген.дир. Фурман А.Ю.; профиль на b2b-center.ru</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
@@ -3111,7 +3127,7 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -3121,7 +3137,7 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3131,29 +3147,29 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>АО «ВОЛХОН»</t>
+          <t>АО «Аспект Северо-Запад»</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>7810383403</t>
+          <t>7810143306</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr"/>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
+          <t>194021 СПб, пр.Пархоменко 32А пом.10Н; ОГРН 1027804851370; ген.дир. Гаевский Д.А.</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>735</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3163,7 +3179,7 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3173,29 +3189,29 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>АО «Дженерал Констракшн»</t>
+          <t>АО «Балтийская инжиниринговая компания»</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>7814529967</t>
+          <t>7810255553</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr"/>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>СПб, Малый пр. В.О. 48к2А пом.12-Н; ОГРН 1037821032061; ген.дир. Кипнис В.Л.</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3205,7 +3221,7 @@
       </c>
       <c r="J55" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3215,18 +3231,18 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>АО «ЛенПолпроект»</t>
+          <t>АО «ВОЛХОН»</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>7801093592</t>
+          <t>7810383403</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr"/>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>199106 СПб, Гаванская ул. 4А / Большой пр. 89А; ОГРН 1027800509879; ген.дир. Кайтмазов Т.В.</t>
+          <t>196006 СПб, ул.Рощинская 36А; ОГРН 1157847331300; ген.дир. Хохлова О.Н.</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
@@ -3237,7 +3253,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3247,7 +3263,7 @@
       </c>
       <c r="J56" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3257,12 +3273,12 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>АО «МГС»</t>
+          <t>АО «Дженерал Констракшн»</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>7814774782</t>
+          <t>7814529967</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr"/>
@@ -3279,7 +3295,7 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>342</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -3299,18 +3315,18 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
+          <t>АО «ЛенПолпроект»</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>7813007615</t>
+          <t>7801093592</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr"/>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
+          <t>199106 СПб, Гаванская ул. 4А / Большой пр. 89А; ОГРН 1027800509879; ген.дир. Кайтмазов Т.В.</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
@@ -3321,7 +3337,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>619</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -3331,7 +3347,7 @@
       </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -3341,29 +3357,29 @@
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>АО «НОУДИГ» (Per Aarsleff)</t>
+          <t>АО «МГС»</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>7802108837</t>
+          <t>7814774782</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr"/>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3373,7 +3389,7 @@
       </c>
       <c r="J59" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -3383,18 +3399,18 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>АО «Петрос»</t>
+          <t>АО «МИН» (Монтажно-наладочное предприятие)</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>7816131635</t>
+          <t>7813007615</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr"/>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
+          <t>195253 СПб, пр.Энергетиков 40к4; ОГРН 1027804199664; ген.дир. Комягинский А.Л.; УК 5,2 млн</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
@@ -3405,7 +3421,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3415,7 +3431,7 @@
       </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -3425,18 +3441,18 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>АО «Полиспаст»</t>
+          <t>АО «НОУДИГ» (Per Aarsleff)</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>7805744573</t>
+          <t>7802108837</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr"/>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
+          <t>190005 СПб, Измайловский пр. 29И пом.18н; ОГРН 1027801572523; ген.дир. Фомин К.Л.</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -3447,7 +3463,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>699</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3467,29 +3483,29 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>АО «РТИ»</t>
+          <t>АО «Петрос»</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>7810471681</t>
+          <t>7816131635</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr"/>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>СПб, Лиговский пр. 200АА пом.7Н; ОГРН 1037835001038; ген.дир. Ромашко А.И.</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>507</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3499,7 +3515,7 @@
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3509,29 +3525,29 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>АО «РЭС» (Региональные электрические сети)</t>
+          <t>АО «Полиспаст»</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>7810785984</t>
+          <t>7805744573</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr"/>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
+          <t>СПб, Приморский пр. 78к5 пом.1-Н; ОГРН 1197847050103; ген.дир. Попова Л.Е.</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -3541,7 +3557,7 @@
       </c>
       <c r="J63" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3567,12 @@
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>АО «РадиоТел-СПб»</t>
+          <t>АО «РТИ»</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>7813395894</t>
+          <t>7810471681</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr"/>
@@ -3573,7 +3589,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -3583,7 +3599,7 @@
       </c>
       <c r="J64" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -3593,29 +3609,29 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>АО «СК «ШПУНТ»</t>
+          <t>АО «РЭС» (Региональные электрические сети)</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>7816375864</t>
+          <t>7810785984</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr"/>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>197110 СПб, Песочная наб. 42А пом.337; ОГРН 1207800004169; ген.дир. Милосветов А.Е.; УК 192 млн</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>566</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -3625,7 +3641,7 @@
       </c>
       <c r="J65" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3635,33 +3651,29 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>АО «СМУ-47»</t>
+          <t>АО «РадиоТел-СПб»</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>7801097276</t>
+          <t>7813395894</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr"/>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>карточка есть на list-org, но контакты в выдачу не попали; в СПб несколько ООО «СМУ-47» с другими ИНН</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>поиск выполнен</t>
-        </is>
-      </c>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr">
         <is>
-          <t>нет данных (проверено)</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>740</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr">
@@ -3671,7 +3683,7 @@
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -3681,12 +3693,12 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>АО «ССМУ № 399»</t>
+          <t>АО «СК «ШПУНТ»</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>7825669885</t>
+          <t>7816375864</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr"/>
@@ -3703,7 +3715,7 @@
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>329</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -3723,29 +3735,33 @@
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>АО «Северен-Телеком»</t>
+          <t>АО «СМУ-47»</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>7816181675</t>
+          <t>7801097276</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr"/>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Комиссара Смирнова 3; ОГРН 1037835033598; ген.дир. Ковтонюк А.В.; телефонная связь; УК 15 млн</t>
-        </is>
-      </c>
-      <c r="F68" s="11" t="inlineStr"/>
+          <t>карточка есть на list-org, но контакты в выдачу не попали; в СПб несколько ООО «СМУ-47» с другими ИНН</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>поиск выполнен</t>
+        </is>
+      </c>
       <c r="G68" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (проверено)</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>687</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
@@ -3755,7 +3771,7 @@
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3765,29 +3781,29 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>АО «Селектел»</t>
+          <t>АО «ССМУ № 399»</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>7810962785</t>
+          <t>7825669885</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr"/>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>нет данных (телефон смотреть на selectel.ru)</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
@@ -3797,7 +3813,7 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -3807,29 +3823,29 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>АО «Спецтранс Инвест»</t>
+          <t>АО «Северен-Телеком»</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>7810687698</t>
+          <t>7816181675</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr"/>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>СПб, ул.Комиссара Смирнова 3; ОГРН 1037835033598; ген.дир. Ковтонюк А.В.; телефонная связь; УК 15 млн</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>328</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -3849,29 +3865,29 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>АО «Строитель»</t>
+          <t>АО «Селектел»</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>7805807079</t>
+          <t>7810962785</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>СПб, ул.Цветочная 21А; ОГРН 1247800067790; ген.дир. Любимов О.И.; УК 130 млн; сайт selectel.ru</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных (телефон смотреть на selectel.ru)</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -3881,7 +3897,7 @@
       </c>
       <c r="J71" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -3891,29 +3907,29 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>АО «Стройинвест»</t>
+          <t>АО «Спецтранс Инвест»</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>7825697956</t>
+          <t>7810687698</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr"/>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr">
@@ -3923,7 +3939,7 @@
       </c>
       <c r="J72" s="10" t="inlineStr">
         <is>
-          <t>1500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -3933,12 +3949,12 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>АО «ТЕРМА»</t>
+          <t>АО «Строитель»</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>7812014779</t>
+          <t>7805807079</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
@@ -3955,7 +3971,7 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr">
@@ -3975,29 +3991,29 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>АО «Техногрупп»</t>
+          <t>АО «Стройинвест»</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>5190044620</t>
+          <t>7825697956</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr"/>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>СПб, ул.Сердобольская 60А пом.3; ОГРН 1037843097600; ген.дир. Приц П.В.</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>718</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
@@ -4007,7 +4023,7 @@
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1500000</t>
         </is>
       </c>
     </row>
@@ -4017,12 +4033,12 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Ассоциация «Невский свет»</t>
+          <t>АО «ТЕРМА»</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>7838342220</t>
+          <t>7812014779</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr"/>
@@ -4039,7 +4055,7 @@
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -4059,29 +4075,29 @@
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>ГУП «Инпредсервис»</t>
+          <t>АО «Техногрупп»</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>7830000909</t>
+          <t>5190044620</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr"/>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>СПб, наб.Кутузова 34; ОГРН 1037843059099; ген.дир. Запевалов В.В.; обслуживание иностранных представительств</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>274</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -4091,7 +4107,7 @@
       </c>
       <c r="J76" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4101,29 +4117,29 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Агентство Шушары»</t>
+          <t>Ассоциация «Невский свет»</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>7820016970</t>
+          <t>7838342220</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr"/>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr">
@@ -4133,7 +4149,7 @@
       </c>
       <c r="J77" s="10" t="inlineStr">
         <is>
-          <t>800000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4143,29 +4159,29 @@
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Б.А.П.»</t>
+          <t>ГУП «Инпредсервис»</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>7825419081</t>
+          <t>7830000909</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr"/>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>СПб, наб.Кутузова 34; ОГРН 1037843059099; ген.дир. Запевалов В.В.; обслуживание иностранных представительств</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
       <c r="G78" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>563</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr">
@@ -4175,7 +4191,7 @@
       </c>
       <c r="J78" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -4185,29 +4201,29 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «ГЛАВПОЖСТРОЙ»</t>
+          <t>ЗАО «Агентство Шушары»</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>7804419563</t>
+          <t>7820016970</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr"/>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>197022 СПб, ул.Академика Павлова 14АА пом.26-Н; ОГРН 1027809015915; ген.дир. Якунчихин В.Г.</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных</t>
         </is>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>650</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr">
@@ -4217,7 +4233,7 @@
       </c>
       <c r="J79" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>800000</t>
         </is>
       </c>
     </row>
@@ -4227,29 +4243,29 @@
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Институт телекоммуникаций»</t>
+          <t>ЗАО «Б.А.П.»</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>7802199182</t>
+          <t>7825419081</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr"/>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
       <c r="G80" s="11" t="inlineStr">
         <is>
-          <t>нет данных (телефон смотреть на itain.ru)</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -4259,7 +4275,7 @@
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4285,12 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «КТСП»</t>
+          <t>ЗАО «ГЛАВПОЖСТРОЙ»</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>7805124273</t>
+          <t>7804419563</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr"/>
@@ -4291,7 +4307,7 @@
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>433</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -4301,7 +4317,7 @@
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -4311,29 +4327,29 @@
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Кислородмонтаж «Северо-Запад СПб»</t>
+          <t>ЗАО «Институт телекоммуникаций»</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>7810477267</t>
+          <t>7802199182</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr"/>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>запись не проверялась — подлежит повторному пробиву</t>
+          <t>194100 СПб, Кантемировская ул. 5к5М; ОГРН 1027801538600; ген.дир. Присяжнюк А.С.; сайты itain.ru, itain.spb.ru</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
       <c r="G82" s="11" t="inlineStr">
         <is>
-          <t>НЕ ПРОВЕРЯЛОСЬ</t>
+          <t>нет данных (телефон смотреть на itain.ru)</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -4343,7 +4359,7 @@
       </c>
       <c r="J82" s="10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
     </row>
@@ -4353,29 +4369,29 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «ПетроЭлектроКомплекс»</t>
+          <t>ЗАО «КТСП»</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>7801128326</t>
+          <t>7805124273</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr"/>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
+          <t>запись не проверялась — подлежит повторному пробиву</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>нет данных (нет в ЕГРЮЛ)</t>
+          <t>НЕ ПРОВЕРЯЛОСЬ</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>664</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -4385,7 +4401,7 @@
       </c>
       <c r="J83" s="10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4411,12 @@
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Промышленная группа «ИнВент»</t>
+          <t>ЗАО «Кислородмонтаж «Северо-Запад СПб»</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>7805240657</t>
+          <t>7810477267</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr"/>
@@ -4417,7 +4433,7 @@
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>927</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -4437,29 +4453,29 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Трест СЗКС» (Севзапкурортстрой)</t>
+          <t>ЗАО «ПетроЭлектроКомплекс»</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>7809006739</t>
+          <t>7801128326</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr"/>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>190013 СПб, Рузовская ул. 16 пом.1н оф.117; ОГРН 1027810295842; ген.дир. Тихомиров С.А.</t>
+          <t>СПб, ул.Большая Разночинная 30К оф.410; ОГРН 1037835035270; ген.дир. Викентьев А.В.</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>нет данных</t>
+          <t>нет данных (нет в ЕГРЮЛ)</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>506</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -4479,29 +4495,29 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>ЗАО «Эра-Инжиниринг»</t>
+          <t>ЗАО «Промышленная группа «